--- a/R_&_D/Platform_Completion/OmniStackAI_Master_Tasks.xlsx
+++ b/R_&_D/Platform_Completion/OmniStackAI_Master_Tasks.xlsx
@@ -1092,7 +1092,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Login and register for the Go backend</t>
+          <t>Complete auth for the Go backend: register, login, logout, me, forgot password, reset password</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -1119,7 +1119,7 @@
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>A Go app with auth has no way for a real user to sign in.</t>
+          <t>A Go app with auth has no way for a real user to sign in. Parity with the Python backend's auth (R-461, R-463), companions included.</t>
         </is>
       </c>
     </row>
@@ -10945,7 +10945,7 @@
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>Login and register for the Go backend</t>
+          <t>Complete auth for the Go backend: register, login, logout, me, forgot password, reset password</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
@@ -10977,7 +10977,7 @@
       <c r="I104" s="3" t="inlineStr"/>
       <c r="J104" s="3" t="inlineStr">
         <is>
-          <t>A Go app with auth has no way for a real user to sign in.</t>
+          <t>A Go app with auth has no way for a real user to sign in. Parity with the Python backend's auth (R-461, R-463), companions included.</t>
         </is>
       </c>
     </row>

--- a/R_&_D/Platform_Completion/OmniStackAI_Master_Tasks.xlsx
+++ b/R_&_D/Platform_Completion/OmniStackAI_Master_Tasks.xlsx
@@ -77,7 +77,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFE699"/>
+        <fgColor rgb="00BDD7EE"/>
       </patternFill>
     </fill>
     <fill>
@@ -88,6 +88,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F8CBAD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE699"/>
       </patternFill>
     </fill>
     <fill>
@@ -113,11 +118,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2F0D9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00BDD7EE"/>
       </patternFill>
     </fill>
   </fills>
@@ -173,10 +173,10 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
@@ -1657,7 +1657,7 @@
           <t>Vibe</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr">
+      <c r="F19" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -1883,7 +1883,7 @@
           <t>Vibe</t>
         </is>
       </c>
-      <c r="F24" s="7" t="inlineStr">
+      <c r="F24" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -1929,7 +1929,7 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="F25" s="7" t="inlineStr">
+      <c r="F25" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -1975,7 +1975,7 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="F26" s="7" t="inlineStr">
+      <c r="F26" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2591,7 +2591,7 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="F40" s="7" t="inlineStr">
+      <c r="F40" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2641,7 +2641,7 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="F41" s="7" t="inlineStr">
+      <c r="F41" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2741,12 +2741,12 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="F43" s="7" t="inlineStr">
+      <c r="F43" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G43" s="10" t="inlineStr">
+      <c r="G43" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -2887,7 +2887,7 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="F46" s="7" t="inlineStr">
+      <c r="F46" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2937,7 +2937,7 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="F47" s="7" t="inlineStr">
+      <c r="F47" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2992,7 +2992,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G48" s="10" t="inlineStr">
+      <c r="G48" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -3042,7 +3042,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G49" s="10" t="inlineStr">
+      <c r="G49" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -3092,7 +3092,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G50" s="11" t="inlineStr">
+      <c r="G50" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -3142,7 +3142,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G51" s="11" t="inlineStr">
+      <c r="G51" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -3192,7 +3192,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G52" s="10" t="inlineStr">
+      <c r="G52" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -3242,7 +3242,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G53" s="10" t="inlineStr">
+      <c r="G53" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -3288,7 +3288,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G54" s="10" t="inlineStr">
+      <c r="G54" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -3330,7 +3330,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G55" s="11" t="inlineStr">
+      <c r="G55" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -3372,7 +3372,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G56" s="11" t="inlineStr">
+      <c r="G56" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -3418,7 +3418,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G57" s="11" t="inlineStr">
+      <c r="G57" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -3460,7 +3460,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G58" s="11" t="inlineStr">
+      <c r="G58" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -3502,7 +3502,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G59" s="11" t="inlineStr">
+      <c r="G59" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -3544,7 +3544,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G60" s="10" t="inlineStr">
+      <c r="G60" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -3585,12 +3585,12 @@
           <t>Vibe</t>
         </is>
       </c>
-      <c r="F61" s="7" t="inlineStr">
+      <c r="F61" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G61" s="10" t="inlineStr">
+      <c r="G61" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -3636,7 +3636,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G62" s="11" t="inlineStr">
+      <c r="G62" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -3682,7 +3682,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G63" s="10" t="inlineStr">
+      <c r="G63" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -3874,7 +3874,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G67" s="10" t="inlineStr">
+      <c r="G67" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -3920,7 +3920,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G68" s="10" t="inlineStr">
+      <c r="G68" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -3966,7 +3966,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G69" s="10" t="inlineStr">
+      <c r="G69" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -4012,7 +4012,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G70" s="10" t="inlineStr">
+      <c r="G70" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -4062,7 +4062,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G71" s="11" t="inlineStr">
+      <c r="G71" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -4108,7 +4108,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G72" s="11" t="inlineStr">
+      <c r="G72" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -4154,7 +4154,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G73" s="11" t="inlineStr">
+      <c r="G73" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -4241,7 +4241,7 @@
           <t>Engineering</t>
         </is>
       </c>
-      <c r="F75" s="7" t="inlineStr">
+      <c r="F75" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -4379,7 +4379,7 @@
           <t>Engineering</t>
         </is>
       </c>
-      <c r="F78" s="7" t="inlineStr">
+      <c r="F78" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -4475,7 +4475,7 @@
           <t>Engineering</t>
         </is>
       </c>
-      <c r="F80" s="7" t="inlineStr">
+      <c r="F80" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -4702,7 +4702,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G85" s="10" t="inlineStr">
+      <c r="G85" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -4747,12 +4747,12 @@
           <t>Engineering</t>
         </is>
       </c>
-      <c r="F86" s="7" t="inlineStr">
+      <c r="F86" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G86" s="10" t="inlineStr">
+      <c r="G86" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -4798,7 +4798,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G87" s="10" t="inlineStr">
+      <c r="G87" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -5028,7 +5028,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G92" s="10" t="inlineStr">
+      <c r="G92" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -5065,7 +5065,7 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="F93" s="7" t="inlineStr">
+      <c r="F93" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -5116,7 +5116,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G94" s="10" t="inlineStr">
+      <c r="G94" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -5158,7 +5158,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G95" s="10" t="inlineStr">
+      <c r="G95" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -5204,7 +5204,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G96" s="10" t="inlineStr">
+      <c r="G96" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -5250,7 +5250,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G97" s="10" t="inlineStr">
+      <c r="G97" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -5292,7 +5292,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G98" s="10" t="inlineStr">
+      <c r="G98" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -5388,7 +5388,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G100" s="10" t="inlineStr">
+      <c r="G100" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -5434,7 +5434,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G101" s="10" t="inlineStr">
+      <c r="G101" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -5480,7 +5480,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G102" s="10" t="inlineStr">
+      <c r="G102" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -5526,7 +5526,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G103" s="10" t="inlineStr">
+      <c r="G103" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -5572,7 +5572,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G104" s="10" t="inlineStr">
+      <c r="G104" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -5618,7 +5618,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G105" s="10" t="inlineStr">
+      <c r="G105" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -5664,7 +5664,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G106" s="10" t="inlineStr">
+      <c r="G106" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -5710,7 +5710,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G107" s="11" t="inlineStr">
+      <c r="G107" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -5756,7 +5756,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G108" s="11" t="inlineStr">
+      <c r="G108" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -5802,7 +5802,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G109" s="11" t="inlineStr">
+      <c r="G109" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -6128,7 +6128,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G116" s="10" t="inlineStr">
+      <c r="G116" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -6266,7 +6266,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G119" s="10" t="inlineStr">
+      <c r="G119" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -6395,7 +6395,7 @@
       </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G2" s="6" t="inlineStr">
@@ -6437,7 +6437,7 @@
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6481,7 +6481,7 @@
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6525,7 +6525,7 @@
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6569,7 +6569,7 @@
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6613,7 +6613,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="F7" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6657,7 +6657,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6701,12 +6701,12 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F9" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="G9" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -6745,7 +6745,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6789,7 +6789,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="F11" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6833,12 +6833,12 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F12" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G12" s="10" t="inlineStr">
+      <c r="G12" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -6877,7 +6877,7 @@
           <t>3 Engineering Mode</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F13" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6921,7 +6921,7 @@
           <t>3 Engineering Mode</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F14" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6965,7 +6965,7 @@
           <t>3 Engineering Mode</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F15" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7009,12 +7009,12 @@
           <t>3 Engineering Mode</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F16" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G16" s="10" t="inlineStr">
+      <c r="G16" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -7053,7 +7053,7 @@
           <t>4 Production ops</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr">
+      <c r="F17" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7093,7 +7093,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="F18" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7137,7 +7137,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr">
+      <c r="F19" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7181,7 +7181,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr">
+      <c r="F20" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7225,7 +7225,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr">
+      <c r="F21" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7265,12 +7265,12 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr">
+      <c r="F22" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G22" s="10" t="inlineStr">
+      <c r="G22" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -7305,7 +7305,7 @@
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="F23" s="7" t="inlineStr">
+      <c r="F23" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7349,7 +7349,7 @@
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="F24" s="7" t="inlineStr">
+      <c r="F24" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7393,7 +7393,7 @@
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="F25" s="7" t="inlineStr">
+      <c r="F25" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7437,12 +7437,12 @@
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="F26" s="7" t="inlineStr">
+      <c r="F26" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G26" s="10" t="inlineStr">
+      <c r="G26" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -7477,12 +7477,12 @@
           <t>4 Production ops</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr">
+      <c r="F27" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G27" s="10" t="inlineStr">
+      <c r="G27" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -7517,12 +7517,12 @@
           <t>4 Production ops</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr">
+      <c r="F28" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G28" s="10" t="inlineStr">
+      <c r="G28" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -7561,12 +7561,12 @@
           <t>4 Production ops</t>
         </is>
       </c>
-      <c r="F29" s="7" t="inlineStr">
+      <c r="F29" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G29" s="10" t="inlineStr">
+      <c r="G29" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -7609,12 +7609,12 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F30" s="7" t="inlineStr">
+      <c r="F30" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G30" s="10" t="inlineStr">
+      <c r="G30" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -7657,12 +7657,12 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F31" s="7" t="inlineStr">
+      <c r="F31" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G31" s="10" t="inlineStr">
+      <c r="G31" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -7705,7 +7705,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F32" s="7" t="inlineStr">
+      <c r="F32" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7753,12 +7753,12 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F33" s="7" t="inlineStr">
+      <c r="F33" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G33" s="10" t="inlineStr">
+      <c r="G33" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -7801,7 +7801,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F34" s="7" t="inlineStr">
+      <c r="F34" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7849,12 +7849,12 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F35" s="7" t="inlineStr">
+      <c r="F35" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G35" s="10" t="inlineStr">
+      <c r="G35" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -7897,7 +7897,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F36" s="7" t="inlineStr">
+      <c r="F36" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7945,7 +7945,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F37" s="7" t="inlineStr">
+      <c r="F37" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7993,7 +7993,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F38" s="7" t="inlineStr">
+      <c r="F38" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8041,12 +8041,12 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F39" s="7" t="inlineStr">
+      <c r="F39" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G39" s="10" t="inlineStr">
+      <c r="G39" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -8089,12 +8089,12 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F40" s="7" t="inlineStr">
+      <c r="F40" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G40" s="10" t="inlineStr">
+      <c r="G40" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -8137,12 +8137,12 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F41" s="7" t="inlineStr">
+      <c r="F41" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G41" s="10" t="inlineStr">
+      <c r="G41" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -8185,12 +8185,12 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F42" s="7" t="inlineStr">
+      <c r="F42" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G42" s="10" t="inlineStr">
+      <c r="G42" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -8233,12 +8233,12 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F43" s="7" t="inlineStr">
+      <c r="F43" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G43" s="10" t="inlineStr">
+      <c r="G43" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -8281,12 +8281,12 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F44" s="7" t="inlineStr">
+      <c r="F44" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G44" s="10" t="inlineStr">
+      <c r="G44" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -8329,12 +8329,12 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F45" s="7" t="inlineStr">
+      <c r="F45" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G45" s="10" t="inlineStr">
+      <c r="G45" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -8377,12 +8377,12 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F46" s="7" t="inlineStr">
+      <c r="F46" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G46" s="10" t="inlineStr">
+      <c r="G46" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -8425,7 +8425,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F47" s="7" t="inlineStr">
+      <c r="F47" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8473,7 +8473,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F48" s="7" t="inlineStr">
+      <c r="F48" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8521,12 +8521,12 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F49" s="7" t="inlineStr">
+      <c r="F49" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G49" s="10" t="inlineStr">
+      <c r="G49" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -8569,12 +8569,12 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F50" s="7" t="inlineStr">
+      <c r="F50" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G50" s="10" t="inlineStr">
+      <c r="G50" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -8617,7 +8617,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F51" s="7" t="inlineStr">
+      <c r="F51" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8665,12 +8665,12 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F52" s="7" t="inlineStr">
+      <c r="F52" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G52" s="11" t="inlineStr">
+      <c r="G52" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -8713,7 +8713,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F53" s="7" t="inlineStr">
+      <c r="F53" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8761,12 +8761,12 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F54" s="7" t="inlineStr">
+      <c r="F54" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G54" s="10" t="inlineStr">
+      <c r="G54" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -8809,7 +8809,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F55" s="7" t="inlineStr">
+      <c r="F55" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8857,12 +8857,12 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F56" s="7" t="inlineStr">
+      <c r="F56" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G56" s="11" t="inlineStr">
+      <c r="G56" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -8905,7 +8905,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F57" s="7" t="inlineStr">
+      <c r="F57" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8953,12 +8953,12 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F58" s="7" t="inlineStr">
+      <c r="F58" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G58" s="10" t="inlineStr">
+      <c r="G58" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -9001,7 +9001,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F59" s="7" t="inlineStr">
+      <c r="F59" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9049,12 +9049,12 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F60" s="7" t="inlineStr">
+      <c r="F60" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G60" s="10" t="inlineStr">
+      <c r="G60" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -9097,12 +9097,12 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F61" s="7" t="inlineStr">
+      <c r="F61" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G61" s="10" t="inlineStr">
+      <c r="G61" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -9145,7 +9145,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F62" s="7" t="inlineStr">
+      <c r="F62" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9193,12 +9193,12 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F63" s="7" t="inlineStr">
+      <c r="F63" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G63" s="11" t="inlineStr">
+      <c r="G63" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -9241,12 +9241,12 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F64" s="7" t="inlineStr">
+      <c r="F64" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G64" s="10" t="inlineStr">
+      <c r="G64" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -9289,12 +9289,12 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F65" s="7" t="inlineStr">
+      <c r="F65" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G65" s="10" t="inlineStr">
+      <c r="G65" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -9337,12 +9337,12 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F66" s="7" t="inlineStr">
+      <c r="F66" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G66" s="10" t="inlineStr">
+      <c r="G66" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -9385,12 +9385,12 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F67" s="7" t="inlineStr">
+      <c r="F67" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G67" s="10" t="inlineStr">
+      <c r="G67" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -9433,12 +9433,12 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F68" s="7" t="inlineStr">
+      <c r="F68" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G68" s="10" t="inlineStr">
+      <c r="G68" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -9481,7 +9481,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F69" s="7" t="inlineStr">
+      <c r="F69" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9525,7 +9525,7 @@
           <t>4 Production ops</t>
         </is>
       </c>
-      <c r="F70" s="7" t="inlineStr">
+      <c r="F70" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9569,7 +9569,7 @@
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="F71" s="7" t="inlineStr">
+      <c r="F71" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9617,7 +9617,7 @@
           <t>3 Engineering Mode</t>
         </is>
       </c>
-      <c r="F72" s="7" t="inlineStr">
+      <c r="F72" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9665,7 +9665,7 @@
           <t>4 Production ops</t>
         </is>
       </c>
-      <c r="F73" s="7" t="inlineStr">
+      <c r="F73" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9709,7 +9709,7 @@
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="F74" s="7" t="inlineStr">
+      <c r="F74" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9753,7 +9753,7 @@
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="F75" s="7" t="inlineStr">
+      <c r="F75" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9801,7 +9801,7 @@
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="F76" s="7" t="inlineStr">
+      <c r="F76" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9849,12 +9849,12 @@
           <t>3 Engineering Mode</t>
         </is>
       </c>
-      <c r="F77" s="7" t="inlineStr">
+      <c r="F77" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G77" s="10" t="inlineStr">
+      <c r="G77" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -9893,7 +9893,7 @@
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="F78" s="7" t="inlineStr">
+      <c r="F78" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9941,12 +9941,12 @@
           <t>4 Production ops</t>
         </is>
       </c>
-      <c r="F79" s="7" t="inlineStr">
+      <c r="F79" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G79" s="10" t="inlineStr">
+      <c r="G79" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -9989,7 +9989,7 @@
           <t>3 Engineering Mode</t>
         </is>
       </c>
-      <c r="F80" s="7" t="inlineStr">
+      <c r="F80" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10033,7 +10033,7 @@
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="F81" s="7" t="inlineStr">
+      <c r="F81" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10073,7 +10073,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F82" s="7" t="inlineStr">
+      <c r="F82" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10117,7 +10117,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F83" s="7" t="inlineStr">
+      <c r="F83" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10161,12 +10161,12 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F84" s="7" t="inlineStr">
+      <c r="F84" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G84" s="10" t="inlineStr">
+      <c r="G84" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -10205,7 +10205,7 @@
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="F85" s="7" t="inlineStr">
+      <c r="F85" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10249,7 +10249,7 @@
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="F86" s="7" t="inlineStr">
+      <c r="F86" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10297,7 +10297,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F87" s="7" t="inlineStr">
+      <c r="F87" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10345,7 +10345,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F88" s="7" t="inlineStr">
+      <c r="F88" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10393,7 +10393,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F89" s="7" t="inlineStr">
+      <c r="F89" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10441,7 +10441,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F90" s="7" t="inlineStr">
+      <c r="F90" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10489,7 +10489,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F91" s="7" t="inlineStr">
+      <c r="F91" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10537,7 +10537,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F92" s="7" t="inlineStr">
+      <c r="F92" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10585,7 +10585,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F93" s="7" t="inlineStr">
+      <c r="F93" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10633,7 +10633,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F94" s="7" t="inlineStr">
+      <c r="F94" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10681,7 +10681,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F95" s="7" t="inlineStr">
+      <c r="F95" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10729,7 +10729,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F96" s="7" t="inlineStr">
+      <c r="F96" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10777,7 +10777,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F97" s="7" t="inlineStr">
+      <c r="F97" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10825,7 +10825,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F98" s="7" t="inlineStr">
+      <c r="F98" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10873,7 +10873,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F99" s="7" t="inlineStr">
+      <c r="F99" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10921,7 +10921,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F100" s="7" t="inlineStr">
+      <c r="F100" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -11958,7 +11958,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G124" s="10" t="inlineStr">
+      <c r="G124" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -12002,7 +12002,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G125" s="10" t="inlineStr">
+      <c r="G125" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -12046,7 +12046,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G126" s="11" t="inlineStr">
+      <c r="G126" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -12090,7 +12090,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G127" s="11" t="inlineStr">
+      <c r="G127" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -12134,7 +12134,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G128" s="10" t="inlineStr">
+      <c r="G128" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -12178,7 +12178,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G129" s="10" t="inlineStr">
+      <c r="G129" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -12222,7 +12222,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G130" s="10" t="inlineStr">
+      <c r="G130" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -12266,7 +12266,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G131" s="11" t="inlineStr">
+      <c r="G131" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -12310,7 +12310,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G132" s="11" t="inlineStr">
+      <c r="G132" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -12354,7 +12354,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G133" s="11" t="inlineStr">
+      <c r="G133" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -12398,7 +12398,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G134" s="11" t="inlineStr">
+      <c r="G134" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -12442,7 +12442,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G135" s="11" t="inlineStr">
+      <c r="G135" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -12486,7 +12486,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G136" s="10" t="inlineStr">
+      <c r="G136" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -12530,7 +12530,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G137" s="11" t="inlineStr">
+      <c r="G137" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -12574,7 +12574,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G138" s="10" t="inlineStr">
+      <c r="G138" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -12750,7 +12750,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G142" s="10" t="inlineStr">
+      <c r="G142" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -12794,7 +12794,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G143" s="10" t="inlineStr">
+      <c r="G143" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -12838,7 +12838,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G144" s="10" t="inlineStr">
+      <c r="G144" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -12882,7 +12882,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G145" s="10" t="inlineStr">
+      <c r="G145" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -12926,7 +12926,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G146" s="11" t="inlineStr">
+      <c r="G146" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -12970,7 +12970,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G147" s="11" t="inlineStr">
+      <c r="G147" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -13014,7 +13014,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G148" s="11" t="inlineStr">
+      <c r="G148" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -13386,7 +13386,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G157" s="10" t="inlineStr">
+      <c r="G157" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -13430,7 +13430,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G158" s="10" t="inlineStr">
+      <c r="G158" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -13630,7 +13630,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G163" s="10" t="inlineStr">
+      <c r="G163" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -13670,7 +13670,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G164" s="10" t="inlineStr">
+      <c r="G164" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -13710,7 +13710,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G165" s="10" t="inlineStr">
+      <c r="G165" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -13750,7 +13750,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G166" s="10" t="inlineStr">
+      <c r="G166" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -13790,7 +13790,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G167" s="10" t="inlineStr">
+      <c r="G167" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -13830,7 +13830,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G168" s="10" t="inlineStr">
+      <c r="G168" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -13918,7 +13918,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G170" s="10" t="inlineStr">
+      <c r="G170" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -13958,7 +13958,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G171" s="10" t="inlineStr">
+      <c r="G171" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -14002,7 +14002,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G172" s="10" t="inlineStr">
+      <c r="G172" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -14042,7 +14042,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G173" s="10" t="inlineStr">
+      <c r="G173" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -14082,7 +14082,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G174" s="10" t="inlineStr">
+      <c r="G174" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -14122,7 +14122,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G175" s="10" t="inlineStr">
+      <c r="G175" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -14162,7 +14162,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G176" s="10" t="inlineStr">
+      <c r="G176" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -14206,7 +14206,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G177" s="11" t="inlineStr">
+      <c r="G177" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -14246,7 +14246,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G178" s="11" t="inlineStr">
+      <c r="G178" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -14290,7 +14290,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G179" s="11" t="inlineStr">
+      <c r="G179" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -14594,7 +14594,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G186" s="10" t="inlineStr">
+      <c r="G186" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -14726,7 +14726,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G189" s="10" t="inlineStr">
+      <c r="G189" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -14806,7 +14806,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G191" s="11" t="inlineStr">
+      <c r="G191" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -14846,7 +14846,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G192" s="10" t="inlineStr">
+      <c r="G192" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -14974,7 +14974,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G195" s="11" t="inlineStr">
+      <c r="G195" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -15014,7 +15014,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G196" s="10" t="inlineStr">
+      <c r="G196" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -15094,7 +15094,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G198" s="10" t="inlineStr">
+      <c r="G198" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -15214,7 +15214,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G201" s="10" t="inlineStr">
+      <c r="G201" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -15254,7 +15254,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G202" s="10" t="inlineStr">
+      <c r="G202" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -15338,7 +15338,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G204" s="10" t="inlineStr">
+      <c r="G204" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -15458,7 +15458,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G207" s="10" t="inlineStr">
+      <c r="G207" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -15538,7 +15538,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G209" s="11" t="inlineStr">
+      <c r="G209" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -15662,7 +15662,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G212" s="10" t="inlineStr">
+      <c r="G212" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -15742,7 +15742,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G214" s="10" t="inlineStr">
+      <c r="G214" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -15822,7 +15822,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G216" s="10" t="inlineStr">
+      <c r="G216" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -15862,7 +15862,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G217" s="10" t="inlineStr">
+      <c r="G217" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -15902,7 +15902,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G218" s="11" t="inlineStr">
+      <c r="G218" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -16226,7 +16226,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G226" s="10" t="inlineStr">
+      <c r="G226" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -16266,7 +16266,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G227" s="10" t="inlineStr">
+      <c r="G227" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -16402,7 +16402,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G230" s="11" t="inlineStr">
+      <c r="G230" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -16446,7 +16446,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G231" s="10" t="inlineStr">
+      <c r="G231" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -16490,7 +16490,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G232" s="10" t="inlineStr">
+      <c r="G232" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -16538,7 +16538,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G233" s="10" t="inlineStr">
+      <c r="G233" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -16582,7 +16582,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G234" s="10" t="inlineStr">
+      <c r="G234" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -16626,7 +16626,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G235" s="11" t="inlineStr">
+      <c r="G235" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -16670,7 +16670,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G236" s="10" t="inlineStr">
+      <c r="G236" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -16714,7 +16714,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G237" s="10" t="inlineStr">
+      <c r="G237" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -16758,7 +16758,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G238" s="11" t="inlineStr">
+      <c r="G238" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -16802,7 +16802,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G239" s="11" t="inlineStr">
+      <c r="G239" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -16846,7 +16846,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G240" s="10" t="inlineStr">
+      <c r="G240" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -16890,7 +16890,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G241" s="10" t="inlineStr">
+      <c r="G241" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -16934,7 +16934,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G242" s="10" t="inlineStr">
+      <c r="G242" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -16982,7 +16982,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G243" s="10" t="inlineStr">
+      <c r="G243" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -17026,7 +17026,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G244" s="11" t="inlineStr">
+      <c r="G244" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -17070,7 +17070,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G245" s="10" t="inlineStr">
+      <c r="G245" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -17114,7 +17114,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G246" s="10" t="inlineStr">
+      <c r="G246" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -17158,7 +17158,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G247" s="10" t="inlineStr">
+      <c r="G247" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -17202,7 +17202,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G248" s="11" t="inlineStr">
+      <c r="G248" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -17246,7 +17246,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G249" s="10" t="inlineStr">
+      <c r="G249" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -17338,7 +17338,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G251" s="11" t="inlineStr">
+      <c r="G251" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -17382,7 +17382,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G252" s="10" t="inlineStr">
+      <c r="G252" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -17426,7 +17426,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G253" s="11" t="inlineStr">
+      <c r="G253" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -17522,7 +17522,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G255" s="11" t="inlineStr">
+      <c r="G255" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -17566,7 +17566,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G256" s="10" t="inlineStr">
+      <c r="G256" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -17614,7 +17614,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G257" s="11" t="inlineStr">
+      <c r="G257" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -17658,7 +17658,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G258" s="11" t="inlineStr">
+      <c r="G258" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -17750,7 +17750,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G260" s="11" t="inlineStr">
+      <c r="G260" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -17794,7 +17794,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G261" s="11" t="inlineStr">
+      <c r="G261" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -17838,7 +17838,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G262" s="10" t="inlineStr">
+      <c r="G262" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -17930,7 +17930,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G264" s="10" t="inlineStr">
+      <c r="G264" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -17974,7 +17974,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G265" s="11" t="inlineStr">
+      <c r="G265" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -18018,7 +18018,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G266" s="10" t="inlineStr">
+      <c r="G266" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -18066,7 +18066,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G267" s="10" t="inlineStr">
+      <c r="G267" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -18114,7 +18114,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G268" s="11" t="inlineStr">
+      <c r="G268" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -18158,7 +18158,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G269" s="11" t="inlineStr">
+      <c r="G269" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -18250,7 +18250,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G271" s="10" t="inlineStr">
+      <c r="G271" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -18338,7 +18338,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G273" s="10" t="inlineStr">
+      <c r="G273" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -18430,7 +18430,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G275" s="10" t="inlineStr">
+      <c r="G275" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -18474,7 +18474,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G276" s="10" t="inlineStr">
+      <c r="G276" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -18518,7 +18518,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G277" s="10" t="inlineStr">
+      <c r="G277" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -18566,7 +18566,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G278" s="11" t="inlineStr">
+      <c r="G278" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -18610,7 +18610,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G279" s="10" t="inlineStr">
+      <c r="G279" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -18798,7 +18798,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G283" s="11" t="inlineStr">
+      <c r="G283" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -18842,7 +18842,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G284" s="10" t="inlineStr">
+      <c r="G284" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -18978,7 +18978,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G287" s="10" t="inlineStr">
+      <c r="G287" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -19022,7 +19022,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G288" s="11" t="inlineStr">
+      <c r="G288" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -19066,7 +19066,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G289" s="11" t="inlineStr">
+      <c r="G289" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -19110,7 +19110,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G290" s="10" t="inlineStr">
+      <c r="G290" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -19158,7 +19158,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G291" s="10" t="inlineStr">
+      <c r="G291" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -19202,7 +19202,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G292" s="11" t="inlineStr">
+      <c r="G292" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -19294,7 +19294,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G294" s="10" t="inlineStr">
+      <c r="G294" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -19338,7 +19338,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G295" s="10" t="inlineStr">
+      <c r="G295" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -19550,7 +19550,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G300" s="10" t="inlineStr">
+      <c r="G300" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -19710,7 +19710,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G304" s="10" t="inlineStr">
+      <c r="G304" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -19870,7 +19870,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G308" s="10" t="inlineStr">
+      <c r="G308" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -19910,7 +19910,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G309" s="10" t="inlineStr">
+      <c r="G309" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -20586,7 +20586,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G325" s="10" t="inlineStr">
+      <c r="G325" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -20630,7 +20630,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G326" s="10" t="inlineStr">
+      <c r="G326" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -20674,7 +20674,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G327" s="10" t="inlineStr">
+      <c r="G327" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -20766,7 +20766,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G329" s="10" t="inlineStr">
+      <c r="G329" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -20942,7 +20942,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G333" s="10" t="inlineStr">
+      <c r="G333" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -20986,7 +20986,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G334" s="10" t="inlineStr">
+      <c r="G334" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -21122,7 +21122,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G337" s="10" t="inlineStr">
+      <c r="G337" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -21170,7 +21170,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G338" s="11" t="inlineStr">
+      <c r="G338" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -21302,7 +21302,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G341" s="10" t="inlineStr">
+      <c r="G341" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -21346,7 +21346,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G342" s="10" t="inlineStr">
+      <c r="G342" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -21390,7 +21390,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G343" s="10" t="inlineStr">
+      <c r="G343" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -21478,7 +21478,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G345" s="10" t="inlineStr">
+      <c r="G345" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -21566,7 +21566,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G347" s="10" t="inlineStr">
+      <c r="G347" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -21702,7 +21702,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G350" s="10" t="inlineStr">
+      <c r="G350" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -21878,7 +21878,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G354" s="10" t="inlineStr">
+      <c r="G354" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -21966,7 +21966,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G356" s="10" t="inlineStr">
+      <c r="G356" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -22010,7 +22010,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G357" s="10" t="inlineStr">
+      <c r="G357" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -22142,7 +22142,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G360" s="10" t="inlineStr">
+      <c r="G360" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -22186,7 +22186,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G361" s="10" t="inlineStr">
+      <c r="G361" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -22362,7 +22362,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G365" s="10" t="inlineStr">
+      <c r="G365" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -22450,7 +22450,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G367" s="10" t="inlineStr">
+      <c r="G367" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -22674,7 +22674,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G372" s="10" t="inlineStr">
+      <c r="G372" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -22718,7 +22718,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G373" s="10" t="inlineStr">
+      <c r="G373" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -22762,7 +22762,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G374" s="10" t="inlineStr">
+      <c r="G374" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -22806,7 +22806,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G375" s="10" t="inlineStr">
+      <c r="G375" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -22894,7 +22894,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G377" s="10" t="inlineStr">
+      <c r="G377" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -22938,7 +22938,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G378" s="11" t="inlineStr">
+      <c r="G378" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -22982,7 +22982,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G379" s="11" t="inlineStr">
+      <c r="G379" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -23026,7 +23026,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G380" s="11" t="inlineStr">
+      <c r="G380" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -23378,7 +23378,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G388" s="10" t="inlineStr">
+      <c r="G388" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -23510,7 +23510,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G391" s="10" t="inlineStr">
+      <c r="G391" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -23554,7 +23554,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G392" s="10" t="inlineStr">
+      <c r="G392" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -23598,7 +23598,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G393" s="10" t="inlineStr">
+      <c r="G393" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -23642,7 +23642,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G394" s="10" t="inlineStr">
+      <c r="G394" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -23686,7 +23686,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G395" s="10" t="inlineStr">
+      <c r="G395" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -23730,7 +23730,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G396" s="10" t="inlineStr">
+      <c r="G396" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -23774,7 +23774,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G397" s="10" t="inlineStr">
+      <c r="G397" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -23906,7 +23906,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G400" s="10" t="inlineStr">
+      <c r="G400" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -23950,7 +23950,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G401" s="10" t="inlineStr">
+      <c r="G401" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -23990,7 +23990,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G402" s="10" t="inlineStr">
+      <c r="G402" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -24078,7 +24078,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G404" s="10" t="inlineStr">
+      <c r="G404" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -24518,7 +24518,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G414" s="10" t="inlineStr">
+      <c r="G414" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -24694,7 +24694,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G418" s="10" t="inlineStr">
+      <c r="G418" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -24782,7 +24782,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G420" s="10" t="inlineStr">
+      <c r="G420" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -24826,7 +24826,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G421" s="11" t="inlineStr">
+      <c r="G421" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -24870,7 +24870,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G422" s="11" t="inlineStr">
+      <c r="G422" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -24914,7 +24914,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G423" s="10" t="inlineStr">
+      <c r="G423" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -24958,7 +24958,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G424" s="11" t="inlineStr">
+      <c r="G424" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25002,7 +25002,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G425" s="10" t="inlineStr">
+      <c r="G425" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -25046,7 +25046,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G426" s="10" t="inlineStr">
+      <c r="G426" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -25090,7 +25090,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G427" s="11" t="inlineStr">
+      <c r="G427" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25222,7 +25222,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G430" s="10" t="inlineStr">
+      <c r="G430" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -25266,7 +25266,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G431" s="11" t="inlineStr">
+      <c r="G431" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25310,7 +25310,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G432" s="11" t="inlineStr">
+      <c r="G432" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25354,7 +25354,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G433" s="10" t="inlineStr">
+      <c r="G433" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -25442,7 +25442,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G435" s="10" t="inlineStr">
+      <c r="G435" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -25486,7 +25486,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G436" s="10" t="inlineStr">
+      <c r="G436" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -25530,7 +25530,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G437" s="10" t="inlineStr">
+      <c r="G437" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -25574,7 +25574,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G438" s="10" t="inlineStr">
+      <c r="G438" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -25618,7 +25618,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G439" s="11" t="inlineStr">
+      <c r="G439" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25662,7 +25662,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G440" s="11" t="inlineStr">
+      <c r="G440" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25706,7 +25706,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G441" s="11" t="inlineStr">
+      <c r="G441" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25750,7 +25750,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G442" s="11" t="inlineStr">
+      <c r="G442" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25794,7 +25794,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G443" s="11" t="inlineStr">
+      <c r="G443" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25838,7 +25838,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G444" s="11" t="inlineStr">
+      <c r="G444" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25882,7 +25882,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G445" s="11" t="inlineStr">
+      <c r="G445" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25926,7 +25926,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G446" s="10" t="inlineStr">
+      <c r="G446" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -26014,7 +26014,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G448" s="11" t="inlineStr">
+      <c r="G448" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -26058,7 +26058,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G449" s="10" t="inlineStr">
+      <c r="G449" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -26102,7 +26102,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G450" s="10" t="inlineStr">
+      <c r="G450" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -26146,7 +26146,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G451" s="11" t="inlineStr">
+      <c r="G451" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -26190,7 +26190,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G452" s="10" t="inlineStr">
+      <c r="G452" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -26234,7 +26234,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G453" s="10" t="inlineStr">
+      <c r="G453" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -26278,7 +26278,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G454" s="10" t="inlineStr">
+      <c r="G454" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -26322,7 +26322,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G455" s="11" t="inlineStr">
+      <c r="G455" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -26366,7 +26366,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G456" s="11" t="inlineStr">
+      <c r="G456" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -26410,7 +26410,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G457" s="10" t="inlineStr">
+      <c r="G457" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -26454,7 +26454,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G458" s="10" t="inlineStr">
+      <c r="G458" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -26498,7 +26498,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G459" s="10" t="inlineStr">
+      <c r="G459" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -26542,7 +26542,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G460" s="11" t="inlineStr">
+      <c r="G460" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -26586,7 +26586,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G461" s="11" t="inlineStr">
+      <c r="G461" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -26630,7 +26630,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G462" s="10" t="inlineStr">
+      <c r="G462" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -26674,7 +26674,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G463" s="11" t="inlineStr">
+      <c r="G463" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -26718,7 +26718,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G464" s="10" t="inlineStr">
+      <c r="G464" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -26762,7 +26762,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G465" s="10" t="inlineStr">
+      <c r="G465" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -26806,7 +26806,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G466" s="10" t="inlineStr">
+      <c r="G466" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -26850,7 +26850,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G467" s="11" t="inlineStr">
+      <c r="G467" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -26894,7 +26894,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G468" s="11" t="inlineStr">
+      <c r="G468" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -26982,7 +26982,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G470" s="10" t="inlineStr">
+      <c r="G470" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -27026,7 +27026,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G471" s="10" t="inlineStr">
+      <c r="G471" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -27114,7 +27114,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G473" s="10" t="inlineStr">
+      <c r="G473" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -27158,7 +27158,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G474" s="11" t="inlineStr">
+      <c r="G474" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -27202,7 +27202,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G475" s="11" t="inlineStr">
+      <c r="G475" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -27246,7 +27246,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G476" s="10" t="inlineStr">
+      <c r="G476" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -27290,7 +27290,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G477" s="10" t="inlineStr">
+      <c r="G477" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -27334,7 +27334,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G478" s="10" t="inlineStr">
+      <c r="G478" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -27378,7 +27378,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G479" s="10" t="inlineStr">
+      <c r="G479" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -27422,7 +27422,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G480" s="11" t="inlineStr">
+      <c r="G480" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -27466,7 +27466,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G481" s="11" t="inlineStr">
+      <c r="G481" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -27510,7 +27510,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G482" s="11" t="inlineStr">
+      <c r="G482" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -27554,7 +27554,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G483" s="11" t="inlineStr">
+      <c r="G483" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -27598,7 +27598,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G484" s="11" t="inlineStr">
+      <c r="G484" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -27642,7 +27642,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G485" s="11" t="inlineStr">
+      <c r="G485" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -27730,7 +27730,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G487" s="10" t="inlineStr">
+      <c r="G487" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -27774,7 +27774,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G488" s="10" t="inlineStr">
+      <c r="G488" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -27818,7 +27818,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G489" s="11" t="inlineStr">
+      <c r="G489" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -27862,7 +27862,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G490" s="10" t="inlineStr">
+      <c r="G490" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -27950,7 +27950,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G492" s="10" t="inlineStr">
+      <c r="G492" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -27994,7 +27994,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G493" s="10" t="inlineStr">
+      <c r="G493" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -28038,7 +28038,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G494" s="11" t="inlineStr">
+      <c r="G494" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -28082,7 +28082,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G495" s="10" t="inlineStr">
+      <c r="G495" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -28126,7 +28126,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G496" s="11" t="inlineStr">
+      <c r="G496" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -28170,7 +28170,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G497" s="11" t="inlineStr">
+      <c r="G497" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -28258,7 +28258,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G499" s="11" t="inlineStr">
+      <c r="G499" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -28390,7 +28390,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G502" s="10" t="inlineStr">
+      <c r="G502" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -28434,7 +28434,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G503" s="10" t="inlineStr">
+      <c r="G503" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -28478,7 +28478,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G504" s="11" t="inlineStr">
+      <c r="G504" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -28522,7 +28522,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G505" s="11" t="inlineStr">
+      <c r="G505" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -28566,7 +28566,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G506" s="10" t="inlineStr">
+      <c r="G506" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -28610,7 +28610,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G507" s="10" t="inlineStr">
+      <c r="G507" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -28654,7 +28654,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G508" s="10" t="inlineStr">
+      <c r="G508" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -28698,7 +28698,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G509" s="10" t="inlineStr">
+      <c r="G509" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -28874,7 +28874,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G513" s="10" t="inlineStr">
+      <c r="G513" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -28918,7 +28918,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G514" s="10" t="inlineStr">
+      <c r="G514" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -28962,7 +28962,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G515" s="11" t="inlineStr">
+      <c r="G515" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -29006,7 +29006,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G516" s="10" t="inlineStr">
+      <c r="G516" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -29050,7 +29050,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G517" s="10" t="inlineStr">
+      <c r="G517" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -29094,7 +29094,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G518" s="10" t="inlineStr">
+      <c r="G518" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -29138,7 +29138,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G519" s="10" t="inlineStr">
+      <c r="G519" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -29182,7 +29182,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G520" s="10" t="inlineStr">
+      <c r="G520" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -29226,7 +29226,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G521" s="11" t="inlineStr">
+      <c r="G521" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -29270,7 +29270,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G522" s="10" t="inlineStr">
+      <c r="G522" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -29358,7 +29358,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G524" s="11" t="inlineStr">
+      <c r="G524" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -29402,7 +29402,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G525" s="10" t="inlineStr">
+      <c r="G525" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -29490,7 +29490,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G527" s="10" t="inlineStr">
+      <c r="G527" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -29534,7 +29534,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G528" s="11" t="inlineStr">
+      <c r="G528" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -29578,7 +29578,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G529" s="11" t="inlineStr">
+      <c r="G529" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -29622,7 +29622,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G530" s="10" t="inlineStr">
+      <c r="G530" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -29666,7 +29666,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G531" s="10" t="inlineStr">
+      <c r="G531" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -29710,7 +29710,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G532" s="10" t="inlineStr">
+      <c r="G532" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -29754,7 +29754,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G533" s="11" t="inlineStr">
+      <c r="G533" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -29798,7 +29798,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G534" s="11" t="inlineStr">
+      <c r="G534" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -29886,7 +29886,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G536" s="11" t="inlineStr">
+      <c r="G536" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -29930,7 +29930,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G537" s="10" t="inlineStr">
+      <c r="G537" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -29974,7 +29974,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G538" s="11" t="inlineStr">
+      <c r="G538" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30018,7 +30018,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G539" s="10" t="inlineStr">
+      <c r="G539" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -30062,7 +30062,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G540" s="11" t="inlineStr">
+      <c r="G540" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30106,7 +30106,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G541" s="10" t="inlineStr">
+      <c r="G541" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -30150,7 +30150,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G542" s="11" t="inlineStr">
+      <c r="G542" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30194,7 +30194,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G543" s="11" t="inlineStr">
+      <c r="G543" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30238,7 +30238,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G544" s="11" t="inlineStr">
+      <c r="G544" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30326,7 +30326,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G546" s="11" t="inlineStr">
+      <c r="G546" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30370,7 +30370,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G547" s="11" t="inlineStr">
+      <c r="G547" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30414,7 +30414,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G548" s="11" t="inlineStr">
+      <c r="G548" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30458,7 +30458,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G549" s="11" t="inlineStr">
+      <c r="G549" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30502,7 +30502,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G550" s="10" t="inlineStr">
+      <c r="G550" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -30546,7 +30546,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G551" s="11" t="inlineStr">
+      <c r="G551" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30590,7 +30590,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G552" s="11" t="inlineStr">
+      <c r="G552" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30634,7 +30634,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G553" s="11" t="inlineStr">
+      <c r="G553" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30678,7 +30678,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G554" s="10" t="inlineStr">
+      <c r="G554" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -30722,7 +30722,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G555" s="10" t="inlineStr">
+      <c r="G555" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -30766,7 +30766,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G556" s="11" t="inlineStr">
+      <c r="G556" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30810,7 +30810,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G557" s="10" t="inlineStr">
+      <c r="G557" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -30898,7 +30898,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G559" s="11" t="inlineStr">
+      <c r="G559" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30942,7 +30942,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G560" s="10" t="inlineStr">
+      <c r="G560" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -30986,7 +30986,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G561" s="11" t="inlineStr">
+      <c r="G561" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -31030,7 +31030,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G562" s="10" t="inlineStr">
+      <c r="G562" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -31074,7 +31074,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G563" s="11" t="inlineStr">
+      <c r="G563" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -31118,7 +31118,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G564" s="10" t="inlineStr">
+      <c r="G564" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -31162,7 +31162,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G565" s="11" t="inlineStr">
+      <c r="G565" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -31294,7 +31294,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G568" s="10" t="inlineStr">
+      <c r="G568" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -31338,7 +31338,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G569" s="10" t="inlineStr">
+      <c r="G569" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -31382,7 +31382,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G570" s="11" t="inlineStr">
+      <c r="G570" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -31426,7 +31426,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G571" s="11" t="inlineStr">
+      <c r="G571" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -31470,7 +31470,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G572" s="10" t="inlineStr">
+      <c r="G572" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -31514,7 +31514,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G573" s="11" t="inlineStr">
+      <c r="G573" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -31558,7 +31558,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G574" s="10" t="inlineStr">
+      <c r="G574" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -31602,7 +31602,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G575" s="10" t="inlineStr">
+      <c r="G575" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -31646,7 +31646,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G576" s="11" t="inlineStr">
+      <c r="G576" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -31690,7 +31690,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G577" s="10" t="inlineStr">
+      <c r="G577" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -31734,7 +31734,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G578" s="10" t="inlineStr">
+      <c r="G578" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -31778,7 +31778,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G579" s="11" t="inlineStr">
+      <c r="G579" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -31822,7 +31822,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G580" s="10" t="inlineStr">
+      <c r="G580" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -31866,7 +31866,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G581" s="11" t="inlineStr">
+      <c r="G581" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -31910,7 +31910,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G582" s="11" t="inlineStr">
+      <c r="G582" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -31954,7 +31954,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G583" s="10" t="inlineStr">
+      <c r="G583" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -31998,7 +31998,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G584" s="10" t="inlineStr">
+      <c r="G584" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -32042,7 +32042,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G585" s="10" t="inlineStr">
+      <c r="G585" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -32086,7 +32086,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G586" s="11" t="inlineStr">
+      <c r="G586" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -32130,7 +32130,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G587" s="11" t="inlineStr">
+      <c r="G587" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -32218,7 +32218,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G589" s="10" t="inlineStr">
+      <c r="G589" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -32262,7 +32262,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G590" s="10" t="inlineStr">
+      <c r="G590" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -32350,7 +32350,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G592" s="10" t="inlineStr">
+      <c r="G592" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -32394,7 +32394,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G593" s="10" t="inlineStr">
+      <c r="G593" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -32438,7 +32438,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G594" s="11" t="inlineStr">
+      <c r="G594" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -32482,7 +32482,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G595" s="11" t="inlineStr">
+      <c r="G595" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -32526,7 +32526,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G596" s="11" t="inlineStr">
+      <c r="G596" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -32570,7 +32570,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G597" s="10" t="inlineStr">
+      <c r="G597" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -32614,7 +32614,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G598" s="11" t="inlineStr">
+      <c r="G598" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -32658,7 +32658,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G599" s="10" t="inlineStr">
+      <c r="G599" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -32702,7 +32702,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G600" s="10" t="inlineStr">
+      <c r="G600" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -32746,7 +32746,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G601" s="10" t="inlineStr">
+      <c r="G601" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -32790,7 +32790,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G602" s="11" t="inlineStr">
+      <c r="G602" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -32834,7 +32834,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G603" s="10" t="inlineStr">
+      <c r="G603" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -32878,7 +32878,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G604" s="10" t="inlineStr">
+      <c r="G604" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -32922,7 +32922,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G605" s="11" t="inlineStr">
+      <c r="G605" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -32966,7 +32966,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G606" s="11" t="inlineStr">
+      <c r="G606" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -33054,7 +33054,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G608" s="11" t="inlineStr">
+      <c r="G608" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -33098,7 +33098,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G609" s="10" t="inlineStr">
+      <c r="G609" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -33142,7 +33142,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G610" s="11" t="inlineStr">
+      <c r="G610" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -33186,7 +33186,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G611" s="10" t="inlineStr">
+      <c r="G611" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -33230,7 +33230,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G612" s="10" t="inlineStr">
+      <c r="G612" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -33274,7 +33274,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G613" s="10" t="inlineStr">
+      <c r="G613" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -33362,7 +33362,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G615" s="11" t="inlineStr">
+      <c r="G615" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -33406,7 +33406,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G616" s="10" t="inlineStr">
+      <c r="G616" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -33441,7 +33441,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F617" s="11" t="inlineStr">
+      <c r="F617" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33485,7 +33485,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F618" s="11" t="inlineStr">
+      <c r="F618" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33529,7 +33529,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F619" s="11" t="inlineStr">
+      <c r="F619" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33573,7 +33573,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F620" s="11" t="inlineStr">
+      <c r="F620" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33617,7 +33617,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F621" s="11" t="inlineStr">
+      <c r="F621" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33661,7 +33661,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F622" s="11" t="inlineStr">
+      <c r="F622" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33705,7 +33705,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F623" s="11" t="inlineStr">
+      <c r="F623" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33749,7 +33749,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F624" s="11" t="inlineStr">
+      <c r="F624" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33789,7 +33789,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F625" s="11" t="inlineStr">
+      <c r="F625" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33833,7 +33833,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F626" s="11" t="inlineStr">
+      <c r="F626" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33873,7 +33873,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F627" s="11" t="inlineStr">
+      <c r="F627" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33917,7 +33917,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F628" s="11" t="inlineStr">
+      <c r="F628" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33957,12 +33957,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F629" s="12" t="inlineStr">
+      <c r="F629" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G629" s="11" t="inlineStr">
+      <c r="G629" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34001,12 +34001,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F630" s="12" t="inlineStr">
+      <c r="F630" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G630" s="11" t="inlineStr">
+      <c r="G630" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34045,12 +34045,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F631" s="12" t="inlineStr">
+      <c r="F631" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G631" s="11" t="inlineStr">
+      <c r="G631" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34089,12 +34089,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F632" s="12" t="inlineStr">
+      <c r="F632" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G632" s="10" t="inlineStr">
+      <c r="G632" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -34133,12 +34133,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F633" s="12" t="inlineStr">
+      <c r="F633" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G633" s="11" t="inlineStr">
+      <c r="G633" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34177,12 +34177,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F634" s="12" t="inlineStr">
+      <c r="F634" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G634" s="11" t="inlineStr">
+      <c r="G634" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34217,12 +34217,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F635" s="12" t="inlineStr">
+      <c r="F635" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G635" s="11" t="inlineStr">
+      <c r="G635" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34261,12 +34261,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F636" s="12" t="inlineStr">
+      <c r="F636" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G636" s="11" t="inlineStr">
+      <c r="G636" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34305,12 +34305,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F637" s="12" t="inlineStr">
+      <c r="F637" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G637" s="11" t="inlineStr">
+      <c r="G637" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34349,12 +34349,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F638" s="12" t="inlineStr">
+      <c r="F638" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G638" s="11" t="inlineStr">
+      <c r="G638" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34389,12 +34389,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F639" s="12" t="inlineStr">
+      <c r="F639" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G639" s="11" t="inlineStr">
+      <c r="G639" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34433,12 +34433,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F640" s="12" t="inlineStr">
+      <c r="F640" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G640" s="11" t="inlineStr">
+      <c r="G640" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34477,12 +34477,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F641" s="12" t="inlineStr">
+      <c r="F641" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G641" s="11" t="inlineStr">
+      <c r="G641" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34521,12 +34521,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F642" s="12" t="inlineStr">
+      <c r="F642" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G642" s="11" t="inlineStr">
+      <c r="G642" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34565,12 +34565,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F643" s="12" t="inlineStr">
+      <c r="F643" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G643" s="11" t="inlineStr">
+      <c r="G643" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34609,12 +34609,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F644" s="12" t="inlineStr">
+      <c r="F644" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G644" s="11" t="inlineStr">
+      <c r="G644" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34653,12 +34653,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F645" s="12" t="inlineStr">
+      <c r="F645" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G645" s="11" t="inlineStr">
+      <c r="G645" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34697,12 +34697,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F646" s="12" t="inlineStr">
+      <c r="F646" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G646" s="11" t="inlineStr">
+      <c r="G646" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34741,12 +34741,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F647" s="12" t="inlineStr">
+      <c r="F647" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G647" s="11" t="inlineStr">
+      <c r="G647" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34785,12 +34785,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F648" s="12" t="inlineStr">
+      <c r="F648" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G648" s="11" t="inlineStr">
+      <c r="G648" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34829,12 +34829,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F649" s="12" t="inlineStr">
+      <c r="F649" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G649" s="11" t="inlineStr">
+      <c r="G649" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34873,12 +34873,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F650" s="12" t="inlineStr">
+      <c r="F650" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G650" s="11" t="inlineStr">
+      <c r="G650" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34917,12 +34917,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F651" s="12" t="inlineStr">
+      <c r="F651" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G651" s="11" t="inlineStr">
+      <c r="G651" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34961,12 +34961,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F652" s="12" t="inlineStr">
+      <c r="F652" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G652" s="11" t="inlineStr">
+      <c r="G652" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35005,12 +35005,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F653" s="12" t="inlineStr">
+      <c r="F653" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G653" s="11" t="inlineStr">
+      <c r="G653" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35045,12 +35045,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F654" s="12" t="inlineStr">
+      <c r="F654" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G654" s="11" t="inlineStr">
+      <c r="G654" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35089,12 +35089,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F655" s="12" t="inlineStr">
+      <c r="F655" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G655" s="11" t="inlineStr">
+      <c r="G655" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35133,12 +35133,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F656" s="12" t="inlineStr">
+      <c r="F656" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G656" s="11" t="inlineStr">
+      <c r="G656" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35173,12 +35173,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F657" s="12" t="inlineStr">
+      <c r="F657" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G657" s="11" t="inlineStr">
+      <c r="G657" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35217,12 +35217,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F658" s="12" t="inlineStr">
+      <c r="F658" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G658" s="11" t="inlineStr">
+      <c r="G658" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35257,12 +35257,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F659" s="12" t="inlineStr">
+      <c r="F659" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G659" s="11" t="inlineStr">
+      <c r="G659" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35297,12 +35297,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F660" s="12" t="inlineStr">
+      <c r="F660" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G660" s="11" t="inlineStr">
+      <c r="G660" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35337,12 +35337,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F661" s="12" t="inlineStr">
+      <c r="F661" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G661" s="11" t="inlineStr">
+      <c r="G661" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35377,12 +35377,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F662" s="12" t="inlineStr">
+      <c r="F662" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G662" s="11" t="inlineStr">
+      <c r="G662" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35421,12 +35421,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F663" s="12" t="inlineStr">
+      <c r="F663" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G663" s="11" t="inlineStr">
+      <c r="G663" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35465,12 +35465,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F664" s="12" t="inlineStr">
+      <c r="F664" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G664" s="11" t="inlineStr">
+      <c r="G664" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35509,12 +35509,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F665" s="12" t="inlineStr">
+      <c r="F665" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G665" s="11" t="inlineStr">
+      <c r="G665" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35549,12 +35549,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F666" s="12" t="inlineStr">
+      <c r="F666" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G666" s="11" t="inlineStr">
+      <c r="G666" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35589,12 +35589,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F667" s="12" t="inlineStr">
+      <c r="F667" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G667" s="11" t="inlineStr">
+      <c r="G667" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35629,12 +35629,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F668" s="12" t="inlineStr">
+      <c r="F668" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G668" s="11" t="inlineStr">
+      <c r="G668" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35669,12 +35669,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F669" s="12" t="inlineStr">
+      <c r="F669" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G669" s="11" t="inlineStr">
+      <c r="G669" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35709,12 +35709,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F670" s="12" t="inlineStr">
+      <c r="F670" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G670" s="11" t="inlineStr">
+      <c r="G670" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35753,12 +35753,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F671" s="12" t="inlineStr">
+      <c r="F671" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G671" s="11" t="inlineStr">
+      <c r="G671" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35793,12 +35793,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F672" s="12" t="inlineStr">
+      <c r="F672" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G672" s="11" t="inlineStr">
+      <c r="G672" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35833,12 +35833,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F673" s="12" t="inlineStr">
+      <c r="F673" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G673" s="11" t="inlineStr">
+      <c r="G673" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35873,12 +35873,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F674" s="12" t="inlineStr">
+      <c r="F674" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G674" s="11" t="inlineStr">
+      <c r="G674" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35913,12 +35913,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F675" s="12" t="inlineStr">
+      <c r="F675" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G675" s="11" t="inlineStr">
+      <c r="G675" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35957,12 +35957,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F676" s="12" t="inlineStr">
+      <c r="F676" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G676" s="11" t="inlineStr">
+      <c r="G676" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -36001,12 +36001,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F677" s="12" t="inlineStr">
+      <c r="F677" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G677" s="11" t="inlineStr">
+      <c r="G677" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -36045,12 +36045,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F678" s="12" t="inlineStr">
+      <c r="F678" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G678" s="11" t="inlineStr">
+      <c r="G678" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -36089,12 +36089,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F679" s="12" t="inlineStr">
+      <c r="F679" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G679" s="11" t="inlineStr">
+      <c r="G679" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -36133,12 +36133,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F680" s="12" t="inlineStr">
+      <c r="F680" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G680" s="11" t="inlineStr">
+      <c r="G680" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -36177,12 +36177,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F681" s="12" t="inlineStr">
+      <c r="F681" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G681" s="11" t="inlineStr">
+      <c r="G681" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -36221,12 +36221,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F682" s="12" t="inlineStr">
+      <c r="F682" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G682" s="11" t="inlineStr">
+      <c r="G682" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -36265,12 +36265,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F683" s="12" t="inlineStr">
+      <c r="F683" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G683" s="11" t="inlineStr">
+      <c r="G683" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -36309,12 +36309,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F684" s="12" t="inlineStr">
+      <c r="F684" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G684" s="11" t="inlineStr">
+      <c r="G684" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -36349,12 +36349,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F685" s="12" t="inlineStr">
+      <c r="F685" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G685" s="11" t="inlineStr">
+      <c r="G685" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -36385,7 +36385,7 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F686" s="13" t="inlineStr">
+      <c r="F686" s="14" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -36425,7 +36425,7 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F687" s="13" t="inlineStr">
+      <c r="F687" s="14" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -36465,7 +36465,7 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F688" s="13" t="inlineStr">
+      <c r="F688" s="14" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -36505,7 +36505,7 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F689" s="13" t="inlineStr">
+      <c r="F689" s="14" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -36545,7 +36545,7 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F690" s="13" t="inlineStr">
+      <c r="F690" s="14" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -36585,7 +36585,7 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F691" s="13" t="inlineStr">
+      <c r="F691" s="14" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -36625,7 +36625,7 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F692" s="13" t="inlineStr">
+      <c r="F692" s="14" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -36665,7 +36665,7 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F693" s="13" t="inlineStr">
+      <c r="F693" s="14" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -36705,7 +36705,7 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F694" s="13" t="inlineStr">
+      <c r="F694" s="14" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -38433,7 +38433,7 @@
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="F734" s="14" t="inlineStr">
+      <c r="F734" s="15" t="inlineStr">
         <is>
           <t>Completed - needs live proof</t>
         </is>
@@ -51049,7 +51049,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F1053" s="14" t="inlineStr">
+      <c r="F1053" s="15" t="inlineStr">
         <is>
           <t>Completed - needs live proof</t>
         </is>
@@ -51097,7 +51097,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F1054" s="14" t="inlineStr">
+      <c r="F1054" s="15" t="inlineStr">
         <is>
           <t>Completed - needs live proof</t>
         </is>
@@ -51145,7 +51145,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F1055" s="14" t="inlineStr">
+      <c r="F1055" s="15" t="inlineStr">
         <is>
           <t>Completed - needs live proof</t>
         </is>
@@ -51193,7 +51193,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F1056" s="14" t="inlineStr">
+      <c r="F1056" s="15" t="inlineStr">
         <is>
           <t>Completed - needs live proof</t>
         </is>
@@ -51241,7 +51241,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F1057" s="14" t="inlineStr">
+      <c r="F1057" s="15" t="inlineStr">
         <is>
           <t>Completed - needs live proof</t>
         </is>
@@ -51361,7 +51361,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F1060" s="14" t="inlineStr">
+      <c r="F1060" s="15" t="inlineStr">
         <is>
           <t>Completed - needs live proof</t>
         </is>
@@ -52493,7 +52493,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F1091" s="14" t="inlineStr">
+      <c r="F1091" s="15" t="inlineStr">
         <is>
           <t>Completed - needs live proof</t>
         </is>
@@ -53490,62 +53490,62 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="B1" s="15" t="inlineStr">
+      <c r="B1" s="16" t="inlineStr">
         <is>
           <t>0 Foundation</t>
         </is>
       </c>
-      <c r="C1" s="15" t="inlineStr">
+      <c r="C1" s="16" t="inlineStr">
         <is>
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="D1" s="15" t="inlineStr">
+      <c r="D1" s="16" t="inlineStr">
         <is>
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="E1" s="15" t="inlineStr">
+      <c r="E1" s="16" t="inlineStr">
         <is>
           <t>3 Engineering Mode</t>
         </is>
       </c>
-      <c r="F1" s="15" t="inlineStr">
+      <c r="F1" s="16" t="inlineStr">
         <is>
           <t>4 Production ops</t>
         </is>
       </c>
-      <c r="G1" s="15" t="inlineStr">
+      <c r="G1" s="16" t="inlineStr">
         <is>
           <t>5 Native mobile (last)</t>
         </is>
       </c>
-      <c r="H1" s="15" t="inlineStr">
+      <c r="H1" s="16" t="inlineStr">
         <is>
           <t>6 Go-live (credentials last)</t>
         </is>
       </c>
-      <c r="I1" s="15" t="inlineStr">
+      <c r="I1" s="16" t="inlineStr">
         <is>
           <t>7 Win the category</t>
         </is>
       </c>
-      <c r="J1" s="15" t="inlineStr">
+      <c r="J1" s="16" t="inlineStr">
         <is>
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="K1" s="15" t="inlineStr">
+      <c r="K1" s="16" t="inlineStr">
         <is>
           <t>Delivered</t>
         </is>
       </c>
-      <c r="L1" s="15" t="inlineStr">
+      <c r="L1" s="16" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
@@ -53641,7 +53641,7 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -53668,7 +53668,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -53681,7 +53681,7 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D5" t="n">
         <v>66</v>
@@ -53708,7 +53708,7 @@
         <v>2</v>
       </c>
       <c r="L5" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6">
@@ -53912,62 +53912,62 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Open queue by priority</t>
         </is>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>0 Foundation</t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="D12" s="15" t="inlineStr">
+      <c r="D12" s="16" t="inlineStr">
         <is>
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="E12" s="15" t="inlineStr">
+      <c r="E12" s="16" t="inlineStr">
         <is>
           <t>3 Engineering Mode</t>
         </is>
       </c>
-      <c r="F12" s="15" t="inlineStr">
+      <c r="F12" s="16" t="inlineStr">
         <is>
           <t>4 Production ops</t>
         </is>
       </c>
-      <c r="G12" s="15" t="inlineStr">
+      <c r="G12" s="16" t="inlineStr">
         <is>
           <t>5 Native mobile (last)</t>
         </is>
       </c>
-      <c r="H12" s="15" t="inlineStr">
+      <c r="H12" s="16" t="inlineStr">
         <is>
           <t>6 Go-live (credentials last)</t>
         </is>
       </c>
-      <c r="I12" s="15" t="inlineStr">
+      <c r="I12" s="16" t="inlineStr">
         <is>
           <t>7 Win the category</t>
         </is>
       </c>
-      <c r="J12" s="15" t="inlineStr">
+      <c r="J12" s="16" t="inlineStr">
         <is>
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="K12" s="15" t="inlineStr">
+      <c r="K12" s="16" t="inlineStr">
         <is>
           <t>Delivered</t>
         </is>
       </c>
-      <c r="L12" s="15" t="inlineStr">
+      <c r="L12" s="16" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
@@ -55282,7 +55282,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -55339,7 +55339,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="G3" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -55386,7 +55386,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -55438,7 +55438,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -55490,12 +55490,12 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="G6" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -55542,7 +55542,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="F7" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -55594,7 +55594,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -55699,7 +55699,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -55742,12 +55742,12 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="F11" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="G11" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -55799,7 +55799,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G12" s="10" t="inlineStr">
+      <c r="G12" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -55846,12 +55846,12 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F13" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G13" s="10" t="inlineStr">
+      <c r="G13" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -55903,7 +55903,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G14" s="11" t="inlineStr">
+      <c r="G14" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -55946,12 +55946,12 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F15" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G15" s="10" t="inlineStr">
+      <c r="G15" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -56055,7 +56055,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G17" s="10" t="inlineStr">
+      <c r="G17" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -56103,7 +56103,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="G18" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -56155,7 +56155,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G19" s="10" t="inlineStr">
+      <c r="G19" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -56198,12 +56198,12 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr">
+      <c r="F20" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G20" s="10" t="inlineStr">
+      <c r="G20" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -56255,7 +56255,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G21" s="10" t="inlineStr">
+      <c r="G21" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -56302,12 +56302,12 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr">
+      <c r="F22" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G22" s="10" t="inlineStr">
+      <c r="G22" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -56359,7 +56359,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G23" s="10" t="inlineStr">
+      <c r="G23" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -56407,7 +56407,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G24" s="11" t="inlineStr">
+      <c r="G24" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -56455,7 +56455,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G25" s="10" t="inlineStr">
+      <c r="G25" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -56503,7 +56503,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G26" s="10" t="inlineStr">
+      <c r="G26" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -56551,7 +56551,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G27" s="11" t="inlineStr">
+      <c r="G27" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -56698,12 +56698,12 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F30" s="7" t="inlineStr">
+      <c r="F30" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G30" s="11" t="inlineStr">
+      <c r="G30" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -56755,7 +56755,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G31" s="11" t="inlineStr">
+      <c r="G31" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -56798,12 +56798,12 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F32" s="7" t="inlineStr">
+      <c r="F32" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G32" s="10" t="inlineStr">
+      <c r="G32" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -56850,12 +56850,12 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F33" s="7" t="inlineStr">
+      <c r="F33" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G33" s="10" t="inlineStr">
+      <c r="G33" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -56902,12 +56902,12 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F34" s="7" t="inlineStr">
+      <c r="F34" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G34" s="10" t="inlineStr">
+      <c r="G34" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -56959,7 +56959,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G35" s="10" t="inlineStr">
+      <c r="G35" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -57007,7 +57007,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G36" s="11" t="inlineStr">
+      <c r="G36" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -57055,7 +57055,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G37" s="11" t="inlineStr">
+      <c r="G37" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -57103,7 +57103,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G38" s="10" t="inlineStr">
+      <c r="G38" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -57198,7 +57198,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F40" s="7" t="inlineStr">
+      <c r="F40" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -57250,12 +57250,12 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F41" s="7" t="inlineStr">
+      <c r="F41" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G41" s="10" t="inlineStr">
+      <c r="G41" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -57302,12 +57302,12 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F42" s="7" t="inlineStr">
+      <c r="F42" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G42" s="10" t="inlineStr">
+      <c r="G42" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -57359,7 +57359,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G43" s="10" t="inlineStr">
+      <c r="G43" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -57402,12 +57402,12 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F44" s="7" t="inlineStr">
+      <c r="F44" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G44" s="10" t="inlineStr">
+      <c r="G44" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -57459,7 +57459,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G45" s="10" t="inlineStr">
+      <c r="G45" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -57502,7 +57502,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F46" s="7" t="inlineStr">
+      <c r="F46" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -57606,7 +57606,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F48" s="7" t="inlineStr">
+      <c r="F48" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -57663,7 +57663,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G49" s="10" t="inlineStr">
+      <c r="G49" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -57711,7 +57711,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G50" s="10" t="inlineStr">
+      <c r="G50" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -57754,12 +57754,12 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F51" s="7" t="inlineStr">
+      <c r="F51" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G51" s="10" t="inlineStr">
+      <c r="G51" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -57811,7 +57811,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G52" s="10" t="inlineStr">
+      <c r="G52" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -57854,12 +57854,12 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F53" s="7" t="inlineStr">
+      <c r="F53" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G53" s="10" t="inlineStr">
+      <c r="G53" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -57911,7 +57911,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G54" s="10" t="inlineStr">
+      <c r="G54" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -57959,7 +57959,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G55" s="11" t="inlineStr">
+      <c r="G55" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -58011,7 +58011,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G56" s="10" t="inlineStr">
+      <c r="G56" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -58054,12 +58054,12 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F57" s="7" t="inlineStr">
+      <c r="F57" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G57" s="10" t="inlineStr">
+      <c r="G57" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -58111,7 +58111,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G58" s="11" t="inlineStr">
+      <c r="G58" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -58159,7 +58159,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G59" s="11" t="inlineStr">
+      <c r="G59" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -58207,7 +58207,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G60" s="10" t="inlineStr">
+      <c r="G60" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -58255,7 +58255,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G61" s="11" t="inlineStr">
+      <c r="G61" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -58298,7 +58298,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F62" s="7" t="inlineStr">
+      <c r="F62" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -58407,7 +58407,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G64" s="10" t="inlineStr">
+      <c r="G64" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -58459,7 +58459,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G65" s="10" t="inlineStr">
+      <c r="G65" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -58511,7 +58511,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G66" s="10" t="inlineStr">
+      <c r="G66" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -58559,7 +58559,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G67" s="11" t="inlineStr">
+      <c r="G67" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -58607,7 +58607,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G68" s="10" t="inlineStr">
+      <c r="G68" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -58650,12 +58650,12 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F69" s="7" t="inlineStr">
+      <c r="F69" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G69" s="10" t="inlineStr">
+      <c r="G69" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -58702,7 +58702,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F70" s="7" t="inlineStr">
+      <c r="F70" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -58754,12 +58754,12 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F71" s="7" t="inlineStr">
+      <c r="F71" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G71" s="10" t="inlineStr">
+      <c r="G71" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -58806,7 +58806,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F72" s="7" t="inlineStr">
+      <c r="F72" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -58863,7 +58863,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G73" s="10" t="inlineStr">
+      <c r="G73" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -58910,12 +58910,12 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F74" s="7" t="inlineStr">
+      <c r="F74" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G74" s="10" t="inlineStr">
+      <c r="G74" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -58962,12 +58962,12 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F75" s="7" t="inlineStr">
+      <c r="F75" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G75" s="10" t="inlineStr">
+      <c r="G75" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -59014,12 +59014,12 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F76" s="7" t="inlineStr">
+      <c r="F76" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G76" s="10" t="inlineStr">
+      <c r="G76" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -59066,7 +59066,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F77" s="7" t="inlineStr">
+      <c r="F77" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -59123,7 +59123,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G78" s="10" t="inlineStr">
+      <c r="G78" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -59170,12 +59170,12 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F79" s="7" t="inlineStr">
+      <c r="F79" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G79" s="10" t="inlineStr">
+      <c r="G79" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -59227,7 +59227,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G80" s="10" t="inlineStr">
+      <c r="G80" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -59274,12 +59274,12 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F81" s="7" t="inlineStr">
+      <c r="F81" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G81" s="10" t="inlineStr">
+      <c r="G81" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -59331,7 +59331,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G82" s="10" t="inlineStr">
+      <c r="G82" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -59374,12 +59374,12 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F83" s="7" t="inlineStr">
+      <c r="F83" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G83" s="11" t="inlineStr">
+      <c r="G83" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -59431,7 +59431,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G84" s="11" t="inlineStr">
+      <c r="G84" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -59626,7 +59626,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F88" s="7" t="inlineStr">
+      <c r="F88" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -59683,7 +59683,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G89" s="10" t="inlineStr">
+      <c r="G89" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -59874,7 +59874,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F93" s="7" t="inlineStr">
+      <c r="F93" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -59931,7 +59931,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G94" s="10" t="inlineStr">
+      <c r="G94" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -59979,7 +59979,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G95" s="10" t="inlineStr">
+      <c r="G95" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -60027,7 +60027,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G96" s="10" t="inlineStr">
+      <c r="G96" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -60070,12 +60070,12 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F97" s="7" t="inlineStr">
+      <c r="F97" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G97" s="11" t="inlineStr">
+      <c r="G97" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -60127,7 +60127,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G98" s="11" t="inlineStr">
+      <c r="G98" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -60175,7 +60175,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G99" s="11" t="inlineStr">
+      <c r="G99" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -60223,7 +60223,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G100" s="11" t="inlineStr">
+      <c r="G100" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -60318,12 +60318,12 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F102" s="7" t="inlineStr">
+      <c r="F102" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G102" s="10" t="inlineStr">
+      <c r="G102" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -60375,7 +60375,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G103" s="11" t="inlineStr">
+      <c r="G103" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -60423,7 +60423,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G104" s="11" t="inlineStr">
+      <c r="G104" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -60471,7 +60471,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G105" s="11" t="inlineStr">
+      <c r="G105" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -60519,7 +60519,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G106" s="11" t="inlineStr">
+      <c r="G106" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -60567,7 +60567,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G107" s="11" t="inlineStr">
+      <c r="G107" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -60615,7 +60615,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G108" s="11" t="inlineStr">
+      <c r="G108" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -60710,7 +60710,7 @@
           <t>Patient: App + Web; Doctor / provider: Web + App; Pharmacy / lab: Web; Clinic operator: Admin</t>
         </is>
       </c>
-      <c r="F110" s="7" t="inlineStr">
+      <c r="F110" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -60762,7 +60762,7 @@
           <t>Patient: App + Web; Doctor / provider: Web + App; Pharmacy / lab: Web; Clinic operator: Admin</t>
         </is>
       </c>
-      <c r="F111" s="7" t="inlineStr">
+      <c r="F111" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -60814,7 +60814,7 @@
           <t>Patient: App + Web; Doctor / provider: Web + App; Pharmacy / lab: Web; Clinic operator: Admin</t>
         </is>
       </c>
-      <c r="F112" s="7" t="inlineStr">
+      <c r="F112" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -60866,7 +60866,7 @@
           <t>Patient: App + Web; Doctor / provider: Web + App; Pharmacy / lab: Web; Clinic operator: Admin</t>
         </is>
       </c>
-      <c r="F113" s="7" t="inlineStr">
+      <c r="F113" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -60918,7 +60918,7 @@
           <t>Patient: App + Web; Doctor / provider: Web + App; Pharmacy / lab: Web; Clinic operator: Admin</t>
         </is>
       </c>
-      <c r="F114" s="7" t="inlineStr">
+      <c r="F114" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -61018,7 +61018,7 @@
           <t>Patient: App + Web; Doctor / provider: Web + App; Pharmacy / lab: Web; Clinic operator: Admin</t>
         </is>
       </c>
-      <c r="F116" s="7" t="inlineStr">
+      <c r="F116" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -61406,7 +61406,7 @@
           <t>Rider: App + Web; Driver: App; Dispatcher: Web; Operator: Admin</t>
         </is>
       </c>
-      <c r="F124" s="7" t="inlineStr">
+      <c r="F124" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -61458,7 +61458,7 @@
           <t>Rider: App + Web; Driver: App; Dispatcher: Web; Operator: Admin</t>
         </is>
       </c>
-      <c r="F125" s="7" t="inlineStr">
+      <c r="F125" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -61510,7 +61510,7 @@
           <t>Rider: App + Web; Driver: App; Dispatcher: Web; Operator: Admin</t>
         </is>
       </c>
-      <c r="F126" s="7" t="inlineStr">
+      <c r="F126" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -61946,7 +61946,7 @@
           <t>Buyer: App + Web; Seller / vendor: Web + App; Marketplace operator: Admin</t>
         </is>
       </c>
-      <c r="F135" s="7" t="inlineStr">
+      <c r="F135" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -61998,7 +61998,7 @@
           <t>Buyer: App + Web; Seller / vendor: Web + App; Marketplace operator: Admin</t>
         </is>
       </c>
-      <c r="F136" s="7" t="inlineStr">
+      <c r="F136" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -62050,7 +62050,7 @@
           <t>Buyer: App + Web; Seller / vendor: Web + App; Marketplace operator: Admin</t>
         </is>
       </c>
-      <c r="F137" s="7" t="inlineStr">
+      <c r="F137" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -62198,7 +62198,7 @@
           <t>Buyer: App + Web; Seller / vendor: Web + App; Marketplace operator: Admin</t>
         </is>
       </c>
-      <c r="F140" s="7" t="inlineStr">
+      <c r="F140" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -62250,7 +62250,7 @@
           <t>Buyer: App + Web; Seller / vendor: Web + App; Marketplace operator: Admin</t>
         </is>
       </c>
-      <c r="F141" s="7" t="inlineStr">
+      <c r="F141" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -62691,7 +62691,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G150" s="10" t="inlineStr">
+      <c r="G150" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -62739,7 +62739,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G151" s="10" t="inlineStr">
+      <c r="G151" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -62787,7 +62787,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G152" s="10" t="inlineStr">
+      <c r="G152" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -62835,7 +62835,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G153" s="10" t="inlineStr">
+      <c r="G153" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -62883,7 +62883,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G154" s="10" t="inlineStr">
+      <c r="G154" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -62931,7 +62931,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G155" s="10" t="inlineStr">
+      <c r="G155" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -62979,7 +62979,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G156" s="10" t="inlineStr">
+      <c r="G156" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -63027,7 +63027,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G157" s="10" t="inlineStr">
+      <c r="G157" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -63075,7 +63075,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G158" s="10" t="inlineStr">
+      <c r="G158" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -63123,7 +63123,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G159" s="10" t="inlineStr">
+      <c r="G159" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -63171,7 +63171,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G160" s="10" t="inlineStr">
+      <c r="G160" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -63219,7 +63219,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G161" s="10" t="inlineStr">
+      <c r="G161" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -63267,7 +63267,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G162" s="10" t="inlineStr">
+      <c r="G162" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -63315,7 +63315,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G163" s="10" t="inlineStr">
+      <c r="G163" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -63363,7 +63363,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G164" s="10" t="inlineStr">
+      <c r="G164" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -63411,7 +63411,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G165" s="10" t="inlineStr">
+      <c r="G165" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -63459,7 +63459,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G166" s="10" t="inlineStr">
+      <c r="G166" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -63507,7 +63507,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G167" s="10" t="inlineStr">
+      <c r="G167" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -63555,7 +63555,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G168" s="10" t="inlineStr">
+      <c r="G168" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -63603,7 +63603,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G169" s="10" t="inlineStr">
+      <c r="G169" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -63651,7 +63651,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G170" s="10" t="inlineStr">
+      <c r="G170" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -63699,7 +63699,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G171" s="10" t="inlineStr">
+      <c r="G171" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -63747,7 +63747,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G172" s="10" t="inlineStr">
+      <c r="G172" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -63795,7 +63795,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G173" s="10" t="inlineStr">
+      <c r="G173" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -63843,7 +63843,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G174" s="10" t="inlineStr">
+      <c r="G174" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -63891,7 +63891,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G175" s="10" t="inlineStr">
+      <c r="G175" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -63939,7 +63939,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G176" s="10" t="inlineStr">
+      <c r="G176" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -63987,7 +63987,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G177" s="10" t="inlineStr">
+      <c r="G177" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -64035,7 +64035,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G178" s="10" t="inlineStr">
+      <c r="G178" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -64083,7 +64083,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G179" s="10" t="inlineStr">
+      <c r="G179" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -64131,7 +64131,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G180" s="10" t="inlineStr">
+      <c r="G180" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -64179,7 +64179,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G181" s="10" t="inlineStr">
+      <c r="G181" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -64227,7 +64227,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G182" s="10" t="inlineStr">
+      <c r="G182" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -64275,7 +64275,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G183" s="10" t="inlineStr">
+      <c r="G183" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -64323,7 +64323,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G184" s="10" t="inlineStr">
+      <c r="G184" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -64371,7 +64371,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G185" s="10" t="inlineStr">
+      <c r="G185" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -64419,7 +64419,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G186" s="10" t="inlineStr">
+      <c r="G186" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -64467,7 +64467,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G187" s="10" t="inlineStr">
+      <c r="G187" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -64515,7 +64515,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G188" s="10" t="inlineStr">
+      <c r="G188" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -64563,7 +64563,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G189" s="10" t="inlineStr">
+      <c r="G189" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -64611,7 +64611,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G190" s="10" t="inlineStr">
+      <c r="G190" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -64659,7 +64659,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G191" s="10" t="inlineStr">
+      <c r="G191" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -64707,7 +64707,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G192" s="10" t="inlineStr">
+      <c r="G192" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -64755,7 +64755,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G193" s="10" t="inlineStr">
+      <c r="G193" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -64803,7 +64803,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G194" s="10" t="inlineStr">
+      <c r="G194" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -64851,7 +64851,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G195" s="10" t="inlineStr">
+      <c r="G195" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -64899,7 +64899,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G196" s="10" t="inlineStr">
+      <c r="G196" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -64947,7 +64947,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G197" s="10" t="inlineStr">
+      <c r="G197" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -64995,7 +64995,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G198" s="10" t="inlineStr">
+      <c r="G198" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -65043,7 +65043,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G199" s="10" t="inlineStr">
+      <c r="G199" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -65091,7 +65091,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G200" s="10" t="inlineStr">
+      <c r="G200" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -65139,7 +65139,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G201" s="10" t="inlineStr">
+      <c r="G201" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -65187,7 +65187,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G202" s="10" t="inlineStr">
+      <c r="G202" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -65235,7 +65235,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G203" s="10" t="inlineStr">
+      <c r="G203" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -65283,7 +65283,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G204" s="10" t="inlineStr">
+      <c r="G204" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -65331,7 +65331,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G205" s="10" t="inlineStr">
+      <c r="G205" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -65379,7 +65379,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G206" s="10" t="inlineStr">
+      <c r="G206" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -65427,7 +65427,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G207" s="10" t="inlineStr">
+      <c r="G207" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -65475,7 +65475,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G208" s="10" t="inlineStr">
+      <c r="G208" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -65523,7 +65523,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G209" s="10" t="inlineStr">
+      <c r="G209" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -65571,7 +65571,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G210" s="10" t="inlineStr">
+      <c r="G210" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -65619,7 +65619,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G211" s="10" t="inlineStr">
+      <c r="G211" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -65667,7 +65667,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G212" s="10" t="inlineStr">
+      <c r="G212" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -65715,7 +65715,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G213" s="10" t="inlineStr">
+      <c r="G213" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -65763,7 +65763,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G214" s="10" t="inlineStr">
+      <c r="G214" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -65811,7 +65811,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G215" s="10" t="inlineStr">
+      <c r="G215" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -65859,7 +65859,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G216" s="10" t="inlineStr">
+      <c r="G216" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -65907,7 +65907,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G217" s="10" t="inlineStr">
+      <c r="G217" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -65955,7 +65955,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G218" s="10" t="inlineStr">
+      <c r="G218" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -66003,7 +66003,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G219" s="10" t="inlineStr">
+      <c r="G219" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -66051,7 +66051,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G220" s="10" t="inlineStr">
+      <c r="G220" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -66099,7 +66099,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G221" s="10" t="inlineStr">
+      <c r="G221" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -66147,7 +66147,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G222" s="10" t="inlineStr">
+      <c r="G222" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -66195,7 +66195,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G223" s="10" t="inlineStr">
+      <c r="G223" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -66243,7 +66243,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G224" s="10" t="inlineStr">
+      <c r="G224" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -66291,7 +66291,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G225" s="10" t="inlineStr">
+      <c r="G225" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -66339,7 +66339,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G226" s="10" t="inlineStr">
+      <c r="G226" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -66387,7 +66387,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G227" s="10" t="inlineStr">
+      <c r="G227" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -66435,7 +66435,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G228" s="10" t="inlineStr">
+      <c r="G228" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -66483,7 +66483,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G229" s="10" t="inlineStr">
+      <c r="G229" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -66531,7 +66531,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G230" s="10" t="inlineStr">
+      <c r="G230" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -66579,7 +66579,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G231" s="10" t="inlineStr">
+      <c r="G231" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -66627,7 +66627,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G232" s="10" t="inlineStr">
+      <c r="G232" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -66675,7 +66675,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G233" s="10" t="inlineStr">
+      <c r="G233" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -66723,7 +66723,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G234" s="10" t="inlineStr">
+      <c r="G234" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -66771,7 +66771,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G235" s="10" t="inlineStr">
+      <c r="G235" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -66819,7 +66819,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G236" s="10" t="inlineStr">
+      <c r="G236" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -66867,7 +66867,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G237" s="10" t="inlineStr">
+      <c r="G237" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -66915,7 +66915,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G238" s="10" t="inlineStr">
+      <c r="G238" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -66963,7 +66963,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G239" s="10" t="inlineStr">
+      <c r="G239" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -67011,7 +67011,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G240" s="10" t="inlineStr">
+      <c r="G240" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -67059,7 +67059,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G241" s="10" t="inlineStr">
+      <c r="G241" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -67107,7 +67107,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G242" s="11" t="inlineStr">
+      <c r="G242" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67155,7 +67155,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G243" s="11" t="inlineStr">
+      <c r="G243" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67203,7 +67203,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G244" s="11" t="inlineStr">
+      <c r="G244" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67251,7 +67251,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G245" s="11" t="inlineStr">
+      <c r="G245" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67299,7 +67299,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G246" s="11" t="inlineStr">
+      <c r="G246" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67347,7 +67347,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G247" s="11" t="inlineStr">
+      <c r="G247" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67395,7 +67395,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G248" s="11" t="inlineStr">
+      <c r="G248" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67443,7 +67443,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G249" s="11" t="inlineStr">
+      <c r="G249" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67491,7 +67491,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G250" s="11" t="inlineStr">
+      <c r="G250" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67539,7 +67539,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G251" s="11" t="inlineStr">
+      <c r="G251" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67587,7 +67587,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G252" s="11" t="inlineStr">
+      <c r="G252" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67635,7 +67635,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G253" s="11" t="inlineStr">
+      <c r="G253" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67683,7 +67683,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G254" s="11" t="inlineStr">
+      <c r="G254" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67731,7 +67731,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G255" s="11" t="inlineStr">
+      <c r="G255" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67779,7 +67779,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G256" s="11" t="inlineStr">
+      <c r="G256" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67827,7 +67827,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G257" s="11" t="inlineStr">
+      <c r="G257" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67875,7 +67875,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G258" s="11" t="inlineStr">
+      <c r="G258" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67923,7 +67923,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G259" s="11" t="inlineStr">
+      <c r="G259" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67971,7 +67971,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G260" s="11" t="inlineStr">
+      <c r="G260" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68019,7 +68019,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G261" s="11" t="inlineStr">
+      <c r="G261" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68067,7 +68067,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G262" s="11" t="inlineStr">
+      <c r="G262" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68115,7 +68115,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G263" s="11" t="inlineStr">
+      <c r="G263" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68163,7 +68163,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G264" s="11" t="inlineStr">
+      <c r="G264" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68211,7 +68211,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G265" s="11" t="inlineStr">
+      <c r="G265" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68259,7 +68259,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G266" s="11" t="inlineStr">
+      <c r="G266" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68307,7 +68307,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G267" s="11" t="inlineStr">
+      <c r="G267" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68355,7 +68355,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G268" s="11" t="inlineStr">
+      <c r="G268" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68403,7 +68403,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G269" s="11" t="inlineStr">
+      <c r="G269" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68451,7 +68451,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G270" s="11" t="inlineStr">
+      <c r="G270" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68499,7 +68499,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G271" s="11" t="inlineStr">
+      <c r="G271" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68547,7 +68547,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G272" s="11" t="inlineStr">
+      <c r="G272" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68595,7 +68595,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G273" s="11" t="inlineStr">
+      <c r="G273" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68643,7 +68643,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G274" s="11" t="inlineStr">
+      <c r="G274" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68691,7 +68691,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G275" s="11" t="inlineStr">
+      <c r="G275" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68739,7 +68739,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G276" s="11" t="inlineStr">
+      <c r="G276" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68787,7 +68787,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G277" s="11" t="inlineStr">
+      <c r="G277" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68835,7 +68835,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G278" s="11" t="inlineStr">
+      <c r="G278" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68883,7 +68883,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G279" s="11" t="inlineStr">
+      <c r="G279" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68931,7 +68931,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G280" s="11" t="inlineStr">
+      <c r="G280" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68979,7 +68979,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G281" s="11" t="inlineStr">
+      <c r="G281" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69027,7 +69027,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G282" s="11" t="inlineStr">
+      <c r="G282" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69075,7 +69075,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G283" s="11" t="inlineStr">
+      <c r="G283" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69123,7 +69123,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G284" s="11" t="inlineStr">
+      <c r="G284" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69171,7 +69171,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G285" s="11" t="inlineStr">
+      <c r="G285" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69219,7 +69219,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G286" s="11" t="inlineStr">
+      <c r="G286" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69267,7 +69267,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G287" s="11" t="inlineStr">
+      <c r="G287" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69315,7 +69315,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G288" s="11" t="inlineStr">
+      <c r="G288" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69363,7 +69363,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G289" s="11" t="inlineStr">
+      <c r="G289" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69411,7 +69411,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G290" s="11" t="inlineStr">
+      <c r="G290" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69459,7 +69459,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G291" s="11" t="inlineStr">
+      <c r="G291" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69507,7 +69507,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G292" s="11" t="inlineStr">
+      <c r="G292" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69555,7 +69555,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G293" s="11" t="inlineStr">
+      <c r="G293" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69603,7 +69603,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G294" s="11" t="inlineStr">
+      <c r="G294" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69651,7 +69651,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G295" s="11" t="inlineStr">
+      <c r="G295" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69699,7 +69699,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G296" s="11" t="inlineStr">
+      <c r="G296" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69747,7 +69747,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G297" s="11" t="inlineStr">
+      <c r="G297" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69795,7 +69795,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G298" s="11" t="inlineStr">
+      <c r="G298" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69843,7 +69843,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G299" s="11" t="inlineStr">
+      <c r="G299" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69891,7 +69891,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G300" s="11" t="inlineStr">
+      <c r="G300" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69939,7 +69939,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G301" s="11" t="inlineStr">
+      <c r="G301" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69987,7 +69987,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G302" s="11" t="inlineStr">
+      <c r="G302" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70035,7 +70035,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G303" s="11" t="inlineStr">
+      <c r="G303" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70083,7 +70083,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G304" s="11" t="inlineStr">
+      <c r="G304" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70131,7 +70131,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G305" s="11" t="inlineStr">
+      <c r="G305" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70179,7 +70179,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G306" s="11" t="inlineStr">
+      <c r="G306" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70227,7 +70227,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G307" s="11" t="inlineStr">
+      <c r="G307" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70275,7 +70275,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G308" s="11" t="inlineStr">
+      <c r="G308" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70323,7 +70323,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G309" s="11" t="inlineStr">
+      <c r="G309" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70371,7 +70371,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G310" s="11" t="inlineStr">
+      <c r="G310" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70419,7 +70419,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G311" s="11" t="inlineStr">
+      <c r="G311" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70467,7 +70467,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G312" s="11" t="inlineStr">
+      <c r="G312" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70515,7 +70515,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G313" s="11" t="inlineStr">
+      <c r="G313" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70563,7 +70563,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G314" s="11" t="inlineStr">
+      <c r="G314" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70611,7 +70611,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G315" s="11" t="inlineStr">
+      <c r="G315" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70659,7 +70659,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G316" s="11" t="inlineStr">
+      <c r="G316" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70707,7 +70707,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G317" s="11" t="inlineStr">
+      <c r="G317" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70755,7 +70755,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G318" s="11" t="inlineStr">
+      <c r="G318" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70803,7 +70803,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G319" s="11" t="inlineStr">
+      <c r="G319" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70851,7 +70851,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G320" s="11" t="inlineStr">
+      <c r="G320" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70899,7 +70899,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G321" s="11" t="inlineStr">
+      <c r="G321" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70947,7 +70947,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G322" s="11" t="inlineStr">
+      <c r="G322" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -71503,7 +71503,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>Completed - needs live proof</t>
         </is>
@@ -71515,7 +71515,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="16" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
@@ -71527,7 +71527,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -71551,7 +71551,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -71563,7 +71563,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
@@ -71575,7 +71575,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -71611,7 +71611,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -71623,7 +71623,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>

--- a/R_&_D/Platform_Completion/OmniStackAI_Master_Tasks.xlsx
+++ b/R_&_D/Platform_Completion/OmniStackAI_Master_Tasks.xlsx
@@ -1399,7 +1399,7 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>R-558 fixed the design system; still needs speed-to-first-screen and visual quality. From specs/table-stakes/01 and the buildout 'intent card' idea. Measured in PC-084: plan 20-29 s (model) and preview start ~14 s are the stages to cut; model-written pages cost ~80 s and their admin page failed to compile, so the repair loop must cover the admin app before model-written pages return to the default path.</t>
+          <t>R-558 fixed the design system; still needs speed-to-first-screen and visual quality. From specs/table-stakes/01 and the buildout 'intent card' idea. Measured in PC-084: plan 20-29 s (model) and preview start ~14 s are the stages to cut; model-written pages cost ~80 s and their admin page failed to compile, so the repair loop must cover the admin app before model-written pages return to the default path. Speed half done 2026-09-26: preview start 17.7 -&gt; 9.6 s (shared warm API environment, surfaces probed together), live prompt -&gt; running app 12-15 s on Groq; fixed model navigation objects breaking pages. Left: visual quality of the first screen; starting the preview during verification (~5 s) once node_modules are not shared.</t>
         </is>
       </c>
     </row>
@@ -6407,7 +6407,7 @@
       <c r="I2" s="3" t="inlineStr"/>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>R-558 fixed the design system; still needs speed-to-first-screen and visual quality. From specs/table-stakes/01 and the buildout 'intent card' idea. Measured in PC-084: plan 20-29 s (model) and preview start ~14 s are the stages to cut; model-written pages cost ~80 s and their admin page failed to compile, so the repair loop must cover the admin app before model-written pages return to the default path.</t>
+          <t>R-558 fixed the design system; still needs speed-to-first-screen and visual quality. From specs/table-stakes/01 and the buildout 'intent card' idea. Measured in PC-084: plan 20-29 s (model) and preview start ~14 s are the stages to cut; model-written pages cost ~80 s and their admin page failed to compile, so the repair loop must cover the admin app before model-written pages return to the default path. Speed half done 2026-09-26: preview start 17.7 -&gt; 9.6 s (shared warm API environment, surfaces probed together), live prompt -&gt; running app 12-15 s on Groq; fixed model navigation objects breaking pages. Left: visual quality of the first screen; starting the preview during verification (~5 s) once node_modules are not shared.</t>
         </is>
       </c>
     </row>

--- a/R_&_D/Platform_Completion/OmniStackAI_Master_Tasks.xlsx
+++ b/R_&_D/Platform_Completion/OmniStackAI_Master_Tasks.xlsx
@@ -92,6 +92,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00BDD7EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFE699"/>
       </patternFill>
     </fill>
@@ -113,11 +118,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2F0D9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00BDD7EE"/>
       </patternFill>
     </fill>
   </fills>
@@ -173,10 +173,10 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
@@ -1929,7 +1929,7 @@
           <t>Vibe</t>
         </is>
       </c>
-      <c r="F25" s="10" t="inlineStr">
+      <c r="F25" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -1975,7 +1975,7 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="F26" s="10" t="inlineStr">
+      <c r="F26" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2021,7 +2021,7 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="F27" s="10" t="inlineStr">
+      <c r="F27" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2637,7 +2637,7 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="F41" s="10" t="inlineStr">
+      <c r="F41" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2687,7 +2687,7 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="F42" s="10" t="inlineStr">
+      <c r="F42" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2787,7 +2787,7 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="F44" s="10" t="inlineStr">
+      <c r="F44" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2933,7 +2933,7 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="F47" s="10" t="inlineStr">
+      <c r="F47" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2983,7 +2983,7 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="F48" s="10" t="inlineStr">
+      <c r="F48" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -3138,7 +3138,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G51" s="11" t="inlineStr">
+      <c r="G51" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -3188,7 +3188,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G52" s="11" t="inlineStr">
+      <c r="G52" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -3376,7 +3376,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G56" s="11" t="inlineStr">
+      <c r="G56" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -3418,7 +3418,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G57" s="11" t="inlineStr">
+      <c r="G57" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -3464,7 +3464,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G58" s="11" t="inlineStr">
+      <c r="G58" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -3506,7 +3506,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G59" s="11" t="inlineStr">
+      <c r="G59" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -3548,7 +3548,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G60" s="11" t="inlineStr">
+      <c r="G60" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -3631,7 +3631,7 @@
           <t>Vibe</t>
         </is>
       </c>
-      <c r="F62" s="10" t="inlineStr">
+      <c r="F62" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -3682,7 +3682,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G63" s="11" t="inlineStr">
+      <c r="G63" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -4108,7 +4108,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G72" s="11" t="inlineStr">
+      <c r="G72" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -4154,7 +4154,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G73" s="11" t="inlineStr">
+      <c r="G73" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -4200,7 +4200,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G74" s="11" t="inlineStr">
+      <c r="G74" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -4287,7 +4287,7 @@
           <t>Engineering</t>
         </is>
       </c>
-      <c r="F76" s="10" t="inlineStr">
+      <c r="F76" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -4425,7 +4425,7 @@
           <t>Engineering</t>
         </is>
       </c>
-      <c r="F79" s="10" t="inlineStr">
+      <c r="F79" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -4521,7 +4521,7 @@
           <t>Engineering</t>
         </is>
       </c>
-      <c r="F81" s="10" t="inlineStr">
+      <c r="F81" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -4793,7 +4793,7 @@
           <t>Engineering</t>
         </is>
       </c>
-      <c r="F87" s="10" t="inlineStr">
+      <c r="F87" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -5111,7 +5111,7 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="F94" s="10" t="inlineStr">
+      <c r="F94" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -5756,7 +5756,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G108" s="11" t="inlineStr">
+      <c r="G108" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -5802,7 +5802,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G109" s="11" t="inlineStr">
+      <c r="G109" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -5848,7 +5848,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G110" s="11" t="inlineStr">
+      <c r="G110" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -6441,7 +6441,7 @@
       </c>
       <c r="F2" s="10" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G2" s="6" t="inlineStr">
@@ -6483,7 +6483,7 @@
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="F3" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6527,7 +6527,7 @@
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6571,7 +6571,7 @@
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="F5" s="10" t="inlineStr">
+      <c r="F5" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6615,7 +6615,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6659,7 +6659,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F7" s="10" t="inlineStr">
+      <c r="F7" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6703,7 +6703,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="F8" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6747,7 +6747,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr">
+      <c r="F9" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6791,7 +6791,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6835,7 +6835,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="F11" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6879,7 +6879,7 @@
           <t>3 Engineering Mode</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr">
+      <c r="F12" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6923,7 +6923,7 @@
           <t>3 Engineering Mode</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="F13" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6967,7 +6967,7 @@
           <t>3 Engineering Mode</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr">
+      <c r="F14" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7011,7 +7011,7 @@
           <t>3 Engineering Mode</t>
         </is>
       </c>
-      <c r="F15" s="10" t="inlineStr">
+      <c r="F15" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7055,7 +7055,7 @@
           <t>4 Production ops</t>
         </is>
       </c>
-      <c r="F16" s="10" t="inlineStr">
+      <c r="F16" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7095,7 +7095,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F17" s="10" t="inlineStr">
+      <c r="F17" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7139,7 +7139,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F18" s="10" t="inlineStr">
+      <c r="F18" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7183,7 +7183,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F19" s="10" t="inlineStr">
+      <c r="F19" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7227,7 +7227,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F20" s="10" t="inlineStr">
+      <c r="F20" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7267,7 +7267,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F21" s="10" t="inlineStr">
+      <c r="F21" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7307,7 +7307,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F22" s="10" t="inlineStr">
+      <c r="F22" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7351,7 +7351,7 @@
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="F23" s="10" t="inlineStr">
+      <c r="F23" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7395,7 +7395,7 @@
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="F24" s="10" t="inlineStr">
+      <c r="F24" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7439,7 +7439,7 @@
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="F25" s="10" t="inlineStr">
+      <c r="F25" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7479,7 +7479,7 @@
           <t>4 Production ops</t>
         </is>
       </c>
-      <c r="F26" s="10" t="inlineStr">
+      <c r="F26" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7519,7 +7519,7 @@
           <t>4 Production ops</t>
         </is>
       </c>
-      <c r="F27" s="10" t="inlineStr">
+      <c r="F27" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7563,7 +7563,7 @@
           <t>4 Production ops</t>
         </is>
       </c>
-      <c r="F28" s="10" t="inlineStr">
+      <c r="F28" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7611,7 +7611,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F29" s="10" t="inlineStr">
+      <c r="F29" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7659,7 +7659,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F30" s="10" t="inlineStr">
+      <c r="F30" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7707,7 +7707,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F31" s="10" t="inlineStr">
+      <c r="F31" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7755,7 +7755,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F32" s="10" t="inlineStr">
+      <c r="F32" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7803,7 +7803,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F33" s="10" t="inlineStr">
+      <c r="F33" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7851,7 +7851,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F34" s="10" t="inlineStr">
+      <c r="F34" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7899,7 +7899,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F35" s="10" t="inlineStr">
+      <c r="F35" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7947,7 +7947,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F36" s="10" t="inlineStr">
+      <c r="F36" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7995,7 +7995,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F37" s="10" t="inlineStr">
+      <c r="F37" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8043,7 +8043,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F38" s="10" t="inlineStr">
+      <c r="F38" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8091,7 +8091,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F39" s="10" t="inlineStr">
+      <c r="F39" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8139,7 +8139,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F40" s="10" t="inlineStr">
+      <c r="F40" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8187,7 +8187,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F41" s="10" t="inlineStr">
+      <c r="F41" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8235,7 +8235,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F42" s="10" t="inlineStr">
+      <c r="F42" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8283,7 +8283,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F43" s="10" t="inlineStr">
+      <c r="F43" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8331,7 +8331,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F44" s="10" t="inlineStr">
+      <c r="F44" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8379,7 +8379,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F45" s="10" t="inlineStr">
+      <c r="F45" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8427,7 +8427,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F46" s="10" t="inlineStr">
+      <c r="F46" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8475,7 +8475,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F47" s="10" t="inlineStr">
+      <c r="F47" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8523,7 +8523,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F48" s="10" t="inlineStr">
+      <c r="F48" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8571,7 +8571,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F49" s="10" t="inlineStr">
+      <c r="F49" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8619,7 +8619,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F50" s="10" t="inlineStr">
+      <c r="F50" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8667,12 +8667,12 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F51" s="10" t="inlineStr">
+      <c r="F51" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G51" s="11" t="inlineStr">
+      <c r="G51" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -8715,7 +8715,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F52" s="10" t="inlineStr">
+      <c r="F52" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8763,7 +8763,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F53" s="10" t="inlineStr">
+      <c r="F53" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8811,7 +8811,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F54" s="10" t="inlineStr">
+      <c r="F54" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8859,12 +8859,12 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F55" s="10" t="inlineStr">
+      <c r="F55" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G55" s="11" t="inlineStr">
+      <c r="G55" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -8907,7 +8907,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F56" s="10" t="inlineStr">
+      <c r="F56" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8955,7 +8955,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F57" s="10" t="inlineStr">
+      <c r="F57" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9003,7 +9003,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F58" s="10" t="inlineStr">
+      <c r="F58" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9051,7 +9051,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F59" s="10" t="inlineStr">
+      <c r="F59" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9099,7 +9099,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F60" s="10" t="inlineStr">
+      <c r="F60" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9147,7 +9147,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F61" s="10" t="inlineStr">
+      <c r="F61" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9195,12 +9195,12 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F62" s="10" t="inlineStr">
+      <c r="F62" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G62" s="11" t="inlineStr">
+      <c r="G62" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -9243,7 +9243,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F63" s="10" t="inlineStr">
+      <c r="F63" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9291,7 +9291,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F64" s="10" t="inlineStr">
+      <c r="F64" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9339,7 +9339,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F65" s="10" t="inlineStr">
+      <c r="F65" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9387,7 +9387,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F66" s="10" t="inlineStr">
+      <c r="F66" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9435,7 +9435,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F67" s="10" t="inlineStr">
+      <c r="F67" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9483,7 +9483,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F68" s="10" t="inlineStr">
+      <c r="F68" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9527,7 +9527,7 @@
           <t>4 Production ops</t>
         </is>
       </c>
-      <c r="F69" s="10" t="inlineStr">
+      <c r="F69" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9571,7 +9571,7 @@
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="F70" s="10" t="inlineStr">
+      <c r="F70" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9619,7 +9619,7 @@
           <t>3 Engineering Mode</t>
         </is>
       </c>
-      <c r="F71" s="10" t="inlineStr">
+      <c r="F71" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9667,7 +9667,7 @@
           <t>4 Production ops</t>
         </is>
       </c>
-      <c r="F72" s="10" t="inlineStr">
+      <c r="F72" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9711,7 +9711,7 @@
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="F73" s="10" t="inlineStr">
+      <c r="F73" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9755,7 +9755,7 @@
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="F74" s="10" t="inlineStr">
+      <c r="F74" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9803,7 +9803,7 @@
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="F75" s="10" t="inlineStr">
+      <c r="F75" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9851,7 +9851,7 @@
           <t>3 Engineering Mode</t>
         </is>
       </c>
-      <c r="F76" s="10" t="inlineStr">
+      <c r="F76" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9895,7 +9895,7 @@
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="F77" s="10" t="inlineStr">
+      <c r="F77" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9943,7 +9943,7 @@
           <t>4 Production ops</t>
         </is>
       </c>
-      <c r="F78" s="10" t="inlineStr">
+      <c r="F78" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9991,7 +9991,7 @@
           <t>3 Engineering Mode</t>
         </is>
       </c>
-      <c r="F79" s="10" t="inlineStr">
+      <c r="F79" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10035,7 +10035,7 @@
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="F80" s="10" t="inlineStr">
+      <c r="F80" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10075,7 +10075,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F81" s="10" t="inlineStr">
+      <c r="F81" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10119,7 +10119,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F82" s="10" t="inlineStr">
+      <c r="F82" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10163,7 +10163,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F83" s="10" t="inlineStr">
+      <c r="F83" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10207,7 +10207,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F84" s="10" t="inlineStr">
+      <c r="F84" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10251,7 +10251,7 @@
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="F85" s="10" t="inlineStr">
+      <c r="F85" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10299,7 +10299,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F86" s="10" t="inlineStr">
+      <c r="F86" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10347,7 +10347,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F87" s="10" t="inlineStr">
+      <c r="F87" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10395,7 +10395,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F88" s="10" t="inlineStr">
+      <c r="F88" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10443,7 +10443,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F89" s="10" t="inlineStr">
+      <c r="F89" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10491,7 +10491,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F90" s="10" t="inlineStr">
+      <c r="F90" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10539,7 +10539,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F91" s="10" t="inlineStr">
+      <c r="F91" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10587,7 +10587,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F92" s="10" t="inlineStr">
+      <c r="F92" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10635,7 +10635,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F93" s="10" t="inlineStr">
+      <c r="F93" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10683,7 +10683,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F94" s="10" t="inlineStr">
+      <c r="F94" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10731,7 +10731,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F95" s="10" t="inlineStr">
+      <c r="F95" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10779,7 +10779,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F96" s="10" t="inlineStr">
+      <c r="F96" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10827,7 +10827,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F97" s="10" t="inlineStr">
+      <c r="F97" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10875,7 +10875,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F98" s="10" t="inlineStr">
+      <c r="F98" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10923,7 +10923,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F99" s="10" t="inlineStr">
+      <c r="F99" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -11960,7 +11960,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G123" s="11" t="inlineStr">
+      <c r="G123" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -12004,7 +12004,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G124" s="11" t="inlineStr">
+      <c r="G124" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -12180,7 +12180,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G128" s="11" t="inlineStr">
+      <c r="G128" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -12224,7 +12224,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G129" s="11" t="inlineStr">
+      <c r="G129" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -12268,7 +12268,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G130" s="11" t="inlineStr">
+      <c r="G130" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -12312,7 +12312,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G131" s="11" t="inlineStr">
+      <c r="G131" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -12356,7 +12356,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G132" s="11" t="inlineStr">
+      <c r="G132" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -12444,7 +12444,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G134" s="11" t="inlineStr">
+      <c r="G134" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -12840,7 +12840,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G143" s="11" t="inlineStr">
+      <c r="G143" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -12884,7 +12884,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G144" s="11" t="inlineStr">
+      <c r="G144" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -12928,7 +12928,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G145" s="11" t="inlineStr">
+      <c r="G145" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -14120,7 +14120,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G174" s="11" t="inlineStr">
+      <c r="G174" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -14160,7 +14160,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G175" s="11" t="inlineStr">
+      <c r="G175" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -14204,7 +14204,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G176" s="11" t="inlineStr">
+      <c r="G176" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -14720,7 +14720,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G188" s="11" t="inlineStr">
+      <c r="G188" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -14888,7 +14888,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G192" s="11" t="inlineStr">
+      <c r="G192" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -15452,7 +15452,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G206" s="11" t="inlineStr">
+      <c r="G206" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -15816,7 +15816,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G215" s="11" t="inlineStr">
+      <c r="G215" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -16316,7 +16316,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G227" s="11" t="inlineStr">
+      <c r="G227" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -16540,7 +16540,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G232" s="11" t="inlineStr">
+      <c r="G232" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -16672,7 +16672,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G235" s="11" t="inlineStr">
+      <c r="G235" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -16716,7 +16716,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G236" s="11" t="inlineStr">
+      <c r="G236" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -16940,7 +16940,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G241" s="11" t="inlineStr">
+      <c r="G241" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -17116,7 +17116,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G245" s="11" t="inlineStr">
+      <c r="G245" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -17252,7 +17252,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G248" s="11" t="inlineStr">
+      <c r="G248" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -17340,7 +17340,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G250" s="11" t="inlineStr">
+      <c r="G250" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -17436,7 +17436,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G252" s="11" t="inlineStr">
+      <c r="G252" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -17528,7 +17528,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G254" s="11" t="inlineStr">
+      <c r="G254" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -17572,7 +17572,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G255" s="11" t="inlineStr">
+      <c r="G255" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -17664,7 +17664,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G257" s="11" t="inlineStr">
+      <c r="G257" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -17708,7 +17708,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G258" s="11" t="inlineStr">
+      <c r="G258" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -17888,7 +17888,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G262" s="11" t="inlineStr">
+      <c r="G262" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -18028,7 +18028,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G265" s="11" t="inlineStr">
+      <c r="G265" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -18072,7 +18072,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G266" s="11" t="inlineStr">
+      <c r="G266" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -18480,7 +18480,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G275" s="11" t="inlineStr">
+      <c r="G275" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -18712,7 +18712,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G280" s="11" t="inlineStr">
+      <c r="G280" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -18936,7 +18936,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G285" s="11" t="inlineStr">
+      <c r="G285" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -18980,7 +18980,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G286" s="11" t="inlineStr">
+      <c r="G286" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -19116,7 +19116,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G289" s="11" t="inlineStr">
+      <c r="G289" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -21084,7 +21084,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G335" s="11" t="inlineStr">
+      <c r="G335" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -22852,7 +22852,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G375" s="11" t="inlineStr">
+      <c r="G375" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -22896,7 +22896,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G376" s="11" t="inlineStr">
+      <c r="G376" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -22940,7 +22940,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G377" s="11" t="inlineStr">
+      <c r="G377" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -24740,7 +24740,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G418" s="11" t="inlineStr">
+      <c r="G418" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -24784,7 +24784,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G419" s="11" t="inlineStr">
+      <c r="G419" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -24872,7 +24872,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G421" s="11" t="inlineStr">
+      <c r="G421" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25004,7 +25004,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G424" s="11" t="inlineStr">
+      <c r="G424" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25180,7 +25180,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G428" s="11" t="inlineStr">
+      <c r="G428" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25224,7 +25224,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G429" s="11" t="inlineStr">
+      <c r="G429" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25532,7 +25532,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G436" s="11" t="inlineStr">
+      <c r="G436" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25576,7 +25576,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G437" s="11" t="inlineStr">
+      <c r="G437" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25620,7 +25620,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G438" s="11" t="inlineStr">
+      <c r="G438" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25664,7 +25664,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G439" s="11" t="inlineStr">
+      <c r="G439" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25708,7 +25708,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G440" s="11" t="inlineStr">
+      <c r="G440" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25752,7 +25752,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G441" s="11" t="inlineStr">
+      <c r="G441" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25796,7 +25796,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G442" s="11" t="inlineStr">
+      <c r="G442" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25928,7 +25928,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G445" s="11" t="inlineStr">
+      <c r="G445" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -26060,7 +26060,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G448" s="11" t="inlineStr">
+      <c r="G448" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -26236,7 +26236,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G452" s="11" t="inlineStr">
+      <c r="G452" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -26280,7 +26280,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G453" s="11" t="inlineStr">
+      <c r="G453" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -26456,7 +26456,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G457" s="11" t="inlineStr">
+      <c r="G457" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -26500,7 +26500,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G458" s="11" t="inlineStr">
+      <c r="G458" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -26588,7 +26588,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G460" s="11" t="inlineStr">
+      <c r="G460" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -26764,7 +26764,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G464" s="11" t="inlineStr">
+      <c r="G464" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -26808,7 +26808,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G465" s="11" t="inlineStr">
+      <c r="G465" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -27072,7 +27072,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G471" s="11" t="inlineStr">
+      <c r="G471" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -27116,7 +27116,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G472" s="11" t="inlineStr">
+      <c r="G472" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -27336,7 +27336,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G477" s="11" t="inlineStr">
+      <c r="G477" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -27380,7 +27380,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G478" s="11" t="inlineStr">
+      <c r="G478" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -27424,7 +27424,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G479" s="11" t="inlineStr">
+      <c r="G479" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -27468,7 +27468,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G480" s="11" t="inlineStr">
+      <c r="G480" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -27512,7 +27512,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G481" s="11" t="inlineStr">
+      <c r="G481" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -27556,7 +27556,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G482" s="11" t="inlineStr">
+      <c r="G482" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -27732,7 +27732,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G486" s="11" t="inlineStr">
+      <c r="G486" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -27952,7 +27952,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G491" s="11" t="inlineStr">
+      <c r="G491" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -28040,7 +28040,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G493" s="11" t="inlineStr">
+      <c r="G493" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -28084,7 +28084,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G494" s="11" t="inlineStr">
+      <c r="G494" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -28172,7 +28172,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G496" s="11" t="inlineStr">
+      <c r="G496" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -28392,7 +28392,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G501" s="11" t="inlineStr">
+      <c r="G501" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -28436,7 +28436,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G502" s="11" t="inlineStr">
+      <c r="G502" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -28876,7 +28876,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G512" s="11" t="inlineStr">
+      <c r="G512" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -29140,7 +29140,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G518" s="11" t="inlineStr">
+      <c r="G518" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -29272,7 +29272,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G521" s="11" t="inlineStr">
+      <c r="G521" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -29448,7 +29448,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G525" s="11" t="inlineStr">
+      <c r="G525" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -29492,7 +29492,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G526" s="11" t="inlineStr">
+      <c r="G526" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -29668,7 +29668,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G530" s="11" t="inlineStr">
+      <c r="G530" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -29712,7 +29712,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G531" s="11" t="inlineStr">
+      <c r="G531" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -29800,7 +29800,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G533" s="11" t="inlineStr">
+      <c r="G533" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -29888,7 +29888,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G535" s="11" t="inlineStr">
+      <c r="G535" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -29976,7 +29976,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G537" s="11" t="inlineStr">
+      <c r="G537" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30064,7 +30064,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G539" s="11" t="inlineStr">
+      <c r="G539" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30108,7 +30108,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G540" s="11" t="inlineStr">
+      <c r="G540" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30152,7 +30152,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G541" s="11" t="inlineStr">
+      <c r="G541" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30240,7 +30240,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G543" s="11" t="inlineStr">
+      <c r="G543" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30284,7 +30284,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G544" s="11" t="inlineStr">
+      <c r="G544" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30328,7 +30328,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G545" s="11" t="inlineStr">
+      <c r="G545" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30372,7 +30372,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G546" s="11" t="inlineStr">
+      <c r="G546" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30460,7 +30460,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G548" s="11" t="inlineStr">
+      <c r="G548" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30504,7 +30504,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G549" s="11" t="inlineStr">
+      <c r="G549" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30548,7 +30548,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G550" s="11" t="inlineStr">
+      <c r="G550" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30680,7 +30680,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G553" s="11" t="inlineStr">
+      <c r="G553" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30812,7 +30812,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G556" s="11" t="inlineStr">
+      <c r="G556" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30900,7 +30900,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G558" s="11" t="inlineStr">
+      <c r="G558" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30988,7 +30988,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G560" s="11" t="inlineStr">
+      <c r="G560" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -31076,7 +31076,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G562" s="11" t="inlineStr">
+      <c r="G562" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -31296,7 +31296,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G567" s="11" t="inlineStr">
+      <c r="G567" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -31340,7 +31340,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G568" s="11" t="inlineStr">
+      <c r="G568" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -31428,7 +31428,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G570" s="11" t="inlineStr">
+      <c r="G570" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -31560,7 +31560,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G573" s="11" t="inlineStr">
+      <c r="G573" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -31692,7 +31692,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G576" s="11" t="inlineStr">
+      <c r="G576" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -31780,7 +31780,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G578" s="11" t="inlineStr">
+      <c r="G578" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -31824,7 +31824,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G579" s="11" t="inlineStr">
+      <c r="G579" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -32000,7 +32000,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G583" s="11" t="inlineStr">
+      <c r="G583" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -32044,7 +32044,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G584" s="11" t="inlineStr">
+      <c r="G584" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -32352,7 +32352,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G591" s="11" t="inlineStr">
+      <c r="G591" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -32396,7 +32396,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G592" s="11" t="inlineStr">
+      <c r="G592" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -32440,7 +32440,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G593" s="11" t="inlineStr">
+      <c r="G593" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -32528,7 +32528,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G595" s="11" t="inlineStr">
+      <c r="G595" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -32704,7 +32704,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G599" s="11" t="inlineStr">
+      <c r="G599" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -32836,7 +32836,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G602" s="11" t="inlineStr">
+      <c r="G602" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -32880,7 +32880,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G603" s="11" t="inlineStr">
+      <c r="G603" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -32968,7 +32968,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G605" s="11" t="inlineStr">
+      <c r="G605" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -33056,7 +33056,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G607" s="11" t="inlineStr">
+      <c r="G607" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -33276,7 +33276,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G612" s="11" t="inlineStr">
+      <c r="G612" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -33355,7 +33355,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F614" s="11" t="inlineStr">
+      <c r="F614" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33399,7 +33399,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F615" s="11" t="inlineStr">
+      <c r="F615" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33443,7 +33443,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F616" s="11" t="inlineStr">
+      <c r="F616" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33487,7 +33487,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F617" s="11" t="inlineStr">
+      <c r="F617" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33531,7 +33531,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F618" s="11" t="inlineStr">
+      <c r="F618" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33575,7 +33575,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F619" s="11" t="inlineStr">
+      <c r="F619" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33619,7 +33619,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F620" s="11" t="inlineStr">
+      <c r="F620" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33663,7 +33663,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F621" s="11" t="inlineStr">
+      <c r="F621" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33703,7 +33703,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F622" s="11" t="inlineStr">
+      <c r="F622" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33747,7 +33747,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F623" s="11" t="inlineStr">
+      <c r="F623" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33787,7 +33787,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F624" s="11" t="inlineStr">
+      <c r="F624" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33831,7 +33831,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F625" s="11" t="inlineStr">
+      <c r="F625" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33871,12 +33871,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F626" s="12" t="inlineStr">
+      <c r="F626" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G626" s="11" t="inlineStr">
+      <c r="G626" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -33915,12 +33915,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F627" s="12" t="inlineStr">
+      <c r="F627" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G627" s="11" t="inlineStr">
+      <c r="G627" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -33959,12 +33959,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F628" s="12" t="inlineStr">
+      <c r="F628" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G628" s="11" t="inlineStr">
+      <c r="G628" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34003,7 +34003,7 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F629" s="12" t="inlineStr">
+      <c r="F629" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
@@ -34047,12 +34047,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F630" s="12" t="inlineStr">
+      <c r="F630" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G630" s="11" t="inlineStr">
+      <c r="G630" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34091,12 +34091,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F631" s="12" t="inlineStr">
+      <c r="F631" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G631" s="11" t="inlineStr">
+      <c r="G631" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34131,12 +34131,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F632" s="12" t="inlineStr">
+      <c r="F632" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G632" s="11" t="inlineStr">
+      <c r="G632" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34175,12 +34175,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F633" s="12" t="inlineStr">
+      <c r="F633" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G633" s="11" t="inlineStr">
+      <c r="G633" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34219,12 +34219,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F634" s="12" t="inlineStr">
+      <c r="F634" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G634" s="11" t="inlineStr">
+      <c r="G634" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34263,12 +34263,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F635" s="12" t="inlineStr">
+      <c r="F635" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G635" s="11" t="inlineStr">
+      <c r="G635" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34303,12 +34303,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F636" s="12" t="inlineStr">
+      <c r="F636" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G636" s="11" t="inlineStr">
+      <c r="G636" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34347,12 +34347,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F637" s="12" t="inlineStr">
+      <c r="F637" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G637" s="11" t="inlineStr">
+      <c r="G637" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34391,12 +34391,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F638" s="12" t="inlineStr">
+      <c r="F638" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G638" s="11" t="inlineStr">
+      <c r="G638" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34435,12 +34435,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F639" s="12" t="inlineStr">
+      <c r="F639" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G639" s="11" t="inlineStr">
+      <c r="G639" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34479,12 +34479,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F640" s="12" t="inlineStr">
+      <c r="F640" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G640" s="11" t="inlineStr">
+      <c r="G640" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34523,12 +34523,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F641" s="12" t="inlineStr">
+      <c r="F641" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G641" s="11" t="inlineStr">
+      <c r="G641" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34567,12 +34567,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F642" s="12" t="inlineStr">
+      <c r="F642" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G642" s="11" t="inlineStr">
+      <c r="G642" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34611,12 +34611,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F643" s="12" t="inlineStr">
+      <c r="F643" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G643" s="11" t="inlineStr">
+      <c r="G643" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34655,12 +34655,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F644" s="12" t="inlineStr">
+      <c r="F644" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G644" s="11" t="inlineStr">
+      <c r="G644" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34699,12 +34699,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F645" s="12" t="inlineStr">
+      <c r="F645" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G645" s="11" t="inlineStr">
+      <c r="G645" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34743,12 +34743,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F646" s="12" t="inlineStr">
+      <c r="F646" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G646" s="11" t="inlineStr">
+      <c r="G646" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34787,12 +34787,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F647" s="12" t="inlineStr">
+      <c r="F647" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G647" s="11" t="inlineStr">
+      <c r="G647" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34831,12 +34831,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F648" s="12" t="inlineStr">
+      <c r="F648" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G648" s="11" t="inlineStr">
+      <c r="G648" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34875,12 +34875,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F649" s="12" t="inlineStr">
+      <c r="F649" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G649" s="11" t="inlineStr">
+      <c r="G649" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34919,12 +34919,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F650" s="12" t="inlineStr">
+      <c r="F650" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G650" s="11" t="inlineStr">
+      <c r="G650" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34959,12 +34959,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F651" s="12" t="inlineStr">
+      <c r="F651" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G651" s="11" t="inlineStr">
+      <c r="G651" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35003,12 +35003,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F652" s="12" t="inlineStr">
+      <c r="F652" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G652" s="11" t="inlineStr">
+      <c r="G652" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35047,12 +35047,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F653" s="12" t="inlineStr">
+      <c r="F653" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G653" s="11" t="inlineStr">
+      <c r="G653" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35087,12 +35087,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F654" s="12" t="inlineStr">
+      <c r="F654" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G654" s="11" t="inlineStr">
+      <c r="G654" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35131,12 +35131,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F655" s="12" t="inlineStr">
+      <c r="F655" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G655" s="11" t="inlineStr">
+      <c r="G655" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35171,12 +35171,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F656" s="12" t="inlineStr">
+      <c r="F656" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G656" s="11" t="inlineStr">
+      <c r="G656" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35211,12 +35211,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F657" s="12" t="inlineStr">
+      <c r="F657" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G657" s="11" t="inlineStr">
+      <c r="G657" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35251,12 +35251,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F658" s="12" t="inlineStr">
+      <c r="F658" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G658" s="11" t="inlineStr">
+      <c r="G658" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35291,12 +35291,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F659" s="12" t="inlineStr">
+      <c r="F659" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G659" s="11" t="inlineStr">
+      <c r="G659" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35335,12 +35335,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F660" s="12" t="inlineStr">
+      <c r="F660" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G660" s="11" t="inlineStr">
+      <c r="G660" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35379,12 +35379,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F661" s="12" t="inlineStr">
+      <c r="F661" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G661" s="11" t="inlineStr">
+      <c r="G661" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35423,12 +35423,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F662" s="12" t="inlineStr">
+      <c r="F662" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G662" s="11" t="inlineStr">
+      <c r="G662" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35463,12 +35463,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F663" s="12" t="inlineStr">
+      <c r="F663" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G663" s="11" t="inlineStr">
+      <c r="G663" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35503,12 +35503,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F664" s="12" t="inlineStr">
+      <c r="F664" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G664" s="11" t="inlineStr">
+      <c r="G664" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35543,12 +35543,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F665" s="12" t="inlineStr">
+      <c r="F665" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G665" s="11" t="inlineStr">
+      <c r="G665" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35583,12 +35583,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F666" s="12" t="inlineStr">
+      <c r="F666" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G666" s="11" t="inlineStr">
+      <c r="G666" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35623,12 +35623,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F667" s="12" t="inlineStr">
+      <c r="F667" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G667" s="11" t="inlineStr">
+      <c r="G667" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35667,12 +35667,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F668" s="12" t="inlineStr">
+      <c r="F668" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G668" s="11" t="inlineStr">
+      <c r="G668" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35707,12 +35707,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F669" s="12" t="inlineStr">
+      <c r="F669" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G669" s="11" t="inlineStr">
+      <c r="G669" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35747,12 +35747,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F670" s="12" t="inlineStr">
+      <c r="F670" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G670" s="11" t="inlineStr">
+      <c r="G670" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35787,12 +35787,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F671" s="12" t="inlineStr">
+      <c r="F671" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G671" s="11" t="inlineStr">
+      <c r="G671" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35827,12 +35827,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F672" s="12" t="inlineStr">
+      <c r="F672" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G672" s="11" t="inlineStr">
+      <c r="G672" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35871,12 +35871,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F673" s="12" t="inlineStr">
+      <c r="F673" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G673" s="11" t="inlineStr">
+      <c r="G673" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35915,12 +35915,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F674" s="12" t="inlineStr">
+      <c r="F674" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G674" s="11" t="inlineStr">
+      <c r="G674" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35959,12 +35959,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F675" s="12" t="inlineStr">
+      <c r="F675" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G675" s="11" t="inlineStr">
+      <c r="G675" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -36003,12 +36003,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F676" s="12" t="inlineStr">
+      <c r="F676" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G676" s="11" t="inlineStr">
+      <c r="G676" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -36047,12 +36047,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F677" s="12" t="inlineStr">
+      <c r="F677" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G677" s="11" t="inlineStr">
+      <c r="G677" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -36091,12 +36091,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F678" s="12" t="inlineStr">
+      <c r="F678" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G678" s="11" t="inlineStr">
+      <c r="G678" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -36135,12 +36135,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F679" s="12" t="inlineStr">
+      <c r="F679" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G679" s="11" t="inlineStr">
+      <c r="G679" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -36179,12 +36179,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F680" s="12" t="inlineStr">
+      <c r="F680" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G680" s="11" t="inlineStr">
+      <c r="G680" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -36223,12 +36223,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F681" s="12" t="inlineStr">
+      <c r="F681" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G681" s="11" t="inlineStr">
+      <c r="G681" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -36263,12 +36263,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F682" s="12" t="inlineStr">
+      <c r="F682" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G682" s="11" t="inlineStr">
+      <c r="G682" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -36299,7 +36299,7 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F683" s="13" t="inlineStr">
+      <c r="F683" s="14" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -36339,7 +36339,7 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F684" s="13" t="inlineStr">
+      <c r="F684" s="14" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -36379,7 +36379,7 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F685" s="13" t="inlineStr">
+      <c r="F685" s="14" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -36419,7 +36419,7 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F686" s="13" t="inlineStr">
+      <c r="F686" s="14" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -36459,7 +36459,7 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F687" s="13" t="inlineStr">
+      <c r="F687" s="14" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -36499,7 +36499,7 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F688" s="13" t="inlineStr">
+      <c r="F688" s="14" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -36539,7 +36539,7 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F689" s="13" t="inlineStr">
+      <c r="F689" s="14" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -36579,7 +36579,7 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F690" s="13" t="inlineStr">
+      <c r="F690" s="14" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -36619,7 +36619,7 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F691" s="13" t="inlineStr">
+      <c r="F691" s="14" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -38539,7 +38539,7 @@
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="F735" s="14" t="inlineStr">
+      <c r="F735" s="15" t="inlineStr">
         <is>
           <t>Completed - needs live proof</t>
         </is>
@@ -51155,7 +51155,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F1054" s="14" t="inlineStr">
+      <c r="F1054" s="15" t="inlineStr">
         <is>
           <t>Completed - needs live proof</t>
         </is>
@@ -51203,7 +51203,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F1055" s="14" t="inlineStr">
+      <c r="F1055" s="15" t="inlineStr">
         <is>
           <t>Completed - needs live proof</t>
         </is>
@@ -51251,7 +51251,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F1056" s="14" t="inlineStr">
+      <c r="F1056" s="15" t="inlineStr">
         <is>
           <t>Completed - needs live proof</t>
         </is>
@@ -51299,7 +51299,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F1057" s="14" t="inlineStr">
+      <c r="F1057" s="15" t="inlineStr">
         <is>
           <t>Completed - needs live proof</t>
         </is>
@@ -51347,7 +51347,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F1058" s="14" t="inlineStr">
+      <c r="F1058" s="15" t="inlineStr">
         <is>
           <t>Completed - needs live proof</t>
         </is>
@@ -51467,7 +51467,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F1061" s="14" t="inlineStr">
+      <c r="F1061" s="15" t="inlineStr">
         <is>
           <t>Completed - needs live proof</t>
         </is>
@@ -52599,7 +52599,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F1092" s="14" t="inlineStr">
+      <c r="F1092" s="15" t="inlineStr">
         <is>
           <t>Completed - needs live proof</t>
         </is>
@@ -53596,62 +53596,62 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="B1" s="15" t="inlineStr">
+      <c r="B1" s="16" t="inlineStr">
         <is>
           <t>0 Foundation</t>
         </is>
       </c>
-      <c r="C1" s="15" t="inlineStr">
+      <c r="C1" s="16" t="inlineStr">
         <is>
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="D1" s="15" t="inlineStr">
+      <c r="D1" s="16" t="inlineStr">
         <is>
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="E1" s="15" t="inlineStr">
+      <c r="E1" s="16" t="inlineStr">
         <is>
           <t>3 Engineering Mode</t>
         </is>
       </c>
-      <c r="F1" s="15" t="inlineStr">
+      <c r="F1" s="16" t="inlineStr">
         <is>
           <t>4 Production ops</t>
         </is>
       </c>
-      <c r="G1" s="15" t="inlineStr">
+      <c r="G1" s="16" t="inlineStr">
         <is>
           <t>5 Native mobile (last)</t>
         </is>
       </c>
-      <c r="H1" s="15" t="inlineStr">
+      <c r="H1" s="16" t="inlineStr">
         <is>
           <t>6 Go-live (credentials last)</t>
         </is>
       </c>
-      <c r="I1" s="15" t="inlineStr">
+      <c r="I1" s="16" t="inlineStr">
         <is>
           <t>7 Win the category</t>
         </is>
       </c>
-      <c r="J1" s="15" t="inlineStr">
+      <c r="J1" s="16" t="inlineStr">
         <is>
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="K1" s="15" t="inlineStr">
+      <c r="K1" s="16" t="inlineStr">
         <is>
           <t>Delivered</t>
         </is>
       </c>
-      <c r="L1" s="15" t="inlineStr">
+      <c r="L1" s="16" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
@@ -53747,7 +53747,7 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -53774,7 +53774,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -53787,7 +53787,7 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D5" t="n">
         <v>66</v>
@@ -53814,7 +53814,7 @@
         <v>4</v>
       </c>
       <c r="L5" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6">
@@ -54018,62 +54018,62 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Open queue by priority</t>
         </is>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>0 Foundation</t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="D12" s="15" t="inlineStr">
+      <c r="D12" s="16" t="inlineStr">
         <is>
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="E12" s="15" t="inlineStr">
+      <c r="E12" s="16" t="inlineStr">
         <is>
           <t>3 Engineering Mode</t>
         </is>
       </c>
-      <c r="F12" s="15" t="inlineStr">
+      <c r="F12" s="16" t="inlineStr">
         <is>
           <t>4 Production ops</t>
         </is>
       </c>
-      <c r="G12" s="15" t="inlineStr">
+      <c r="G12" s="16" t="inlineStr">
         <is>
           <t>5 Native mobile (last)</t>
         </is>
       </c>
-      <c r="H12" s="15" t="inlineStr">
+      <c r="H12" s="16" t="inlineStr">
         <is>
           <t>6 Go-live (credentials last)</t>
         </is>
       </c>
-      <c r="I12" s="15" t="inlineStr">
+      <c r="I12" s="16" t="inlineStr">
         <is>
           <t>7 Win the category</t>
         </is>
       </c>
-      <c r="J12" s="15" t="inlineStr">
+      <c r="J12" s="16" t="inlineStr">
         <is>
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="K12" s="15" t="inlineStr">
+      <c r="K12" s="16" t="inlineStr">
         <is>
           <t>Delivered</t>
         </is>
       </c>
-      <c r="L12" s="15" t="inlineStr">
+      <c r="L12" s="16" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
@@ -55388,7 +55388,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="F2" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -55492,7 +55492,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -55544,7 +55544,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F5" s="10" t="inlineStr">
+      <c r="F5" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -55596,7 +55596,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -55648,7 +55648,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F7" s="10" t="inlineStr">
+      <c r="F7" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -55700,7 +55700,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="F8" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -55848,7 +55848,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="F11" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -55952,7 +55952,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="F13" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -56009,7 +56009,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G14" s="11" t="inlineStr">
+      <c r="G14" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -56052,7 +56052,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F15" s="10" t="inlineStr">
+      <c r="F15" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -56304,7 +56304,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F20" s="10" t="inlineStr">
+      <c r="F20" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -56408,7 +56408,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F22" s="10" t="inlineStr">
+      <c r="F22" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -56513,7 +56513,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G24" s="11" t="inlineStr">
+      <c r="G24" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -56657,7 +56657,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G27" s="11" t="inlineStr">
+      <c r="G27" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -56804,12 +56804,12 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F30" s="10" t="inlineStr">
+      <c r="F30" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G30" s="11" t="inlineStr">
+      <c r="G30" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -56861,7 +56861,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G31" s="11" t="inlineStr">
+      <c r="G31" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -56904,7 +56904,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F32" s="10" t="inlineStr">
+      <c r="F32" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -56956,7 +56956,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F33" s="10" t="inlineStr">
+      <c r="F33" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -57008,7 +57008,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F34" s="10" t="inlineStr">
+      <c r="F34" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -57113,7 +57113,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G36" s="11" t="inlineStr">
+      <c r="G36" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -57161,7 +57161,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G37" s="11" t="inlineStr">
+      <c r="G37" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -57304,7 +57304,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F40" s="10" t="inlineStr">
+      <c r="F40" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -57356,7 +57356,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F41" s="10" t="inlineStr">
+      <c r="F41" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -57408,7 +57408,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F42" s="10" t="inlineStr">
+      <c r="F42" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -57508,7 +57508,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F44" s="10" t="inlineStr">
+      <c r="F44" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -57608,7 +57608,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F46" s="10" t="inlineStr">
+      <c r="F46" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -57712,7 +57712,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F48" s="10" t="inlineStr">
+      <c r="F48" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -57860,7 +57860,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F51" s="10" t="inlineStr">
+      <c r="F51" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -57960,7 +57960,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F53" s="10" t="inlineStr">
+      <c r="F53" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -58065,7 +58065,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G55" s="11" t="inlineStr">
+      <c r="G55" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -58160,7 +58160,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F57" s="10" t="inlineStr">
+      <c r="F57" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -58217,7 +58217,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G58" s="11" t="inlineStr">
+      <c r="G58" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -58265,7 +58265,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G59" s="11" t="inlineStr">
+      <c r="G59" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -58361,7 +58361,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G61" s="11" t="inlineStr">
+      <c r="G61" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -58404,7 +58404,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F62" s="10" t="inlineStr">
+      <c r="F62" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -58665,7 +58665,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G67" s="11" t="inlineStr">
+      <c r="G67" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -58756,7 +58756,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F69" s="10" t="inlineStr">
+      <c r="F69" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -58808,7 +58808,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F70" s="10" t="inlineStr">
+      <c r="F70" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -58860,7 +58860,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F71" s="10" t="inlineStr">
+      <c r="F71" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -58912,7 +58912,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F72" s="10" t="inlineStr">
+      <c r="F72" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -59016,7 +59016,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F74" s="10" t="inlineStr">
+      <c r="F74" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -59068,7 +59068,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F75" s="10" t="inlineStr">
+      <c r="F75" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -59120,7 +59120,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F76" s="10" t="inlineStr">
+      <c r="F76" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -59172,7 +59172,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F77" s="10" t="inlineStr">
+      <c r="F77" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -59276,7 +59276,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F79" s="10" t="inlineStr">
+      <c r="F79" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -59380,7 +59380,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F81" s="10" t="inlineStr">
+      <c r="F81" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -59480,12 +59480,12 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F83" s="10" t="inlineStr">
+      <c r="F83" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G83" s="11" t="inlineStr">
+      <c r="G83" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -59537,7 +59537,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G84" s="11" t="inlineStr">
+      <c r="G84" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -59732,7 +59732,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F88" s="10" t="inlineStr">
+      <c r="F88" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -59980,7 +59980,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F93" s="10" t="inlineStr">
+      <c r="F93" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -60176,12 +60176,12 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F97" s="10" t="inlineStr">
+      <c r="F97" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G97" s="11" t="inlineStr">
+      <c r="G97" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -60233,7 +60233,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G98" s="11" t="inlineStr">
+      <c r="G98" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -60281,7 +60281,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G99" s="11" t="inlineStr">
+      <c r="G99" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -60329,7 +60329,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G100" s="11" t="inlineStr">
+      <c r="G100" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -60424,7 +60424,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F102" s="10" t="inlineStr">
+      <c r="F102" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -60481,7 +60481,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G103" s="11" t="inlineStr">
+      <c r="G103" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -60529,7 +60529,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G104" s="11" t="inlineStr">
+      <c r="G104" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -60577,7 +60577,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G105" s="11" t="inlineStr">
+      <c r="G105" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -60625,7 +60625,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G106" s="11" t="inlineStr">
+      <c r="G106" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -60673,7 +60673,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G107" s="11" t="inlineStr">
+      <c r="G107" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -60721,7 +60721,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G108" s="11" t="inlineStr">
+      <c r="G108" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -60816,7 +60816,7 @@
           <t>Patient: App + Web; Doctor / provider: Web + App; Pharmacy / lab: Web; Clinic operator: Admin</t>
         </is>
       </c>
-      <c r="F110" s="10" t="inlineStr">
+      <c r="F110" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -60868,7 +60868,7 @@
           <t>Patient: App + Web; Doctor / provider: Web + App; Pharmacy / lab: Web; Clinic operator: Admin</t>
         </is>
       </c>
-      <c r="F111" s="10" t="inlineStr">
+      <c r="F111" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -60920,7 +60920,7 @@
           <t>Patient: App + Web; Doctor / provider: Web + App; Pharmacy / lab: Web; Clinic operator: Admin</t>
         </is>
       </c>
-      <c r="F112" s="10" t="inlineStr">
+      <c r="F112" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -60972,7 +60972,7 @@
           <t>Patient: App + Web; Doctor / provider: Web + App; Pharmacy / lab: Web; Clinic operator: Admin</t>
         </is>
       </c>
-      <c r="F113" s="10" t="inlineStr">
+      <c r="F113" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -61024,7 +61024,7 @@
           <t>Patient: App + Web; Doctor / provider: Web + App; Pharmacy / lab: Web; Clinic operator: Admin</t>
         </is>
       </c>
-      <c r="F114" s="10" t="inlineStr">
+      <c r="F114" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -61124,7 +61124,7 @@
           <t>Patient: App + Web; Doctor / provider: Web + App; Pharmacy / lab: Web; Clinic operator: Admin</t>
         </is>
       </c>
-      <c r="F116" s="10" t="inlineStr">
+      <c r="F116" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -61512,7 +61512,7 @@
           <t>Rider: App + Web; Driver: App; Dispatcher: Web; Operator: Admin</t>
         </is>
       </c>
-      <c r="F124" s="10" t="inlineStr">
+      <c r="F124" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -61564,7 +61564,7 @@
           <t>Rider: App + Web; Driver: App; Dispatcher: Web; Operator: Admin</t>
         </is>
       </c>
-      <c r="F125" s="10" t="inlineStr">
+      <c r="F125" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -61616,7 +61616,7 @@
           <t>Rider: App + Web; Driver: App; Dispatcher: Web; Operator: Admin</t>
         </is>
       </c>
-      <c r="F126" s="10" t="inlineStr">
+      <c r="F126" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -62052,7 +62052,7 @@
           <t>Buyer: App + Web; Seller / vendor: Web + App; Marketplace operator: Admin</t>
         </is>
       </c>
-      <c r="F135" s="10" t="inlineStr">
+      <c r="F135" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -62104,7 +62104,7 @@
           <t>Buyer: App + Web; Seller / vendor: Web + App; Marketplace operator: Admin</t>
         </is>
       </c>
-      <c r="F136" s="10" t="inlineStr">
+      <c r="F136" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -62156,7 +62156,7 @@
           <t>Buyer: App + Web; Seller / vendor: Web + App; Marketplace operator: Admin</t>
         </is>
       </c>
-      <c r="F137" s="10" t="inlineStr">
+      <c r="F137" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -62304,7 +62304,7 @@
           <t>Buyer: App + Web; Seller / vendor: Web + App; Marketplace operator: Admin</t>
         </is>
       </c>
-      <c r="F140" s="10" t="inlineStr">
+      <c r="F140" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -62356,7 +62356,7 @@
           <t>Buyer: App + Web; Seller / vendor: Web + App; Marketplace operator: Admin</t>
         </is>
       </c>
-      <c r="F141" s="10" t="inlineStr">
+      <c r="F141" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -67213,7 +67213,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G242" s="11" t="inlineStr">
+      <c r="G242" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67261,7 +67261,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G243" s="11" t="inlineStr">
+      <c r="G243" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67309,7 +67309,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G244" s="11" t="inlineStr">
+      <c r="G244" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67357,7 +67357,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G245" s="11" t="inlineStr">
+      <c r="G245" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67405,7 +67405,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G246" s="11" t="inlineStr">
+      <c r="G246" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67453,7 +67453,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G247" s="11" t="inlineStr">
+      <c r="G247" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67501,7 +67501,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G248" s="11" t="inlineStr">
+      <c r="G248" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67549,7 +67549,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G249" s="11" t="inlineStr">
+      <c r="G249" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67597,7 +67597,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G250" s="11" t="inlineStr">
+      <c r="G250" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67645,7 +67645,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G251" s="11" t="inlineStr">
+      <c r="G251" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67693,7 +67693,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G252" s="11" t="inlineStr">
+      <c r="G252" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67741,7 +67741,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G253" s="11" t="inlineStr">
+      <c r="G253" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67789,7 +67789,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G254" s="11" t="inlineStr">
+      <c r="G254" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67837,7 +67837,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G255" s="11" t="inlineStr">
+      <c r="G255" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67885,7 +67885,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G256" s="11" t="inlineStr">
+      <c r="G256" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67933,7 +67933,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G257" s="11" t="inlineStr">
+      <c r="G257" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67981,7 +67981,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G258" s="11" t="inlineStr">
+      <c r="G258" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68029,7 +68029,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G259" s="11" t="inlineStr">
+      <c r="G259" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68077,7 +68077,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G260" s="11" t="inlineStr">
+      <c r="G260" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68125,7 +68125,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G261" s="11" t="inlineStr">
+      <c r="G261" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68173,7 +68173,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G262" s="11" t="inlineStr">
+      <c r="G262" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68221,7 +68221,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G263" s="11" t="inlineStr">
+      <c r="G263" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68269,7 +68269,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G264" s="11" t="inlineStr">
+      <c r="G264" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68317,7 +68317,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G265" s="11" t="inlineStr">
+      <c r="G265" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68365,7 +68365,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G266" s="11" t="inlineStr">
+      <c r="G266" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68413,7 +68413,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G267" s="11" t="inlineStr">
+      <c r="G267" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68461,7 +68461,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G268" s="11" t="inlineStr">
+      <c r="G268" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68509,7 +68509,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G269" s="11" t="inlineStr">
+      <c r="G269" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68557,7 +68557,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G270" s="11" t="inlineStr">
+      <c r="G270" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68605,7 +68605,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G271" s="11" t="inlineStr">
+      <c r="G271" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68653,7 +68653,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G272" s="11" t="inlineStr">
+      <c r="G272" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68701,7 +68701,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G273" s="11" t="inlineStr">
+      <c r="G273" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68749,7 +68749,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G274" s="11" t="inlineStr">
+      <c r="G274" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68797,7 +68797,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G275" s="11" t="inlineStr">
+      <c r="G275" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68845,7 +68845,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G276" s="11" t="inlineStr">
+      <c r="G276" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68893,7 +68893,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G277" s="11" t="inlineStr">
+      <c r="G277" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68941,7 +68941,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G278" s="11" t="inlineStr">
+      <c r="G278" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68989,7 +68989,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G279" s="11" t="inlineStr">
+      <c r="G279" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69037,7 +69037,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G280" s="11" t="inlineStr">
+      <c r="G280" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69085,7 +69085,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G281" s="11" t="inlineStr">
+      <c r="G281" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69133,7 +69133,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G282" s="11" t="inlineStr">
+      <c r="G282" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69181,7 +69181,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G283" s="11" t="inlineStr">
+      <c r="G283" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69229,7 +69229,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G284" s="11" t="inlineStr">
+      <c r="G284" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69277,7 +69277,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G285" s="11" t="inlineStr">
+      <c r="G285" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69325,7 +69325,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G286" s="11" t="inlineStr">
+      <c r="G286" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69373,7 +69373,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G287" s="11" t="inlineStr">
+      <c r="G287" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69421,7 +69421,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G288" s="11" t="inlineStr">
+      <c r="G288" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69469,7 +69469,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G289" s="11" t="inlineStr">
+      <c r="G289" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69517,7 +69517,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G290" s="11" t="inlineStr">
+      <c r="G290" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69565,7 +69565,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G291" s="11" t="inlineStr">
+      <c r="G291" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69613,7 +69613,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G292" s="11" t="inlineStr">
+      <c r="G292" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69661,7 +69661,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G293" s="11" t="inlineStr">
+      <c r="G293" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69709,7 +69709,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G294" s="11" t="inlineStr">
+      <c r="G294" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69757,7 +69757,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G295" s="11" t="inlineStr">
+      <c r="G295" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69805,7 +69805,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G296" s="11" t="inlineStr">
+      <c r="G296" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69853,7 +69853,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G297" s="11" t="inlineStr">
+      <c r="G297" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69901,7 +69901,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G298" s="11" t="inlineStr">
+      <c r="G298" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69949,7 +69949,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G299" s="11" t="inlineStr">
+      <c r="G299" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69997,7 +69997,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G300" s="11" t="inlineStr">
+      <c r="G300" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70045,7 +70045,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G301" s="11" t="inlineStr">
+      <c r="G301" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70093,7 +70093,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G302" s="11" t="inlineStr">
+      <c r="G302" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70141,7 +70141,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G303" s="11" t="inlineStr">
+      <c r="G303" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70189,7 +70189,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G304" s="11" t="inlineStr">
+      <c r="G304" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70237,7 +70237,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G305" s="11" t="inlineStr">
+      <c r="G305" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70285,7 +70285,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G306" s="11" t="inlineStr">
+      <c r="G306" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70333,7 +70333,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G307" s="11" t="inlineStr">
+      <c r="G307" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70381,7 +70381,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G308" s="11" t="inlineStr">
+      <c r="G308" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70429,7 +70429,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G309" s="11" t="inlineStr">
+      <c r="G309" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70477,7 +70477,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G310" s="11" t="inlineStr">
+      <c r="G310" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70525,7 +70525,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G311" s="11" t="inlineStr">
+      <c r="G311" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70573,7 +70573,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G312" s="11" t="inlineStr">
+      <c r="G312" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70621,7 +70621,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G313" s="11" t="inlineStr">
+      <c r="G313" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70669,7 +70669,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G314" s="11" t="inlineStr">
+      <c r="G314" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70717,7 +70717,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G315" s="11" t="inlineStr">
+      <c r="G315" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70765,7 +70765,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G316" s="11" t="inlineStr">
+      <c r="G316" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70813,7 +70813,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G317" s="11" t="inlineStr">
+      <c r="G317" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70861,7 +70861,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G318" s="11" t="inlineStr">
+      <c r="G318" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70909,7 +70909,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G319" s="11" t="inlineStr">
+      <c r="G319" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70957,7 +70957,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G320" s="11" t="inlineStr">
+      <c r="G320" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -71005,7 +71005,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G321" s="11" t="inlineStr">
+      <c r="G321" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -71053,7 +71053,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G322" s="11" t="inlineStr">
+      <c r="G322" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -71609,7 +71609,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>Completed - needs live proof</t>
         </is>
@@ -71621,7 +71621,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="16" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
@@ -71633,7 +71633,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -71657,7 +71657,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -71669,7 +71669,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
@@ -71681,7 +71681,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -71729,7 +71729,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>

--- a/R_&_D/Platform_Completion/OmniStackAI_Master_Tasks.xlsx
+++ b/R_&_D/Platform_Completion/OmniStackAI_Master_Tasks.xlsx
@@ -92,6 +92,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00BDD7EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFE699"/>
       </patternFill>
     </fill>
@@ -113,11 +118,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2F0D9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00BDD7EE"/>
       </patternFill>
     </fill>
   </fills>
@@ -173,10 +173,10 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1799,9 +1799,9 @@
           <t>Platform</t>
         </is>
       </c>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
@@ -1975,7 +1975,7 @@
           <t>Vibe</t>
         </is>
       </c>
-      <c r="F26" s="10" t="inlineStr">
+      <c r="F26" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2021,7 +2021,7 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="F27" s="10" t="inlineStr">
+      <c r="F27" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2067,7 +2067,7 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="F28" s="10" t="inlineStr">
+      <c r="F28" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2683,7 +2683,7 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="F42" s="10" t="inlineStr">
+      <c r="F42" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2733,7 +2733,7 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="F43" s="10" t="inlineStr">
+      <c r="F43" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2833,7 +2833,7 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="F45" s="10" t="inlineStr">
+      <c r="F45" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2979,7 +2979,7 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="F48" s="10" t="inlineStr">
+      <c r="F48" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -3029,7 +3029,7 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="F49" s="10" t="inlineStr">
+      <c r="F49" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -3184,7 +3184,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G52" s="11" t="inlineStr">
+      <c r="G52" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -3234,7 +3234,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G53" s="11" t="inlineStr">
+      <c r="G53" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -3422,7 +3422,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G57" s="11" t="inlineStr">
+      <c r="G57" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -3464,7 +3464,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G58" s="11" t="inlineStr">
+      <c r="G58" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -3510,7 +3510,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G59" s="11" t="inlineStr">
+      <c r="G59" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -3552,7 +3552,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G60" s="11" t="inlineStr">
+      <c r="G60" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -3594,7 +3594,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G61" s="11" t="inlineStr">
+      <c r="G61" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -3677,7 +3677,7 @@
           <t>Vibe</t>
         </is>
       </c>
-      <c r="F63" s="10" t="inlineStr">
+      <c r="F63" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -3728,7 +3728,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G64" s="11" t="inlineStr">
+      <c r="G64" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -4154,7 +4154,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G73" s="11" t="inlineStr">
+      <c r="G73" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -4200,7 +4200,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G74" s="11" t="inlineStr">
+      <c r="G74" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -4246,7 +4246,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G75" s="11" t="inlineStr">
+      <c r="G75" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -4333,7 +4333,7 @@
           <t>Engineering</t>
         </is>
       </c>
-      <c r="F77" s="10" t="inlineStr">
+      <c r="F77" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -4471,7 +4471,7 @@
           <t>Engineering</t>
         </is>
       </c>
-      <c r="F80" s="10" t="inlineStr">
+      <c r="F80" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -4567,7 +4567,7 @@
           <t>Engineering</t>
         </is>
       </c>
-      <c r="F82" s="10" t="inlineStr">
+      <c r="F82" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -4839,7 +4839,7 @@
           <t>Engineering</t>
         </is>
       </c>
-      <c r="F88" s="10" t="inlineStr">
+      <c r="F88" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -5157,7 +5157,7 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="F95" s="10" t="inlineStr">
+      <c r="F95" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -5802,7 +5802,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G109" s="11" t="inlineStr">
+      <c r="G109" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -5848,7 +5848,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G110" s="11" t="inlineStr">
+      <c r="G110" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -5894,7 +5894,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G111" s="11" t="inlineStr">
+      <c r="G111" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -6462,12 +6462,12 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>PC-013</t>
+          <t>PC-009</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Verified integrations catalog with health tests</t>
+          <t>Hosted multi-tenant service: per-user isolation of builds, sessions and previews; quotas; egress policy</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Vibe</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -6487,31 +6487,31 @@
       </c>
       <c r="F2" s="10" t="inlineStr">
         <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr"/>
       <c r="I2" s="3" t="inlineStr"/>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>R-511 Connectors v1 exists.</t>
+          <t>Today the Studio is one trusted operator's tool. Built cloud-neutral and proven locally (Colima); the cloud account (D-2) is plugged in at PC-070.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>PC-014</t>
+          <t>PC-013</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Local/offline models as a first-class path: build fully on Ollama, recommend a model per machine</t>
+          <t>Verified integrations catalog with health tests</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -6521,7 +6521,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Vibe</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -6529,7 +6529,7 @@
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="F3" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6543,19 +6543,19 @@
       <c r="I3" s="3" t="inlineStr"/>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>Ollama adapter exists (R-003/R-006). Found in PC-084: .env names qwen2.5-coder:14b but only 7b is installed, and the adapter refuses a pinned model it was not configured with — detect installed models instead of trusting the setting.</t>
+          <t>R-511 Connectors v1 exists.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>R-574</t>
+          <t>PC-014</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Store publishing for React Native apps: EAS build and submit to Play Store and App Store, proven with real accounts</t>
+          <t>Local/offline models as a first-class path: build fully on Ollama, recommend a model per machine</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -6573,7 +6573,7 @@
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6587,19 +6587,19 @@
       <c r="I4" s="3" t="inlineStr"/>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>R-546/R-547 generate the EAS config. Everything up to the upload is built and tested; the Apple and Google accounts (D-7) are plugged in at PC-070.</t>
+          <t>Ollama adapter exists (R-003/R-006). Found in PC-084: .env names qwen2.5-coder:14b but only 7b is installed, and the adapter refuses a pinned model it was not configured with — detect installed models instead of trusting the setting.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>PC-017</t>
+          <t>R-574</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Pack framework core: manifest v2 schema, registry/loader, composer (merge, wire, validate, conflict rules)</t>
+          <t>Store publishing for React Native apps: EAS build and submit to Play Store and App Store, proven with real accounts</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -6614,10 +6614,10 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>2 Maximum features</t>
-        </is>
-      </c>
-      <c r="F5" s="10" t="inlineStr">
+          <t>1 Vibe Mode live</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6631,19 +6631,19 @@
       <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>Solution Pack manifests, registry and application exist (R-434..R-445); v2 adds ir_delta, state machines, page templates, dependencies. From specs/pack-framework 01, 02.</t>
+          <t>R-546/R-547 generate the EAS config. Everything up to the upload is built and tested; the Apple and Google accounts (D-7) are plugged in at PC-070.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>PC-075</t>
+          <t>PC-017</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Role-based app generator: a complete app per role (nav, pages, API scope, permissions)</t>
+          <t>Pack framework core: manifest v2 schema, registry/loader, composer (merge, wire, validate, conflict rules)</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -6661,7 +6661,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6675,19 +6675,19 @@
       <c r="I6" s="3" t="inlineStr"/>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>R-555/R-562 already build one app per role; the spec asks for role-scoped pages and APIs. From specs/pack-framework/06b.</t>
+          <t>Solution Pack manifests, registry and application exist (R-434..R-445); v2 adds ir_delta, state machines, page templates, dependencies. From specs/pack-framework 01, 02.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>PC-077</t>
+          <t>PC-075</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Rich seed data generator: realistic, domain-aware, deterministic demo data</t>
+          <t>Role-based app generator: a complete app per role (nav, pages, API scope, permissions)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -6705,33 +6705,33 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F7" s="10" t="inlineStr">
+      <c r="F7" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G7" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr"/>
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>Fixture seeds exist (R-248) and must stay deterministic (R-586). From specs/pack-framework/06e.</t>
+          <t>R-555/R-562 already build one app per role; the spec asks for role-scoped pages and APIs. From specs/pack-framework/06b.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>PC-073</t>
+          <t>PC-077</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Horizontal packs, wave 1: the P0/P1 universal packs as manifest v2 packs that work alone and compose (HP-* rows)</t>
+          <t>Rich seed data generator: realistic, domain-aware, deterministic demo data</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -6749,33 +6749,33 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="F8" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr"/>
       <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>Core first (auth, database, API, design system, admin, payments, notifications, files, realtime, workflows), then the mobile &amp; device and AI packs. Each pack packages a capability built by its own task. Full list: PACK_CATALOG.md.</t>
+          <t>Fixture seeds exist (R-248) and must stay deterministic (R-586). From specs/pack-framework/06e.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>PC-074</t>
+          <t>PC-073</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Vertical packs, wave 1: healthcare, mobility, commerce (VP-* rows) on every surface: API, web, app, admin panel</t>
+          <t>Horizontal packs, wave 1: the P0/P1 universal packs as manifest v2 packs that work alone and compose (HP-* rows)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -6793,7 +6793,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr">
+      <c r="F9" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6807,19 +6807,19 @@
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>Built from the CareClinic, RideNow and Bazaar templates.</t>
+          <t>Core first (auth, database, API, design system, admin, payments, notifications, files, realtime, workflows), then the mobile &amp; device and AI packs. Each pack packages a capability built by its own task. Full list: PACK_CATALOG.md.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>PC-020</t>
+          <t>PC-074</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Brand kit / Style DNA UI across all surfaces</t>
+          <t>Vertical packs, wave 1: healthcare, mobility, commerce (VP-* rows) on every surface: API, web, app, admin panel</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -6829,7 +6829,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Vibe</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -6837,33 +6837,33 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G10" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr"/>
       <c r="I10" s="3" t="inlineStr"/>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>brand.json exists (R-548); needs the UI. Buildout idea 'R-526'.</t>
+          <t>Built from the CareClinic, RideNow and Bazaar templates.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>PC-023</t>
+          <t>PC-020</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Stack chooser: pick web/admin/mobile/backend, refused with a reason when unsupported</t>
+          <t>Brand kit / Style DNA UI across all surfaces</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -6873,41 +6873,41 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Vibe</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>3 Engineering Mode</t>
-        </is>
-      </c>
-      <c r="F11" s="10" t="inlineStr">
+          <t>2 Maximum features</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr"/>
       <c r="I11" s="3" t="inlineStr"/>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>R-565 carries the stack in the IR; needs the UI.</t>
+          <t>brand.json exists (R-548); needs the UI. Buildout idea 'R-526'.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>R-579</t>
+          <t>PC-023</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>GitHub import and push-back</t>
+          <t>Stack chooser: pick web/admin/mobile/backend, refused with a reason when unsupported</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -6925,7 +6925,7 @@
           <t>3 Engineering Mode</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr">
+      <c r="F12" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6939,19 +6939,19 @@
       <c r="I12" s="3" t="inlineStr"/>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>R-501 can push a generated project; import is missing.</t>
+          <t>R-565 carries the stack in the IR; needs the UI.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>PC-025</t>
+          <t>R-579</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Verification report view: per-surface compile, tests, security, in the Studio</t>
+          <t>GitHub import and push-back</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -6969,7 +6969,7 @@
           <t>3 Engineering Mode</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="F13" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6983,19 +6983,19 @@
       <c r="I13" s="3" t="inlineStr"/>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>R-560/R-561/R-508 produce the data; nothing shows it as a report.</t>
+          <t>R-501 can push a generated project; import is missing.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>PC-029</t>
+          <t>PC-025</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Team collaboration: roles, approvals, preview comments</t>
+          <t>Verification report view: per-surface compile, tests, security, in the Studio</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -7013,33 +7013,33 @@
           <t>3 Engineering Mode</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr">
+      <c r="F14" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G14" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr"/>
       <c r="I14" s="3" t="inlineStr"/>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>R-515 gives teams.</t>
+          <t>R-560/R-561/R-508 produce the data; nothing shows it as a report.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>PC-036</t>
+          <t>PC-029</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Migration safety checks for generated schema changes</t>
+          <t>Team collaboration: roles, approvals, preview comments</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -7049,55 +7049,59 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>4 Production ops</t>
-        </is>
-      </c>
-      <c r="F15" s="10" t="inlineStr">
+          <t>3 Engineering Mode</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr"/>
       <c r="I15" s="3" t="inlineStr"/>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>R-584 flags data loss; needs a real gate.</t>
+          <t>R-515 gives teams.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>ARCH-DOMAIN-IR</t>
+          <t>PC-036</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Domain IR: guards, business rules, field masks, row filters, page templates</t>
+          <t>Migration safety checks for generated schema changes</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>docs/ARCHITECTURE_MASTER_PLAN.md §5.2</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr"/>
+          <t>Platform_Completion queue</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>2 Maximum features</t>
-        </is>
-      </c>
-      <c r="F16" s="10" t="inlineStr">
+          <t>4 Production ops</t>
+        </is>
+      </c>
+      <c r="F16" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7107,32 +7111,28 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>R-570</t>
-        </is>
-      </c>
+      <c r="H16" s="3" t="inlineStr"/>
       <c r="I16" s="3" t="inlineStr"/>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>State machines done (R-566); field masks and row filters are R-570; guards and rules R-571.</t>
+          <t>R-584 flags data loss; needs a real gate.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>ARCH-GENERATORS</t>
+          <t>ARCH-DOMAIN-IR</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Advanced generators: state machine, role app, page template, shared package, seed data, form wizard, realtime</t>
+          <t>Domain IR: guards, business rules, field masks, row filters, page templates</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>docs/ARCHITECTURE_MASTER_PLAN.md §5.3</t>
+          <t>docs/ARCHITECTURE_MASTER_PLAN.md §5.2</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr"/>
@@ -7141,7 +7141,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F17" s="10" t="inlineStr">
+      <c r="F17" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7153,74 +7153,74 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>PC-017</t>
+          <t>R-570</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr"/>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>State machine done (R-566/588/589); shared package R-572; form wizard PC-059; realtime R-569.</t>
+          <t>State machines done (R-566); field masks and row filters are R-570; guards and rules R-571.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>ARCH-PIPELINE</t>
+          <t>ARCH-GENERATORS</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Vibe pipeline: classify -&gt; select packs -&gt; compose IR -&gt; generate -&gt; provision -&gt; preview in 90 s</t>
+          <t>Advanced generators: state machine, role app, page template, shared package, seed data, form wizard, realtime</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>docs/ARCHITECTURE_MASTER_PLAN.md §4.1</t>
+          <t>docs/ARCHITECTURE_MASTER_PLAN.md §5.3</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr"/>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Delivered</t>
-        </is>
-      </c>
-      <c r="F18" s="10" t="inlineStr">
+          <t>2 Maximum features</t>
+        </is>
+      </c>
+      <c r="F18" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>P0</t>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>PC-004</t>
+          <t>PC-017</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr"/>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>Generate and preview exist; provision is PC-049.</t>
+          <t>State machine done (R-566/588/589); shared package R-572; form wizard PC-059; realtime R-569.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>ARCH-PWA</t>
+          <t>ARCH-PIPELINE</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>PWA / offline support</t>
+          <t>Vibe pipeline: classify -&gt; select packs -&gt; compose IR -&gt; generate -&gt; provision -&gt; preview in 90 s</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>docs/ARCHITECTURE_MASTER_PLAN.md §10 Phase 4</t>
+          <t>docs/ARCHITECTURE_MASTER_PLAN.md §4.1</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr"/>
@@ -7229,7 +7229,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F19" s="10" t="inlineStr">
+      <c r="F19" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7241,47 +7241,51 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>R-573</t>
+          <t>PC-004</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr"/>
-      <c r="J19" s="3" t="inlineStr"/>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>Generate and preview exist; provision is PC-049.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>BP-BRANDKIT</t>
+          <t>ARCH-PWA</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Style DNA UI and brand kit studio</t>
+          <t>PWA / offline support</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Platform_Buildout section 8 ('R-526')</t>
+          <t>docs/ARCHITECTURE_MASTER_PLAN.md §10 Phase 4</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr"/>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>2 Maximum features</t>
-        </is>
-      </c>
-      <c r="F20" s="10" t="inlineStr">
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="F20" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G20" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>PC-020</t>
+          <t>R-573</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr"/>
@@ -7290,70 +7294,66 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>BP-SWITCHER</t>
+          <t>BP-BRANDKIT</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Multi-app ecosystem switcher and persona simulator</t>
+          <t>Style DNA UI and brand kit studio</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Platform_Buildout section 8 ('R-521')</t>
+          <t>Platform_Buildout section 8 ('R-526')</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr"/>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Delivered</t>
-        </is>
-      </c>
-      <c r="F21" s="10" t="inlineStr">
+          <t>2 Maximum features</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>PC-006</t>
+          <t>PC-020</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr"/>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>Multi-app preview exists (R-520, R-553); personas do not.</t>
-        </is>
-      </c>
+      <c r="J21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>GA-03</t>
+          <t>BP-SWITCHER</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>First-class Ollama-compatible provider with quality eval</t>
+          <t>Multi-app ecosystem switcher and persona simulator</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Tracker RND_Gap_Audit</t>
+          <t>Platform_Buildout section 8 ('R-521')</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr"/>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>1 Vibe Mode live</t>
-        </is>
-      </c>
-      <c r="F22" s="10" t="inlineStr">
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="F22" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7365,25 +7365,25 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>PC-014</t>
+          <t>PC-006</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr"/>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>Provider done (R-006); eval missing.</t>
+          <t>Multi-app preview exists (R-520, R-553); personas do not.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>GA-04</t>
+          <t>GA-03</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Per-model safe context registry, no silent truncation</t>
+          <t>First-class Ollama-compatible provider with quality eval</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -7397,7 +7397,7 @@
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="F23" s="10" t="inlineStr">
+      <c r="F23" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7415,19 +7415,19 @@
       <c r="I23" s="3" t="inlineStr"/>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>Safe input budget exists (R-522).</t>
+          <t>Provider done (R-006); eval missing.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>GA-05</t>
+          <t>GA-04</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Route by measured task, eval, latency, context and cost</t>
+          <t>Per-model safe context registry, no silent truncation</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -7441,14 +7441,14 @@
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="F24" s="10" t="inlineStr">
+      <c r="F24" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G24" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -7457,17 +7457,21 @@
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr"/>
-      <c r="J24" s="3" t="inlineStr"/>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>Safe input budget exists (R-522).</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>GA-07</t>
+          <t>GA-05</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Environments local -&gt; test -&gt; preview -&gt; staging -&gt; prod with typed config</t>
+          <t>Route by measured task, eval, latency, context and cost</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -7478,10 +7482,10 @@
       <c r="D25" s="3" t="inlineStr"/>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>4 Production ops</t>
-        </is>
-      </c>
-      <c r="F25" s="10" t="inlineStr">
+          <t>1 Vibe Mode live</t>
+        </is>
+      </c>
+      <c r="F25" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7493,7 +7497,7 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>PC-040</t>
+          <t>PC-014</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr"/>
@@ -7502,12 +7506,12 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>GA-11</t>
+          <t>GA-07</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Pinned supply chain, SBOM/provenance, patch SLA</t>
+          <t>Environments local -&gt; test -&gt; preview -&gt; staging -&gt; prod with typed config</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -7521,7 +7525,7 @@
           <t>4 Production ops</t>
         </is>
       </c>
-      <c r="F26" s="10" t="inlineStr">
+      <c r="F26" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7533,30 +7537,26 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>PC-035</t>
+          <t>PC-040</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr"/>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>Lockfiles pinned; SBOM missing.</t>
-        </is>
-      </c>
+      <c r="J26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>GAP-TESTTOOLS</t>
+          <t>GA-11</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Pin the testing toolchain (Playwright, pytest, go test, k6)</t>
+          <t>Pinned supply chain, SBOM/provenance, patch SLA</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>V6_Review_and_Gap_Analysis section 3</t>
+          <t>Tracker RND_Gap_Audit</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr"/>
@@ -7565,7 +7565,7 @@
           <t>4 Production ops</t>
         </is>
       </c>
-      <c r="F27" s="10" t="inlineStr">
+      <c r="F27" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7577,43 +7577,39 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>PC-037</t>
+          <t>PC-035</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr"/>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>pytest/unittest, go test and Playwright (templates) are in use; k6 is not.</t>
+          <t>Lockfiles pinned; SBOM missing.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>HP-accessibility</t>
+          <t>GAP-TESTTOOLS</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack accessibility: WCAG 2.1 AA, automated axe checks</t>
+          <t>Pin the testing toolchain (Playwright, pytest, go test, k6)</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>spec</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>UI &amp; experience</t>
-        </is>
-      </c>
+          <t>V6_Review_and_Gap_Analysis section 3</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr"/>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>2 Maximum features</t>
-        </is>
-      </c>
-      <c r="F28" s="10" t="inlineStr">
+          <t>4 Production ops</t>
+        </is>
+      </c>
+      <c r="F28" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7625,35 +7621,35 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>PC-078</t>
+          <t>PC-037</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr"/>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>Accessible UI exists (R-296).</t>
+          <t>pytest/unittest, go test and Playwright (templates) are in use; k6 is not.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>HP-activity-feed</t>
+          <t>HP-accessibility</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack activity-feed: Activity streams, timelines, follow/subscribe</t>
+          <t>Horizontal pack accessibility: WCAG 2.1 AA, automated axe checks</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>new (registry dependency)</t>
+          <t>spec</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Realtime &amp; communication</t>
+          <t>UI &amp; experience</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -7661,7 +7657,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F29" s="10" t="inlineStr">
+      <c r="F29" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7679,29 +7675,29 @@
       <c r="I29" s="3" t="inlineStr"/>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>Timeline component exists (R-336).</t>
+          <t>Accessible UI exists (R-296).</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>HP-admin-crud</t>
+          <t>HP-activity-feed</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack admin-crud: Generated admin: tables, filters, bulk actions, exports</t>
+          <t>Horizontal pack activity-feed: Activity streams, timelines, follow/subscribe</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>spec</t>
+          <t>new (registry dependency)</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Core platform</t>
+          <t>Realtime &amp; communication</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -7709,47 +7705,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F30" s="10" t="inlineStr">
+      <c r="F30" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G30" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>PC-073</t>
+          <t>PC-078</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr"/>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>Admin app exists (R-542, R-270, R-271).</t>
+          <t>Timeline component exists (R-336).</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>HP-analytics-events</t>
+          <t>HP-admin-crud</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack analytics-events: Event tracking, funnels, cohorts (PostHog/GA4)</t>
+          <t>Horizontal pack admin-crud: Generated admin: tables, filters, bulk actions, exports</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>spec, registry</t>
+          <t>spec</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Data &amp; storage</t>
+          <t>Core platform</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -7757,47 +7753,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F31" s="10" t="inlineStr">
+      <c r="F31" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G31" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>PC-078</t>
+          <t>PC-073</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr"/>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>Published-app analytics exists (R-513).</t>
+          <t>Admin app exists (R-542, R-270, R-271).</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>HP-api-core</t>
+          <t>HP-analytics-events</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack api-core: REST API, validation, OpenAPI, errors, rate limiting</t>
+          <t>Horizontal pack analytics-events: Event tracking, funnels, cohorts (PostHog/GA4)</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>registry</t>
+          <t>spec, registry</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Core platform</t>
+          <t>Data &amp; storage</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -7805,42 +7801,42 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F32" s="10" t="inlineStr">
+      <c r="F32" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G32" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G32" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>PC-073</t>
+          <t>PC-078</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr"/>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>Python/Go/Node APIs exist (R-229, R-230, R-517).</t>
+          <t>Published-app analytics exists (R-513).</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>HP-api-docs</t>
+          <t>HP-api-core</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack api-docs: OpenAPI, Swagger UI, Postman collection, SDKs</t>
+          <t>Horizontal pack api-core: REST API, validation, OpenAPI, errors, rate limiting</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>spec</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -7853,47 +7849,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F33" s="10" t="inlineStr">
+      <c r="F33" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G33" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>PC-078</t>
+          <t>PC-073</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr"/>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>OpenAPI exists (R-260, R-588).</t>
+          <t>Python/Go/Node APIs exist (R-229, R-230, R-517).</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>HP-app-store-assets</t>
+          <t>HP-api-docs</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack app-store-assets: Icons, splash, screenshots, store listing metadata</t>
+          <t>Horizontal pack api-docs: OpenAPI, Swagger UI, Postman collection, SDKs</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>spec</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Mobile &amp; device (stack-aware: React Native, Kotlin, Swift)</t>
+          <t>Core platform</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -7901,47 +7897,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F34" s="10" t="inlineStr">
+      <c r="F34" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G34" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>PC-073</t>
+          <t>PC-078</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr"/>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>Icons and EAS config exist (R-546, R-547); R-574.</t>
+          <t>OpenAPI exists (R-260, R-588).</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>HP-auth-rbac</t>
+          <t>HP-app-store-assets</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack auth-rbac: Login, register, roles, sessions, MFA, OAuth, passkeys</t>
+          <t>Horizontal pack app-store-assets: Icons, splash, screenshots, store listing metadata</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>spec, registry</t>
+          <t>new</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Core platform</t>
+          <t>Mobile &amp; device (stack-aware: React Native, Kotlin, Swift)</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -7949,7 +7945,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F35" s="10" t="inlineStr">
+      <c r="F35" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7967,29 +7963,29 @@
       <c r="I35" s="3" t="inlineStr"/>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>Auth exists (R-461, R-241..R-243); Go login R-591.</t>
+          <t>Icons and EAS config exist (R-546, R-547); R-574.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>HP-camera-qr</t>
+          <t>HP-auth-rbac</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack camera-qr: Camera, photo/video capture, QR and barcode scanning</t>
+          <t>Horizontal pack auth-rbac: Login, register, roles, sessions, MFA, OAuth, passkeys</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>PRD (+ registry 'barcode')</t>
+          <t>spec, registry</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Mobile &amp; device (stack-aware: React Native, Kotlin, Swift)</t>
+          <t>Core platform</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -7997,7 +7993,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F36" s="10" t="inlineStr">
+      <c r="F36" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8015,29 +8011,29 @@
       <c r="I36" s="3" t="inlineStr"/>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>QR generation exists (R-382).</t>
+          <t>Auth exists (R-461, R-241..R-243); Go login R-591.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>HP-charts-dashboards</t>
+          <t>HP-camera-qr</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack charts-dashboards: Charts, dashboards, live series</t>
+          <t>Horizontal pack camera-qr: Camera, photo/video capture, QR and barcode scanning</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>registry</t>
+          <t>PRD (+ registry 'barcode')</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>UI &amp; experience</t>
+          <t>Mobile &amp; device (stack-aware: React Native, Kotlin, Swift)</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -8045,37 +8041,37 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F37" s="10" t="inlineStr">
+      <c r="F37" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G37" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>PC-078</t>
+          <t>PC-073</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr"/>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>Chart suite exists (R-370).</t>
+          <t>QR generation exists (R-382).</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>HP-ci-cd</t>
+          <t>HP-charts-dashboards</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack ci-cd: CI workflows, containers, Helm, preview environments</t>
+          <t>Horizontal pack charts-dashboards: Charts, dashboards, live series</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -8085,7 +8081,7 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Core platform</t>
+          <t>UI &amp; experience</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -8093,7 +8089,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F38" s="10" t="inlineStr">
+      <c r="F38" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8111,29 +8107,29 @@
       <c r="I38" s="3" t="inlineStr"/>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>CI/CD workflow generation exists (R-452).</t>
+          <t>Chart suite exists (R-370).</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>HP-communications</t>
+          <t>HP-ci-cd</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack communications: 1:1 and group chat, threads, mentions, reactions, attachments</t>
+          <t>Horizontal pack ci-cd: CI workflows, containers, Helm, preview environments</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>spec, registry</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Realtime &amp; communication</t>
+          <t>Core platform</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -8141,7 +8137,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F39" s="10" t="inlineStr">
+      <c r="F39" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8159,29 +8155,29 @@
       <c r="I39" s="3" t="inlineStr"/>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>Chat component exists (R-384).</t>
+          <t>CI/CD workflow generation exists (R-452).</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>HP-config-env</t>
+          <t>HP-communications</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack config-env: Typed env config, secret references, multi-environment</t>
+          <t>Horizontal pack communications: 1:1 and group chat, threads, mentions, reactions, attachments</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>registry</t>
+          <t>spec, registry</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Core platform</t>
+          <t>Realtime &amp; communication</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -8189,7 +8185,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F40" s="10" t="inlineStr">
+      <c r="F40" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8207,29 +8203,29 @@
       <c r="I40" s="3" t="inlineStr"/>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>Credential templates exist (R-547).</t>
+          <t>Chat component exists (R-384).</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>HP-consent-management</t>
+          <t>HP-config-env</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack consent-management: Consent capture and ledger, cookie preferences</t>
+          <t>Horizontal pack config-env: Typed env config, secret references, multi-environment</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>new (registry dependency)</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Security &amp; compliance</t>
+          <t>Core platform</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -8237,7 +8233,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F41" s="10" t="inlineStr">
+      <c r="F41" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8255,29 +8251,29 @@
       <c r="I41" s="3" t="inlineStr"/>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>Cookie consent component exists (R-402).</t>
+          <t>Credential templates exist (R-547).</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>HP-custom-domains</t>
+          <t>HP-consent-management</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack custom-domains: Custom domains, DNS, TLS certificates</t>
+          <t>Horizontal pack consent-management: Consent capture and ledger, cookie preferences</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>new (registry dependency 'dns')</t>
+          <t>new (registry dependency)</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Core platform</t>
+          <t>Security &amp; compliance</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -8285,7 +8281,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F42" s="10" t="inlineStr">
+      <c r="F42" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8303,29 +8299,29 @@
       <c r="I42" s="3" t="inlineStr"/>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>Custom domains exist for published apps (R-510).</t>
+          <t>Cookie consent component exists (R-402).</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>HP-data-import-export</t>
+          <t>HP-custom-domains</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack data-import-export: CSV/Excel import with mapping and validation; bulk export</t>
+          <t>Horizontal pack custom-domains: Custom domains, DNS, TLS certificates</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>new (registry dependency 'dns')</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>Data &amp; storage</t>
+          <t>Core platform</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -8333,7 +8329,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F43" s="10" t="inlineStr">
+      <c r="F43" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8351,29 +8347,29 @@
       <c r="I43" s="3" t="inlineStr"/>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>CSV/JSON export exists (R-271, R-308).</t>
+          <t>Custom domains exist for published apps (R-510).</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>HP-data-tables</t>
+          <t>HP-data-import-export</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack data-tables: Virtualised tables, grouping, column picker, export</t>
+          <t>Horizontal pack data-import-export: CSV/Excel import with mapping and validation; bulk export</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>registry</t>
+          <t>new</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>UI &amp; experience</t>
+          <t>Data &amp; storage</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -8381,7 +8377,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F44" s="10" t="inlineStr">
+      <c r="F44" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8399,19 +8395,19 @@
       <c r="I44" s="3" t="inlineStr"/>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>Data grid exists (R-329).</t>
+          <t>CSV/JSON export exists (R-271, R-308).</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>HP-database-pg</t>
+          <t>HP-data-tables</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack database-pg: PostgreSQL schema, migrations, seeds, row-level security</t>
+          <t>Horizontal pack data-tables: Virtualised tables, grouping, column picker, export</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -8421,7 +8417,7 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Core platform</t>
+          <t>UI &amp; experience</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -8429,37 +8425,37 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F45" s="10" t="inlineStr">
+      <c r="F45" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G45" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G45" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>PC-073</t>
+          <t>PC-078</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr"/>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>Schema/migrations/seeds exist (R-238, R-248).</t>
+          <t>Data grid exists (R-329).</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>HP-design-system</t>
+          <t>HP-database-pg</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack design-system: Design tokens, components, motion, dark mode</t>
+          <t>Horizontal pack database-pg: PostgreSQL schema, migrations, seeds, row-level security</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -8469,7 +8465,7 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>UI &amp; experience</t>
+          <t>Core platform</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -8477,7 +8473,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F46" s="10" t="inlineStr">
+      <c r="F46" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8495,29 +8491,29 @@
       <c r="I46" s="3" t="inlineStr"/>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>Design system exists (R-558, R-324, R-491).</t>
+          <t>Schema/migrations/seeds exist (R-238, R-248).</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>HP-e-sign</t>
+          <t>HP-design-system</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack e-sign: Document signing, signer flows, certificates</t>
+          <t>Horizontal pack design-system: Design tokens, components, motion, dark mode</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>new (registry dependency)</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>Business logic &amp; workflow</t>
+          <t>UI &amp; experience</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -8525,47 +8521,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F47" s="10" t="inlineStr">
+      <c r="F47" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G47" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>PC-078</t>
+          <t>PC-073</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr"/>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>Signature pad exists (R-372).</t>
+          <t>Design system exists (R-558, R-324, R-491).</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>HP-integration-hub</t>
+          <t>HP-e-sign</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack integration-hub: Connectors (Slack, HubSpot, Salesforce ...), workflow builder</t>
+          <t>Horizontal pack e-sign: Document signing, signer flows, certificates</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>registry</t>
+          <t>new (registry dependency)</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Integration &amp; AI</t>
+          <t>Business logic &amp; workflow</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
@@ -8573,7 +8569,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F48" s="10" t="inlineStr">
+      <c r="F48" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8591,29 +8587,29 @@
       <c r="I48" s="3" t="inlineStr"/>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>Connectors v1 exist (R-511).</t>
+          <t>Signature pad exists (R-372).</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>HP-maps-geo</t>
+          <t>HP-integration-hub</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack maps-geo: Maps, geocoding, geofences, routes, address autocomplete</t>
+          <t>Horizontal pack integration-hub: Connectors (Slack, HubSpot, Salesforce ...), workflow builder</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>registry ('mapping', listed under mobility), PRD</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>UI &amp; experience</t>
+          <t>Integration &amp; AI</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -8621,47 +8617,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F49" s="10" t="inlineStr">
+      <c r="F49" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G49" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G49" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>PC-073</t>
+          <t>PC-078</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr"/>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>Geo-map component exists (R-387).</t>
+          <t>Connectors v1 exist (R-511).</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>HP-media-player-device</t>
+          <t>HP-maps-geo</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack media-player-device: Audio/video playback, background audio, casting</t>
+          <t>Horizontal pack maps-geo: Maps, geocoding, geofences, routes, address autocomplete</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>registry ('mapping', listed under mobility), PRD</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Mobile &amp; device (stack-aware: React Native, Kotlin, Swift)</t>
+          <t>UI &amp; experience</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -8669,47 +8665,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F50" s="10" t="inlineStr">
+      <c r="F50" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G50" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>PC-079</t>
+          <t>PC-073</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr"/>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>Web media players exist (R-376, R-390).</t>
+          <t>Geo-map component exists (R-387).</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>HP-multi-app</t>
+          <t>HP-media-player-device</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack multi-app: Shared API, cross-app auth, preview proxy, deploy coordination</t>
+          <t>Horizontal pack media-player-device: Audio/video playback, background audio, casting</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>spec</t>
+          <t>new</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Core platform</t>
+          <t>Mobile &amp; device (stack-aware: React Native, Kotlin, Swift)</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -8717,47 +8713,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F51" s="10" t="inlineStr">
+      <c r="F51" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G51" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G51" s="12" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>PC-073</t>
+          <t>PC-079</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr"/>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>Ecosystem monorepo exists (R-554, R-447, R-553).</t>
+          <t>Web media players exist (R-376, R-390).</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>HP-multi-currency</t>
+          <t>HP-multi-app</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack multi-currency: Currencies, exchange rates, price lists</t>
+          <t>Horizontal pack multi-app: Shared API, cross-app auth, preview proxy, deploy coordination</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>registry (listed under commerce)</t>
+          <t>spec</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Commerce &amp; payments</t>
+          <t>Core platform</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
@@ -8765,47 +8761,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F52" s="10" t="inlineStr">
+      <c r="F52" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G52" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G52" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>PC-078</t>
+          <t>PC-073</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr"/>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>Currency input exists (R-409).</t>
+          <t>Ecosystem monorepo exists (R-554, R-447, R-553).</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>HP-notifications</t>
+          <t>HP-multi-currency</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack notifications: Email, SMS, push, in-app centre, preferences, digests</t>
+          <t>Horizontal pack multi-currency: Currencies, exchange rates, price lists</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>spec, registry</t>
+          <t>registry (listed under commerce)</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Realtime &amp; communication</t>
+          <t>Commerce &amp; payments</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
@@ -8813,47 +8809,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F53" s="10" t="inlineStr">
+      <c r="F53" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G53" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G53" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>PC-073</t>
+          <t>PC-078</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr"/>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>Email exists (R-516); PC-053.</t>
+          <t>Currency input exists (R-409).</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>HP-onboarding-tours</t>
+          <t>HP-notifications</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack onboarding-tours: Product tours and spotlight guides</t>
+          <t>Horizontal pack notifications: Email, SMS, push, in-app centre, preferences, digests</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>spec, registry</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>UI &amp; experience</t>
+          <t>Realtime &amp; communication</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
@@ -8861,47 +8857,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F54" s="10" t="inlineStr">
+      <c r="F54" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G54" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>PC-079</t>
+          <t>PC-073</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr"/>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>Tour component exists (R-363).</t>
+          <t>Email exists (R-516); PC-053.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>HP-payments-core</t>
+          <t>HP-onboarding-tours</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack payments-core: Stripe/Razorpay/Paddle payments, refunds, disputes</t>
+          <t>Horizontal pack onboarding-tours: Product tours and spotlight guides</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>spec, registry, PRD</t>
+          <t>new</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Commerce &amp; payments</t>
+          <t>UI &amp; experience</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -8909,47 +8905,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F55" s="10" t="inlineStr">
+      <c r="F55" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G55" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G55" s="12" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>PC-073</t>
+          <t>PC-079</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr"/>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>Checkout exists (R-512).</t>
+          <t>Tour component exists (R-363).</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>HP-pdf-documents</t>
+          <t>HP-payments-core</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack pdf-documents: Document templates, PDF generation, document store</t>
+          <t>Horizontal pack payments-core: Stripe/Razorpay/Paddle payments, refunds, disputes</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>new (registry dependencies 'documents', 'pdf-generation')</t>
+          <t>spec, registry, PRD</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Data &amp; storage</t>
+          <t>Commerce &amp; payments</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
@@ -8957,47 +8953,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F56" s="10" t="inlineStr">
+      <c r="F56" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G56" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G56" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>PC-078</t>
+          <t>PC-073</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr"/>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>PDF viewer component exists (R-388).</t>
+          <t>Checkout exists (R-512).</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>HP-pwa</t>
+          <t>HP-pdf-documents</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack pwa: Installable app, service worker, offline, push, QR</t>
+          <t>Horizontal pack pdf-documents: Document templates, PDF generation, document store</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>spec</t>
+          <t>new (registry dependencies 'documents', 'pdf-generation')</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>UI &amp; experience</t>
+          <t>Data &amp; storage</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
@@ -9005,37 +9001,37 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F57" s="10" t="inlineStr">
+      <c r="F57" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G57" s="6" t="inlineStr">
-        <is>
-          <t>P0</t>
+      <c r="G57" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>PC-073</t>
+          <t>PC-078</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr"/>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>R-573.</t>
+          <t>PDF viewer component exists (R-388).</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>HP-ratings-reviews</t>
+          <t>HP-pwa</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack ratings-reviews: Stars, reviews, moderation, aggregates</t>
+          <t>Horizontal pack pwa: Installable app, service worker, offline, push, QR</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -9045,7 +9041,7 @@
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Business logic &amp; workflow</t>
+          <t>UI &amp; experience</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
@@ -9053,47 +9049,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F58" s="10" t="inlineStr">
+      <c r="F58" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G58" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>PC-078</t>
+          <t>PC-073</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr"/>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>Rating component exists (R-333).</t>
+          <t>R-573.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>HP-rich-text</t>
+          <t>HP-ratings-reviews</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack rich-text: Rich text editor, mentions, slash commands</t>
+          <t>Horizontal pack ratings-reviews: Stars, reviews, moderation, aggregates</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>registry</t>
+          <t>spec</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>UI &amp; experience</t>
+          <t>Business logic &amp; workflow</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -9101,7 +9097,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F59" s="10" t="inlineStr">
+      <c r="F59" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9119,29 +9115,29 @@
       <c r="I59" s="3" t="inlineStr"/>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>Markdown editor exists (R-365).</t>
+          <t>Rating component exists (R-333).</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>HP-scheduling</t>
+          <t>HP-rich-text</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack scheduling: Calendars, recurrence, conflicts, time zones, bookings, reminders</t>
+          <t>Horizontal pack rich-text: Rich text editor, mentions, slash commands</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>spec, registry</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Business logic &amp; workflow</t>
+          <t>UI &amp; experience</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
@@ -9149,37 +9145,37 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F60" s="10" t="inlineStr">
+      <c r="F60" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G60" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G60" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>PC-073</t>
+          <t>PC-078</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr"/>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>Calendar/time-picker components exist (R-366, R-371).</t>
+          <t>Markdown editor exists (R-365).</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>HP-search-engine</t>
+          <t>HP-scheduling</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack search-engine: Meilisearch/Typesense, facets, typo tolerance</t>
+          <t>Horizontal pack scheduling: Calendars, recurrence, conflicts, time zones, bookings, reminders</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -9189,7 +9185,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Data &amp; storage</t>
+          <t>Business logic &amp; workflow</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
@@ -9197,47 +9193,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F61" s="10" t="inlineStr">
+      <c r="F61" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G61" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="G61" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>PC-079</t>
+          <t>PC-073</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr"/>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>Keyword search exists (R-261); PC-058.</t>
+          <t>Calendar/time-picker components exist (R-366, R-371).</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>HP-secrets</t>
+          <t>HP-search-engine</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack secrets: Secret management, rotation, audit</t>
+          <t>Horizontal pack search-engine: Meilisearch/Typesense, facets, typo tolerance</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>spec</t>
+          <t>spec, registry</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>Security &amp; compliance</t>
+          <t>Data &amp; storage</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
@@ -9245,47 +9241,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F62" s="10" t="inlineStr">
+      <c r="F62" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G62" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G62" s="12" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>PC-078</t>
+          <t>PC-079</t>
         </is>
       </c>
       <c r="I62" s="3" t="inlineStr"/>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>Platform secrets exist (R-503).</t>
+          <t>Keyword search exists (R-261); PC-058.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>HP-seo</t>
+          <t>HP-secrets</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack seo: Metadata, sitemaps, structured data, AI-search readiness</t>
+          <t>Horizontal pack secrets: Secret management, rotation, audit</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>new (registry dependency)</t>
+          <t>spec</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>UI &amp; experience</t>
+          <t>Security &amp; compliance</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
@@ -9293,7 +9289,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F63" s="10" t="inlineStr">
+      <c r="F63" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9311,29 +9307,29 @@
       <c r="I63" s="3" t="inlineStr"/>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>SEO exists (R-505).</t>
+          <t>Platform secrets exist (R-503).</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>HP-task-management</t>
+          <t>HP-seo</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack task-management: Tasks, assignees, due dates, boards</t>
+          <t>Horizontal pack seo: Metadata, sitemaps, structured data, AI-search readiness</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>new (registry dependency 'tasks')</t>
+          <t>new (registry dependency)</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>Business logic &amp; workflow</t>
+          <t>UI &amp; experience</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
@@ -9341,7 +9337,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F64" s="10" t="inlineStr">
+      <c r="F64" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9359,29 +9355,29 @@
       <c r="I64" s="3" t="inlineStr"/>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>Kanban component exists (R-367).</t>
+          <t>SEO exists (R-505).</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>HP-theming-branding</t>
+          <t>HP-task-management</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack theming-branding: Brand kit applied to every surface</t>
+          <t>Horizontal pack task-management: Tasks, assignees, due dates, boards</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>new (registry dependency 'tasks')</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>UI &amp; experience</t>
+          <t>Business logic &amp; workflow</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
@@ -9389,7 +9385,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F65" s="10" t="inlineStr">
+      <c r="F65" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9407,29 +9403,29 @@
       <c r="I65" s="3" t="inlineStr"/>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>brand.json exists (R-548); PC-020.</t>
+          <t>Kanban component exists (R-367).</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>HP-webhooks</t>
+          <t>HP-theming-branding</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack webhooks: Outgoing webhooks, retries, signatures, replay</t>
+          <t>Horizontal pack theming-branding: Brand kit applied to every surface</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>spec, registry</t>
+          <t>new</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>Realtime &amp; communication</t>
+          <t>UI &amp; experience</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
@@ -9437,7 +9433,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F66" s="10" t="inlineStr">
+      <c r="F66" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9455,19 +9451,19 @@
       <c r="I66" s="3" t="inlineStr"/>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>Cross-surface webhooks exist (R-448); PC-057.</t>
+          <t>brand.json exists (R-548); PC-020.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>HP-workflows-core</t>
+          <t>HP-webhooks</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack workflows-core: State machines, transitions, guards, actions, audit</t>
+          <t>Horizontal pack webhooks: Outgoing webhooks, retries, signatures, replay</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -9477,7 +9473,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>Business logic &amp; workflow</t>
+          <t>Realtime &amp; communication</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
@@ -9485,51 +9481,55 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F67" s="10" t="inlineStr">
+      <c r="F67" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G67" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G67" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H67" s="3" t="inlineStr">
         <is>
-          <t>PC-073</t>
+          <t>PC-078</t>
         </is>
       </c>
       <c r="I67" s="3" t="inlineStr"/>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>Transitions done (R-566, R-588, R-589); guards R-571; buttons R-590.</t>
+          <t>Cross-surface webhooks exist (R-448); PC-057.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>PG-17</t>
+          <t>HP-workflows-core</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>A fresh AI/developer session resumes the task from Git + durable state</t>
+          <t>Horizontal pack workflows-core: State machines, transitions, guards, actions, audit</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>Tracker Production_Gates</t>
-        </is>
-      </c>
-      <c r="D68" s="3" t="inlineStr"/>
+          <t>spec, registry</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Business logic &amp; workflow</t>
+        </is>
+      </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>4 Production ops</t>
-        </is>
-      </c>
-      <c r="F68" s="10" t="inlineStr">
+          <t>2 Maximum features</t>
+        </is>
+      </c>
+      <c r="F68" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9541,25 +9541,25 @@
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>PC-067</t>
+          <t>PC-073</t>
         </is>
       </c>
       <c r="I68" s="3" t="inlineStr"/>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>AGENTS.md, CURRENT_TASK.yaml and this queue exist; the formal drill does not.</t>
+          <t>Transitions done (R-566, R-588, R-589); guards R-571; buttons R-590.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>PG-19</t>
+          <t>PG-17</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Local model endpoint exposure/auth/network policy</t>
+          <t>A fresh AI/developer session resumes the task from Git + durable state</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
@@ -9570,10 +9570,10 @@
       <c r="D69" s="3" t="inlineStr"/>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>1 Vibe Mode live</t>
-        </is>
-      </c>
-      <c r="F69" s="10" t="inlineStr">
+          <t>4 Production ops</t>
+        </is>
+      </c>
+      <c r="F69" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9585,43 +9585,39 @@
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>PC-014</t>
+          <t>PC-067</t>
         </is>
       </c>
       <c r="I69" s="3" t="inlineStr"/>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>Ollama is loopback-only (R-003).</t>
+          <t>AGENTS.md, CURRENT_TASK.yaml and this queue exist; the formal drill does not.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>R-027</t>
+          <t>PG-19</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>pgvector initially</t>
+          <t>Local model endpoint exposure/auth/network policy</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>Execution_Tracker_v6</t>
-        </is>
-      </c>
-      <c r="D70" s="3" t="inlineStr">
-        <is>
-          <t>Data</t>
-        </is>
-      </c>
+          <t>Tracker Production_Gates</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr"/>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>3 Engineering Mode</t>
-        </is>
-      </c>
-      <c r="F70" s="10" t="inlineStr">
+          <t>1 Vibe Mode live</t>
+        </is>
+      </c>
+      <c r="F70" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9633,25 +9629,25 @@
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>R-581</t>
+          <t>PC-014</t>
         </is>
       </c>
       <c r="I70" s="3" t="inlineStr"/>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>Extension installed, no embeddings table.</t>
+          <t>Ollama is loopback-only (R-003).</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>R-040</t>
+          <t>R-027</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>Migration safety checks</t>
+          <t>pgvector initially</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -9661,15 +9657,15 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>4 Production ops</t>
-        </is>
-      </c>
-      <c r="F71" s="10" t="inlineStr">
+          <t>3 Engineering Mode</t>
+        </is>
+      </c>
+      <c r="F71" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9681,21 +9677,25 @@
       </c>
       <c r="H71" s="3" t="inlineStr">
         <is>
-          <t>PC-036</t>
+          <t>R-581</t>
         </is>
       </c>
       <c r="I71" s="3" t="inlineStr"/>
-      <c r="J71" s="3" t="inlineStr"/>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>Extension installed, no embeddings table.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>R-055</t>
+          <t>R-040</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>Verified integration catalog</t>
+          <t>Migration safety checks</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -9705,15 +9705,15 @@
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>Integrations</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>1 Vibe Mode live</t>
-        </is>
-      </c>
-      <c r="F72" s="10" t="inlineStr">
+          <t>4 Production ops</t>
+        </is>
+      </c>
+      <c r="F72" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9725,7 +9725,7 @@
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>PC-013</t>
+          <t>PC-036</t>
         </is>
       </c>
       <c r="I72" s="3" t="inlineStr"/>
@@ -9734,12 +9734,12 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>R-062</t>
+          <t>R-055</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>App Store / TestFlight automation</t>
+          <t>Verified integration catalog</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -9749,7 +9749,7 @@
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>Deployment</t>
+          <t>Integrations</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
@@ -9757,7 +9757,7 @@
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="F73" s="10" t="inlineStr">
+      <c r="F73" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9769,25 +9769,21 @@
       </c>
       <c r="H73" s="3" t="inlineStr">
         <is>
-          <t>R-574</t>
+          <t>PC-013</t>
         </is>
       </c>
       <c r="I73" s="3" t="inlineStr"/>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>React Native first; native reuses the pipeline (PC-044).</t>
-        </is>
-      </c>
+      <c r="J73" s="3" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>R-063</t>
+          <t>R-062</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>Play Store automation</t>
+          <t>App Store / TestFlight automation</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -9805,7 +9801,7 @@
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="F74" s="10" t="inlineStr">
+      <c r="F74" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9830,12 +9826,12 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>R-064</t>
+          <t>R-063</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>RBAC + approvals</t>
+          <t>Play Store automation</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -9845,41 +9841,45 @@
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Deployment</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>3 Engineering Mode</t>
-        </is>
-      </c>
-      <c r="F75" s="10" t="inlineStr">
+          <t>1 Vibe Mode live</t>
+        </is>
+      </c>
+      <c r="F75" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G75" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G75" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H75" s="3" t="inlineStr">
         <is>
-          <t>PC-029</t>
+          <t>R-574</t>
         </is>
       </c>
       <c r="I75" s="3" t="inlineStr"/>
-      <c r="J75" s="3" t="inlineStr"/>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>React Native first; native reuses the pipeline (PC-044).</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>R-080</t>
+          <t>R-064</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>Self-hosted/local models</t>
+          <t>RBAC + approvals</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -9889,45 +9889,41 @@
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>Models</t>
+          <t>Collaboration</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>1 Vibe Mode live</t>
-        </is>
-      </c>
-      <c r="F76" s="10" t="inlineStr">
+          <t>3 Engineering Mode</t>
+        </is>
+      </c>
+      <c r="F76" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G76" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G76" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>PC-014</t>
+          <t>PC-029</t>
         </is>
       </c>
       <c r="I76" s="3" t="inlineStr"/>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>Ollama adapter exists (R-003, R-006).</t>
-        </is>
-      </c>
+      <c r="J76" s="3" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>R-126</t>
+          <t>R-080</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>Organization &gt; Workspace &gt; Project &gt; Environment model</t>
+          <t>Self-hosted/local models</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
@@ -9937,45 +9933,45 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>Product Foundation</t>
+          <t>Models</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>4 Production ops</t>
-        </is>
-      </c>
-      <c r="F77" s="10" t="inlineStr">
+          <t>1 Vibe Mode live</t>
+        </is>
+      </c>
+      <c r="F77" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G77" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G77" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H77" s="3" t="inlineStr">
         <is>
-          <t>PC-040</t>
+          <t>PC-014</t>
         </is>
       </c>
       <c r="I77" s="3" t="inlineStr"/>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>Org, workspace and project exist (R-499, R-515).</t>
+          <t>Ollama adapter exists (R-003, R-006).</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>R-135</t>
+          <t>R-126</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>Stack selection wizard</t>
+          <t>Organization &gt; Workspace &gt; Project &gt; Environment model</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -9985,41 +9981,45 @@
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>Framework Strategy</t>
+          <t>Product Foundation</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>3 Engineering Mode</t>
-        </is>
-      </c>
-      <c r="F78" s="10" t="inlineStr">
+          <t>4 Production ops</t>
+        </is>
+      </c>
+      <c r="F78" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G78" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G78" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>PC-023</t>
+          <t>PC-040</t>
         </is>
       </c>
       <c r="I78" s="3" t="inlineStr"/>
-      <c r="J78" s="3" t="inlineStr"/>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>Org, workspace and project exist (R-499, R-515).</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>R-194</t>
+          <t>R-135</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>Hybrid BYOK/local mode</t>
+          <t>Stack selection wizard</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
@@ -10029,15 +10029,15 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Framework Strategy</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>1 Vibe Mode live</t>
-        </is>
-      </c>
-      <c r="F79" s="10" t="inlineStr">
+          <t>3 Engineering Mode</t>
+        </is>
+      </c>
+      <c r="F79" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10049,7 +10049,7 @@
       </c>
       <c r="H79" s="3" t="inlineStr">
         <is>
-          <t>PC-014</t>
+          <t>PC-023</t>
         </is>
       </c>
       <c r="I79" s="3" t="inlineStr"/>
@@ -10058,26 +10058,30 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>SPEC-PACK-01</t>
+          <t>R-194</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>Pack manifest v2 schema</t>
+          <t>Hybrid BYOK/local mode</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>specs/pack-framework/01</t>
-        </is>
-      </c>
-      <c r="D80" s="3" t="inlineStr"/>
+          <t>Execution_Tracker_v6</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>Execution</t>
+        </is>
+      </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>2 Maximum features</t>
-        </is>
-      </c>
-      <c r="F80" s="10" t="inlineStr">
+          <t>1 Vibe Mode live</t>
+        </is>
+      </c>
+      <c r="F80" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10089,30 +10093,26 @@
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>PC-017</t>
+          <t>PC-014</t>
         </is>
       </c>
       <c r="I80" s="3" t="inlineStr"/>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>Draft spec (called R-600 inside).</t>
-        </is>
-      </c>
+      <c r="J80" s="3" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>SPEC-PACK-06B</t>
+          <t>SPEC-PACK-01</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>Role-based app generator</t>
+          <t>Pack manifest v2 schema</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>specs/pack-framework/06b</t>
+          <t>specs/pack-framework/01</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr"/>
@@ -10121,7 +10121,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F81" s="10" t="inlineStr">
+      <c r="F81" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10133,30 +10133,30 @@
       </c>
       <c r="H81" s="3" t="inlineStr">
         <is>
-          <t>PC-075</t>
+          <t>PC-017</t>
         </is>
       </c>
       <c r="I81" s="3" t="inlineStr"/>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>R-555 and R-562 build one app per role; the spec asks for more.</t>
+          <t>Draft spec (called R-600 inside).</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>SPEC-PACK-06E</t>
+          <t>SPEC-PACK-06B</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>Rich seed data generator</t>
+          <t>Role-based app generator</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>specs/pack-framework/06e</t>
+          <t>specs/pack-framework/06b</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr"/>
@@ -10165,86 +10165,86 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F82" s="10" t="inlineStr">
+      <c r="F82" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G82" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G82" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>PC-077</t>
+          <t>PC-075</t>
         </is>
       </c>
       <c r="I82" s="3" t="inlineStr"/>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>Seeds exist (R-248); the spec asks for realistic volume.</t>
+          <t>R-555 and R-562 build one app per role; the spec asks for more.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>SPEC-TS-01</t>
+          <t>SPEC-PACK-06E</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>Instant chat -&gt; pretty UI</t>
+          <t>Rich seed data generator</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>specs/table-stakes/01</t>
+          <t>specs/pack-framework/06e</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr"/>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>Delivered</t>
-        </is>
-      </c>
-      <c r="F83" s="10" t="inlineStr">
+          <t>2 Maximum features</t>
+        </is>
+      </c>
+      <c r="F83" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G83" s="6" t="inlineStr">
-        <is>
-          <t>P0</t>
+      <c r="G83" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H83" s="3" t="inlineStr">
         <is>
-          <t>PC-006</t>
+          <t>PC-077</t>
         </is>
       </c>
       <c r="I83" s="3" t="inlineStr"/>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>Draft spec.</t>
+          <t>Seeds exist (R-248); the spec asks for realistic volume.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>SPEC-TS-03</t>
+          <t>SPEC-TS-01</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>One-click deploy</t>
+          <t>Instant chat -&gt; pretty UI</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>specs/table-stakes/03</t>
+          <t>specs/table-stakes/01</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr"/>
@@ -10253,7 +10253,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F84" s="10" t="inlineStr">
+      <c r="F84" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10265,7 +10265,7 @@
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>PC-008</t>
+          <t>PC-006</t>
         </is>
       </c>
       <c r="I84" s="3" t="inlineStr"/>
@@ -10278,60 +10278,56 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>VP-appointments</t>
+          <t>SPEC-TS-03</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>Vertical pack appointments: Appointments, slots, reminders, waitlist</t>
+          <t>One-click deploy</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>registry</t>
-        </is>
-      </c>
-      <c r="D85" s="3" t="inlineStr">
-        <is>
-          <t>Healthcare &amp; life sciences (healthcare-core)</t>
-        </is>
-      </c>
+          <t>specs/table-stakes/03</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr"/>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>2 Maximum features</t>
-        </is>
-      </c>
-      <c r="F85" s="10" t="inlineStr">
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="F85" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G85" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G85" s="6" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="H85" s="3" t="inlineStr">
         <is>
-          <t>PC-074</t>
+          <t>PC-008</t>
         </is>
       </c>
       <c r="I85" s="3" t="inlineStr"/>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>CareClinic template.</t>
+          <t>Draft spec.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>VP-cart-checkout</t>
+          <t>VP-appointments</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>Vertical pack cart-checkout: Cart, coupons, checkout sessions</t>
+          <t>Vertical pack appointments: Appointments, slots, reminders, waitlist</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -10341,7 +10337,7 @@
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>Marketplace &amp; commerce (commerce-core)</t>
+          <t>Healthcare &amp; life sciences (healthcare-core)</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
@@ -10349,7 +10345,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F86" s="10" t="inlineStr">
+      <c r="F86" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10367,19 +10363,19 @@
       <c r="I86" s="3" t="inlineStr"/>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>Bazaar template.</t>
+          <t>CareClinic template.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>VP-commissions</t>
+          <t>VP-cart-checkout</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>Vertical pack commissions: Commission rules, splits, payout cycles</t>
+          <t>Vertical pack cart-checkout: Cart, coupons, checkout sessions</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
@@ -10397,7 +10393,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F87" s="10" t="inlineStr">
+      <c r="F87" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10415,19 +10411,19 @@
       <c r="I87" s="3" t="inlineStr"/>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>Bazaar ledger.</t>
+          <t>Bazaar template.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>VP-dispatch</t>
+          <t>VP-commissions</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>Vertical pack dispatch: Zones, assignment rules, heatmaps</t>
+          <t>Vertical pack commissions: Commission rules, splits, payout cycles</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
@@ -10437,7 +10433,7 @@
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>Mobility &amp; on-demand (mobility-core)</t>
+          <t>Marketplace &amp; commerce (commerce-core)</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
@@ -10445,7 +10441,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F88" s="10" t="inlineStr">
+      <c r="F88" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10463,19 +10459,19 @@
       <c r="I88" s="3" t="inlineStr"/>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>RideNow template (partial).</t>
+          <t>Bazaar ledger.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>VP-drivers</t>
+          <t>VP-dispatch</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>Vertical pack drivers: Drivers, vehicles, documents, earnings</t>
+          <t>Vertical pack dispatch: Zones, assignment rules, heatmaps</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
@@ -10493,7 +10489,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F89" s="10" t="inlineStr">
+      <c r="F89" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10511,19 +10507,19 @@
       <c r="I89" s="3" t="inlineStr"/>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>RideNow template.</t>
+          <t>RideNow template (partial).</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>VP-emr</t>
+          <t>VP-drivers</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>Vertical pack emr: Encounters, notes, diagnoses, vitals</t>
+          <t>Vertical pack drivers: Drivers, vehicles, documents, earnings</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
@@ -10533,7 +10529,7 @@
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>Healthcare &amp; life sciences (healthcare-core)</t>
+          <t>Mobility &amp; on-demand (mobility-core)</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
@@ -10541,7 +10537,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F90" s="10" t="inlineStr">
+      <c r="F90" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10559,19 +10555,19 @@
       <c r="I90" s="3" t="inlineStr"/>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>CareClinic template (partial).</t>
+          <t>RideNow template.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>VP-listings</t>
+          <t>VP-emr</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>Vertical pack listings: Listings, categories, variants, media</t>
+          <t>Vertical pack emr: Encounters, notes, diagnoses, vitals</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -10581,7 +10577,7 @@
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>Marketplace &amp; commerce (commerce-core)</t>
+          <t>Healthcare &amp; life sciences (healthcare-core)</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
@@ -10589,7 +10585,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F91" s="10" t="inlineStr">
+      <c r="F91" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10607,24 +10603,24 @@
       <c r="I91" s="3" t="inlineStr"/>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>Bazaar template.</t>
+          <t>CareClinic template (partial).</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>VP-orders</t>
+          <t>VP-listings</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>Vertical pack orders: Orders, line items, timelines</t>
+          <t>Vertical pack listings: Listings, categories, variants, media</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>new (registry dependency)</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
@@ -10637,7 +10633,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F92" s="10" t="inlineStr">
+      <c r="F92" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10662,22 +10658,22 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>VP-patients</t>
+          <t>VP-orders</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>Vertical pack patients: Patients, records, insurance, consent</t>
+          <t>Vertical pack orders: Orders, line items, timelines</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>registry</t>
+          <t>new (registry dependency)</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>Healthcare &amp; life sciences (healthcare-core)</t>
+          <t>Marketplace &amp; commerce (commerce-core)</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
@@ -10685,7 +10681,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F93" s="10" t="inlineStr">
+      <c r="F93" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10703,19 +10699,19 @@
       <c r="I93" s="3" t="inlineStr"/>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>CareClinic template.</t>
+          <t>Bazaar template.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>VP-prescriptions</t>
+          <t>VP-patients</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>Vertical pack prescriptions: Prescriptions, medications, pharmacies</t>
+          <t>Vertical pack patients: Patients, records, insurance, consent</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -10733,7 +10729,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F94" s="10" t="inlineStr">
+      <c r="F94" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10751,19 +10747,19 @@
       <c r="I94" s="3" t="inlineStr"/>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>CareClinic template (partial).</t>
+          <t>CareClinic template.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>VP-providers</t>
+          <t>VP-prescriptions</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>Vertical pack providers: Providers, specialties, licences, schedules</t>
+          <t>Vertical pack prescriptions: Prescriptions, medications, pharmacies</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -10781,7 +10777,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F95" s="10" t="inlineStr">
+      <c r="F95" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10799,19 +10795,19 @@
       <c r="I95" s="3" t="inlineStr"/>
       <c r="J95" s="3" t="inlineStr">
         <is>
-          <t>CareClinic template.</t>
+          <t>CareClinic template (partial).</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>VP-rides</t>
+          <t>VP-providers</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>Vertical pack rides: Rides, routes, fares, matching, receipts</t>
+          <t>Vertical pack providers: Providers, specialties, licences, schedules</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
@@ -10821,7 +10817,7 @@
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>Mobility &amp; on-demand (mobility-core)</t>
+          <t>Healthcare &amp; life sciences (healthcare-core)</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
@@ -10829,7 +10825,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F96" s="10" t="inlineStr">
+      <c r="F96" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10847,19 +10843,19 @@
       <c r="I96" s="3" t="inlineStr"/>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>RideNow template.</t>
+          <t>CareClinic template.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>VP-telehealth</t>
+          <t>VP-rides</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>Vertical pack telehealth: Video consults, consent, technical checks</t>
+          <t>Vertical pack rides: Rides, routes, fares, matching, receipts</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
@@ -10869,7 +10865,7 @@
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>Healthcare &amp; life sciences (healthcare-core)</t>
+          <t>Mobility &amp; on-demand (mobility-core)</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
@@ -10877,7 +10873,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F97" s="10" t="inlineStr">
+      <c r="F97" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10895,19 +10891,19 @@
       <c r="I97" s="3" t="inlineStr"/>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>CareClinic template.</t>
+          <t>RideNow template.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>VP-vendors</t>
+          <t>VP-telehealth</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>Vertical pack vendors: Vendors, storefronts, verification</t>
+          <t>Vertical pack telehealth: Video consults, consent, technical checks</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
@@ -10917,7 +10913,7 @@
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>Marketplace &amp; commerce (commerce-core)</t>
+          <t>Healthcare &amp; life sciences (healthcare-core)</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
@@ -10925,7 +10921,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F98" s="10" t="inlineStr">
+      <c r="F98" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10943,63 +10939,67 @@
       <c r="I98" s="3" t="inlineStr"/>
       <c r="J98" s="3" t="inlineStr">
         <is>
-          <t>Bazaar template.</t>
+          <t>CareClinic template.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>PC-096</t>
+          <t>VP-vendors</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>In-browser WebContainer preview engine behind the PC-007 engine switch (Node in the visitor's browser; licence key supplied at PC-070)</t>
+          <t>Vertical pack vendors: Vendors, storefronts, verification</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>Platform_Completion queue</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>Vibe</t>
+          <t>Marketplace &amp; commerce (commerce-core)</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>1 Vibe Mode live</t>
-        </is>
-      </c>
-      <c r="F99" s="8" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G99" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="H99" s="3" t="inlineStr"/>
+          <t>2 Maximum features</t>
+        </is>
+      </c>
+      <c r="F99" s="11" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G99" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>PC-074</t>
+        </is>
+      </c>
       <c r="I99" s="3" t="inlineStr"/>
       <c r="J99" s="3" t="inlineStr">
         <is>
-          <t>Split out of PC-007 on 2026-09-27: PC-007 delivers the engine switch and the open-source container engine; WebContainer needs StackBlitz's commercial licence (D-6) and runs Node only, so Python/Go APIs still need a server-side engine behind it.</t>
+          <t>Bazaar template.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>PC-097</t>
+          <t>PC-096</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>Compile repair covers every Next surface (admin console and ecosystem role surfaces), not only the main web app</t>
+          <t>In-browser WebContainer preview engine behind the PC-007 engine switch (Node in the visitor's browser; licence key supplied at PC-070)</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
@@ -11009,7 +11009,7 @@
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Vibe</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
@@ -11022,28 +11022,28 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G100" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G100" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H100" s="3" t="inlineStr"/>
       <c r="I100" s="3" t="inlineStr"/>
       <c r="J100" s="3" t="inlineStr">
         <is>
-          <t>Found publishing a clinic app on 2026-09-27: the `provider` role surface shipped a model-written page with an invented import and misused components; the build never checked it. PC-008 now type-checks every Next surface and publish refuses a broken app with the compiler's reason; this task makes the repair loop fix or revert those pages as it does for web.</t>
+          <t>Split out of PC-007 on 2026-09-27: PC-007 delivers the engine switch and the open-source container engine; WebContainer needs StackBlitz's commercial licence (D-6) and runs Node only, so Python/Go APIs still need a server-side engine behind it.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>PC-009</t>
+          <t>PC-097</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>Hosted multi-tenant service: per-user isolation of builds, sessions and previews; quotas; egress policy</t>
+          <t>Compile repair covers every Next surface (admin console and ecosystem role surfaces), not only the main web app</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
@@ -11053,7 +11053,7 @@
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>Platform</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
@@ -11066,16 +11066,16 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G101" s="6" t="inlineStr">
-        <is>
-          <t>P0</t>
+      <c r="G101" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H101" s="3" t="inlineStr"/>
       <c r="I101" s="3" t="inlineStr"/>
       <c r="J101" s="3" t="inlineStr">
         <is>
-          <t>Today the Studio is one trusted operator's tool. Built cloud-neutral and proven locally (Colima); the cloud account (D-2) is plugged in at PC-070.</t>
+          <t>Found publishing a clinic app on 2026-09-27: the `provider` role surface shipped a model-written page with an invented import and misused components; the build never checked it. PC-008 now type-checks every Next surface and publish refuses a broken app with the compiler's reason; this task makes the repair loop fix or revert those pages as it does for web.</t>
         </is>
       </c>
     </row>
@@ -12006,7 +12006,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G123" s="11" t="inlineStr">
+      <c r="G123" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -12050,7 +12050,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G124" s="11" t="inlineStr">
+      <c r="G124" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -12226,7 +12226,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G128" s="11" t="inlineStr">
+      <c r="G128" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -12270,7 +12270,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G129" s="11" t="inlineStr">
+      <c r="G129" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -12314,7 +12314,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G130" s="11" t="inlineStr">
+      <c r="G130" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -12358,7 +12358,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G131" s="11" t="inlineStr">
+      <c r="G131" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -12402,7 +12402,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G132" s="11" t="inlineStr">
+      <c r="G132" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -12490,7 +12490,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G134" s="11" t="inlineStr">
+      <c r="G134" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -12886,7 +12886,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G143" s="11" t="inlineStr">
+      <c r="G143" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -12930,7 +12930,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G144" s="11" t="inlineStr">
+      <c r="G144" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -12974,7 +12974,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G145" s="11" t="inlineStr">
+      <c r="G145" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -14166,7 +14166,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G174" s="11" t="inlineStr">
+      <c r="G174" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -14206,7 +14206,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G175" s="11" t="inlineStr">
+      <c r="G175" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -14250,7 +14250,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G176" s="11" t="inlineStr">
+      <c r="G176" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -14766,7 +14766,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G188" s="11" t="inlineStr">
+      <c r="G188" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -14934,7 +14934,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G192" s="11" t="inlineStr">
+      <c r="G192" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -15498,7 +15498,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G206" s="11" t="inlineStr">
+      <c r="G206" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -15862,7 +15862,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G215" s="11" t="inlineStr">
+      <c r="G215" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -16362,7 +16362,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G227" s="11" t="inlineStr">
+      <c r="G227" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -16586,7 +16586,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G232" s="11" t="inlineStr">
+      <c r="G232" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -16718,7 +16718,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G235" s="11" t="inlineStr">
+      <c r="G235" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -16762,7 +16762,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G236" s="11" t="inlineStr">
+      <c r="G236" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -16986,7 +16986,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G241" s="11" t="inlineStr">
+      <c r="G241" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -17162,7 +17162,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G245" s="11" t="inlineStr">
+      <c r="G245" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -17298,7 +17298,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G248" s="11" t="inlineStr">
+      <c r="G248" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -17386,7 +17386,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G250" s="11" t="inlineStr">
+      <c r="G250" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -17482,7 +17482,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G252" s="11" t="inlineStr">
+      <c r="G252" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -17574,7 +17574,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G254" s="11" t="inlineStr">
+      <c r="G254" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -17618,7 +17618,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G255" s="11" t="inlineStr">
+      <c r="G255" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -17710,7 +17710,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G257" s="11" t="inlineStr">
+      <c r="G257" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -17754,7 +17754,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G258" s="11" t="inlineStr">
+      <c r="G258" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -17934,7 +17934,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G262" s="11" t="inlineStr">
+      <c r="G262" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -18074,7 +18074,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G265" s="11" t="inlineStr">
+      <c r="G265" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -18118,7 +18118,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G266" s="11" t="inlineStr">
+      <c r="G266" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -18526,7 +18526,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G275" s="11" t="inlineStr">
+      <c r="G275" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -18758,7 +18758,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G280" s="11" t="inlineStr">
+      <c r="G280" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -18982,7 +18982,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G285" s="11" t="inlineStr">
+      <c r="G285" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -19026,7 +19026,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G286" s="11" t="inlineStr">
+      <c r="G286" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -19162,7 +19162,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G289" s="11" t="inlineStr">
+      <c r="G289" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -21130,7 +21130,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G335" s="11" t="inlineStr">
+      <c r="G335" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -22898,7 +22898,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G375" s="11" t="inlineStr">
+      <c r="G375" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -22942,7 +22942,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G376" s="11" t="inlineStr">
+      <c r="G376" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -22986,7 +22986,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G377" s="11" t="inlineStr">
+      <c r="G377" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -24786,7 +24786,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G418" s="11" t="inlineStr">
+      <c r="G418" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -24830,7 +24830,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G419" s="11" t="inlineStr">
+      <c r="G419" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -24918,7 +24918,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G421" s="11" t="inlineStr">
+      <c r="G421" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25050,7 +25050,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G424" s="11" t="inlineStr">
+      <c r="G424" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25226,7 +25226,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G428" s="11" t="inlineStr">
+      <c r="G428" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25270,7 +25270,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G429" s="11" t="inlineStr">
+      <c r="G429" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25578,7 +25578,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G436" s="11" t="inlineStr">
+      <c r="G436" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25622,7 +25622,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G437" s="11" t="inlineStr">
+      <c r="G437" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25666,7 +25666,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G438" s="11" t="inlineStr">
+      <c r="G438" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25710,7 +25710,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G439" s="11" t="inlineStr">
+      <c r="G439" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25754,7 +25754,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G440" s="11" t="inlineStr">
+      <c r="G440" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25798,7 +25798,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G441" s="11" t="inlineStr">
+      <c r="G441" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25842,7 +25842,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G442" s="11" t="inlineStr">
+      <c r="G442" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25974,7 +25974,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G445" s="11" t="inlineStr">
+      <c r="G445" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -26106,7 +26106,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G448" s="11" t="inlineStr">
+      <c r="G448" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -26282,7 +26282,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G452" s="11" t="inlineStr">
+      <c r="G452" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -26326,7 +26326,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G453" s="11" t="inlineStr">
+      <c r="G453" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -26502,7 +26502,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G457" s="11" t="inlineStr">
+      <c r="G457" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -26546,7 +26546,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G458" s="11" t="inlineStr">
+      <c r="G458" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -26634,7 +26634,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G460" s="11" t="inlineStr">
+      <c r="G460" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -26810,7 +26810,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G464" s="11" t="inlineStr">
+      <c r="G464" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -26854,7 +26854,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G465" s="11" t="inlineStr">
+      <c r="G465" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -27118,7 +27118,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G471" s="11" t="inlineStr">
+      <c r="G471" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -27162,7 +27162,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G472" s="11" t="inlineStr">
+      <c r="G472" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -27382,7 +27382,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G477" s="11" t="inlineStr">
+      <c r="G477" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -27426,7 +27426,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G478" s="11" t="inlineStr">
+      <c r="G478" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -27470,7 +27470,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G479" s="11" t="inlineStr">
+      <c r="G479" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -27514,7 +27514,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G480" s="11" t="inlineStr">
+      <c r="G480" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -27558,7 +27558,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G481" s="11" t="inlineStr">
+      <c r="G481" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -27602,7 +27602,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G482" s="11" t="inlineStr">
+      <c r="G482" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -27778,7 +27778,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G486" s="11" t="inlineStr">
+      <c r="G486" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -27998,7 +27998,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G491" s="11" t="inlineStr">
+      <c r="G491" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -28086,7 +28086,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G493" s="11" t="inlineStr">
+      <c r="G493" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -28130,7 +28130,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G494" s="11" t="inlineStr">
+      <c r="G494" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -28218,7 +28218,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G496" s="11" t="inlineStr">
+      <c r="G496" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -28438,7 +28438,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G501" s="11" t="inlineStr">
+      <c r="G501" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -28482,7 +28482,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G502" s="11" t="inlineStr">
+      <c r="G502" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -28922,7 +28922,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G512" s="11" t="inlineStr">
+      <c r="G512" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -29186,7 +29186,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G518" s="11" t="inlineStr">
+      <c r="G518" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -29318,7 +29318,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G521" s="11" t="inlineStr">
+      <c r="G521" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -29494,7 +29494,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G525" s="11" t="inlineStr">
+      <c r="G525" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -29538,7 +29538,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G526" s="11" t="inlineStr">
+      <c r="G526" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -29714,7 +29714,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G530" s="11" t="inlineStr">
+      <c r="G530" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -29758,7 +29758,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G531" s="11" t="inlineStr">
+      <c r="G531" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -29846,7 +29846,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G533" s="11" t="inlineStr">
+      <c r="G533" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -29934,7 +29934,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G535" s="11" t="inlineStr">
+      <c r="G535" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30022,7 +30022,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G537" s="11" t="inlineStr">
+      <c r="G537" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30110,7 +30110,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G539" s="11" t="inlineStr">
+      <c r="G539" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30154,7 +30154,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G540" s="11" t="inlineStr">
+      <c r="G540" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30198,7 +30198,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G541" s="11" t="inlineStr">
+      <c r="G541" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30286,7 +30286,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G543" s="11" t="inlineStr">
+      <c r="G543" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30330,7 +30330,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G544" s="11" t="inlineStr">
+      <c r="G544" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30374,7 +30374,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G545" s="11" t="inlineStr">
+      <c r="G545" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30418,7 +30418,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G546" s="11" t="inlineStr">
+      <c r="G546" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30506,7 +30506,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G548" s="11" t="inlineStr">
+      <c r="G548" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30550,7 +30550,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G549" s="11" t="inlineStr">
+      <c r="G549" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30594,7 +30594,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G550" s="11" t="inlineStr">
+      <c r="G550" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30726,7 +30726,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G553" s="11" t="inlineStr">
+      <c r="G553" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30858,7 +30858,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G556" s="11" t="inlineStr">
+      <c r="G556" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30946,7 +30946,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G558" s="11" t="inlineStr">
+      <c r="G558" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -31034,7 +31034,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G560" s="11" t="inlineStr">
+      <c r="G560" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -31122,7 +31122,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G562" s="11" t="inlineStr">
+      <c r="G562" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -31342,7 +31342,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G567" s="11" t="inlineStr">
+      <c r="G567" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -31386,7 +31386,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G568" s="11" t="inlineStr">
+      <c r="G568" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -31474,7 +31474,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G570" s="11" t="inlineStr">
+      <c r="G570" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -31606,7 +31606,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G573" s="11" t="inlineStr">
+      <c r="G573" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -31738,7 +31738,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G576" s="11" t="inlineStr">
+      <c r="G576" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -31826,7 +31826,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G578" s="11" t="inlineStr">
+      <c r="G578" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -31870,7 +31870,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G579" s="11" t="inlineStr">
+      <c r="G579" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -32046,7 +32046,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G583" s="11" t="inlineStr">
+      <c r="G583" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -32090,7 +32090,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G584" s="11" t="inlineStr">
+      <c r="G584" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -32398,7 +32398,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G591" s="11" t="inlineStr">
+      <c r="G591" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -32442,7 +32442,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G592" s="11" t="inlineStr">
+      <c r="G592" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -32486,7 +32486,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G593" s="11" t="inlineStr">
+      <c r="G593" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -32574,7 +32574,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G595" s="11" t="inlineStr">
+      <c r="G595" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -32750,7 +32750,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G599" s="11" t="inlineStr">
+      <c r="G599" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -32882,7 +32882,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G602" s="11" t="inlineStr">
+      <c r="G602" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -32926,7 +32926,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G603" s="11" t="inlineStr">
+      <c r="G603" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -33014,7 +33014,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G605" s="11" t="inlineStr">
+      <c r="G605" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -33102,7 +33102,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G607" s="11" t="inlineStr">
+      <c r="G607" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -33322,7 +33322,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G612" s="11" t="inlineStr">
+      <c r="G612" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -33401,7 +33401,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F614" s="11" t="inlineStr">
+      <c r="F614" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33445,7 +33445,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F615" s="11" t="inlineStr">
+      <c r="F615" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33489,7 +33489,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F616" s="11" t="inlineStr">
+      <c r="F616" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33533,7 +33533,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F617" s="11" t="inlineStr">
+      <c r="F617" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33577,7 +33577,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F618" s="11" t="inlineStr">
+      <c r="F618" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33621,7 +33621,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F619" s="11" t="inlineStr">
+      <c r="F619" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33665,7 +33665,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F620" s="11" t="inlineStr">
+      <c r="F620" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33709,7 +33709,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F621" s="11" t="inlineStr">
+      <c r="F621" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33749,7 +33749,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F622" s="11" t="inlineStr">
+      <c r="F622" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33793,7 +33793,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F623" s="11" t="inlineStr">
+      <c r="F623" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33833,7 +33833,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F624" s="11" t="inlineStr">
+      <c r="F624" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33877,7 +33877,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F625" s="11" t="inlineStr">
+      <c r="F625" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33917,12 +33917,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F626" s="12" t="inlineStr">
+      <c r="F626" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G626" s="11" t="inlineStr">
+      <c r="G626" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -33961,12 +33961,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F627" s="12" t="inlineStr">
+      <c r="F627" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G627" s="11" t="inlineStr">
+      <c r="G627" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34005,12 +34005,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F628" s="12" t="inlineStr">
+      <c r="F628" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G628" s="11" t="inlineStr">
+      <c r="G628" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34049,7 +34049,7 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F629" s="12" t="inlineStr">
+      <c r="F629" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
@@ -34093,12 +34093,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F630" s="12" t="inlineStr">
+      <c r="F630" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G630" s="11" t="inlineStr">
+      <c r="G630" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34137,12 +34137,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F631" s="12" t="inlineStr">
+      <c r="F631" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G631" s="11" t="inlineStr">
+      <c r="G631" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34177,12 +34177,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F632" s="12" t="inlineStr">
+      <c r="F632" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G632" s="11" t="inlineStr">
+      <c r="G632" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34221,12 +34221,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F633" s="12" t="inlineStr">
+      <c r="F633" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G633" s="11" t="inlineStr">
+      <c r="G633" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34265,12 +34265,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F634" s="12" t="inlineStr">
+      <c r="F634" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G634" s="11" t="inlineStr">
+      <c r="G634" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34309,12 +34309,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F635" s="12" t="inlineStr">
+      <c r="F635" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G635" s="11" t="inlineStr">
+      <c r="G635" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34349,12 +34349,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F636" s="12" t="inlineStr">
+      <c r="F636" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G636" s="11" t="inlineStr">
+      <c r="G636" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34393,12 +34393,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F637" s="12" t="inlineStr">
+      <c r="F637" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G637" s="11" t="inlineStr">
+      <c r="G637" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34437,12 +34437,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F638" s="12" t="inlineStr">
+      <c r="F638" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G638" s="11" t="inlineStr">
+      <c r="G638" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34481,12 +34481,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F639" s="12" t="inlineStr">
+      <c r="F639" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G639" s="11" t="inlineStr">
+      <c r="G639" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34525,12 +34525,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F640" s="12" t="inlineStr">
+      <c r="F640" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G640" s="11" t="inlineStr">
+      <c r="G640" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34569,12 +34569,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F641" s="12" t="inlineStr">
+      <c r="F641" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G641" s="11" t="inlineStr">
+      <c r="G641" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34613,12 +34613,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F642" s="12" t="inlineStr">
+      <c r="F642" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G642" s="11" t="inlineStr">
+      <c r="G642" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34657,12 +34657,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F643" s="12" t="inlineStr">
+      <c r="F643" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G643" s="11" t="inlineStr">
+      <c r="G643" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34701,12 +34701,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F644" s="12" t="inlineStr">
+      <c r="F644" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G644" s="11" t="inlineStr">
+      <c r="G644" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34745,12 +34745,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F645" s="12" t="inlineStr">
+      <c r="F645" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G645" s="11" t="inlineStr">
+      <c r="G645" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34789,12 +34789,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F646" s="12" t="inlineStr">
+      <c r="F646" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G646" s="11" t="inlineStr">
+      <c r="G646" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34833,12 +34833,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F647" s="12" t="inlineStr">
+      <c r="F647" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G647" s="11" t="inlineStr">
+      <c r="G647" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34877,12 +34877,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F648" s="12" t="inlineStr">
+      <c r="F648" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G648" s="11" t="inlineStr">
+      <c r="G648" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34921,12 +34921,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F649" s="12" t="inlineStr">
+      <c r="F649" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G649" s="11" t="inlineStr">
+      <c r="G649" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34965,12 +34965,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F650" s="12" t="inlineStr">
+      <c r="F650" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G650" s="11" t="inlineStr">
+      <c r="G650" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35005,12 +35005,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F651" s="12" t="inlineStr">
+      <c r="F651" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G651" s="11" t="inlineStr">
+      <c r="G651" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35049,12 +35049,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F652" s="12" t="inlineStr">
+      <c r="F652" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G652" s="11" t="inlineStr">
+      <c r="G652" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35093,12 +35093,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F653" s="12" t="inlineStr">
+      <c r="F653" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G653" s="11" t="inlineStr">
+      <c r="G653" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35133,12 +35133,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F654" s="12" t="inlineStr">
+      <c r="F654" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G654" s="11" t="inlineStr">
+      <c r="G654" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35177,12 +35177,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F655" s="12" t="inlineStr">
+      <c r="F655" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G655" s="11" t="inlineStr">
+      <c r="G655" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35217,12 +35217,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F656" s="12" t="inlineStr">
+      <c r="F656" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G656" s="11" t="inlineStr">
+      <c r="G656" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35257,12 +35257,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F657" s="12" t="inlineStr">
+      <c r="F657" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G657" s="11" t="inlineStr">
+      <c r="G657" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35297,12 +35297,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F658" s="12" t="inlineStr">
+      <c r="F658" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G658" s="11" t="inlineStr">
+      <c r="G658" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35337,12 +35337,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F659" s="12" t="inlineStr">
+      <c r="F659" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G659" s="11" t="inlineStr">
+      <c r="G659" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35381,12 +35381,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F660" s="12" t="inlineStr">
+      <c r="F660" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G660" s="11" t="inlineStr">
+      <c r="G660" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35425,12 +35425,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F661" s="12" t="inlineStr">
+      <c r="F661" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G661" s="11" t="inlineStr">
+      <c r="G661" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35469,12 +35469,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F662" s="12" t="inlineStr">
+      <c r="F662" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G662" s="11" t="inlineStr">
+      <c r="G662" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35509,12 +35509,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F663" s="12" t="inlineStr">
+      <c r="F663" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G663" s="11" t="inlineStr">
+      <c r="G663" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35549,12 +35549,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F664" s="12" t="inlineStr">
+      <c r="F664" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G664" s="11" t="inlineStr">
+      <c r="G664" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35589,12 +35589,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F665" s="12" t="inlineStr">
+      <c r="F665" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G665" s="11" t="inlineStr">
+      <c r="G665" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35629,12 +35629,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F666" s="12" t="inlineStr">
+      <c r="F666" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G666" s="11" t="inlineStr">
+      <c r="G666" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35669,12 +35669,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F667" s="12" t="inlineStr">
+      <c r="F667" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G667" s="11" t="inlineStr">
+      <c r="G667" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35713,12 +35713,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F668" s="12" t="inlineStr">
+      <c r="F668" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G668" s="11" t="inlineStr">
+      <c r="G668" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35753,12 +35753,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F669" s="12" t="inlineStr">
+      <c r="F669" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G669" s="11" t="inlineStr">
+      <c r="G669" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35793,12 +35793,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F670" s="12" t="inlineStr">
+      <c r="F670" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G670" s="11" t="inlineStr">
+      <c r="G670" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35833,12 +35833,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F671" s="12" t="inlineStr">
+      <c r="F671" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G671" s="11" t="inlineStr">
+      <c r="G671" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35873,12 +35873,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F672" s="12" t="inlineStr">
+      <c r="F672" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G672" s="11" t="inlineStr">
+      <c r="G672" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35917,12 +35917,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F673" s="12" t="inlineStr">
+      <c r="F673" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G673" s="11" t="inlineStr">
+      <c r="G673" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35961,12 +35961,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F674" s="12" t="inlineStr">
+      <c r="F674" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G674" s="11" t="inlineStr">
+      <c r="G674" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -36005,12 +36005,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F675" s="12" t="inlineStr">
+      <c r="F675" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G675" s="11" t="inlineStr">
+      <c r="G675" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -36049,12 +36049,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F676" s="12" t="inlineStr">
+      <c r="F676" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G676" s="11" t="inlineStr">
+      <c r="G676" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -36093,12 +36093,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F677" s="12" t="inlineStr">
+      <c r="F677" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G677" s="11" t="inlineStr">
+      <c r="G677" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -36137,12 +36137,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F678" s="12" t="inlineStr">
+      <c r="F678" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G678" s="11" t="inlineStr">
+      <c r="G678" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -36181,12 +36181,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F679" s="12" t="inlineStr">
+      <c r="F679" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G679" s="11" t="inlineStr">
+      <c r="G679" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -36225,12 +36225,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F680" s="12" t="inlineStr">
+      <c r="F680" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G680" s="11" t="inlineStr">
+      <c r="G680" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -36269,12 +36269,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F681" s="12" t="inlineStr">
+      <c r="F681" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G681" s="11" t="inlineStr">
+      <c r="G681" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -36309,12 +36309,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F682" s="12" t="inlineStr">
+      <c r="F682" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G682" s="11" t="inlineStr">
+      <c r="G682" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -36345,7 +36345,7 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F683" s="13" t="inlineStr">
+      <c r="F683" s="14" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -36385,7 +36385,7 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F684" s="13" t="inlineStr">
+      <c r="F684" s="14" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -36425,7 +36425,7 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F685" s="13" t="inlineStr">
+      <c r="F685" s="14" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -36465,7 +36465,7 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F686" s="13" t="inlineStr">
+      <c r="F686" s="14" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -36505,7 +36505,7 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F687" s="13" t="inlineStr">
+      <c r="F687" s="14" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -36545,7 +36545,7 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F688" s="13" t="inlineStr">
+      <c r="F688" s="14" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -36585,7 +36585,7 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F689" s="13" t="inlineStr">
+      <c r="F689" s="14" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -36625,7 +36625,7 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F690" s="13" t="inlineStr">
+      <c r="F690" s="14" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -36665,7 +36665,7 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F691" s="13" t="inlineStr">
+      <c r="F691" s="14" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -38633,7 +38633,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F736" s="14" t="inlineStr">
+      <c r="F736" s="15" t="inlineStr">
         <is>
           <t>Completed - needs live proof</t>
         </is>
@@ -51249,7 +51249,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F1055" s="14" t="inlineStr">
+      <c r="F1055" s="15" t="inlineStr">
         <is>
           <t>Completed - needs live proof</t>
         </is>
@@ -51297,7 +51297,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F1056" s="14" t="inlineStr">
+      <c r="F1056" s="15" t="inlineStr">
         <is>
           <t>Completed - needs live proof</t>
         </is>
@@ -51345,7 +51345,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F1057" s="14" t="inlineStr">
+      <c r="F1057" s="15" t="inlineStr">
         <is>
           <t>Completed - needs live proof</t>
         </is>
@@ -51393,7 +51393,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F1058" s="14" t="inlineStr">
+      <c r="F1058" s="15" t="inlineStr">
         <is>
           <t>Completed - needs live proof</t>
         </is>
@@ -51441,7 +51441,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F1059" s="14" t="inlineStr">
+      <c r="F1059" s="15" t="inlineStr">
         <is>
           <t>Completed - needs live proof</t>
         </is>
@@ -51561,7 +51561,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F1062" s="14" t="inlineStr">
+      <c r="F1062" s="15" t="inlineStr">
         <is>
           <t>Completed - needs live proof</t>
         </is>
@@ -52693,7 +52693,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F1093" s="14" t="inlineStr">
+      <c r="F1093" s="15" t="inlineStr">
         <is>
           <t>Completed - needs live proof</t>
         </is>
@@ -53690,62 +53690,62 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="B1" s="15" t="inlineStr">
+      <c r="B1" s="16" t="inlineStr">
         <is>
           <t>0 Foundation</t>
         </is>
       </c>
-      <c r="C1" s="15" t="inlineStr">
+      <c r="C1" s="16" t="inlineStr">
         <is>
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="D1" s="15" t="inlineStr">
+      <c r="D1" s="16" t="inlineStr">
         <is>
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="E1" s="15" t="inlineStr">
+      <c r="E1" s="16" t="inlineStr">
         <is>
           <t>3 Engineering Mode</t>
         </is>
       </c>
-      <c r="F1" s="15" t="inlineStr">
+      <c r="F1" s="16" t="inlineStr">
         <is>
           <t>4 Production ops</t>
         </is>
       </c>
-      <c r="G1" s="15" t="inlineStr">
+      <c r="G1" s="16" t="inlineStr">
         <is>
           <t>5 Native mobile (last)</t>
         </is>
       </c>
-      <c r="H1" s="15" t="inlineStr">
+      <c r="H1" s="16" t="inlineStr">
         <is>
           <t>6 Go-live (credentials last)</t>
         </is>
       </c>
-      <c r="I1" s="15" t="inlineStr">
+      <c r="I1" s="16" t="inlineStr">
         <is>
           <t>7 Win the category</t>
         </is>
       </c>
-      <c r="J1" s="15" t="inlineStr">
+      <c r="J1" s="16" t="inlineStr">
         <is>
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="K1" s="15" t="inlineStr">
+      <c r="K1" s="16" t="inlineStr">
         <is>
           <t>Delivered</t>
         </is>
       </c>
-      <c r="L1" s="15" t="inlineStr">
+      <c r="L1" s="16" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
@@ -53841,7 +53841,7 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -53868,7 +53868,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -53921,7 +53921,7 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D6" t="n">
         <v>336</v>
@@ -53948,7 +53948,7 @@
         <v>9</v>
       </c>
       <c r="L6" t="n">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="7">
@@ -54112,62 +54112,62 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Open queue by priority</t>
         </is>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>0 Foundation</t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="D12" s="15" t="inlineStr">
+      <c r="D12" s="16" t="inlineStr">
         <is>
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="E12" s="15" t="inlineStr">
+      <c r="E12" s="16" t="inlineStr">
         <is>
           <t>3 Engineering Mode</t>
         </is>
       </c>
-      <c r="F12" s="15" t="inlineStr">
+      <c r="F12" s="16" t="inlineStr">
         <is>
           <t>4 Production ops</t>
         </is>
       </c>
-      <c r="G12" s="15" t="inlineStr">
+      <c r="G12" s="16" t="inlineStr">
         <is>
           <t>5 Native mobile (last)</t>
         </is>
       </c>
-      <c r="H12" s="15" t="inlineStr">
+      <c r="H12" s="16" t="inlineStr">
         <is>
           <t>6 Go-live (credentials last)</t>
         </is>
       </c>
-      <c r="I12" s="15" t="inlineStr">
+      <c r="I12" s="16" t="inlineStr">
         <is>
           <t>7 Win the category</t>
         </is>
       </c>
-      <c r="J12" s="15" t="inlineStr">
+      <c r="J12" s="16" t="inlineStr">
         <is>
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="K12" s="15" t="inlineStr">
+      <c r="K12" s="16" t="inlineStr">
         <is>
           <t>Delivered</t>
         </is>
       </c>
-      <c r="L12" s="15" t="inlineStr">
+      <c r="L12" s="16" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
@@ -55482,7 +55482,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="F2" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -55586,7 +55586,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -55638,7 +55638,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F5" s="10" t="inlineStr">
+      <c r="F5" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -55690,7 +55690,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -55742,7 +55742,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F7" s="10" t="inlineStr">
+      <c r="F7" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -55794,7 +55794,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="F8" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -55942,7 +55942,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="F11" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -56046,7 +56046,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="F13" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -56103,7 +56103,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G14" s="11" t="inlineStr">
+      <c r="G14" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -56146,7 +56146,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F15" s="10" t="inlineStr">
+      <c r="F15" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -56398,7 +56398,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F20" s="10" t="inlineStr">
+      <c r="F20" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -56502,7 +56502,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F22" s="10" t="inlineStr">
+      <c r="F22" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -56607,7 +56607,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G24" s="11" t="inlineStr">
+      <c r="G24" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -56751,7 +56751,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G27" s="11" t="inlineStr">
+      <c r="G27" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -56898,12 +56898,12 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F30" s="10" t="inlineStr">
+      <c r="F30" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G30" s="11" t="inlineStr">
+      <c r="G30" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -56955,7 +56955,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G31" s="11" t="inlineStr">
+      <c r="G31" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -56998,7 +56998,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F32" s="10" t="inlineStr">
+      <c r="F32" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -57050,7 +57050,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F33" s="10" t="inlineStr">
+      <c r="F33" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -57102,7 +57102,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F34" s="10" t="inlineStr">
+      <c r="F34" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -57207,7 +57207,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G36" s="11" t="inlineStr">
+      <c r="G36" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -57255,7 +57255,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G37" s="11" t="inlineStr">
+      <c r="G37" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -57398,7 +57398,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F40" s="10" t="inlineStr">
+      <c r="F40" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -57450,7 +57450,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F41" s="10" t="inlineStr">
+      <c r="F41" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -57502,7 +57502,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F42" s="10" t="inlineStr">
+      <c r="F42" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -57602,7 +57602,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F44" s="10" t="inlineStr">
+      <c r="F44" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -57702,7 +57702,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F46" s="10" t="inlineStr">
+      <c r="F46" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -57806,7 +57806,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F48" s="10" t="inlineStr">
+      <c r="F48" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -57954,7 +57954,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F51" s="10" t="inlineStr">
+      <c r="F51" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -58054,7 +58054,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F53" s="10" t="inlineStr">
+      <c r="F53" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -58159,7 +58159,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G55" s="11" t="inlineStr">
+      <c r="G55" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -58254,7 +58254,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F57" s="10" t="inlineStr">
+      <c r="F57" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -58311,7 +58311,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G58" s="11" t="inlineStr">
+      <c r="G58" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -58359,7 +58359,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G59" s="11" t="inlineStr">
+      <c r="G59" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -58455,7 +58455,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G61" s="11" t="inlineStr">
+      <c r="G61" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -58498,7 +58498,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F62" s="10" t="inlineStr">
+      <c r="F62" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -58759,7 +58759,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G67" s="11" t="inlineStr">
+      <c r="G67" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -58850,7 +58850,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F69" s="10" t="inlineStr">
+      <c r="F69" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -58902,7 +58902,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F70" s="10" t="inlineStr">
+      <c r="F70" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -58954,7 +58954,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F71" s="10" t="inlineStr">
+      <c r="F71" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -59006,7 +59006,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F72" s="10" t="inlineStr">
+      <c r="F72" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -59110,7 +59110,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F74" s="10" t="inlineStr">
+      <c r="F74" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -59162,7 +59162,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F75" s="10" t="inlineStr">
+      <c r="F75" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -59214,7 +59214,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F76" s="10" t="inlineStr">
+      <c r="F76" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -59266,7 +59266,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F77" s="10" t="inlineStr">
+      <c r="F77" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -59370,7 +59370,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F79" s="10" t="inlineStr">
+      <c r="F79" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -59474,7 +59474,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F81" s="10" t="inlineStr">
+      <c r="F81" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -59574,12 +59574,12 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F83" s="10" t="inlineStr">
+      <c r="F83" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G83" s="11" t="inlineStr">
+      <c r="G83" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -59631,7 +59631,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G84" s="11" t="inlineStr">
+      <c r="G84" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -59826,7 +59826,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F88" s="10" t="inlineStr">
+      <c r="F88" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -60074,7 +60074,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F93" s="10" t="inlineStr">
+      <c r="F93" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -60270,12 +60270,12 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F97" s="10" t="inlineStr">
+      <c r="F97" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G97" s="11" t="inlineStr">
+      <c r="G97" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -60327,7 +60327,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G98" s="11" t="inlineStr">
+      <c r="G98" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -60375,7 +60375,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G99" s="11" t="inlineStr">
+      <c r="G99" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -60423,7 +60423,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G100" s="11" t="inlineStr">
+      <c r="G100" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -60518,7 +60518,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F102" s="10" t="inlineStr">
+      <c r="F102" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -60575,7 +60575,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G103" s="11" t="inlineStr">
+      <c r="G103" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -60623,7 +60623,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G104" s="11" t="inlineStr">
+      <c r="G104" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -60671,7 +60671,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G105" s="11" t="inlineStr">
+      <c r="G105" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -60719,7 +60719,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G106" s="11" t="inlineStr">
+      <c r="G106" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -60767,7 +60767,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G107" s="11" t="inlineStr">
+      <c r="G107" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -60815,7 +60815,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G108" s="11" t="inlineStr">
+      <c r="G108" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -60910,7 +60910,7 @@
           <t>Patient: App + Web; Doctor / provider: Web + App; Pharmacy / lab: Web; Clinic operator: Admin</t>
         </is>
       </c>
-      <c r="F110" s="10" t="inlineStr">
+      <c r="F110" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -60962,7 +60962,7 @@
           <t>Patient: App + Web; Doctor / provider: Web + App; Pharmacy / lab: Web; Clinic operator: Admin</t>
         </is>
       </c>
-      <c r="F111" s="10" t="inlineStr">
+      <c r="F111" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -61014,7 +61014,7 @@
           <t>Patient: App + Web; Doctor / provider: Web + App; Pharmacy / lab: Web; Clinic operator: Admin</t>
         </is>
       </c>
-      <c r="F112" s="10" t="inlineStr">
+      <c r="F112" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -61066,7 +61066,7 @@
           <t>Patient: App + Web; Doctor / provider: Web + App; Pharmacy / lab: Web; Clinic operator: Admin</t>
         </is>
       </c>
-      <c r="F113" s="10" t="inlineStr">
+      <c r="F113" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -61118,7 +61118,7 @@
           <t>Patient: App + Web; Doctor / provider: Web + App; Pharmacy / lab: Web; Clinic operator: Admin</t>
         </is>
       </c>
-      <c r="F114" s="10" t="inlineStr">
+      <c r="F114" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -61218,7 +61218,7 @@
           <t>Patient: App + Web; Doctor / provider: Web + App; Pharmacy / lab: Web; Clinic operator: Admin</t>
         </is>
       </c>
-      <c r="F116" s="10" t="inlineStr">
+      <c r="F116" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -61606,7 +61606,7 @@
           <t>Rider: App + Web; Driver: App; Dispatcher: Web; Operator: Admin</t>
         </is>
       </c>
-      <c r="F124" s="10" t="inlineStr">
+      <c r="F124" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -61658,7 +61658,7 @@
           <t>Rider: App + Web; Driver: App; Dispatcher: Web; Operator: Admin</t>
         </is>
       </c>
-      <c r="F125" s="10" t="inlineStr">
+      <c r="F125" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -61710,7 +61710,7 @@
           <t>Rider: App + Web; Driver: App; Dispatcher: Web; Operator: Admin</t>
         </is>
       </c>
-      <c r="F126" s="10" t="inlineStr">
+      <c r="F126" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -62146,7 +62146,7 @@
           <t>Buyer: App + Web; Seller / vendor: Web + App; Marketplace operator: Admin</t>
         </is>
       </c>
-      <c r="F135" s="10" t="inlineStr">
+      <c r="F135" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -62198,7 +62198,7 @@
           <t>Buyer: App + Web; Seller / vendor: Web + App; Marketplace operator: Admin</t>
         </is>
       </c>
-      <c r="F136" s="10" t="inlineStr">
+      <c r="F136" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -62250,7 +62250,7 @@
           <t>Buyer: App + Web; Seller / vendor: Web + App; Marketplace operator: Admin</t>
         </is>
       </c>
-      <c r="F137" s="10" t="inlineStr">
+      <c r="F137" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -62398,7 +62398,7 @@
           <t>Buyer: App + Web; Seller / vendor: Web + App; Marketplace operator: Admin</t>
         </is>
       </c>
-      <c r="F140" s="10" t="inlineStr">
+      <c r="F140" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -62450,7 +62450,7 @@
           <t>Buyer: App + Web; Seller / vendor: Web + App; Marketplace operator: Admin</t>
         </is>
       </c>
-      <c r="F141" s="10" t="inlineStr">
+      <c r="F141" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -67307,7 +67307,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G242" s="11" t="inlineStr">
+      <c r="G242" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67355,7 +67355,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G243" s="11" t="inlineStr">
+      <c r="G243" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67403,7 +67403,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G244" s="11" t="inlineStr">
+      <c r="G244" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67451,7 +67451,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G245" s="11" t="inlineStr">
+      <c r="G245" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67499,7 +67499,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G246" s="11" t="inlineStr">
+      <c r="G246" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67547,7 +67547,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G247" s="11" t="inlineStr">
+      <c r="G247" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67595,7 +67595,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G248" s="11" t="inlineStr">
+      <c r="G248" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67643,7 +67643,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G249" s="11" t="inlineStr">
+      <c r="G249" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67691,7 +67691,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G250" s="11" t="inlineStr">
+      <c r="G250" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67739,7 +67739,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G251" s="11" t="inlineStr">
+      <c r="G251" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67787,7 +67787,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G252" s="11" t="inlineStr">
+      <c r="G252" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67835,7 +67835,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G253" s="11" t="inlineStr">
+      <c r="G253" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67883,7 +67883,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G254" s="11" t="inlineStr">
+      <c r="G254" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67931,7 +67931,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G255" s="11" t="inlineStr">
+      <c r="G255" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67979,7 +67979,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G256" s="11" t="inlineStr">
+      <c r="G256" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68027,7 +68027,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G257" s="11" t="inlineStr">
+      <c r="G257" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68075,7 +68075,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G258" s="11" t="inlineStr">
+      <c r="G258" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68123,7 +68123,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G259" s="11" t="inlineStr">
+      <c r="G259" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68171,7 +68171,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G260" s="11" t="inlineStr">
+      <c r="G260" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68219,7 +68219,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G261" s="11" t="inlineStr">
+      <c r="G261" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68267,7 +68267,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G262" s="11" t="inlineStr">
+      <c r="G262" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68315,7 +68315,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G263" s="11" t="inlineStr">
+      <c r="G263" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68363,7 +68363,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G264" s="11" t="inlineStr">
+      <c r="G264" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68411,7 +68411,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G265" s="11" t="inlineStr">
+      <c r="G265" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68459,7 +68459,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G266" s="11" t="inlineStr">
+      <c r="G266" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68507,7 +68507,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G267" s="11" t="inlineStr">
+      <c r="G267" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68555,7 +68555,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G268" s="11" t="inlineStr">
+      <c r="G268" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68603,7 +68603,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G269" s="11" t="inlineStr">
+      <c r="G269" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68651,7 +68651,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G270" s="11" t="inlineStr">
+      <c r="G270" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68699,7 +68699,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G271" s="11" t="inlineStr">
+      <c r="G271" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68747,7 +68747,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G272" s="11" t="inlineStr">
+      <c r="G272" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68795,7 +68795,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G273" s="11" t="inlineStr">
+      <c r="G273" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68843,7 +68843,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G274" s="11" t="inlineStr">
+      <c r="G274" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68891,7 +68891,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G275" s="11" t="inlineStr">
+      <c r="G275" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68939,7 +68939,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G276" s="11" t="inlineStr">
+      <c r="G276" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68987,7 +68987,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G277" s="11" t="inlineStr">
+      <c r="G277" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69035,7 +69035,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G278" s="11" t="inlineStr">
+      <c r="G278" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69083,7 +69083,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G279" s="11" t="inlineStr">
+      <c r="G279" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69131,7 +69131,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G280" s="11" t="inlineStr">
+      <c r="G280" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69179,7 +69179,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G281" s="11" t="inlineStr">
+      <c r="G281" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69227,7 +69227,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G282" s="11" t="inlineStr">
+      <c r="G282" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69275,7 +69275,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G283" s="11" t="inlineStr">
+      <c r="G283" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69323,7 +69323,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G284" s="11" t="inlineStr">
+      <c r="G284" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69371,7 +69371,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G285" s="11" t="inlineStr">
+      <c r="G285" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69419,7 +69419,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G286" s="11" t="inlineStr">
+      <c r="G286" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69467,7 +69467,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G287" s="11" t="inlineStr">
+      <c r="G287" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69515,7 +69515,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G288" s="11" t="inlineStr">
+      <c r="G288" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69563,7 +69563,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G289" s="11" t="inlineStr">
+      <c r="G289" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69611,7 +69611,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G290" s="11" t="inlineStr">
+      <c r="G290" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69659,7 +69659,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G291" s="11" t="inlineStr">
+      <c r="G291" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69707,7 +69707,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G292" s="11" t="inlineStr">
+      <c r="G292" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69755,7 +69755,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G293" s="11" t="inlineStr">
+      <c r="G293" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69803,7 +69803,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G294" s="11" t="inlineStr">
+      <c r="G294" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69851,7 +69851,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G295" s="11" t="inlineStr">
+      <c r="G295" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69899,7 +69899,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G296" s="11" t="inlineStr">
+      <c r="G296" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69947,7 +69947,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G297" s="11" t="inlineStr">
+      <c r="G297" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69995,7 +69995,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G298" s="11" t="inlineStr">
+      <c r="G298" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70043,7 +70043,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G299" s="11" t="inlineStr">
+      <c r="G299" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70091,7 +70091,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G300" s="11" t="inlineStr">
+      <c r="G300" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70139,7 +70139,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G301" s="11" t="inlineStr">
+      <c r="G301" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70187,7 +70187,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G302" s="11" t="inlineStr">
+      <c r="G302" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70235,7 +70235,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G303" s="11" t="inlineStr">
+      <c r="G303" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70283,7 +70283,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G304" s="11" t="inlineStr">
+      <c r="G304" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70331,7 +70331,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G305" s="11" t="inlineStr">
+      <c r="G305" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70379,7 +70379,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G306" s="11" t="inlineStr">
+      <c r="G306" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70427,7 +70427,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G307" s="11" t="inlineStr">
+      <c r="G307" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70475,7 +70475,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G308" s="11" t="inlineStr">
+      <c r="G308" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70523,7 +70523,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G309" s="11" t="inlineStr">
+      <c r="G309" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70571,7 +70571,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G310" s="11" t="inlineStr">
+      <c r="G310" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70619,7 +70619,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G311" s="11" t="inlineStr">
+      <c r="G311" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70667,7 +70667,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G312" s="11" t="inlineStr">
+      <c r="G312" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70715,7 +70715,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G313" s="11" t="inlineStr">
+      <c r="G313" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70763,7 +70763,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G314" s="11" t="inlineStr">
+      <c r="G314" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70811,7 +70811,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G315" s="11" t="inlineStr">
+      <c r="G315" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70859,7 +70859,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G316" s="11" t="inlineStr">
+      <c r="G316" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70907,7 +70907,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G317" s="11" t="inlineStr">
+      <c r="G317" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70955,7 +70955,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G318" s="11" t="inlineStr">
+      <c r="G318" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -71003,7 +71003,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G319" s="11" t="inlineStr">
+      <c r="G319" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -71051,7 +71051,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G320" s="11" t="inlineStr">
+      <c r="G320" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -71099,7 +71099,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G321" s="11" t="inlineStr">
+      <c r="G321" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -71147,7 +71147,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G322" s="11" t="inlineStr">
+      <c r="G322" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -71703,7 +71703,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>Completed - needs live proof</t>
         </is>
@@ -71715,7 +71715,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="16" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
@@ -71727,7 +71727,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -71751,7 +71751,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -71763,7 +71763,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
@@ -71775,7 +71775,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -71823,7 +71823,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>

--- a/R_&_D/Platform_Completion/OmniStackAI_Master_Tasks.xlsx
+++ b/R_&_D/Platform_Completion/OmniStackAI_Master_Tasks.xlsx
@@ -92,6 +92,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00BDD7EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFE699"/>
       </patternFill>
     </fill>
@@ -113,11 +118,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2F0D9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00BDD7EE"/>
       </patternFill>
     </fill>
   </fills>
@@ -173,10 +173,10 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1845,9 +1845,9 @@
           <t>Platform</t>
         </is>
       </c>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
@@ -1975,7 +1975,7 @@
           <t>Vibe</t>
         </is>
       </c>
-      <c r="F26" s="10" t="inlineStr">
+      <c r="F26" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2021,7 +2021,7 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="F27" s="10" t="inlineStr">
+      <c r="F27" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2067,7 +2067,7 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="F28" s="10" t="inlineStr">
+      <c r="F28" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2683,7 +2683,7 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="F42" s="10" t="inlineStr">
+      <c r="F42" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2733,7 +2733,7 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="F43" s="10" t="inlineStr">
+      <c r="F43" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2833,7 +2833,7 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="F45" s="10" t="inlineStr">
+      <c r="F45" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2979,7 +2979,7 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="F48" s="10" t="inlineStr">
+      <c r="F48" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -3029,7 +3029,7 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="F49" s="10" t="inlineStr">
+      <c r="F49" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -3184,7 +3184,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G52" s="11" t="inlineStr">
+      <c r="G52" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -3234,7 +3234,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G53" s="11" t="inlineStr">
+      <c r="G53" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -3422,7 +3422,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G57" s="11" t="inlineStr">
+      <c r="G57" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -3464,7 +3464,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G58" s="11" t="inlineStr">
+      <c r="G58" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -3510,7 +3510,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G59" s="11" t="inlineStr">
+      <c r="G59" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -3552,7 +3552,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G60" s="11" t="inlineStr">
+      <c r="G60" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -3594,7 +3594,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G61" s="11" t="inlineStr">
+      <c r="G61" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -3677,7 +3677,7 @@
           <t>Vibe</t>
         </is>
       </c>
-      <c r="F63" s="10" t="inlineStr">
+      <c r="F63" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -3728,7 +3728,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G64" s="11" t="inlineStr">
+      <c r="G64" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -4154,7 +4154,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G73" s="11" t="inlineStr">
+      <c r="G73" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -4200,7 +4200,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G74" s="11" t="inlineStr">
+      <c r="G74" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -4246,7 +4246,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G75" s="11" t="inlineStr">
+      <c r="G75" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -4333,7 +4333,7 @@
           <t>Engineering</t>
         </is>
       </c>
-      <c r="F77" s="10" t="inlineStr">
+      <c r="F77" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -4471,7 +4471,7 @@
           <t>Engineering</t>
         </is>
       </c>
-      <c r="F80" s="10" t="inlineStr">
+      <c r="F80" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -4567,7 +4567,7 @@
           <t>Engineering</t>
         </is>
       </c>
-      <c r="F82" s="10" t="inlineStr">
+      <c r="F82" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -4839,7 +4839,7 @@
           <t>Engineering</t>
         </is>
       </c>
-      <c r="F88" s="10" t="inlineStr">
+      <c r="F88" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -5157,7 +5157,7 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="F95" s="10" t="inlineStr">
+      <c r="F95" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -5802,7 +5802,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G109" s="11" t="inlineStr">
+      <c r="G109" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -5848,7 +5848,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G110" s="11" t="inlineStr">
+      <c r="G110" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -5894,7 +5894,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G111" s="11" t="inlineStr">
+      <c r="G111" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -6462,12 +6462,12 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>PC-013</t>
+          <t>PC-010</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Verified integrations catalog with health tests</t>
+          <t>Credit fairness: estimate before a build, no charge for internal retries, per-task budgets, cost guardrails</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Vibe</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -6487,31 +6487,27 @@
       </c>
       <c r="F2" s="10" t="inlineStr">
         <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr"/>
       <c r="I2" s="3" t="inlineStr"/>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>R-511 Connectors v1 exists.</t>
-        </is>
-      </c>
+      <c r="J2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>PC-014</t>
+          <t>PC-013</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Local/offline models as a first-class path: build fully on Ollama, recommend a model per machine</t>
+          <t>Verified integrations catalog with health tests</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -6521,7 +6517,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Vibe</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -6529,7 +6525,7 @@
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="F3" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6543,19 +6539,19 @@
       <c r="I3" s="3" t="inlineStr"/>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>Ollama adapter exists (R-003/R-006). Found in PC-084: .env names qwen2.5-coder:14b but only 7b is installed, and the adapter refuses a pinned model it was not configured with — detect installed models instead of trusting the setting.</t>
+          <t>R-511 Connectors v1 exists.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>R-574</t>
+          <t>PC-014</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Store publishing for React Native apps: EAS build and submit to Play Store and App Store, proven with real accounts</t>
+          <t>Local/offline models as a first-class path: build fully on Ollama, recommend a model per machine</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -6573,7 +6569,7 @@
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6587,19 +6583,19 @@
       <c r="I4" s="3" t="inlineStr"/>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>R-546/R-547 generate the EAS config. Everything up to the upload is built and tested; the Apple and Google accounts (D-7) are plugged in at PC-070.</t>
+          <t>Ollama adapter exists (R-003/R-006). Found in PC-084: .env names qwen2.5-coder:14b but only 7b is installed, and the adapter refuses a pinned model it was not configured with — detect installed models instead of trusting the setting.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>PC-017</t>
+          <t>R-574</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Pack framework core: manifest v2 schema, registry/loader, composer (merge, wire, validate, conflict rules)</t>
+          <t>Store publishing for React Native apps: EAS build and submit to Play Store and App Store, proven with real accounts</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -6614,10 +6610,10 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>2 Maximum features</t>
-        </is>
-      </c>
-      <c r="F5" s="10" t="inlineStr">
+          <t>1 Vibe Mode live</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6631,19 +6627,19 @@
       <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>Solution Pack manifests, registry and application exist (R-434..R-445); v2 adds ir_delta, state machines, page templates, dependencies. From specs/pack-framework 01, 02.</t>
+          <t>R-546/R-547 generate the EAS config. Everything up to the upload is built and tested; the Apple and Google accounts (D-7) are plugged in at PC-070.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>PC-075</t>
+          <t>PC-017</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Role-based app generator: a complete app per role (nav, pages, API scope, permissions)</t>
+          <t>Pack framework core: manifest v2 schema, registry/loader, composer (merge, wire, validate, conflict rules)</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -6661,7 +6657,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6675,19 +6671,19 @@
       <c r="I6" s="3" t="inlineStr"/>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>R-555/R-562 already build one app per role; the spec asks for role-scoped pages and APIs. From specs/pack-framework/06b.</t>
+          <t>Solution Pack manifests, registry and application exist (R-434..R-445); v2 adds ir_delta, state machines, page templates, dependencies. From specs/pack-framework 01, 02.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>PC-077</t>
+          <t>PC-075</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Rich seed data generator: realistic, domain-aware, deterministic demo data</t>
+          <t>Role-based app generator: a complete app per role (nav, pages, API scope, permissions)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -6705,33 +6701,33 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F7" s="10" t="inlineStr">
+      <c r="F7" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G7" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr"/>
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>Fixture seeds exist (R-248) and must stay deterministic (R-586). From specs/pack-framework/06e.</t>
+          <t>R-555/R-562 already build one app per role; the spec asks for role-scoped pages and APIs. From specs/pack-framework/06b.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>PC-073</t>
+          <t>PC-077</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Horizontal packs, wave 1: the P0/P1 universal packs as manifest v2 packs that work alone and compose (HP-* rows)</t>
+          <t>Rich seed data generator: realistic, domain-aware, deterministic demo data</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -6749,33 +6745,33 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="F8" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr"/>
       <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>Core first (auth, database, API, design system, admin, payments, notifications, files, realtime, workflows), then the mobile &amp; device and AI packs. Each pack packages a capability built by its own task. Full list: PACK_CATALOG.md.</t>
+          <t>Fixture seeds exist (R-248) and must stay deterministic (R-586). From specs/pack-framework/06e.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>PC-074</t>
+          <t>PC-073</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Vertical packs, wave 1: healthcare, mobility, commerce (VP-* rows) on every surface: API, web, app, admin panel</t>
+          <t>Horizontal packs, wave 1: the P0/P1 universal packs as manifest v2 packs that work alone and compose (HP-* rows)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -6793,7 +6789,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr">
+      <c r="F9" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6807,19 +6803,19 @@
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>Built from the CareClinic, RideNow and Bazaar templates.</t>
+          <t>Core first (auth, database, API, design system, admin, payments, notifications, files, realtime, workflows), then the mobile &amp; device and AI packs. Each pack packages a capability built by its own task. Full list: PACK_CATALOG.md.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>PC-020</t>
+          <t>PC-074</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Brand kit / Style DNA UI across all surfaces</t>
+          <t>Vertical packs, wave 1: healthcare, mobility, commerce (VP-* rows) on every surface: API, web, app, admin panel</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -6829,7 +6825,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Vibe</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -6837,33 +6833,33 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G10" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr"/>
       <c r="I10" s="3" t="inlineStr"/>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>brand.json exists (R-548); needs the UI. Buildout idea 'R-526'.</t>
+          <t>Built from the CareClinic, RideNow and Bazaar templates.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>PC-023</t>
+          <t>PC-020</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Stack chooser: pick web/admin/mobile/backend, refused with a reason when unsupported</t>
+          <t>Brand kit / Style DNA UI across all surfaces</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -6873,41 +6869,41 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Vibe</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>3 Engineering Mode</t>
-        </is>
-      </c>
-      <c r="F11" s="10" t="inlineStr">
+          <t>2 Maximum features</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr"/>
       <c r="I11" s="3" t="inlineStr"/>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>R-565 carries the stack in the IR; needs the UI.</t>
+          <t>brand.json exists (R-548); needs the UI. Buildout idea 'R-526'.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>R-579</t>
+          <t>PC-023</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>GitHub import and push-back</t>
+          <t>Stack chooser: pick web/admin/mobile/backend, refused with a reason when unsupported</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -6925,7 +6921,7 @@
           <t>3 Engineering Mode</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr">
+      <c r="F12" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6939,19 +6935,19 @@
       <c r="I12" s="3" t="inlineStr"/>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>R-501 can push a generated project; import is missing.</t>
+          <t>R-565 carries the stack in the IR; needs the UI.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>PC-025</t>
+          <t>R-579</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Verification report view: per-surface compile, tests, security, in the Studio</t>
+          <t>GitHub import and push-back</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -6969,7 +6965,7 @@
           <t>3 Engineering Mode</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="F13" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6983,19 +6979,19 @@
       <c r="I13" s="3" t="inlineStr"/>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>R-560/R-561/R-508 produce the data; nothing shows it as a report.</t>
+          <t>R-501 can push a generated project; import is missing.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>PC-029</t>
+          <t>PC-025</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Team collaboration: roles, approvals, preview comments</t>
+          <t>Verification report view: per-surface compile, tests, security, in the Studio</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -7013,33 +7009,33 @@
           <t>3 Engineering Mode</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr">
+      <c r="F14" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G14" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr"/>
       <c r="I14" s="3" t="inlineStr"/>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>R-515 gives teams.</t>
+          <t>R-560/R-561/R-508 produce the data; nothing shows it as a report.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>PC-036</t>
+          <t>PC-029</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Migration safety checks for generated schema changes</t>
+          <t>Team collaboration: roles, approvals, preview comments</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -7049,55 +7045,59 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>4 Production ops</t>
-        </is>
-      </c>
-      <c r="F15" s="10" t="inlineStr">
+          <t>3 Engineering Mode</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr"/>
       <c r="I15" s="3" t="inlineStr"/>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>R-584 flags data loss; needs a real gate.</t>
+          <t>R-515 gives teams.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>ARCH-DOMAIN-IR</t>
+          <t>PC-036</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Domain IR: guards, business rules, field masks, row filters, page templates</t>
+          <t>Migration safety checks for generated schema changes</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>docs/ARCHITECTURE_MASTER_PLAN.md §5.2</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr"/>
+          <t>Platform_Completion queue</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>2 Maximum features</t>
-        </is>
-      </c>
-      <c r="F16" s="10" t="inlineStr">
+          <t>4 Production ops</t>
+        </is>
+      </c>
+      <c r="F16" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7107,32 +7107,28 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>R-570</t>
-        </is>
-      </c>
+      <c r="H16" s="3" t="inlineStr"/>
       <c r="I16" s="3" t="inlineStr"/>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>State machines done (R-566); field masks and row filters are R-570; guards and rules R-571.</t>
+          <t>R-584 flags data loss; needs a real gate.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>ARCH-GENERATORS</t>
+          <t>ARCH-DOMAIN-IR</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Advanced generators: state machine, role app, page template, shared package, seed data, form wizard, realtime</t>
+          <t>Domain IR: guards, business rules, field masks, row filters, page templates</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>docs/ARCHITECTURE_MASTER_PLAN.md §5.3</t>
+          <t>docs/ARCHITECTURE_MASTER_PLAN.md §5.2</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr"/>
@@ -7141,7 +7137,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F17" s="10" t="inlineStr">
+      <c r="F17" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7153,74 +7149,74 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>PC-017</t>
+          <t>R-570</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr"/>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>State machine done (R-566/588/589); shared package R-572; form wizard PC-059; realtime R-569.</t>
+          <t>State machines done (R-566); field masks and row filters are R-570; guards and rules R-571.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>ARCH-PIPELINE</t>
+          <t>ARCH-GENERATORS</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Vibe pipeline: classify -&gt; select packs -&gt; compose IR -&gt; generate -&gt; provision -&gt; preview in 90 s</t>
+          <t>Advanced generators: state machine, role app, page template, shared package, seed data, form wizard, realtime</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>docs/ARCHITECTURE_MASTER_PLAN.md §4.1</t>
+          <t>docs/ARCHITECTURE_MASTER_PLAN.md §5.3</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr"/>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Delivered</t>
-        </is>
-      </c>
-      <c r="F18" s="10" t="inlineStr">
+          <t>2 Maximum features</t>
+        </is>
+      </c>
+      <c r="F18" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>P0</t>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>PC-004</t>
+          <t>PC-017</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr"/>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>Generate and preview exist; provision is PC-049.</t>
+          <t>State machine done (R-566/588/589); shared package R-572; form wizard PC-059; realtime R-569.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>ARCH-PWA</t>
+          <t>ARCH-PIPELINE</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>PWA / offline support</t>
+          <t>Vibe pipeline: classify -&gt; select packs -&gt; compose IR -&gt; generate -&gt; provision -&gt; preview in 90 s</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>docs/ARCHITECTURE_MASTER_PLAN.md §10 Phase 4</t>
+          <t>docs/ARCHITECTURE_MASTER_PLAN.md §4.1</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr"/>
@@ -7229,7 +7225,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F19" s="10" t="inlineStr">
+      <c r="F19" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7241,47 +7237,51 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>R-573</t>
+          <t>PC-004</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr"/>
-      <c r="J19" s="3" t="inlineStr"/>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>Generate and preview exist; provision is PC-049.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>BP-BRANDKIT</t>
+          <t>ARCH-PWA</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Style DNA UI and brand kit studio</t>
+          <t>PWA / offline support</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Platform_Buildout section 8 ('R-526')</t>
+          <t>docs/ARCHITECTURE_MASTER_PLAN.md §10 Phase 4</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr"/>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>2 Maximum features</t>
-        </is>
-      </c>
-      <c r="F20" s="10" t="inlineStr">
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="F20" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G20" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>PC-020</t>
+          <t>R-573</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr"/>
@@ -7290,70 +7290,66 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>BP-SWITCHER</t>
+          <t>BP-BRANDKIT</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Multi-app ecosystem switcher and persona simulator</t>
+          <t>Style DNA UI and brand kit studio</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Platform_Buildout section 8 ('R-521')</t>
+          <t>Platform_Buildout section 8 ('R-526')</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr"/>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Delivered</t>
-        </is>
-      </c>
-      <c r="F21" s="10" t="inlineStr">
+          <t>2 Maximum features</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>PC-006</t>
+          <t>PC-020</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr"/>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>Multi-app preview exists (R-520, R-553); personas do not.</t>
-        </is>
-      </c>
+      <c r="J21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>GA-03</t>
+          <t>BP-SWITCHER</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>First-class Ollama-compatible provider with quality eval</t>
+          <t>Multi-app ecosystem switcher and persona simulator</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Tracker RND_Gap_Audit</t>
+          <t>Platform_Buildout section 8 ('R-521')</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr"/>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>1 Vibe Mode live</t>
-        </is>
-      </c>
-      <c r="F22" s="10" t="inlineStr">
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="F22" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7365,25 +7361,25 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>PC-014</t>
+          <t>PC-006</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr"/>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>Provider done (R-006); eval missing.</t>
+          <t>Multi-app preview exists (R-520, R-553); personas do not.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>GA-04</t>
+          <t>GA-03</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Per-model safe context registry, no silent truncation</t>
+          <t>First-class Ollama-compatible provider with quality eval</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -7397,7 +7393,7 @@
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="F23" s="10" t="inlineStr">
+      <c r="F23" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7415,19 +7411,19 @@
       <c r="I23" s="3" t="inlineStr"/>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>Safe input budget exists (R-522).</t>
+          <t>Provider done (R-006); eval missing.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>GA-05</t>
+          <t>GA-04</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Route by measured task, eval, latency, context and cost</t>
+          <t>Per-model safe context registry, no silent truncation</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -7441,14 +7437,14 @@
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="F24" s="10" t="inlineStr">
+      <c r="F24" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G24" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -7457,17 +7453,21 @@
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr"/>
-      <c r="J24" s="3" t="inlineStr"/>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>Safe input budget exists (R-522).</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>GA-07</t>
+          <t>GA-05</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Environments local -&gt; test -&gt; preview -&gt; staging -&gt; prod with typed config</t>
+          <t>Route by measured task, eval, latency, context and cost</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -7478,10 +7478,10 @@
       <c r="D25" s="3" t="inlineStr"/>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>4 Production ops</t>
-        </is>
-      </c>
-      <c r="F25" s="10" t="inlineStr">
+          <t>1 Vibe Mode live</t>
+        </is>
+      </c>
+      <c r="F25" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7493,7 +7493,7 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>PC-040</t>
+          <t>PC-014</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr"/>
@@ -7502,12 +7502,12 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>GA-11</t>
+          <t>GA-07</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Pinned supply chain, SBOM/provenance, patch SLA</t>
+          <t>Environments local -&gt; test -&gt; preview -&gt; staging -&gt; prod with typed config</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -7521,7 +7521,7 @@
           <t>4 Production ops</t>
         </is>
       </c>
-      <c r="F26" s="10" t="inlineStr">
+      <c r="F26" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7533,30 +7533,26 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>PC-035</t>
+          <t>PC-040</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr"/>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>Lockfiles pinned; SBOM missing.</t>
-        </is>
-      </c>
+      <c r="J26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>GAP-TESTTOOLS</t>
+          <t>GA-11</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Pin the testing toolchain (Playwright, pytest, go test, k6)</t>
+          <t>Pinned supply chain, SBOM/provenance, patch SLA</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>V6_Review_and_Gap_Analysis section 3</t>
+          <t>Tracker RND_Gap_Audit</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr"/>
@@ -7565,7 +7561,7 @@
           <t>4 Production ops</t>
         </is>
       </c>
-      <c r="F27" s="10" t="inlineStr">
+      <c r="F27" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7577,43 +7573,39 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>PC-037</t>
+          <t>PC-035</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr"/>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>pytest/unittest, go test and Playwright (templates) are in use; k6 is not.</t>
+          <t>Lockfiles pinned; SBOM missing.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>HP-accessibility</t>
+          <t>GAP-TESTTOOLS</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack accessibility: WCAG 2.1 AA, automated axe checks</t>
+          <t>Pin the testing toolchain (Playwright, pytest, go test, k6)</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>spec</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>UI &amp; experience</t>
-        </is>
-      </c>
+          <t>V6_Review_and_Gap_Analysis section 3</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr"/>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>2 Maximum features</t>
-        </is>
-      </c>
-      <c r="F28" s="10" t="inlineStr">
+          <t>4 Production ops</t>
+        </is>
+      </c>
+      <c r="F28" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7625,35 +7617,35 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>PC-078</t>
+          <t>PC-037</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr"/>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>Accessible UI exists (R-296).</t>
+          <t>pytest/unittest, go test and Playwright (templates) are in use; k6 is not.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>HP-activity-feed</t>
+          <t>HP-accessibility</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack activity-feed: Activity streams, timelines, follow/subscribe</t>
+          <t>Horizontal pack accessibility: WCAG 2.1 AA, automated axe checks</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>new (registry dependency)</t>
+          <t>spec</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Realtime &amp; communication</t>
+          <t>UI &amp; experience</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -7661,7 +7653,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F29" s="10" t="inlineStr">
+      <c r="F29" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7679,29 +7671,29 @@
       <c r="I29" s="3" t="inlineStr"/>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>Timeline component exists (R-336).</t>
+          <t>Accessible UI exists (R-296).</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>HP-admin-crud</t>
+          <t>HP-activity-feed</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack admin-crud: Generated admin: tables, filters, bulk actions, exports</t>
+          <t>Horizontal pack activity-feed: Activity streams, timelines, follow/subscribe</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>spec</t>
+          <t>new (registry dependency)</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Core platform</t>
+          <t>Realtime &amp; communication</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -7709,47 +7701,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F30" s="10" t="inlineStr">
+      <c r="F30" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G30" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>PC-073</t>
+          <t>PC-078</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr"/>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>Admin app exists (R-542, R-270, R-271).</t>
+          <t>Timeline component exists (R-336).</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>HP-analytics-events</t>
+          <t>HP-admin-crud</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack analytics-events: Event tracking, funnels, cohorts (PostHog/GA4)</t>
+          <t>Horizontal pack admin-crud: Generated admin: tables, filters, bulk actions, exports</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>spec, registry</t>
+          <t>spec</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Data &amp; storage</t>
+          <t>Core platform</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -7757,47 +7749,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F31" s="10" t="inlineStr">
+      <c r="F31" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G31" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>PC-078</t>
+          <t>PC-073</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr"/>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>Published-app analytics exists (R-513).</t>
+          <t>Admin app exists (R-542, R-270, R-271).</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>HP-api-core</t>
+          <t>HP-analytics-events</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack api-core: REST API, validation, OpenAPI, errors, rate limiting</t>
+          <t>Horizontal pack analytics-events: Event tracking, funnels, cohorts (PostHog/GA4)</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>registry</t>
+          <t>spec, registry</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Core platform</t>
+          <t>Data &amp; storage</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -7805,42 +7797,42 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F32" s="10" t="inlineStr">
+      <c r="F32" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G32" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G32" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>PC-073</t>
+          <t>PC-078</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr"/>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>Python/Go/Node APIs exist (R-229, R-230, R-517).</t>
+          <t>Published-app analytics exists (R-513).</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>HP-api-docs</t>
+          <t>HP-api-core</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack api-docs: OpenAPI, Swagger UI, Postman collection, SDKs</t>
+          <t>Horizontal pack api-core: REST API, validation, OpenAPI, errors, rate limiting</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>spec</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -7853,47 +7845,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F33" s="10" t="inlineStr">
+      <c r="F33" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G33" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>PC-078</t>
+          <t>PC-073</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr"/>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>OpenAPI exists (R-260, R-588).</t>
+          <t>Python/Go/Node APIs exist (R-229, R-230, R-517).</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>HP-app-store-assets</t>
+          <t>HP-api-docs</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack app-store-assets: Icons, splash, screenshots, store listing metadata</t>
+          <t>Horizontal pack api-docs: OpenAPI, Swagger UI, Postman collection, SDKs</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>spec</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Mobile &amp; device (stack-aware: React Native, Kotlin, Swift)</t>
+          <t>Core platform</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -7901,47 +7893,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F34" s="10" t="inlineStr">
+      <c r="F34" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G34" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>PC-073</t>
+          <t>PC-078</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr"/>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>Icons and EAS config exist (R-546, R-547); R-574.</t>
+          <t>OpenAPI exists (R-260, R-588).</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>HP-auth-rbac</t>
+          <t>HP-app-store-assets</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack auth-rbac: Login, register, roles, sessions, MFA, OAuth, passkeys</t>
+          <t>Horizontal pack app-store-assets: Icons, splash, screenshots, store listing metadata</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>spec, registry</t>
+          <t>new</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Core platform</t>
+          <t>Mobile &amp; device (stack-aware: React Native, Kotlin, Swift)</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -7949,7 +7941,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F35" s="10" t="inlineStr">
+      <c r="F35" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7967,29 +7959,29 @@
       <c r="I35" s="3" t="inlineStr"/>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>Auth exists (R-461, R-241..R-243); Go login R-591.</t>
+          <t>Icons and EAS config exist (R-546, R-547); R-574.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>HP-camera-qr</t>
+          <t>HP-auth-rbac</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack camera-qr: Camera, photo/video capture, QR and barcode scanning</t>
+          <t>Horizontal pack auth-rbac: Login, register, roles, sessions, MFA, OAuth, passkeys</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>PRD (+ registry 'barcode')</t>
+          <t>spec, registry</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Mobile &amp; device (stack-aware: React Native, Kotlin, Swift)</t>
+          <t>Core platform</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -7997,7 +7989,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F36" s="10" t="inlineStr">
+      <c r="F36" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8015,29 +8007,29 @@
       <c r="I36" s="3" t="inlineStr"/>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>QR generation exists (R-382).</t>
+          <t>Auth exists (R-461, R-241..R-243); Go login R-591.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>HP-charts-dashboards</t>
+          <t>HP-camera-qr</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack charts-dashboards: Charts, dashboards, live series</t>
+          <t>Horizontal pack camera-qr: Camera, photo/video capture, QR and barcode scanning</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>registry</t>
+          <t>PRD (+ registry 'barcode')</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>UI &amp; experience</t>
+          <t>Mobile &amp; device (stack-aware: React Native, Kotlin, Swift)</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -8045,37 +8037,37 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F37" s="10" t="inlineStr">
+      <c r="F37" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G37" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>PC-078</t>
+          <t>PC-073</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr"/>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>Chart suite exists (R-370).</t>
+          <t>QR generation exists (R-382).</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>HP-ci-cd</t>
+          <t>HP-charts-dashboards</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack ci-cd: CI workflows, containers, Helm, preview environments</t>
+          <t>Horizontal pack charts-dashboards: Charts, dashboards, live series</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -8085,7 +8077,7 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Core platform</t>
+          <t>UI &amp; experience</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -8093,7 +8085,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F38" s="10" t="inlineStr">
+      <c r="F38" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8111,29 +8103,29 @@
       <c r="I38" s="3" t="inlineStr"/>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>CI/CD workflow generation exists (R-452).</t>
+          <t>Chart suite exists (R-370).</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>HP-communications</t>
+          <t>HP-ci-cd</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack communications: 1:1 and group chat, threads, mentions, reactions, attachments</t>
+          <t>Horizontal pack ci-cd: CI workflows, containers, Helm, preview environments</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>spec, registry</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Realtime &amp; communication</t>
+          <t>Core platform</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -8141,7 +8133,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F39" s="10" t="inlineStr">
+      <c r="F39" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8159,29 +8151,29 @@
       <c r="I39" s="3" t="inlineStr"/>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>Chat component exists (R-384).</t>
+          <t>CI/CD workflow generation exists (R-452).</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>HP-config-env</t>
+          <t>HP-communications</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack config-env: Typed env config, secret references, multi-environment</t>
+          <t>Horizontal pack communications: 1:1 and group chat, threads, mentions, reactions, attachments</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>registry</t>
+          <t>spec, registry</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Core platform</t>
+          <t>Realtime &amp; communication</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -8189,7 +8181,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F40" s="10" t="inlineStr">
+      <c r="F40" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8207,29 +8199,29 @@
       <c r="I40" s="3" t="inlineStr"/>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>Credential templates exist (R-547).</t>
+          <t>Chat component exists (R-384).</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>HP-consent-management</t>
+          <t>HP-config-env</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack consent-management: Consent capture and ledger, cookie preferences</t>
+          <t>Horizontal pack config-env: Typed env config, secret references, multi-environment</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>new (registry dependency)</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Security &amp; compliance</t>
+          <t>Core platform</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -8237,7 +8229,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F41" s="10" t="inlineStr">
+      <c r="F41" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8255,29 +8247,29 @@
       <c r="I41" s="3" t="inlineStr"/>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>Cookie consent component exists (R-402).</t>
+          <t>Credential templates exist (R-547).</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>HP-custom-domains</t>
+          <t>HP-consent-management</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack custom-domains: Custom domains, DNS, TLS certificates</t>
+          <t>Horizontal pack consent-management: Consent capture and ledger, cookie preferences</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>new (registry dependency 'dns')</t>
+          <t>new (registry dependency)</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Core platform</t>
+          <t>Security &amp; compliance</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -8285,7 +8277,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F42" s="10" t="inlineStr">
+      <c r="F42" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8303,29 +8295,29 @@
       <c r="I42" s="3" t="inlineStr"/>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>Custom domains exist for published apps (R-510).</t>
+          <t>Cookie consent component exists (R-402).</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>HP-data-import-export</t>
+          <t>HP-custom-domains</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack data-import-export: CSV/Excel import with mapping and validation; bulk export</t>
+          <t>Horizontal pack custom-domains: Custom domains, DNS, TLS certificates</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>new (registry dependency 'dns')</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>Data &amp; storage</t>
+          <t>Core platform</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -8333,7 +8325,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F43" s="10" t="inlineStr">
+      <c r="F43" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8351,29 +8343,29 @@
       <c r="I43" s="3" t="inlineStr"/>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>CSV/JSON export exists (R-271, R-308).</t>
+          <t>Custom domains exist for published apps (R-510).</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>HP-data-tables</t>
+          <t>HP-data-import-export</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack data-tables: Virtualised tables, grouping, column picker, export</t>
+          <t>Horizontal pack data-import-export: CSV/Excel import with mapping and validation; bulk export</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>registry</t>
+          <t>new</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>UI &amp; experience</t>
+          <t>Data &amp; storage</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -8381,7 +8373,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F44" s="10" t="inlineStr">
+      <c r="F44" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8399,19 +8391,19 @@
       <c r="I44" s="3" t="inlineStr"/>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>Data grid exists (R-329).</t>
+          <t>CSV/JSON export exists (R-271, R-308).</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>HP-database-pg</t>
+          <t>HP-data-tables</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack database-pg: PostgreSQL schema, migrations, seeds, row-level security</t>
+          <t>Horizontal pack data-tables: Virtualised tables, grouping, column picker, export</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -8421,7 +8413,7 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Core platform</t>
+          <t>UI &amp; experience</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -8429,37 +8421,37 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F45" s="10" t="inlineStr">
+      <c r="F45" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G45" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G45" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>PC-073</t>
+          <t>PC-078</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr"/>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>Schema/migrations/seeds exist (R-238, R-248).</t>
+          <t>Data grid exists (R-329).</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>HP-design-system</t>
+          <t>HP-database-pg</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack design-system: Design tokens, components, motion, dark mode</t>
+          <t>Horizontal pack database-pg: PostgreSQL schema, migrations, seeds, row-level security</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -8469,7 +8461,7 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>UI &amp; experience</t>
+          <t>Core platform</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -8477,7 +8469,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F46" s="10" t="inlineStr">
+      <c r="F46" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8495,29 +8487,29 @@
       <c r="I46" s="3" t="inlineStr"/>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>Design system exists (R-558, R-324, R-491).</t>
+          <t>Schema/migrations/seeds exist (R-238, R-248).</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>HP-e-sign</t>
+          <t>HP-design-system</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack e-sign: Document signing, signer flows, certificates</t>
+          <t>Horizontal pack design-system: Design tokens, components, motion, dark mode</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>new (registry dependency)</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>Business logic &amp; workflow</t>
+          <t>UI &amp; experience</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -8525,47 +8517,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F47" s="10" t="inlineStr">
+      <c r="F47" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G47" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>PC-078</t>
+          <t>PC-073</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr"/>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>Signature pad exists (R-372).</t>
+          <t>Design system exists (R-558, R-324, R-491).</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>HP-integration-hub</t>
+          <t>HP-e-sign</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack integration-hub: Connectors (Slack, HubSpot, Salesforce ...), workflow builder</t>
+          <t>Horizontal pack e-sign: Document signing, signer flows, certificates</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>registry</t>
+          <t>new (registry dependency)</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Integration &amp; AI</t>
+          <t>Business logic &amp; workflow</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
@@ -8573,7 +8565,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F48" s="10" t="inlineStr">
+      <c r="F48" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8591,29 +8583,29 @@
       <c r="I48" s="3" t="inlineStr"/>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>Connectors v1 exist (R-511).</t>
+          <t>Signature pad exists (R-372).</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>HP-maps-geo</t>
+          <t>HP-integration-hub</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack maps-geo: Maps, geocoding, geofences, routes, address autocomplete</t>
+          <t>Horizontal pack integration-hub: Connectors (Slack, HubSpot, Salesforce ...), workflow builder</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>registry ('mapping', listed under mobility), PRD</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>UI &amp; experience</t>
+          <t>Integration &amp; AI</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -8621,47 +8613,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F49" s="10" t="inlineStr">
+      <c r="F49" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G49" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G49" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>PC-073</t>
+          <t>PC-078</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr"/>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>Geo-map component exists (R-387).</t>
+          <t>Connectors v1 exist (R-511).</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>HP-media-player-device</t>
+          <t>HP-maps-geo</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack media-player-device: Audio/video playback, background audio, casting</t>
+          <t>Horizontal pack maps-geo: Maps, geocoding, geofences, routes, address autocomplete</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>registry ('mapping', listed under mobility), PRD</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Mobile &amp; device (stack-aware: React Native, Kotlin, Swift)</t>
+          <t>UI &amp; experience</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -8669,47 +8661,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F50" s="10" t="inlineStr">
+      <c r="F50" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G50" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>PC-079</t>
+          <t>PC-073</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr"/>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>Web media players exist (R-376, R-390).</t>
+          <t>Geo-map component exists (R-387).</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>HP-multi-app</t>
+          <t>HP-media-player-device</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack multi-app: Shared API, cross-app auth, preview proxy, deploy coordination</t>
+          <t>Horizontal pack media-player-device: Audio/video playback, background audio, casting</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>spec</t>
+          <t>new</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Core platform</t>
+          <t>Mobile &amp; device (stack-aware: React Native, Kotlin, Swift)</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -8717,47 +8709,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F51" s="10" t="inlineStr">
+      <c r="F51" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G51" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G51" s="12" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>PC-073</t>
+          <t>PC-079</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr"/>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>Ecosystem monorepo exists (R-554, R-447, R-553).</t>
+          <t>Web media players exist (R-376, R-390).</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>HP-multi-currency</t>
+          <t>HP-multi-app</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack multi-currency: Currencies, exchange rates, price lists</t>
+          <t>Horizontal pack multi-app: Shared API, cross-app auth, preview proxy, deploy coordination</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>registry (listed under commerce)</t>
+          <t>spec</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Commerce &amp; payments</t>
+          <t>Core platform</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
@@ -8765,47 +8757,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F52" s="10" t="inlineStr">
+      <c r="F52" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G52" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G52" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>PC-078</t>
+          <t>PC-073</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr"/>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>Currency input exists (R-409).</t>
+          <t>Ecosystem monorepo exists (R-554, R-447, R-553).</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>HP-notifications</t>
+          <t>HP-multi-currency</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack notifications: Email, SMS, push, in-app centre, preferences, digests</t>
+          <t>Horizontal pack multi-currency: Currencies, exchange rates, price lists</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>spec, registry</t>
+          <t>registry (listed under commerce)</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Realtime &amp; communication</t>
+          <t>Commerce &amp; payments</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
@@ -8813,47 +8805,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F53" s="10" t="inlineStr">
+      <c r="F53" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G53" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G53" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>PC-073</t>
+          <t>PC-078</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr"/>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>Email exists (R-516); PC-053.</t>
+          <t>Currency input exists (R-409).</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>HP-onboarding-tours</t>
+          <t>HP-notifications</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack onboarding-tours: Product tours and spotlight guides</t>
+          <t>Horizontal pack notifications: Email, SMS, push, in-app centre, preferences, digests</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>spec, registry</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>UI &amp; experience</t>
+          <t>Realtime &amp; communication</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
@@ -8861,47 +8853,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F54" s="10" t="inlineStr">
+      <c r="F54" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G54" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>PC-079</t>
+          <t>PC-073</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr"/>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>Tour component exists (R-363).</t>
+          <t>Email exists (R-516); PC-053.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>HP-payments-core</t>
+          <t>HP-onboarding-tours</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack payments-core: Stripe/Razorpay/Paddle payments, refunds, disputes</t>
+          <t>Horizontal pack onboarding-tours: Product tours and spotlight guides</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>spec, registry, PRD</t>
+          <t>new</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Commerce &amp; payments</t>
+          <t>UI &amp; experience</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -8909,47 +8901,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F55" s="10" t="inlineStr">
+      <c r="F55" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G55" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G55" s="12" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>PC-073</t>
+          <t>PC-079</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr"/>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>Checkout exists (R-512).</t>
+          <t>Tour component exists (R-363).</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>HP-pdf-documents</t>
+          <t>HP-payments-core</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack pdf-documents: Document templates, PDF generation, document store</t>
+          <t>Horizontal pack payments-core: Stripe/Razorpay/Paddle payments, refunds, disputes</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>new (registry dependencies 'documents', 'pdf-generation')</t>
+          <t>spec, registry, PRD</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Data &amp; storage</t>
+          <t>Commerce &amp; payments</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
@@ -8957,47 +8949,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F56" s="10" t="inlineStr">
+      <c r="F56" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G56" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G56" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>PC-078</t>
+          <t>PC-073</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr"/>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>PDF viewer component exists (R-388).</t>
+          <t>Checkout exists (R-512).</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>HP-pwa</t>
+          <t>HP-pdf-documents</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack pwa: Installable app, service worker, offline, push, QR</t>
+          <t>Horizontal pack pdf-documents: Document templates, PDF generation, document store</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>spec</t>
+          <t>new (registry dependencies 'documents', 'pdf-generation')</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>UI &amp; experience</t>
+          <t>Data &amp; storage</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
@@ -9005,37 +8997,37 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F57" s="10" t="inlineStr">
+      <c r="F57" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G57" s="6" t="inlineStr">
-        <is>
-          <t>P0</t>
+      <c r="G57" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>PC-073</t>
+          <t>PC-078</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr"/>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>R-573.</t>
+          <t>PDF viewer component exists (R-388).</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>HP-ratings-reviews</t>
+          <t>HP-pwa</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack ratings-reviews: Stars, reviews, moderation, aggregates</t>
+          <t>Horizontal pack pwa: Installable app, service worker, offline, push, QR</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -9045,7 +9037,7 @@
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Business logic &amp; workflow</t>
+          <t>UI &amp; experience</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
@@ -9053,47 +9045,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F58" s="10" t="inlineStr">
+      <c r="F58" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G58" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>PC-078</t>
+          <t>PC-073</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr"/>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>Rating component exists (R-333).</t>
+          <t>R-573.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>HP-rich-text</t>
+          <t>HP-ratings-reviews</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack rich-text: Rich text editor, mentions, slash commands</t>
+          <t>Horizontal pack ratings-reviews: Stars, reviews, moderation, aggregates</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>registry</t>
+          <t>spec</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>UI &amp; experience</t>
+          <t>Business logic &amp; workflow</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -9101,7 +9093,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F59" s="10" t="inlineStr">
+      <c r="F59" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9119,29 +9111,29 @@
       <c r="I59" s="3" t="inlineStr"/>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>Markdown editor exists (R-365).</t>
+          <t>Rating component exists (R-333).</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>HP-scheduling</t>
+          <t>HP-rich-text</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack scheduling: Calendars, recurrence, conflicts, time zones, bookings, reminders</t>
+          <t>Horizontal pack rich-text: Rich text editor, mentions, slash commands</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>spec, registry</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Business logic &amp; workflow</t>
+          <t>UI &amp; experience</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
@@ -9149,37 +9141,37 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F60" s="10" t="inlineStr">
+      <c r="F60" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G60" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G60" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>PC-073</t>
+          <t>PC-078</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr"/>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>Calendar/time-picker components exist (R-366, R-371).</t>
+          <t>Markdown editor exists (R-365).</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>HP-search-engine</t>
+          <t>HP-scheduling</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack search-engine: Meilisearch/Typesense, facets, typo tolerance</t>
+          <t>Horizontal pack scheduling: Calendars, recurrence, conflicts, time zones, bookings, reminders</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -9189,7 +9181,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Data &amp; storage</t>
+          <t>Business logic &amp; workflow</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
@@ -9197,47 +9189,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F61" s="10" t="inlineStr">
+      <c r="F61" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G61" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="G61" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>PC-079</t>
+          <t>PC-073</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr"/>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>Keyword search exists (R-261); PC-058.</t>
+          <t>Calendar/time-picker components exist (R-366, R-371).</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>HP-secrets</t>
+          <t>HP-search-engine</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack secrets: Secret management, rotation, audit</t>
+          <t>Horizontal pack search-engine: Meilisearch/Typesense, facets, typo tolerance</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>spec</t>
+          <t>spec, registry</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>Security &amp; compliance</t>
+          <t>Data &amp; storage</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
@@ -9245,47 +9237,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F62" s="10" t="inlineStr">
+      <c r="F62" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G62" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G62" s="12" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>PC-078</t>
+          <t>PC-079</t>
         </is>
       </c>
       <c r="I62" s="3" t="inlineStr"/>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>Platform secrets exist (R-503).</t>
+          <t>Keyword search exists (R-261); PC-058.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>HP-seo</t>
+          <t>HP-secrets</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack seo: Metadata, sitemaps, structured data, AI-search readiness</t>
+          <t>Horizontal pack secrets: Secret management, rotation, audit</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>new (registry dependency)</t>
+          <t>spec</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>UI &amp; experience</t>
+          <t>Security &amp; compliance</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
@@ -9293,7 +9285,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F63" s="10" t="inlineStr">
+      <c r="F63" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9311,29 +9303,29 @@
       <c r="I63" s="3" t="inlineStr"/>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>SEO exists (R-505).</t>
+          <t>Platform secrets exist (R-503).</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>HP-task-management</t>
+          <t>HP-seo</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack task-management: Tasks, assignees, due dates, boards</t>
+          <t>Horizontal pack seo: Metadata, sitemaps, structured data, AI-search readiness</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>new (registry dependency 'tasks')</t>
+          <t>new (registry dependency)</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>Business logic &amp; workflow</t>
+          <t>UI &amp; experience</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
@@ -9341,7 +9333,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F64" s="10" t="inlineStr">
+      <c r="F64" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9359,29 +9351,29 @@
       <c r="I64" s="3" t="inlineStr"/>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>Kanban component exists (R-367).</t>
+          <t>SEO exists (R-505).</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>HP-theming-branding</t>
+          <t>HP-task-management</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack theming-branding: Brand kit applied to every surface</t>
+          <t>Horizontal pack task-management: Tasks, assignees, due dates, boards</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>new (registry dependency 'tasks')</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>UI &amp; experience</t>
+          <t>Business logic &amp; workflow</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
@@ -9389,7 +9381,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F65" s="10" t="inlineStr">
+      <c r="F65" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9407,29 +9399,29 @@
       <c r="I65" s="3" t="inlineStr"/>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>brand.json exists (R-548); PC-020.</t>
+          <t>Kanban component exists (R-367).</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>HP-webhooks</t>
+          <t>HP-theming-branding</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack webhooks: Outgoing webhooks, retries, signatures, replay</t>
+          <t>Horizontal pack theming-branding: Brand kit applied to every surface</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>spec, registry</t>
+          <t>new</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>Realtime &amp; communication</t>
+          <t>UI &amp; experience</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
@@ -9437,7 +9429,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F66" s="10" t="inlineStr">
+      <c r="F66" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9455,19 +9447,19 @@
       <c r="I66" s="3" t="inlineStr"/>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>Cross-surface webhooks exist (R-448); PC-057.</t>
+          <t>brand.json exists (R-548); PC-020.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>HP-workflows-core</t>
+          <t>HP-webhooks</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack workflows-core: State machines, transitions, guards, actions, audit</t>
+          <t>Horizontal pack webhooks: Outgoing webhooks, retries, signatures, replay</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -9477,7 +9469,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>Business logic &amp; workflow</t>
+          <t>Realtime &amp; communication</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
@@ -9485,51 +9477,55 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F67" s="10" t="inlineStr">
+      <c r="F67" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G67" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G67" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H67" s="3" t="inlineStr">
         <is>
-          <t>PC-073</t>
+          <t>PC-078</t>
         </is>
       </c>
       <c r="I67" s="3" t="inlineStr"/>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>Transitions done (R-566, R-588, R-589); guards R-571; buttons R-590.</t>
+          <t>Cross-surface webhooks exist (R-448); PC-057.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>PG-17</t>
+          <t>HP-workflows-core</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>A fresh AI/developer session resumes the task from Git + durable state</t>
+          <t>Horizontal pack workflows-core: State machines, transitions, guards, actions, audit</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>Tracker Production_Gates</t>
-        </is>
-      </c>
-      <c r="D68" s="3" t="inlineStr"/>
+          <t>spec, registry</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Business logic &amp; workflow</t>
+        </is>
+      </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>4 Production ops</t>
-        </is>
-      </c>
-      <c r="F68" s="10" t="inlineStr">
+          <t>2 Maximum features</t>
+        </is>
+      </c>
+      <c r="F68" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9541,25 +9537,25 @@
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>PC-067</t>
+          <t>PC-073</t>
         </is>
       </c>
       <c r="I68" s="3" t="inlineStr"/>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>AGENTS.md, CURRENT_TASK.yaml and this queue exist; the formal drill does not.</t>
+          <t>Transitions done (R-566, R-588, R-589); guards R-571; buttons R-590.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>PG-19</t>
+          <t>PG-17</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Local model endpoint exposure/auth/network policy</t>
+          <t>A fresh AI/developer session resumes the task from Git + durable state</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
@@ -9570,10 +9566,10 @@
       <c r="D69" s="3" t="inlineStr"/>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>1 Vibe Mode live</t>
-        </is>
-      </c>
-      <c r="F69" s="10" t="inlineStr">
+          <t>4 Production ops</t>
+        </is>
+      </c>
+      <c r="F69" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9585,43 +9581,39 @@
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>PC-014</t>
+          <t>PC-067</t>
         </is>
       </c>
       <c r="I69" s="3" t="inlineStr"/>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>Ollama is loopback-only (R-003).</t>
+          <t>AGENTS.md, CURRENT_TASK.yaml and this queue exist; the formal drill does not.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>R-027</t>
+          <t>PG-19</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>pgvector initially</t>
+          <t>Local model endpoint exposure/auth/network policy</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>Execution_Tracker_v6</t>
-        </is>
-      </c>
-      <c r="D70" s="3" t="inlineStr">
-        <is>
-          <t>Data</t>
-        </is>
-      </c>
+          <t>Tracker Production_Gates</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr"/>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>3 Engineering Mode</t>
-        </is>
-      </c>
-      <c r="F70" s="10" t="inlineStr">
+          <t>1 Vibe Mode live</t>
+        </is>
+      </c>
+      <c r="F70" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9633,25 +9625,25 @@
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>R-581</t>
+          <t>PC-014</t>
         </is>
       </c>
       <c r="I70" s="3" t="inlineStr"/>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>Extension installed, no embeddings table.</t>
+          <t>Ollama is loopback-only (R-003).</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>R-040</t>
+          <t>R-027</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>Migration safety checks</t>
+          <t>pgvector initially</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -9661,15 +9653,15 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>4 Production ops</t>
-        </is>
-      </c>
-      <c r="F71" s="10" t="inlineStr">
+          <t>3 Engineering Mode</t>
+        </is>
+      </c>
+      <c r="F71" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9681,21 +9673,25 @@
       </c>
       <c r="H71" s="3" t="inlineStr">
         <is>
-          <t>PC-036</t>
+          <t>R-581</t>
         </is>
       </c>
       <c r="I71" s="3" t="inlineStr"/>
-      <c r="J71" s="3" t="inlineStr"/>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>Extension installed, no embeddings table.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>R-055</t>
+          <t>R-040</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>Verified integration catalog</t>
+          <t>Migration safety checks</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -9705,15 +9701,15 @@
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>Integrations</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>1 Vibe Mode live</t>
-        </is>
-      </c>
-      <c r="F72" s="10" t="inlineStr">
+          <t>4 Production ops</t>
+        </is>
+      </c>
+      <c r="F72" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9725,7 +9721,7 @@
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>PC-013</t>
+          <t>PC-036</t>
         </is>
       </c>
       <c r="I72" s="3" t="inlineStr"/>
@@ -9734,12 +9730,12 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>R-062</t>
+          <t>R-055</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>App Store / TestFlight automation</t>
+          <t>Verified integration catalog</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -9749,7 +9745,7 @@
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>Deployment</t>
+          <t>Integrations</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
@@ -9757,7 +9753,7 @@
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="F73" s="10" t="inlineStr">
+      <c r="F73" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9769,25 +9765,21 @@
       </c>
       <c r="H73" s="3" t="inlineStr">
         <is>
-          <t>R-574</t>
+          <t>PC-013</t>
         </is>
       </c>
       <c r="I73" s="3" t="inlineStr"/>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>React Native first; native reuses the pipeline (PC-044).</t>
-        </is>
-      </c>
+      <c r="J73" s="3" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>R-063</t>
+          <t>R-062</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>Play Store automation</t>
+          <t>App Store / TestFlight automation</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -9805,7 +9797,7 @@
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="F74" s="10" t="inlineStr">
+      <c r="F74" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9830,12 +9822,12 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>R-064</t>
+          <t>R-063</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>RBAC + approvals</t>
+          <t>Play Store automation</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -9845,41 +9837,45 @@
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Deployment</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>3 Engineering Mode</t>
-        </is>
-      </c>
-      <c r="F75" s="10" t="inlineStr">
+          <t>1 Vibe Mode live</t>
+        </is>
+      </c>
+      <c r="F75" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G75" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G75" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H75" s="3" t="inlineStr">
         <is>
-          <t>PC-029</t>
+          <t>R-574</t>
         </is>
       </c>
       <c r="I75" s="3" t="inlineStr"/>
-      <c r="J75" s="3" t="inlineStr"/>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>React Native first; native reuses the pipeline (PC-044).</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>R-080</t>
+          <t>R-064</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>Self-hosted/local models</t>
+          <t>RBAC + approvals</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -9889,45 +9885,41 @@
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>Models</t>
+          <t>Collaboration</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>1 Vibe Mode live</t>
-        </is>
-      </c>
-      <c r="F76" s="10" t="inlineStr">
+          <t>3 Engineering Mode</t>
+        </is>
+      </c>
+      <c r="F76" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G76" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G76" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>PC-014</t>
+          <t>PC-029</t>
         </is>
       </c>
       <c r="I76" s="3" t="inlineStr"/>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>Ollama adapter exists (R-003, R-006).</t>
-        </is>
-      </c>
+      <c r="J76" s="3" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>R-126</t>
+          <t>R-080</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>Organization &gt; Workspace &gt; Project &gt; Environment model</t>
+          <t>Self-hosted/local models</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
@@ -9937,45 +9929,45 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>Product Foundation</t>
+          <t>Models</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>4 Production ops</t>
-        </is>
-      </c>
-      <c r="F77" s="10" t="inlineStr">
+          <t>1 Vibe Mode live</t>
+        </is>
+      </c>
+      <c r="F77" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G77" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G77" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H77" s="3" t="inlineStr">
         <is>
-          <t>PC-040</t>
+          <t>PC-014</t>
         </is>
       </c>
       <c r="I77" s="3" t="inlineStr"/>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>Org, workspace and project exist (R-499, R-515).</t>
+          <t>Ollama adapter exists (R-003, R-006).</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>R-135</t>
+          <t>R-126</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>Stack selection wizard</t>
+          <t>Organization &gt; Workspace &gt; Project &gt; Environment model</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -9985,41 +9977,45 @@
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>Framework Strategy</t>
+          <t>Product Foundation</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>3 Engineering Mode</t>
-        </is>
-      </c>
-      <c r="F78" s="10" t="inlineStr">
+          <t>4 Production ops</t>
+        </is>
+      </c>
+      <c r="F78" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G78" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G78" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>PC-023</t>
+          <t>PC-040</t>
         </is>
       </c>
       <c r="I78" s="3" t="inlineStr"/>
-      <c r="J78" s="3" t="inlineStr"/>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>Org, workspace and project exist (R-499, R-515).</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>R-194</t>
+          <t>R-135</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>Hybrid BYOK/local mode</t>
+          <t>Stack selection wizard</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
@@ -10029,15 +10025,15 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Framework Strategy</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>1 Vibe Mode live</t>
-        </is>
-      </c>
-      <c r="F79" s="10" t="inlineStr">
+          <t>3 Engineering Mode</t>
+        </is>
+      </c>
+      <c r="F79" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10049,7 +10045,7 @@
       </c>
       <c r="H79" s="3" t="inlineStr">
         <is>
-          <t>PC-014</t>
+          <t>PC-023</t>
         </is>
       </c>
       <c r="I79" s="3" t="inlineStr"/>
@@ -10058,26 +10054,30 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>SPEC-PACK-01</t>
+          <t>R-194</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>Pack manifest v2 schema</t>
+          <t>Hybrid BYOK/local mode</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>specs/pack-framework/01</t>
-        </is>
-      </c>
-      <c r="D80" s="3" t="inlineStr"/>
+          <t>Execution_Tracker_v6</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>Execution</t>
+        </is>
+      </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>2 Maximum features</t>
-        </is>
-      </c>
-      <c r="F80" s="10" t="inlineStr">
+          <t>1 Vibe Mode live</t>
+        </is>
+      </c>
+      <c r="F80" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10089,30 +10089,26 @@
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>PC-017</t>
+          <t>PC-014</t>
         </is>
       </c>
       <c r="I80" s="3" t="inlineStr"/>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>Draft spec (called R-600 inside).</t>
-        </is>
-      </c>
+      <c r="J80" s="3" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>SPEC-PACK-06B</t>
+          <t>SPEC-PACK-01</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>Role-based app generator</t>
+          <t>Pack manifest v2 schema</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>specs/pack-framework/06b</t>
+          <t>specs/pack-framework/01</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr"/>
@@ -10121,7 +10117,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F81" s="10" t="inlineStr">
+      <c r="F81" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10133,30 +10129,30 @@
       </c>
       <c r="H81" s="3" t="inlineStr">
         <is>
-          <t>PC-075</t>
+          <t>PC-017</t>
         </is>
       </c>
       <c r="I81" s="3" t="inlineStr"/>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>R-555 and R-562 build one app per role; the spec asks for more.</t>
+          <t>Draft spec (called R-600 inside).</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>SPEC-PACK-06E</t>
+          <t>SPEC-PACK-06B</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>Rich seed data generator</t>
+          <t>Role-based app generator</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>specs/pack-framework/06e</t>
+          <t>specs/pack-framework/06b</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr"/>
@@ -10165,86 +10161,86 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F82" s="10" t="inlineStr">
+      <c r="F82" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G82" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G82" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>PC-077</t>
+          <t>PC-075</t>
         </is>
       </c>
       <c r="I82" s="3" t="inlineStr"/>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>Seeds exist (R-248); the spec asks for realistic volume.</t>
+          <t>R-555 and R-562 build one app per role; the spec asks for more.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>SPEC-TS-01</t>
+          <t>SPEC-PACK-06E</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>Instant chat -&gt; pretty UI</t>
+          <t>Rich seed data generator</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>specs/table-stakes/01</t>
+          <t>specs/pack-framework/06e</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr"/>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>Delivered</t>
-        </is>
-      </c>
-      <c r="F83" s="10" t="inlineStr">
+          <t>2 Maximum features</t>
+        </is>
+      </c>
+      <c r="F83" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G83" s="6" t="inlineStr">
-        <is>
-          <t>P0</t>
+      <c r="G83" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H83" s="3" t="inlineStr">
         <is>
-          <t>PC-006</t>
+          <t>PC-077</t>
         </is>
       </c>
       <c r="I83" s="3" t="inlineStr"/>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>Draft spec.</t>
+          <t>Seeds exist (R-248); the spec asks for realistic volume.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>SPEC-TS-03</t>
+          <t>SPEC-TS-01</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>One-click deploy</t>
+          <t>Instant chat -&gt; pretty UI</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>specs/table-stakes/03</t>
+          <t>specs/table-stakes/01</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr"/>
@@ -10253,7 +10249,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F84" s="10" t="inlineStr">
+      <c r="F84" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10265,7 +10261,7 @@
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>PC-008</t>
+          <t>PC-006</t>
         </is>
       </c>
       <c r="I84" s="3" t="inlineStr"/>
@@ -10278,60 +10274,56 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>VP-appointments</t>
+          <t>SPEC-TS-03</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>Vertical pack appointments: Appointments, slots, reminders, waitlist</t>
+          <t>One-click deploy</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>registry</t>
-        </is>
-      </c>
-      <c r="D85" s="3" t="inlineStr">
-        <is>
-          <t>Healthcare &amp; life sciences (healthcare-core)</t>
-        </is>
-      </c>
+          <t>specs/table-stakes/03</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr"/>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>2 Maximum features</t>
-        </is>
-      </c>
-      <c r="F85" s="10" t="inlineStr">
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="F85" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G85" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G85" s="6" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="H85" s="3" t="inlineStr">
         <is>
-          <t>PC-074</t>
+          <t>PC-008</t>
         </is>
       </c>
       <c r="I85" s="3" t="inlineStr"/>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>CareClinic template.</t>
+          <t>Draft spec.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>VP-cart-checkout</t>
+          <t>VP-appointments</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>Vertical pack cart-checkout: Cart, coupons, checkout sessions</t>
+          <t>Vertical pack appointments: Appointments, slots, reminders, waitlist</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -10341,7 +10333,7 @@
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>Marketplace &amp; commerce (commerce-core)</t>
+          <t>Healthcare &amp; life sciences (healthcare-core)</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
@@ -10349,7 +10341,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F86" s="10" t="inlineStr">
+      <c r="F86" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10367,19 +10359,19 @@
       <c r="I86" s="3" t="inlineStr"/>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>Bazaar template.</t>
+          <t>CareClinic template.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>VP-commissions</t>
+          <t>VP-cart-checkout</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>Vertical pack commissions: Commission rules, splits, payout cycles</t>
+          <t>Vertical pack cart-checkout: Cart, coupons, checkout sessions</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
@@ -10397,7 +10389,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F87" s="10" t="inlineStr">
+      <c r="F87" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10415,19 +10407,19 @@
       <c r="I87" s="3" t="inlineStr"/>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>Bazaar ledger.</t>
+          <t>Bazaar template.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>VP-dispatch</t>
+          <t>VP-commissions</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>Vertical pack dispatch: Zones, assignment rules, heatmaps</t>
+          <t>Vertical pack commissions: Commission rules, splits, payout cycles</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
@@ -10437,7 +10429,7 @@
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>Mobility &amp; on-demand (mobility-core)</t>
+          <t>Marketplace &amp; commerce (commerce-core)</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
@@ -10445,7 +10437,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F88" s="10" t="inlineStr">
+      <c r="F88" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10463,19 +10455,19 @@
       <c r="I88" s="3" t="inlineStr"/>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>RideNow template (partial).</t>
+          <t>Bazaar ledger.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>VP-drivers</t>
+          <t>VP-dispatch</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>Vertical pack drivers: Drivers, vehicles, documents, earnings</t>
+          <t>Vertical pack dispatch: Zones, assignment rules, heatmaps</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
@@ -10493,7 +10485,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F89" s="10" t="inlineStr">
+      <c r="F89" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10511,19 +10503,19 @@
       <c r="I89" s="3" t="inlineStr"/>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>RideNow template.</t>
+          <t>RideNow template (partial).</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>VP-emr</t>
+          <t>VP-drivers</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>Vertical pack emr: Encounters, notes, diagnoses, vitals</t>
+          <t>Vertical pack drivers: Drivers, vehicles, documents, earnings</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
@@ -10533,7 +10525,7 @@
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>Healthcare &amp; life sciences (healthcare-core)</t>
+          <t>Mobility &amp; on-demand (mobility-core)</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
@@ -10541,7 +10533,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F90" s="10" t="inlineStr">
+      <c r="F90" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10559,19 +10551,19 @@
       <c r="I90" s="3" t="inlineStr"/>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>CareClinic template (partial).</t>
+          <t>RideNow template.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>VP-listings</t>
+          <t>VP-emr</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>Vertical pack listings: Listings, categories, variants, media</t>
+          <t>Vertical pack emr: Encounters, notes, diagnoses, vitals</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -10581,7 +10573,7 @@
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>Marketplace &amp; commerce (commerce-core)</t>
+          <t>Healthcare &amp; life sciences (healthcare-core)</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
@@ -10589,7 +10581,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F91" s="10" t="inlineStr">
+      <c r="F91" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10607,24 +10599,24 @@
       <c r="I91" s="3" t="inlineStr"/>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>Bazaar template.</t>
+          <t>CareClinic template (partial).</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>VP-orders</t>
+          <t>VP-listings</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>Vertical pack orders: Orders, line items, timelines</t>
+          <t>Vertical pack listings: Listings, categories, variants, media</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>new (registry dependency)</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
@@ -10637,7 +10629,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F92" s="10" t="inlineStr">
+      <c r="F92" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10662,22 +10654,22 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>VP-patients</t>
+          <t>VP-orders</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>Vertical pack patients: Patients, records, insurance, consent</t>
+          <t>Vertical pack orders: Orders, line items, timelines</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>registry</t>
+          <t>new (registry dependency)</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>Healthcare &amp; life sciences (healthcare-core)</t>
+          <t>Marketplace &amp; commerce (commerce-core)</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
@@ -10685,7 +10677,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F93" s="10" t="inlineStr">
+      <c r="F93" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10703,19 +10695,19 @@
       <c r="I93" s="3" t="inlineStr"/>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>CareClinic template.</t>
+          <t>Bazaar template.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>VP-prescriptions</t>
+          <t>VP-patients</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>Vertical pack prescriptions: Prescriptions, medications, pharmacies</t>
+          <t>Vertical pack patients: Patients, records, insurance, consent</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -10733,7 +10725,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F94" s="10" t="inlineStr">
+      <c r="F94" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10751,19 +10743,19 @@
       <c r="I94" s="3" t="inlineStr"/>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>CareClinic template (partial).</t>
+          <t>CareClinic template.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>VP-providers</t>
+          <t>VP-prescriptions</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>Vertical pack providers: Providers, specialties, licences, schedules</t>
+          <t>Vertical pack prescriptions: Prescriptions, medications, pharmacies</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -10781,7 +10773,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F95" s="10" t="inlineStr">
+      <c r="F95" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10799,19 +10791,19 @@
       <c r="I95" s="3" t="inlineStr"/>
       <c r="J95" s="3" t="inlineStr">
         <is>
-          <t>CareClinic template.</t>
+          <t>CareClinic template (partial).</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>VP-rides</t>
+          <t>VP-providers</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>Vertical pack rides: Rides, routes, fares, matching, receipts</t>
+          <t>Vertical pack providers: Providers, specialties, licences, schedules</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
@@ -10821,7 +10813,7 @@
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>Mobility &amp; on-demand (mobility-core)</t>
+          <t>Healthcare &amp; life sciences (healthcare-core)</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
@@ -10829,7 +10821,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F96" s="10" t="inlineStr">
+      <c r="F96" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10847,19 +10839,19 @@
       <c r="I96" s="3" t="inlineStr"/>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>RideNow template.</t>
+          <t>CareClinic template.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>VP-telehealth</t>
+          <t>VP-rides</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>Vertical pack telehealth: Video consults, consent, technical checks</t>
+          <t>Vertical pack rides: Rides, routes, fares, matching, receipts</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
@@ -10869,7 +10861,7 @@
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>Healthcare &amp; life sciences (healthcare-core)</t>
+          <t>Mobility &amp; on-demand (mobility-core)</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
@@ -10877,7 +10869,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F97" s="10" t="inlineStr">
+      <c r="F97" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10895,19 +10887,19 @@
       <c r="I97" s="3" t="inlineStr"/>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>CareClinic template.</t>
+          <t>RideNow template.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>VP-vendors</t>
+          <t>VP-telehealth</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>Vertical pack vendors: Vendors, storefronts, verification</t>
+          <t>Vertical pack telehealth: Video consults, consent, technical checks</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
@@ -10917,7 +10909,7 @@
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>Marketplace &amp; commerce (commerce-core)</t>
+          <t>Healthcare &amp; life sciences (healthcare-core)</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
@@ -10925,7 +10917,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F98" s="10" t="inlineStr">
+      <c r="F98" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10943,63 +10935,67 @@
       <c r="I98" s="3" t="inlineStr"/>
       <c r="J98" s="3" t="inlineStr">
         <is>
-          <t>Bazaar template.</t>
+          <t>CareClinic template.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>PC-096</t>
+          <t>VP-vendors</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>In-browser WebContainer preview engine behind the PC-007 engine switch (Node in the visitor's browser; licence key supplied at PC-070)</t>
+          <t>Vertical pack vendors: Vendors, storefronts, verification</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>Platform_Completion queue</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>Vibe</t>
+          <t>Marketplace &amp; commerce (commerce-core)</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>1 Vibe Mode live</t>
-        </is>
-      </c>
-      <c r="F99" s="8" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G99" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="H99" s="3" t="inlineStr"/>
+          <t>2 Maximum features</t>
+        </is>
+      </c>
+      <c r="F99" s="11" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G99" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>PC-074</t>
+        </is>
+      </c>
       <c r="I99" s="3" t="inlineStr"/>
       <c r="J99" s="3" t="inlineStr">
         <is>
-          <t>Split out of PC-007 on 2026-09-27: PC-007 delivers the engine switch and the open-source container engine; WebContainer needs StackBlitz's commercial licence (D-6) and runs Node only, so Python/Go APIs still need a server-side engine behind it.</t>
+          <t>Bazaar template.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>PC-097</t>
+          <t>PC-096</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>Compile repair covers every Next surface (admin console and ecosystem role surfaces), not only the main web app</t>
+          <t>In-browser WebContainer preview engine behind the PC-007 engine switch (Node in the visitor's browser; licence key supplied at PC-070)</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
@@ -11009,7 +11005,7 @@
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Vibe</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
@@ -11022,28 +11018,28 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G100" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G100" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H100" s="3" t="inlineStr"/>
       <c r="I100" s="3" t="inlineStr"/>
       <c r="J100" s="3" t="inlineStr">
         <is>
-          <t>Found publishing a clinic app on 2026-09-27: the `provider` role surface shipped a model-written page with an invented import and misused components; the build never checked it. PC-008 now type-checks every Next surface and publish refuses a broken app with the compiler's reason; this task makes the repair loop fix or revert those pages as it does for web.</t>
+          <t>Split out of PC-007 on 2026-09-27: PC-007 delivers the engine switch and the open-source container engine; WebContainer needs StackBlitz's commercial licence (D-6) and runs Node only, so Python/Go APIs still need a server-side engine behind it.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>PC-010</t>
+          <t>PC-097</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>Credit fairness: estimate before a build, no charge for internal retries, per-task budgets, cost guardrails</t>
+          <t>Compile repair covers every Next surface (admin console and ecosystem role surfaces), not only the main web app</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
@@ -11053,7 +11049,7 @@
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>Platform</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
@@ -11066,14 +11062,18 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G101" s="6" t="inlineStr">
-        <is>
-          <t>P0</t>
+      <c r="G101" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H101" s="3" t="inlineStr"/>
       <c r="I101" s="3" t="inlineStr"/>
-      <c r="J101" s="3" t="inlineStr"/>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>Found publishing a clinic app on 2026-09-27: the `provider` role surface shipped a model-written page with an invented import and misused components; the build never checked it. PC-008 now type-checks every Next surface and publish refuses a broken app with the compiler's reason; this task makes the repair loop fix or revert those pages as it does for web.</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
@@ -11962,7 +11962,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G122" s="11" t="inlineStr">
+      <c r="G122" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -12006,7 +12006,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G123" s="11" t="inlineStr">
+      <c r="G123" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -12182,7 +12182,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G127" s="11" t="inlineStr">
+      <c r="G127" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -12226,7 +12226,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G128" s="11" t="inlineStr">
+      <c r="G128" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -12270,7 +12270,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G129" s="11" t="inlineStr">
+      <c r="G129" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -12314,7 +12314,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G130" s="11" t="inlineStr">
+      <c r="G130" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -12358,7 +12358,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G131" s="11" t="inlineStr">
+      <c r="G131" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -12446,7 +12446,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G133" s="11" t="inlineStr">
+      <c r="G133" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -12842,7 +12842,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G142" s="11" t="inlineStr">
+      <c r="G142" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -12886,7 +12886,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G143" s="11" t="inlineStr">
+      <c r="G143" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -12930,7 +12930,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G144" s="11" t="inlineStr">
+      <c r="G144" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -14122,7 +14122,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G173" s="11" t="inlineStr">
+      <c r="G173" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -14162,7 +14162,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G174" s="11" t="inlineStr">
+      <c r="G174" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -14206,7 +14206,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G175" s="11" t="inlineStr">
+      <c r="G175" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -14722,7 +14722,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G187" s="11" t="inlineStr">
+      <c r="G187" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -14890,7 +14890,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G191" s="11" t="inlineStr">
+      <c r="G191" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -15454,7 +15454,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G205" s="11" t="inlineStr">
+      <c r="G205" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -15818,7 +15818,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G214" s="11" t="inlineStr">
+      <c r="G214" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -16318,7 +16318,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G226" s="11" t="inlineStr">
+      <c r="G226" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -16542,7 +16542,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G231" s="11" t="inlineStr">
+      <c r="G231" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -16674,7 +16674,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G234" s="11" t="inlineStr">
+      <c r="G234" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -16718,7 +16718,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G235" s="11" t="inlineStr">
+      <c r="G235" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -16942,7 +16942,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G240" s="11" t="inlineStr">
+      <c r="G240" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -17118,7 +17118,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G244" s="11" t="inlineStr">
+      <c r="G244" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -17254,7 +17254,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G247" s="11" t="inlineStr">
+      <c r="G247" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -17342,7 +17342,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G249" s="11" t="inlineStr">
+      <c r="G249" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -17438,7 +17438,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G251" s="11" t="inlineStr">
+      <c r="G251" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -17530,7 +17530,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G253" s="11" t="inlineStr">
+      <c r="G253" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -17574,7 +17574,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G254" s="11" t="inlineStr">
+      <c r="G254" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -17666,7 +17666,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G256" s="11" t="inlineStr">
+      <c r="G256" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -17710,7 +17710,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G257" s="11" t="inlineStr">
+      <c r="G257" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -17890,7 +17890,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G261" s="11" t="inlineStr">
+      <c r="G261" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -18030,7 +18030,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G264" s="11" t="inlineStr">
+      <c r="G264" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -18074,7 +18074,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G265" s="11" t="inlineStr">
+      <c r="G265" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -18482,7 +18482,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G274" s="11" t="inlineStr">
+      <c r="G274" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -18714,7 +18714,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G279" s="11" t="inlineStr">
+      <c r="G279" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -18938,7 +18938,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G284" s="11" t="inlineStr">
+      <c r="G284" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -18982,7 +18982,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G285" s="11" t="inlineStr">
+      <c r="G285" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -19118,7 +19118,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G288" s="11" t="inlineStr">
+      <c r="G288" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -21086,7 +21086,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G334" s="11" t="inlineStr">
+      <c r="G334" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -22854,7 +22854,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G374" s="11" t="inlineStr">
+      <c r="G374" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -22898,7 +22898,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G375" s="11" t="inlineStr">
+      <c r="G375" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -22942,7 +22942,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G376" s="11" t="inlineStr">
+      <c r="G376" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -24742,7 +24742,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G417" s="11" t="inlineStr">
+      <c r="G417" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -24786,7 +24786,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G418" s="11" t="inlineStr">
+      <c r="G418" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -24874,7 +24874,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G420" s="11" t="inlineStr">
+      <c r="G420" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25006,7 +25006,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G423" s="11" t="inlineStr">
+      <c r="G423" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25182,7 +25182,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G427" s="11" t="inlineStr">
+      <c r="G427" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25226,7 +25226,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G428" s="11" t="inlineStr">
+      <c r="G428" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25534,7 +25534,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G435" s="11" t="inlineStr">
+      <c r="G435" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25578,7 +25578,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G436" s="11" t="inlineStr">
+      <c r="G436" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25622,7 +25622,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G437" s="11" t="inlineStr">
+      <c r="G437" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25666,7 +25666,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G438" s="11" t="inlineStr">
+      <c r="G438" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25710,7 +25710,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G439" s="11" t="inlineStr">
+      <c r="G439" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25754,7 +25754,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G440" s="11" t="inlineStr">
+      <c r="G440" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25798,7 +25798,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G441" s="11" t="inlineStr">
+      <c r="G441" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25930,7 +25930,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G444" s="11" t="inlineStr">
+      <c r="G444" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -26062,7 +26062,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G447" s="11" t="inlineStr">
+      <c r="G447" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -26238,7 +26238,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G451" s="11" t="inlineStr">
+      <c r="G451" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -26282,7 +26282,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G452" s="11" t="inlineStr">
+      <c r="G452" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -26458,7 +26458,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G456" s="11" t="inlineStr">
+      <c r="G456" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -26502,7 +26502,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G457" s="11" t="inlineStr">
+      <c r="G457" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -26590,7 +26590,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G459" s="11" t="inlineStr">
+      <c r="G459" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -26766,7 +26766,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G463" s="11" t="inlineStr">
+      <c r="G463" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -26810,7 +26810,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G464" s="11" t="inlineStr">
+      <c r="G464" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -27074,7 +27074,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G470" s="11" t="inlineStr">
+      <c r="G470" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -27118,7 +27118,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G471" s="11" t="inlineStr">
+      <c r="G471" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -27338,7 +27338,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G476" s="11" t="inlineStr">
+      <c r="G476" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -27382,7 +27382,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G477" s="11" t="inlineStr">
+      <c r="G477" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -27426,7 +27426,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G478" s="11" t="inlineStr">
+      <c r="G478" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -27470,7 +27470,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G479" s="11" t="inlineStr">
+      <c r="G479" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -27514,7 +27514,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G480" s="11" t="inlineStr">
+      <c r="G480" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -27558,7 +27558,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G481" s="11" t="inlineStr">
+      <c r="G481" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -27734,7 +27734,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G485" s="11" t="inlineStr">
+      <c r="G485" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -27954,7 +27954,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G490" s="11" t="inlineStr">
+      <c r="G490" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -28042,7 +28042,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G492" s="11" t="inlineStr">
+      <c r="G492" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -28086,7 +28086,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G493" s="11" t="inlineStr">
+      <c r="G493" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -28174,7 +28174,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G495" s="11" t="inlineStr">
+      <c r="G495" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -28394,7 +28394,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G500" s="11" t="inlineStr">
+      <c r="G500" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -28438,7 +28438,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G501" s="11" t="inlineStr">
+      <c r="G501" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -28878,7 +28878,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G511" s="11" t="inlineStr">
+      <c r="G511" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -29142,7 +29142,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G517" s="11" t="inlineStr">
+      <c r="G517" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -29274,7 +29274,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G520" s="11" t="inlineStr">
+      <c r="G520" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -29450,7 +29450,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G524" s="11" t="inlineStr">
+      <c r="G524" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -29494,7 +29494,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G525" s="11" t="inlineStr">
+      <c r="G525" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -29670,7 +29670,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G529" s="11" t="inlineStr">
+      <c r="G529" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -29714,7 +29714,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G530" s="11" t="inlineStr">
+      <c r="G530" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -29802,7 +29802,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G532" s="11" t="inlineStr">
+      <c r="G532" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -29890,7 +29890,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G534" s="11" t="inlineStr">
+      <c r="G534" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -29978,7 +29978,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G536" s="11" t="inlineStr">
+      <c r="G536" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30066,7 +30066,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G538" s="11" t="inlineStr">
+      <c r="G538" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30110,7 +30110,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G539" s="11" t="inlineStr">
+      <c r="G539" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30154,7 +30154,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G540" s="11" t="inlineStr">
+      <c r="G540" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30242,7 +30242,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G542" s="11" t="inlineStr">
+      <c r="G542" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30286,7 +30286,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G543" s="11" t="inlineStr">
+      <c r="G543" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30330,7 +30330,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G544" s="11" t="inlineStr">
+      <c r="G544" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30374,7 +30374,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G545" s="11" t="inlineStr">
+      <c r="G545" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30462,7 +30462,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G547" s="11" t="inlineStr">
+      <c r="G547" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30506,7 +30506,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G548" s="11" t="inlineStr">
+      <c r="G548" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30550,7 +30550,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G549" s="11" t="inlineStr">
+      <c r="G549" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30682,7 +30682,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G552" s="11" t="inlineStr">
+      <c r="G552" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30814,7 +30814,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G555" s="11" t="inlineStr">
+      <c r="G555" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30902,7 +30902,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G557" s="11" t="inlineStr">
+      <c r="G557" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30990,7 +30990,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G559" s="11" t="inlineStr">
+      <c r="G559" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -31078,7 +31078,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G561" s="11" t="inlineStr">
+      <c r="G561" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -31298,7 +31298,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G566" s="11" t="inlineStr">
+      <c r="G566" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -31342,7 +31342,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G567" s="11" t="inlineStr">
+      <c r="G567" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -31430,7 +31430,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G569" s="11" t="inlineStr">
+      <c r="G569" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -31562,7 +31562,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G572" s="11" t="inlineStr">
+      <c r="G572" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -31694,7 +31694,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G575" s="11" t="inlineStr">
+      <c r="G575" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -31782,7 +31782,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G577" s="11" t="inlineStr">
+      <c r="G577" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -31826,7 +31826,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G578" s="11" t="inlineStr">
+      <c r="G578" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -32002,7 +32002,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G582" s="11" t="inlineStr">
+      <c r="G582" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -32046,7 +32046,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G583" s="11" t="inlineStr">
+      <c r="G583" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -32354,7 +32354,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G590" s="11" t="inlineStr">
+      <c r="G590" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -32398,7 +32398,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G591" s="11" t="inlineStr">
+      <c r="G591" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -32442,7 +32442,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G592" s="11" t="inlineStr">
+      <c r="G592" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -32530,7 +32530,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G594" s="11" t="inlineStr">
+      <c r="G594" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -32706,7 +32706,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G598" s="11" t="inlineStr">
+      <c r="G598" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -32838,7 +32838,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G601" s="11" t="inlineStr">
+      <c r="G601" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -32882,7 +32882,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G602" s="11" t="inlineStr">
+      <c r="G602" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -32970,7 +32970,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G604" s="11" t="inlineStr">
+      <c r="G604" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -33058,7 +33058,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G606" s="11" t="inlineStr">
+      <c r="G606" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -33278,7 +33278,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G611" s="11" t="inlineStr">
+      <c r="G611" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -33357,7 +33357,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F613" s="11" t="inlineStr">
+      <c r="F613" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33401,7 +33401,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F614" s="11" t="inlineStr">
+      <c r="F614" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33445,7 +33445,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F615" s="11" t="inlineStr">
+      <c r="F615" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33489,7 +33489,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F616" s="11" t="inlineStr">
+      <c r="F616" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33533,7 +33533,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F617" s="11" t="inlineStr">
+      <c r="F617" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33577,7 +33577,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F618" s="11" t="inlineStr">
+      <c r="F618" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33621,7 +33621,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F619" s="11" t="inlineStr">
+      <c r="F619" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33665,7 +33665,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F620" s="11" t="inlineStr">
+      <c r="F620" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33705,7 +33705,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F621" s="11" t="inlineStr">
+      <c r="F621" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33749,7 +33749,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F622" s="11" t="inlineStr">
+      <c r="F622" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33789,7 +33789,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F623" s="11" t="inlineStr">
+      <c r="F623" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33833,7 +33833,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F624" s="11" t="inlineStr">
+      <c r="F624" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33873,12 +33873,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F625" s="12" t="inlineStr">
+      <c r="F625" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G625" s="11" t="inlineStr">
+      <c r="G625" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -33917,12 +33917,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F626" s="12" t="inlineStr">
+      <c r="F626" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G626" s="11" t="inlineStr">
+      <c r="G626" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -33961,12 +33961,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F627" s="12" t="inlineStr">
+      <c r="F627" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G627" s="11" t="inlineStr">
+      <c r="G627" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34005,7 +34005,7 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F628" s="12" t="inlineStr">
+      <c r="F628" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
@@ -34049,12 +34049,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F629" s="12" t="inlineStr">
+      <c r="F629" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G629" s="11" t="inlineStr">
+      <c r="G629" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34093,12 +34093,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F630" s="12" t="inlineStr">
+      <c r="F630" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G630" s="11" t="inlineStr">
+      <c r="G630" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34133,12 +34133,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F631" s="12" t="inlineStr">
+      <c r="F631" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G631" s="11" t="inlineStr">
+      <c r="G631" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34177,12 +34177,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F632" s="12" t="inlineStr">
+      <c r="F632" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G632" s="11" t="inlineStr">
+      <c r="G632" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34221,12 +34221,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F633" s="12" t="inlineStr">
+      <c r="F633" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G633" s="11" t="inlineStr">
+      <c r="G633" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34265,12 +34265,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F634" s="12" t="inlineStr">
+      <c r="F634" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G634" s="11" t="inlineStr">
+      <c r="G634" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34305,12 +34305,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F635" s="12" t="inlineStr">
+      <c r="F635" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G635" s="11" t="inlineStr">
+      <c r="G635" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34349,12 +34349,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F636" s="12" t="inlineStr">
+      <c r="F636" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G636" s="11" t="inlineStr">
+      <c r="G636" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34393,12 +34393,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F637" s="12" t="inlineStr">
+      <c r="F637" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G637" s="11" t="inlineStr">
+      <c r="G637" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34437,12 +34437,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F638" s="12" t="inlineStr">
+      <c r="F638" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G638" s="11" t="inlineStr">
+      <c r="G638" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34481,12 +34481,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F639" s="12" t="inlineStr">
+      <c r="F639" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G639" s="11" t="inlineStr">
+      <c r="G639" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34525,12 +34525,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F640" s="12" t="inlineStr">
+      <c r="F640" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G640" s="11" t="inlineStr">
+      <c r="G640" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34569,12 +34569,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F641" s="12" t="inlineStr">
+      <c r="F641" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G641" s="11" t="inlineStr">
+      <c r="G641" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34613,12 +34613,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F642" s="12" t="inlineStr">
+      <c r="F642" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G642" s="11" t="inlineStr">
+      <c r="G642" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34657,12 +34657,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F643" s="12" t="inlineStr">
+      <c r="F643" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G643" s="11" t="inlineStr">
+      <c r="G643" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34701,12 +34701,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F644" s="12" t="inlineStr">
+      <c r="F644" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G644" s="11" t="inlineStr">
+      <c r="G644" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34745,12 +34745,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F645" s="12" t="inlineStr">
+      <c r="F645" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G645" s="11" t="inlineStr">
+      <c r="G645" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34789,12 +34789,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F646" s="12" t="inlineStr">
+      <c r="F646" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G646" s="11" t="inlineStr">
+      <c r="G646" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34833,12 +34833,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F647" s="12" t="inlineStr">
+      <c r="F647" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G647" s="11" t="inlineStr">
+      <c r="G647" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34877,12 +34877,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F648" s="12" t="inlineStr">
+      <c r="F648" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G648" s="11" t="inlineStr">
+      <c r="G648" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34921,12 +34921,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F649" s="12" t="inlineStr">
+      <c r="F649" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G649" s="11" t="inlineStr">
+      <c r="G649" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34961,12 +34961,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F650" s="12" t="inlineStr">
+      <c r="F650" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G650" s="11" t="inlineStr">
+      <c r="G650" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35005,12 +35005,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F651" s="12" t="inlineStr">
+      <c r="F651" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G651" s="11" t="inlineStr">
+      <c r="G651" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35049,12 +35049,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F652" s="12" t="inlineStr">
+      <c r="F652" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G652" s="11" t="inlineStr">
+      <c r="G652" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35089,12 +35089,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F653" s="12" t="inlineStr">
+      <c r="F653" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G653" s="11" t="inlineStr">
+      <c r="G653" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35133,12 +35133,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F654" s="12" t="inlineStr">
+      <c r="F654" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G654" s="11" t="inlineStr">
+      <c r="G654" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35173,12 +35173,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F655" s="12" t="inlineStr">
+      <c r="F655" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G655" s="11" t="inlineStr">
+      <c r="G655" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35213,12 +35213,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F656" s="12" t="inlineStr">
+      <c r="F656" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G656" s="11" t="inlineStr">
+      <c r="G656" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35253,12 +35253,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F657" s="12" t="inlineStr">
+      <c r="F657" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G657" s="11" t="inlineStr">
+      <c r="G657" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35293,12 +35293,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F658" s="12" t="inlineStr">
+      <c r="F658" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G658" s="11" t="inlineStr">
+      <c r="G658" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35337,12 +35337,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F659" s="12" t="inlineStr">
+      <c r="F659" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G659" s="11" t="inlineStr">
+      <c r="G659" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35381,12 +35381,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F660" s="12" t="inlineStr">
+      <c r="F660" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G660" s="11" t="inlineStr">
+      <c r="G660" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35425,12 +35425,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F661" s="12" t="inlineStr">
+      <c r="F661" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G661" s="11" t="inlineStr">
+      <c r="G661" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35465,12 +35465,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F662" s="12" t="inlineStr">
+      <c r="F662" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G662" s="11" t="inlineStr">
+      <c r="G662" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35505,12 +35505,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F663" s="12" t="inlineStr">
+      <c r="F663" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G663" s="11" t="inlineStr">
+      <c r="G663" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35545,12 +35545,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F664" s="12" t="inlineStr">
+      <c r="F664" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G664" s="11" t="inlineStr">
+      <c r="G664" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35585,12 +35585,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F665" s="12" t="inlineStr">
+      <c r="F665" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G665" s="11" t="inlineStr">
+      <c r="G665" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35625,12 +35625,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F666" s="12" t="inlineStr">
+      <c r="F666" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G666" s="11" t="inlineStr">
+      <c r="G666" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35669,12 +35669,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F667" s="12" t="inlineStr">
+      <c r="F667" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G667" s="11" t="inlineStr">
+      <c r="G667" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35709,12 +35709,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F668" s="12" t="inlineStr">
+      <c r="F668" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G668" s="11" t="inlineStr">
+      <c r="G668" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35749,12 +35749,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F669" s="12" t="inlineStr">
+      <c r="F669" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G669" s="11" t="inlineStr">
+      <c r="G669" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35789,12 +35789,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F670" s="12" t="inlineStr">
+      <c r="F670" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G670" s="11" t="inlineStr">
+      <c r="G670" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35829,12 +35829,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F671" s="12" t="inlineStr">
+      <c r="F671" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G671" s="11" t="inlineStr">
+      <c r="G671" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35873,12 +35873,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F672" s="12" t="inlineStr">
+      <c r="F672" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G672" s="11" t="inlineStr">
+      <c r="G672" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35917,12 +35917,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F673" s="12" t="inlineStr">
+      <c r="F673" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G673" s="11" t="inlineStr">
+      <c r="G673" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35961,12 +35961,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F674" s="12" t="inlineStr">
+      <c r="F674" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G674" s="11" t="inlineStr">
+      <c r="G674" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -36005,12 +36005,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F675" s="12" t="inlineStr">
+      <c r="F675" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G675" s="11" t="inlineStr">
+      <c r="G675" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -36049,12 +36049,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F676" s="12" t="inlineStr">
+      <c r="F676" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G676" s="11" t="inlineStr">
+      <c r="G676" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -36093,12 +36093,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F677" s="12" t="inlineStr">
+      <c r="F677" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G677" s="11" t="inlineStr">
+      <c r="G677" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -36137,12 +36137,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F678" s="12" t="inlineStr">
+      <c r="F678" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G678" s="11" t="inlineStr">
+      <c r="G678" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -36181,12 +36181,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F679" s="12" t="inlineStr">
+      <c r="F679" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G679" s="11" t="inlineStr">
+      <c r="G679" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -36225,12 +36225,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F680" s="12" t="inlineStr">
+      <c r="F680" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G680" s="11" t="inlineStr">
+      <c r="G680" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -36265,12 +36265,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F681" s="12" t="inlineStr">
+      <c r="F681" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G681" s="11" t="inlineStr">
+      <c r="G681" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -36301,7 +36301,7 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F682" s="13" t="inlineStr">
+      <c r="F682" s="14" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -36341,7 +36341,7 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F683" s="13" t="inlineStr">
+      <c r="F683" s="14" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -36381,7 +36381,7 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F684" s="13" t="inlineStr">
+      <c r="F684" s="14" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -36421,7 +36421,7 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F685" s="13" t="inlineStr">
+      <c r="F685" s="14" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -36461,7 +36461,7 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F686" s="13" t="inlineStr">
+      <c r="F686" s="14" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -36501,7 +36501,7 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F687" s="13" t="inlineStr">
+      <c r="F687" s="14" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -36541,7 +36541,7 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F688" s="13" t="inlineStr">
+      <c r="F688" s="14" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -36581,7 +36581,7 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F689" s="13" t="inlineStr">
+      <c r="F689" s="14" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -36621,7 +36621,7 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F690" s="13" t="inlineStr">
+      <c r="F690" s="14" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -38637,7 +38637,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F736" s="14" t="inlineStr">
+      <c r="F736" s="15" t="inlineStr">
         <is>
           <t>Completed - needs live proof</t>
         </is>
@@ -51253,7 +51253,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F1055" s="14" t="inlineStr">
+      <c r="F1055" s="15" t="inlineStr">
         <is>
           <t>Completed - needs live proof</t>
         </is>
@@ -51301,7 +51301,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F1056" s="14" t="inlineStr">
+      <c r="F1056" s="15" t="inlineStr">
         <is>
           <t>Completed - needs live proof</t>
         </is>
@@ -51349,7 +51349,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F1057" s="14" t="inlineStr">
+      <c r="F1057" s="15" t="inlineStr">
         <is>
           <t>Completed - needs live proof</t>
         </is>
@@ -51397,7 +51397,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F1058" s="14" t="inlineStr">
+      <c r="F1058" s="15" t="inlineStr">
         <is>
           <t>Completed - needs live proof</t>
         </is>
@@ -51445,7 +51445,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F1059" s="14" t="inlineStr">
+      <c r="F1059" s="15" t="inlineStr">
         <is>
           <t>Completed - needs live proof</t>
         </is>
@@ -51565,7 +51565,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F1062" s="14" t="inlineStr">
+      <c r="F1062" s="15" t="inlineStr">
         <is>
           <t>Completed - needs live proof</t>
         </is>
@@ -52697,7 +52697,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F1093" s="14" t="inlineStr">
+      <c r="F1093" s="15" t="inlineStr">
         <is>
           <t>Completed - needs live proof</t>
         </is>
@@ -53694,62 +53694,62 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="B1" s="15" t="inlineStr">
+      <c r="B1" s="16" t="inlineStr">
         <is>
           <t>0 Foundation</t>
         </is>
       </c>
-      <c r="C1" s="15" t="inlineStr">
+      <c r="C1" s="16" t="inlineStr">
         <is>
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="D1" s="15" t="inlineStr">
+      <c r="D1" s="16" t="inlineStr">
         <is>
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="E1" s="15" t="inlineStr">
+      <c r="E1" s="16" t="inlineStr">
         <is>
           <t>3 Engineering Mode</t>
         </is>
       </c>
-      <c r="F1" s="15" t="inlineStr">
+      <c r="F1" s="16" t="inlineStr">
         <is>
           <t>4 Production ops</t>
         </is>
       </c>
-      <c r="G1" s="15" t="inlineStr">
+      <c r="G1" s="16" t="inlineStr">
         <is>
           <t>5 Native mobile (last)</t>
         </is>
       </c>
-      <c r="H1" s="15" t="inlineStr">
+      <c r="H1" s="16" t="inlineStr">
         <is>
           <t>6 Go-live (credentials last)</t>
         </is>
       </c>
-      <c r="I1" s="15" t="inlineStr">
+      <c r="I1" s="16" t="inlineStr">
         <is>
           <t>7 Win the category</t>
         </is>
       </c>
-      <c r="J1" s="15" t="inlineStr">
+      <c r="J1" s="16" t="inlineStr">
         <is>
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="K1" s="15" t="inlineStr">
+      <c r="K1" s="16" t="inlineStr">
         <is>
           <t>Delivered</t>
         </is>
       </c>
-      <c r="L1" s="15" t="inlineStr">
+      <c r="L1" s="16" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
@@ -53845,7 +53845,7 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -53872,7 +53872,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -53925,7 +53925,7 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D6" t="n">
         <v>336</v>
@@ -53952,7 +53952,7 @@
         <v>15</v>
       </c>
       <c r="L6" t="n">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="7">
@@ -54116,62 +54116,62 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Open queue by priority</t>
         </is>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>0 Foundation</t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="D12" s="15" t="inlineStr">
+      <c r="D12" s="16" t="inlineStr">
         <is>
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="E12" s="15" t="inlineStr">
+      <c r="E12" s="16" t="inlineStr">
         <is>
           <t>3 Engineering Mode</t>
         </is>
       </c>
-      <c r="F12" s="15" t="inlineStr">
+      <c r="F12" s="16" t="inlineStr">
         <is>
           <t>4 Production ops</t>
         </is>
       </c>
-      <c r="G12" s="15" t="inlineStr">
+      <c r="G12" s="16" t="inlineStr">
         <is>
           <t>5 Native mobile (last)</t>
         </is>
       </c>
-      <c r="H12" s="15" t="inlineStr">
+      <c r="H12" s="16" t="inlineStr">
         <is>
           <t>6 Go-live (credentials last)</t>
         </is>
       </c>
-      <c r="I12" s="15" t="inlineStr">
+      <c r="I12" s="16" t="inlineStr">
         <is>
           <t>7 Win the category</t>
         </is>
       </c>
-      <c r="J12" s="15" t="inlineStr">
+      <c r="J12" s="16" t="inlineStr">
         <is>
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="K12" s="15" t="inlineStr">
+      <c r="K12" s="16" t="inlineStr">
         <is>
           <t>Delivered</t>
         </is>
       </c>
-      <c r="L12" s="15" t="inlineStr">
+      <c r="L12" s="16" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
@@ -55486,7 +55486,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="F2" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -55590,7 +55590,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -55642,7 +55642,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F5" s="10" t="inlineStr">
+      <c r="F5" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -55694,7 +55694,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -55746,7 +55746,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F7" s="10" t="inlineStr">
+      <c r="F7" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -55798,7 +55798,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="F8" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -55946,7 +55946,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="F11" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -56050,7 +56050,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="F13" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -56107,7 +56107,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G14" s="11" t="inlineStr">
+      <c r="G14" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -56150,7 +56150,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F15" s="10" t="inlineStr">
+      <c r="F15" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -56402,7 +56402,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F20" s="10" t="inlineStr">
+      <c r="F20" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -56506,7 +56506,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F22" s="10" t="inlineStr">
+      <c r="F22" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -56611,7 +56611,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G24" s="11" t="inlineStr">
+      <c r="G24" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -56755,7 +56755,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G27" s="11" t="inlineStr">
+      <c r="G27" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -56902,12 +56902,12 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F30" s="10" t="inlineStr">
+      <c r="F30" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G30" s="11" t="inlineStr">
+      <c r="G30" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -56959,7 +56959,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G31" s="11" t="inlineStr">
+      <c r="G31" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -57002,7 +57002,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F32" s="10" t="inlineStr">
+      <c r="F32" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -57054,7 +57054,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F33" s="10" t="inlineStr">
+      <c r="F33" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -57106,7 +57106,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F34" s="10" t="inlineStr">
+      <c r="F34" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -57211,7 +57211,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G36" s="11" t="inlineStr">
+      <c r="G36" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -57259,7 +57259,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G37" s="11" t="inlineStr">
+      <c r="G37" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -57402,7 +57402,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F40" s="10" t="inlineStr">
+      <c r="F40" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -57454,7 +57454,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F41" s="10" t="inlineStr">
+      <c r="F41" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -57506,7 +57506,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F42" s="10" t="inlineStr">
+      <c r="F42" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -57606,7 +57606,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F44" s="10" t="inlineStr">
+      <c r="F44" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -57706,7 +57706,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F46" s="10" t="inlineStr">
+      <c r="F46" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -57810,7 +57810,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F48" s="10" t="inlineStr">
+      <c r="F48" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -57958,7 +57958,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F51" s="10" t="inlineStr">
+      <c r="F51" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -58058,7 +58058,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F53" s="10" t="inlineStr">
+      <c r="F53" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -58163,7 +58163,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G55" s="11" t="inlineStr">
+      <c r="G55" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -58258,7 +58258,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F57" s="10" t="inlineStr">
+      <c r="F57" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -58315,7 +58315,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G58" s="11" t="inlineStr">
+      <c r="G58" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -58363,7 +58363,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G59" s="11" t="inlineStr">
+      <c r="G59" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -58459,7 +58459,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G61" s="11" t="inlineStr">
+      <c r="G61" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -58502,7 +58502,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F62" s="10" t="inlineStr">
+      <c r="F62" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -58763,7 +58763,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G67" s="11" t="inlineStr">
+      <c r="G67" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -58854,7 +58854,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F69" s="10" t="inlineStr">
+      <c r="F69" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -58906,7 +58906,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F70" s="10" t="inlineStr">
+      <c r="F70" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -58958,7 +58958,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F71" s="10" t="inlineStr">
+      <c r="F71" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -59010,7 +59010,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F72" s="10" t="inlineStr">
+      <c r="F72" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -59114,7 +59114,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F74" s="10" t="inlineStr">
+      <c r="F74" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -59166,7 +59166,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F75" s="10" t="inlineStr">
+      <c r="F75" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -59218,7 +59218,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F76" s="10" t="inlineStr">
+      <c r="F76" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -59270,7 +59270,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F77" s="10" t="inlineStr">
+      <c r="F77" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -59374,7 +59374,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F79" s="10" t="inlineStr">
+      <c r="F79" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -59478,7 +59478,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F81" s="10" t="inlineStr">
+      <c r="F81" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -59578,12 +59578,12 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F83" s="10" t="inlineStr">
+      <c r="F83" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G83" s="11" t="inlineStr">
+      <c r="G83" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -59635,7 +59635,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G84" s="11" t="inlineStr">
+      <c r="G84" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -59830,7 +59830,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F88" s="10" t="inlineStr">
+      <c r="F88" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -60078,7 +60078,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F93" s="10" t="inlineStr">
+      <c r="F93" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -60274,12 +60274,12 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F97" s="10" t="inlineStr">
+      <c r="F97" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G97" s="11" t="inlineStr">
+      <c r="G97" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -60331,7 +60331,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G98" s="11" t="inlineStr">
+      <c r="G98" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -60379,7 +60379,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G99" s="11" t="inlineStr">
+      <c r="G99" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -60427,7 +60427,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G100" s="11" t="inlineStr">
+      <c r="G100" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -60522,7 +60522,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F102" s="10" t="inlineStr">
+      <c r="F102" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -60579,7 +60579,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G103" s="11" t="inlineStr">
+      <c r="G103" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -60627,7 +60627,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G104" s="11" t="inlineStr">
+      <c r="G104" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -60675,7 +60675,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G105" s="11" t="inlineStr">
+      <c r="G105" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -60723,7 +60723,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G106" s="11" t="inlineStr">
+      <c r="G106" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -60771,7 +60771,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G107" s="11" t="inlineStr">
+      <c r="G107" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -60819,7 +60819,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G108" s="11" t="inlineStr">
+      <c r="G108" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -60914,7 +60914,7 @@
           <t>Patient: App + Web; Doctor / provider: Web + App; Pharmacy / lab: Web; Clinic operator: Admin</t>
         </is>
       </c>
-      <c r="F110" s="10" t="inlineStr">
+      <c r="F110" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -60966,7 +60966,7 @@
           <t>Patient: App + Web; Doctor / provider: Web + App; Pharmacy / lab: Web; Clinic operator: Admin</t>
         </is>
       </c>
-      <c r="F111" s="10" t="inlineStr">
+      <c r="F111" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -61018,7 +61018,7 @@
           <t>Patient: App + Web; Doctor / provider: Web + App; Pharmacy / lab: Web; Clinic operator: Admin</t>
         </is>
       </c>
-      <c r="F112" s="10" t="inlineStr">
+      <c r="F112" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -61070,7 +61070,7 @@
           <t>Patient: App + Web; Doctor / provider: Web + App; Pharmacy / lab: Web; Clinic operator: Admin</t>
         </is>
       </c>
-      <c r="F113" s="10" t="inlineStr">
+      <c r="F113" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -61122,7 +61122,7 @@
           <t>Patient: App + Web; Doctor / provider: Web + App; Pharmacy / lab: Web; Clinic operator: Admin</t>
         </is>
       </c>
-      <c r="F114" s="10" t="inlineStr">
+      <c r="F114" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -61222,7 +61222,7 @@
           <t>Patient: App + Web; Doctor / provider: Web + App; Pharmacy / lab: Web; Clinic operator: Admin</t>
         </is>
       </c>
-      <c r="F116" s="10" t="inlineStr">
+      <c r="F116" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -61610,7 +61610,7 @@
           <t>Rider: App + Web; Driver: App; Dispatcher: Web; Operator: Admin</t>
         </is>
       </c>
-      <c r="F124" s="10" t="inlineStr">
+      <c r="F124" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -61662,7 +61662,7 @@
           <t>Rider: App + Web; Driver: App; Dispatcher: Web; Operator: Admin</t>
         </is>
       </c>
-      <c r="F125" s="10" t="inlineStr">
+      <c r="F125" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -61714,7 +61714,7 @@
           <t>Rider: App + Web; Driver: App; Dispatcher: Web; Operator: Admin</t>
         </is>
       </c>
-      <c r="F126" s="10" t="inlineStr">
+      <c r="F126" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -62150,7 +62150,7 @@
           <t>Buyer: App + Web; Seller / vendor: Web + App; Marketplace operator: Admin</t>
         </is>
       </c>
-      <c r="F135" s="10" t="inlineStr">
+      <c r="F135" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -62202,7 +62202,7 @@
           <t>Buyer: App + Web; Seller / vendor: Web + App; Marketplace operator: Admin</t>
         </is>
       </c>
-      <c r="F136" s="10" t="inlineStr">
+      <c r="F136" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -62254,7 +62254,7 @@
           <t>Buyer: App + Web; Seller / vendor: Web + App; Marketplace operator: Admin</t>
         </is>
       </c>
-      <c r="F137" s="10" t="inlineStr">
+      <c r="F137" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -62402,7 +62402,7 @@
           <t>Buyer: App + Web; Seller / vendor: Web + App; Marketplace operator: Admin</t>
         </is>
       </c>
-      <c r="F140" s="10" t="inlineStr">
+      <c r="F140" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -62454,7 +62454,7 @@
           <t>Buyer: App + Web; Seller / vendor: Web + App; Marketplace operator: Admin</t>
         </is>
       </c>
-      <c r="F141" s="10" t="inlineStr">
+      <c r="F141" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -67311,7 +67311,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G242" s="11" t="inlineStr">
+      <c r="G242" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67359,7 +67359,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G243" s="11" t="inlineStr">
+      <c r="G243" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67407,7 +67407,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G244" s="11" t="inlineStr">
+      <c r="G244" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67455,7 +67455,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G245" s="11" t="inlineStr">
+      <c r="G245" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67503,7 +67503,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G246" s="11" t="inlineStr">
+      <c r="G246" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67551,7 +67551,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G247" s="11" t="inlineStr">
+      <c r="G247" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67599,7 +67599,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G248" s="11" t="inlineStr">
+      <c r="G248" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67647,7 +67647,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G249" s="11" t="inlineStr">
+      <c r="G249" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67695,7 +67695,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G250" s="11" t="inlineStr">
+      <c r="G250" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67743,7 +67743,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G251" s="11" t="inlineStr">
+      <c r="G251" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67791,7 +67791,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G252" s="11" t="inlineStr">
+      <c r="G252" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67839,7 +67839,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G253" s="11" t="inlineStr">
+      <c r="G253" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67887,7 +67887,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G254" s="11" t="inlineStr">
+      <c r="G254" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67935,7 +67935,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G255" s="11" t="inlineStr">
+      <c r="G255" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67983,7 +67983,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G256" s="11" t="inlineStr">
+      <c r="G256" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68031,7 +68031,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G257" s="11" t="inlineStr">
+      <c r="G257" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68079,7 +68079,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G258" s="11" t="inlineStr">
+      <c r="G258" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68127,7 +68127,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G259" s="11" t="inlineStr">
+      <c r="G259" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68175,7 +68175,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G260" s="11" t="inlineStr">
+      <c r="G260" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68223,7 +68223,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G261" s="11" t="inlineStr">
+      <c r="G261" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68271,7 +68271,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G262" s="11" t="inlineStr">
+      <c r="G262" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68319,7 +68319,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G263" s="11" t="inlineStr">
+      <c r="G263" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68367,7 +68367,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G264" s="11" t="inlineStr">
+      <c r="G264" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68415,7 +68415,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G265" s="11" t="inlineStr">
+      <c r="G265" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68463,7 +68463,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G266" s="11" t="inlineStr">
+      <c r="G266" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68511,7 +68511,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G267" s="11" t="inlineStr">
+      <c r="G267" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68559,7 +68559,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G268" s="11" t="inlineStr">
+      <c r="G268" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68607,7 +68607,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G269" s="11" t="inlineStr">
+      <c r="G269" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68655,7 +68655,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G270" s="11" t="inlineStr">
+      <c r="G270" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68703,7 +68703,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G271" s="11" t="inlineStr">
+      <c r="G271" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68751,7 +68751,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G272" s="11" t="inlineStr">
+      <c r="G272" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68799,7 +68799,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G273" s="11" t="inlineStr">
+      <c r="G273" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68847,7 +68847,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G274" s="11" t="inlineStr">
+      <c r="G274" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68895,7 +68895,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G275" s="11" t="inlineStr">
+      <c r="G275" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68943,7 +68943,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G276" s="11" t="inlineStr">
+      <c r="G276" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68991,7 +68991,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G277" s="11" t="inlineStr">
+      <c r="G277" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69039,7 +69039,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G278" s="11" t="inlineStr">
+      <c r="G278" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69087,7 +69087,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G279" s="11" t="inlineStr">
+      <c r="G279" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69135,7 +69135,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G280" s="11" t="inlineStr">
+      <c r="G280" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69183,7 +69183,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G281" s="11" t="inlineStr">
+      <c r="G281" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69231,7 +69231,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G282" s="11" t="inlineStr">
+      <c r="G282" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69279,7 +69279,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G283" s="11" t="inlineStr">
+      <c r="G283" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69327,7 +69327,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G284" s="11" t="inlineStr">
+      <c r="G284" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69375,7 +69375,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G285" s="11" t="inlineStr">
+      <c r="G285" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69423,7 +69423,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G286" s="11" t="inlineStr">
+      <c r="G286" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69471,7 +69471,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G287" s="11" t="inlineStr">
+      <c r="G287" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69519,7 +69519,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G288" s="11" t="inlineStr">
+      <c r="G288" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69567,7 +69567,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G289" s="11" t="inlineStr">
+      <c r="G289" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69615,7 +69615,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G290" s="11" t="inlineStr">
+      <c r="G290" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69663,7 +69663,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G291" s="11" t="inlineStr">
+      <c r="G291" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69711,7 +69711,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G292" s="11" t="inlineStr">
+      <c r="G292" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69759,7 +69759,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G293" s="11" t="inlineStr">
+      <c r="G293" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69807,7 +69807,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G294" s="11" t="inlineStr">
+      <c r="G294" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69855,7 +69855,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G295" s="11" t="inlineStr">
+      <c r="G295" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69903,7 +69903,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G296" s="11" t="inlineStr">
+      <c r="G296" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69951,7 +69951,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G297" s="11" t="inlineStr">
+      <c r="G297" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69999,7 +69999,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G298" s="11" t="inlineStr">
+      <c r="G298" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70047,7 +70047,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G299" s="11" t="inlineStr">
+      <c r="G299" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70095,7 +70095,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G300" s="11" t="inlineStr">
+      <c r="G300" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70143,7 +70143,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G301" s="11" t="inlineStr">
+      <c r="G301" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70191,7 +70191,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G302" s="11" t="inlineStr">
+      <c r="G302" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70239,7 +70239,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G303" s="11" t="inlineStr">
+      <c r="G303" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70287,7 +70287,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G304" s="11" t="inlineStr">
+      <c r="G304" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70335,7 +70335,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G305" s="11" t="inlineStr">
+      <c r="G305" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70383,7 +70383,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G306" s="11" t="inlineStr">
+      <c r="G306" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70431,7 +70431,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G307" s="11" t="inlineStr">
+      <c r="G307" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70479,7 +70479,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G308" s="11" t="inlineStr">
+      <c r="G308" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70527,7 +70527,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G309" s="11" t="inlineStr">
+      <c r="G309" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70575,7 +70575,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G310" s="11" t="inlineStr">
+      <c r="G310" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70623,7 +70623,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G311" s="11" t="inlineStr">
+      <c r="G311" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70671,7 +70671,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G312" s="11" t="inlineStr">
+      <c r="G312" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70719,7 +70719,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G313" s="11" t="inlineStr">
+      <c r="G313" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70767,7 +70767,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G314" s="11" t="inlineStr">
+      <c r="G314" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70815,7 +70815,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G315" s="11" t="inlineStr">
+      <c r="G315" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70863,7 +70863,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G316" s="11" t="inlineStr">
+      <c r="G316" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70911,7 +70911,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G317" s="11" t="inlineStr">
+      <c r="G317" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70959,7 +70959,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G318" s="11" t="inlineStr">
+      <c r="G318" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -71007,7 +71007,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G319" s="11" t="inlineStr">
+      <c r="G319" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -71055,7 +71055,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G320" s="11" t="inlineStr">
+      <c r="G320" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -71103,7 +71103,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G321" s="11" t="inlineStr">
+      <c r="G321" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -71151,7 +71151,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G322" s="11" t="inlineStr">
+      <c r="G322" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -71707,7 +71707,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>Completed - needs live proof</t>
         </is>
@@ -71719,7 +71719,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="16" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
@@ -71731,7 +71731,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -71755,7 +71755,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -71767,7 +71767,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
@@ -71779,7 +71779,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -71827,7 +71827,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>

--- a/R_&_D/Platform_Completion/OmniStackAI_Master_Tasks.xlsx
+++ b/R_&_D/Platform_Completion/OmniStackAI_Master_Tasks.xlsx
@@ -92,6 +92,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00BDD7EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFE699"/>
       </patternFill>
     </fill>
@@ -113,11 +118,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2F0D9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00BDD7EE"/>
       </patternFill>
     </fill>
   </fills>
@@ -173,10 +173,10 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1891,9 +1891,9 @@
           <t>Platform</t>
         </is>
       </c>
-      <c r="F24" s="8" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
@@ -1979,7 +1979,7 @@
           <t>Vibe</t>
         </is>
       </c>
-      <c r="F26" s="10" t="inlineStr">
+      <c r="F26" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2025,7 +2025,7 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="F27" s="10" t="inlineStr">
+      <c r="F27" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2071,7 +2071,7 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="F28" s="10" t="inlineStr">
+      <c r="F28" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2687,7 +2687,7 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="F42" s="10" t="inlineStr">
+      <c r="F42" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2737,7 +2737,7 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="F43" s="10" t="inlineStr">
+      <c r="F43" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2837,7 +2837,7 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="F45" s="10" t="inlineStr">
+      <c r="F45" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2983,7 +2983,7 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="F48" s="10" t="inlineStr">
+      <c r="F48" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -3033,7 +3033,7 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="F49" s="10" t="inlineStr">
+      <c r="F49" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -3188,7 +3188,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G52" s="11" t="inlineStr">
+      <c r="G52" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -3238,7 +3238,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G53" s="11" t="inlineStr">
+      <c r="G53" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -3426,7 +3426,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G57" s="11" t="inlineStr">
+      <c r="G57" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -3468,7 +3468,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G58" s="11" t="inlineStr">
+      <c r="G58" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -3514,7 +3514,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G59" s="11" t="inlineStr">
+      <c r="G59" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -3556,7 +3556,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G60" s="11" t="inlineStr">
+      <c r="G60" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -3598,7 +3598,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G61" s="11" t="inlineStr">
+      <c r="G61" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -3681,7 +3681,7 @@
           <t>Vibe</t>
         </is>
       </c>
-      <c r="F63" s="10" t="inlineStr">
+      <c r="F63" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -3732,7 +3732,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G64" s="11" t="inlineStr">
+      <c r="G64" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -4158,7 +4158,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G73" s="11" t="inlineStr">
+      <c r="G73" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -4204,7 +4204,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G74" s="11" t="inlineStr">
+      <c r="G74" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -4250,7 +4250,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G75" s="11" t="inlineStr">
+      <c r="G75" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -4337,7 +4337,7 @@
           <t>Engineering</t>
         </is>
       </c>
-      <c r="F77" s="10" t="inlineStr">
+      <c r="F77" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -4475,7 +4475,7 @@
           <t>Engineering</t>
         </is>
       </c>
-      <c r="F80" s="10" t="inlineStr">
+      <c r="F80" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -4571,7 +4571,7 @@
           <t>Engineering</t>
         </is>
       </c>
-      <c r="F82" s="10" t="inlineStr">
+      <c r="F82" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -4843,7 +4843,7 @@
           <t>Engineering</t>
         </is>
       </c>
-      <c r="F88" s="10" t="inlineStr">
+      <c r="F88" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -5161,7 +5161,7 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="F95" s="10" t="inlineStr">
+      <c r="F95" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -5806,7 +5806,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G109" s="11" t="inlineStr">
+      <c r="G109" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -5852,7 +5852,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G110" s="11" t="inlineStr">
+      <c r="G110" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -5898,7 +5898,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G111" s="11" t="inlineStr">
+      <c r="G111" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -6466,12 +6466,12 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>PC-013</t>
+          <t>PC-011</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Verified integrations catalog with health tests</t>
+          <t>Plans, entitlements, credit top-up and super_admin console (Phase E)</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Vibe</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -6491,31 +6491,31 @@
       </c>
       <c r="F2" s="10" t="inlineStr">
         <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr"/>
       <c r="I2" s="3" t="inlineStr"/>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>R-511 Connectors v1 exists.</t>
+          <t>Stripe and Razorpay adapters complete and tested in their test modes; live keys (D-3) at PC-070. Found in R-590: self-registered users get role 'user', which is not one of the plan's roles, so role-guarded actions need an admin to assign roles — include a role manager in the generated admin console.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>PC-014</t>
+          <t>PC-013</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Local/offline models as a first-class path: build fully on Ollama, recommend a model per machine</t>
+          <t>Verified integrations catalog with health tests</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -6525,7 +6525,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Vibe</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -6533,7 +6533,7 @@
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="F3" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6547,19 +6547,19 @@
       <c r="I3" s="3" t="inlineStr"/>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>Ollama adapter exists (R-003/R-006). Found in PC-084: .env names qwen2.5-coder:14b but only 7b is installed, and the adapter refuses a pinned model it was not configured with — detect installed models instead of trusting the setting.</t>
+          <t>R-511 Connectors v1 exists.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>R-574</t>
+          <t>PC-014</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Store publishing for React Native apps: EAS build and submit to Play Store and App Store, proven with real accounts</t>
+          <t>Local/offline models as a first-class path: build fully on Ollama, recommend a model per machine</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -6577,7 +6577,7 @@
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6591,19 +6591,19 @@
       <c r="I4" s="3" t="inlineStr"/>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>R-546/R-547 generate the EAS config. Everything up to the upload is built and tested; the Apple and Google accounts (D-7) are plugged in at PC-070.</t>
+          <t>Ollama adapter exists (R-003/R-006). Found in PC-084: .env names qwen2.5-coder:14b but only 7b is installed, and the adapter refuses a pinned model it was not configured with — detect installed models instead of trusting the setting.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>PC-017</t>
+          <t>R-574</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Pack framework core: manifest v2 schema, registry/loader, composer (merge, wire, validate, conflict rules)</t>
+          <t>Store publishing for React Native apps: EAS build and submit to Play Store and App Store, proven with real accounts</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -6618,10 +6618,10 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>2 Maximum features</t>
-        </is>
-      </c>
-      <c r="F5" s="10" t="inlineStr">
+          <t>1 Vibe Mode live</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6635,19 +6635,19 @@
       <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>Solution Pack manifests, registry and application exist (R-434..R-445); v2 adds ir_delta, state machines, page templates, dependencies. From specs/pack-framework 01, 02.</t>
+          <t>R-546/R-547 generate the EAS config. Everything up to the upload is built and tested; the Apple and Google accounts (D-7) are plugged in at PC-070.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>PC-075</t>
+          <t>PC-017</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Role-based app generator: a complete app per role (nav, pages, API scope, permissions)</t>
+          <t>Pack framework core: manifest v2 schema, registry/loader, composer (merge, wire, validate, conflict rules)</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -6665,7 +6665,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6679,19 +6679,19 @@
       <c r="I6" s="3" t="inlineStr"/>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>R-555/R-562 already build one app per role; the spec asks for role-scoped pages and APIs. From specs/pack-framework/06b.</t>
+          <t>Solution Pack manifests, registry and application exist (R-434..R-445); v2 adds ir_delta, state machines, page templates, dependencies. From specs/pack-framework 01, 02.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>PC-077</t>
+          <t>PC-075</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Rich seed data generator: realistic, domain-aware, deterministic demo data</t>
+          <t>Role-based app generator: a complete app per role (nav, pages, API scope, permissions)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -6709,33 +6709,33 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F7" s="10" t="inlineStr">
+      <c r="F7" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G7" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr"/>
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>Fixture seeds exist (R-248) and must stay deterministic (R-586). From specs/pack-framework/06e.</t>
+          <t>R-555/R-562 already build one app per role; the spec asks for role-scoped pages and APIs. From specs/pack-framework/06b.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>PC-073</t>
+          <t>PC-077</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Horizontal packs, wave 1: the P0/P1 universal packs as manifest v2 packs that work alone and compose (HP-* rows)</t>
+          <t>Rich seed data generator: realistic, domain-aware, deterministic demo data</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -6753,33 +6753,33 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="F8" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr"/>
       <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>Core first (auth, database, API, design system, admin, payments, notifications, files, realtime, workflows), then the mobile &amp; device and AI packs. Each pack packages a capability built by its own task. Full list: PACK_CATALOG.md.</t>
+          <t>Fixture seeds exist (R-248) and must stay deterministic (R-586). From specs/pack-framework/06e.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>PC-074</t>
+          <t>PC-073</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Vertical packs, wave 1: healthcare, mobility, commerce (VP-* rows) on every surface: API, web, app, admin panel</t>
+          <t>Horizontal packs, wave 1: the P0/P1 universal packs as manifest v2 packs that work alone and compose (HP-* rows)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -6797,7 +6797,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr">
+      <c r="F9" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6811,19 +6811,19 @@
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>Built from the CareClinic, RideNow and Bazaar templates.</t>
+          <t>Core first (auth, database, API, design system, admin, payments, notifications, files, realtime, workflows), then the mobile &amp; device and AI packs. Each pack packages a capability built by its own task. Full list: PACK_CATALOG.md.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>PC-020</t>
+          <t>PC-074</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Brand kit / Style DNA UI across all surfaces</t>
+          <t>Vertical packs, wave 1: healthcare, mobility, commerce (VP-* rows) on every surface: API, web, app, admin panel</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -6833,7 +6833,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Vibe</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -6841,33 +6841,33 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G10" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr"/>
       <c r="I10" s="3" t="inlineStr"/>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>brand.json exists (R-548); needs the UI. Buildout idea 'R-526'.</t>
+          <t>Built from the CareClinic, RideNow and Bazaar templates.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>PC-023</t>
+          <t>PC-020</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Stack chooser: pick web/admin/mobile/backend, refused with a reason when unsupported</t>
+          <t>Brand kit / Style DNA UI across all surfaces</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -6877,41 +6877,41 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Vibe</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>3 Engineering Mode</t>
-        </is>
-      </c>
-      <c r="F11" s="10" t="inlineStr">
+          <t>2 Maximum features</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr"/>
       <c r="I11" s="3" t="inlineStr"/>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>R-565 carries the stack in the IR; needs the UI.</t>
+          <t>brand.json exists (R-548); needs the UI. Buildout idea 'R-526'.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>R-579</t>
+          <t>PC-023</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>GitHub import and push-back</t>
+          <t>Stack chooser: pick web/admin/mobile/backend, refused with a reason when unsupported</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -6929,7 +6929,7 @@
           <t>3 Engineering Mode</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr">
+      <c r="F12" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6943,19 +6943,19 @@
       <c r="I12" s="3" t="inlineStr"/>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>R-501 can push a generated project; import is missing.</t>
+          <t>R-565 carries the stack in the IR; needs the UI.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>PC-025</t>
+          <t>R-579</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Verification report view: per-surface compile, tests, security, in the Studio</t>
+          <t>GitHub import and push-back</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -6973,7 +6973,7 @@
           <t>3 Engineering Mode</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="F13" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6987,19 +6987,19 @@
       <c r="I13" s="3" t="inlineStr"/>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>R-560/R-561/R-508 produce the data; nothing shows it as a report.</t>
+          <t>R-501 can push a generated project; import is missing.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>PC-029</t>
+          <t>PC-025</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Team collaboration: roles, approvals, preview comments</t>
+          <t>Verification report view: per-surface compile, tests, security, in the Studio</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -7017,33 +7017,33 @@
           <t>3 Engineering Mode</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr">
+      <c r="F14" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G14" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr"/>
       <c r="I14" s="3" t="inlineStr"/>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>R-515 gives teams.</t>
+          <t>R-560/R-561/R-508 produce the data; nothing shows it as a report.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>PC-036</t>
+          <t>PC-029</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Migration safety checks for generated schema changes</t>
+          <t>Team collaboration: roles, approvals, preview comments</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -7053,55 +7053,59 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>4 Production ops</t>
-        </is>
-      </c>
-      <c r="F15" s="10" t="inlineStr">
+          <t>3 Engineering Mode</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr"/>
       <c r="I15" s="3" t="inlineStr"/>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>R-584 flags data loss; needs a real gate.</t>
+          <t>R-515 gives teams.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>ARCH-DOMAIN-IR</t>
+          <t>PC-036</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Domain IR: guards, business rules, field masks, row filters, page templates</t>
+          <t>Migration safety checks for generated schema changes</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>docs/ARCHITECTURE_MASTER_PLAN.md §5.2</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr"/>
+          <t>Platform_Completion queue</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>2 Maximum features</t>
-        </is>
-      </c>
-      <c r="F16" s="10" t="inlineStr">
+          <t>4 Production ops</t>
+        </is>
+      </c>
+      <c r="F16" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7111,32 +7115,28 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>R-570</t>
-        </is>
-      </c>
+      <c r="H16" s="3" t="inlineStr"/>
       <c r="I16" s="3" t="inlineStr"/>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>State machines done (R-566); field masks and row filters are R-570; guards and rules R-571.</t>
+          <t>R-584 flags data loss; needs a real gate.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>ARCH-GENERATORS</t>
+          <t>ARCH-DOMAIN-IR</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Advanced generators: state machine, role app, page template, shared package, seed data, form wizard, realtime</t>
+          <t>Domain IR: guards, business rules, field masks, row filters, page templates</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>docs/ARCHITECTURE_MASTER_PLAN.md §5.3</t>
+          <t>docs/ARCHITECTURE_MASTER_PLAN.md §5.2</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr"/>
@@ -7145,7 +7145,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F17" s="10" t="inlineStr">
+      <c r="F17" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7157,74 +7157,74 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>PC-017</t>
+          <t>R-570</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr"/>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>State machine done (R-566/588/589); shared package R-572; form wizard PC-059; realtime R-569.</t>
+          <t>State machines done (R-566); field masks and row filters are R-570; guards and rules R-571.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>ARCH-PIPELINE</t>
+          <t>ARCH-GENERATORS</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Vibe pipeline: classify -&gt; select packs -&gt; compose IR -&gt; generate -&gt; provision -&gt; preview in 90 s</t>
+          <t>Advanced generators: state machine, role app, page template, shared package, seed data, form wizard, realtime</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>docs/ARCHITECTURE_MASTER_PLAN.md §4.1</t>
+          <t>docs/ARCHITECTURE_MASTER_PLAN.md §5.3</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr"/>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Delivered</t>
-        </is>
-      </c>
-      <c r="F18" s="10" t="inlineStr">
+          <t>2 Maximum features</t>
+        </is>
+      </c>
+      <c r="F18" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>P0</t>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>PC-004</t>
+          <t>PC-017</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr"/>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>Generate and preview exist; provision is PC-049.</t>
+          <t>State machine done (R-566/588/589); shared package R-572; form wizard PC-059; realtime R-569.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>ARCH-PWA</t>
+          <t>ARCH-PIPELINE</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>PWA / offline support</t>
+          <t>Vibe pipeline: classify -&gt; select packs -&gt; compose IR -&gt; generate -&gt; provision -&gt; preview in 90 s</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>docs/ARCHITECTURE_MASTER_PLAN.md §10 Phase 4</t>
+          <t>docs/ARCHITECTURE_MASTER_PLAN.md §4.1</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr"/>
@@ -7233,7 +7233,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F19" s="10" t="inlineStr">
+      <c r="F19" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7245,47 +7245,51 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>R-573</t>
+          <t>PC-004</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr"/>
-      <c r="J19" s="3" t="inlineStr"/>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>Generate and preview exist; provision is PC-049.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>BP-BRANDKIT</t>
+          <t>ARCH-PWA</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Style DNA UI and brand kit studio</t>
+          <t>PWA / offline support</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Platform_Buildout section 8 ('R-526')</t>
+          <t>docs/ARCHITECTURE_MASTER_PLAN.md §10 Phase 4</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr"/>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>2 Maximum features</t>
-        </is>
-      </c>
-      <c r="F20" s="10" t="inlineStr">
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="F20" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G20" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>PC-020</t>
+          <t>R-573</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr"/>
@@ -7294,70 +7298,66 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>BP-SWITCHER</t>
+          <t>BP-BRANDKIT</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Multi-app ecosystem switcher and persona simulator</t>
+          <t>Style DNA UI and brand kit studio</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Platform_Buildout section 8 ('R-521')</t>
+          <t>Platform_Buildout section 8 ('R-526')</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr"/>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Delivered</t>
-        </is>
-      </c>
-      <c r="F21" s="10" t="inlineStr">
+          <t>2 Maximum features</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>PC-006</t>
+          <t>PC-020</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr"/>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>Multi-app preview exists (R-520, R-553); personas do not.</t>
-        </is>
-      </c>
+      <c r="J21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>GA-03</t>
+          <t>BP-SWITCHER</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>First-class Ollama-compatible provider with quality eval</t>
+          <t>Multi-app ecosystem switcher and persona simulator</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Tracker RND_Gap_Audit</t>
+          <t>Platform_Buildout section 8 ('R-521')</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr"/>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>1 Vibe Mode live</t>
-        </is>
-      </c>
-      <c r="F22" s="10" t="inlineStr">
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="F22" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7369,25 +7369,25 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>PC-014</t>
+          <t>PC-006</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr"/>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>Provider done (R-006); eval missing.</t>
+          <t>Multi-app preview exists (R-520, R-553); personas do not.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>GA-04</t>
+          <t>GA-03</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Per-model safe context registry, no silent truncation</t>
+          <t>First-class Ollama-compatible provider with quality eval</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -7401,7 +7401,7 @@
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="F23" s="10" t="inlineStr">
+      <c r="F23" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7419,19 +7419,19 @@
       <c r="I23" s="3" t="inlineStr"/>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>Safe input budget exists (R-522).</t>
+          <t>Provider done (R-006); eval missing.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>GA-05</t>
+          <t>GA-04</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Route by measured task, eval, latency, context and cost</t>
+          <t>Per-model safe context registry, no silent truncation</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -7445,14 +7445,14 @@
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="F24" s="10" t="inlineStr">
+      <c r="F24" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G24" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -7461,17 +7461,21 @@
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr"/>
-      <c r="J24" s="3" t="inlineStr"/>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>Safe input budget exists (R-522).</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>GA-07</t>
+          <t>GA-05</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Environments local -&gt; test -&gt; preview -&gt; staging -&gt; prod with typed config</t>
+          <t>Route by measured task, eval, latency, context and cost</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -7482,10 +7486,10 @@
       <c r="D25" s="3" t="inlineStr"/>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>4 Production ops</t>
-        </is>
-      </c>
-      <c r="F25" s="10" t="inlineStr">
+          <t>1 Vibe Mode live</t>
+        </is>
+      </c>
+      <c r="F25" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7497,7 +7501,7 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>PC-040</t>
+          <t>PC-014</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr"/>
@@ -7506,12 +7510,12 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>GA-11</t>
+          <t>GA-07</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Pinned supply chain, SBOM/provenance, patch SLA</t>
+          <t>Environments local -&gt; test -&gt; preview -&gt; staging -&gt; prod with typed config</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -7525,7 +7529,7 @@
           <t>4 Production ops</t>
         </is>
       </c>
-      <c r="F26" s="10" t="inlineStr">
+      <c r="F26" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7537,30 +7541,26 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>PC-035</t>
+          <t>PC-040</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr"/>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>Lockfiles pinned; SBOM missing.</t>
-        </is>
-      </c>
+      <c r="J26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>GAP-TESTTOOLS</t>
+          <t>GA-11</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Pin the testing toolchain (Playwright, pytest, go test, k6)</t>
+          <t>Pinned supply chain, SBOM/provenance, patch SLA</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>V6_Review_and_Gap_Analysis section 3</t>
+          <t>Tracker RND_Gap_Audit</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr"/>
@@ -7569,7 +7569,7 @@
           <t>4 Production ops</t>
         </is>
       </c>
-      <c r="F27" s="10" t="inlineStr">
+      <c r="F27" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7581,43 +7581,39 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>PC-037</t>
+          <t>PC-035</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr"/>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>pytest/unittest, go test and Playwright (templates) are in use; k6 is not.</t>
+          <t>Lockfiles pinned; SBOM missing.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>HP-accessibility</t>
+          <t>GAP-TESTTOOLS</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack accessibility: WCAG 2.1 AA, automated axe checks</t>
+          <t>Pin the testing toolchain (Playwright, pytest, go test, k6)</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>spec</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>UI &amp; experience</t>
-        </is>
-      </c>
+          <t>V6_Review_and_Gap_Analysis section 3</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr"/>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>2 Maximum features</t>
-        </is>
-      </c>
-      <c r="F28" s="10" t="inlineStr">
+          <t>4 Production ops</t>
+        </is>
+      </c>
+      <c r="F28" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7629,35 +7625,35 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>PC-078</t>
+          <t>PC-037</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr"/>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>Accessible UI exists (R-296).</t>
+          <t>pytest/unittest, go test and Playwright (templates) are in use; k6 is not.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>HP-activity-feed</t>
+          <t>HP-accessibility</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack activity-feed: Activity streams, timelines, follow/subscribe</t>
+          <t>Horizontal pack accessibility: WCAG 2.1 AA, automated axe checks</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>new (registry dependency)</t>
+          <t>spec</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Realtime &amp; communication</t>
+          <t>UI &amp; experience</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -7665,7 +7661,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F29" s="10" t="inlineStr">
+      <c r="F29" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7683,29 +7679,29 @@
       <c r="I29" s="3" t="inlineStr"/>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>Timeline component exists (R-336).</t>
+          <t>Accessible UI exists (R-296).</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>HP-admin-crud</t>
+          <t>HP-activity-feed</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack admin-crud: Generated admin: tables, filters, bulk actions, exports</t>
+          <t>Horizontal pack activity-feed: Activity streams, timelines, follow/subscribe</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>spec</t>
+          <t>new (registry dependency)</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Core platform</t>
+          <t>Realtime &amp; communication</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -7713,47 +7709,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F30" s="10" t="inlineStr">
+      <c r="F30" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G30" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>PC-073</t>
+          <t>PC-078</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr"/>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>Admin app exists (R-542, R-270, R-271).</t>
+          <t>Timeline component exists (R-336).</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>HP-analytics-events</t>
+          <t>HP-admin-crud</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack analytics-events: Event tracking, funnels, cohorts (PostHog/GA4)</t>
+          <t>Horizontal pack admin-crud: Generated admin: tables, filters, bulk actions, exports</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>spec, registry</t>
+          <t>spec</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Data &amp; storage</t>
+          <t>Core platform</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -7761,47 +7757,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F31" s="10" t="inlineStr">
+      <c r="F31" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G31" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>PC-078</t>
+          <t>PC-073</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr"/>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>Published-app analytics exists (R-513).</t>
+          <t>Admin app exists (R-542, R-270, R-271).</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>HP-api-core</t>
+          <t>HP-analytics-events</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack api-core: REST API, validation, OpenAPI, errors, rate limiting</t>
+          <t>Horizontal pack analytics-events: Event tracking, funnels, cohorts (PostHog/GA4)</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>registry</t>
+          <t>spec, registry</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Core platform</t>
+          <t>Data &amp; storage</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -7809,42 +7805,42 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F32" s="10" t="inlineStr">
+      <c r="F32" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G32" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G32" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>PC-073</t>
+          <t>PC-078</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr"/>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>Python/Go/Node APIs exist (R-229, R-230, R-517).</t>
+          <t>Published-app analytics exists (R-513).</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>HP-api-docs</t>
+          <t>HP-api-core</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack api-docs: OpenAPI, Swagger UI, Postman collection, SDKs</t>
+          <t>Horizontal pack api-core: REST API, validation, OpenAPI, errors, rate limiting</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>spec</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -7857,47 +7853,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F33" s="10" t="inlineStr">
+      <c r="F33" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G33" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>PC-078</t>
+          <t>PC-073</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr"/>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>OpenAPI exists (R-260, R-588).</t>
+          <t>Python/Go/Node APIs exist (R-229, R-230, R-517).</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>HP-app-store-assets</t>
+          <t>HP-api-docs</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack app-store-assets: Icons, splash, screenshots, store listing metadata</t>
+          <t>Horizontal pack api-docs: OpenAPI, Swagger UI, Postman collection, SDKs</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>spec</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Mobile &amp; device (stack-aware: React Native, Kotlin, Swift)</t>
+          <t>Core platform</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -7905,47 +7901,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F34" s="10" t="inlineStr">
+      <c r="F34" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G34" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>PC-073</t>
+          <t>PC-078</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr"/>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>Icons and EAS config exist (R-546, R-547); R-574.</t>
+          <t>OpenAPI exists (R-260, R-588).</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>HP-auth-rbac</t>
+          <t>HP-app-store-assets</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack auth-rbac: Login, register, roles, sessions, MFA, OAuth, passkeys</t>
+          <t>Horizontal pack app-store-assets: Icons, splash, screenshots, store listing metadata</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>spec, registry</t>
+          <t>new</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Core platform</t>
+          <t>Mobile &amp; device (stack-aware: React Native, Kotlin, Swift)</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -7953,7 +7949,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F35" s="10" t="inlineStr">
+      <c r="F35" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7971,29 +7967,29 @@
       <c r="I35" s="3" t="inlineStr"/>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>Auth exists (R-461, R-241..R-243); Go login R-591.</t>
+          <t>Icons and EAS config exist (R-546, R-547); R-574.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>HP-camera-qr</t>
+          <t>HP-auth-rbac</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack camera-qr: Camera, photo/video capture, QR and barcode scanning</t>
+          <t>Horizontal pack auth-rbac: Login, register, roles, sessions, MFA, OAuth, passkeys</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>PRD (+ registry 'barcode')</t>
+          <t>spec, registry</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Mobile &amp; device (stack-aware: React Native, Kotlin, Swift)</t>
+          <t>Core platform</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -8001,7 +7997,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F36" s="10" t="inlineStr">
+      <c r="F36" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8019,29 +8015,29 @@
       <c r="I36" s="3" t="inlineStr"/>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>QR generation exists (R-382).</t>
+          <t>Auth exists (R-461, R-241..R-243); Go login R-591.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>HP-charts-dashboards</t>
+          <t>HP-camera-qr</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack charts-dashboards: Charts, dashboards, live series</t>
+          <t>Horizontal pack camera-qr: Camera, photo/video capture, QR and barcode scanning</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>registry</t>
+          <t>PRD (+ registry 'barcode')</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>UI &amp; experience</t>
+          <t>Mobile &amp; device (stack-aware: React Native, Kotlin, Swift)</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -8049,37 +8045,37 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F37" s="10" t="inlineStr">
+      <c r="F37" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G37" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>PC-078</t>
+          <t>PC-073</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr"/>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>Chart suite exists (R-370).</t>
+          <t>QR generation exists (R-382).</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>HP-ci-cd</t>
+          <t>HP-charts-dashboards</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack ci-cd: CI workflows, containers, Helm, preview environments</t>
+          <t>Horizontal pack charts-dashboards: Charts, dashboards, live series</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -8089,7 +8085,7 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Core platform</t>
+          <t>UI &amp; experience</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -8097,7 +8093,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F38" s="10" t="inlineStr">
+      <c r="F38" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8115,29 +8111,29 @@
       <c r="I38" s="3" t="inlineStr"/>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>CI/CD workflow generation exists (R-452).</t>
+          <t>Chart suite exists (R-370).</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>HP-communications</t>
+          <t>HP-ci-cd</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack communications: 1:1 and group chat, threads, mentions, reactions, attachments</t>
+          <t>Horizontal pack ci-cd: CI workflows, containers, Helm, preview environments</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>spec, registry</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Realtime &amp; communication</t>
+          <t>Core platform</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -8145,7 +8141,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F39" s="10" t="inlineStr">
+      <c r="F39" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8163,29 +8159,29 @@
       <c r="I39" s="3" t="inlineStr"/>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>Chat component exists (R-384).</t>
+          <t>CI/CD workflow generation exists (R-452).</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>HP-config-env</t>
+          <t>HP-communications</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack config-env: Typed env config, secret references, multi-environment</t>
+          <t>Horizontal pack communications: 1:1 and group chat, threads, mentions, reactions, attachments</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>registry</t>
+          <t>spec, registry</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Core platform</t>
+          <t>Realtime &amp; communication</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -8193,7 +8189,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F40" s="10" t="inlineStr">
+      <c r="F40" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8211,29 +8207,29 @@
       <c r="I40" s="3" t="inlineStr"/>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>Credential templates exist (R-547).</t>
+          <t>Chat component exists (R-384).</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>HP-consent-management</t>
+          <t>HP-config-env</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack consent-management: Consent capture and ledger, cookie preferences</t>
+          <t>Horizontal pack config-env: Typed env config, secret references, multi-environment</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>new (registry dependency)</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Security &amp; compliance</t>
+          <t>Core platform</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -8241,7 +8237,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F41" s="10" t="inlineStr">
+      <c r="F41" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8259,29 +8255,29 @@
       <c r="I41" s="3" t="inlineStr"/>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>Cookie consent component exists (R-402).</t>
+          <t>Credential templates exist (R-547).</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>HP-custom-domains</t>
+          <t>HP-consent-management</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack custom-domains: Custom domains, DNS, TLS certificates</t>
+          <t>Horizontal pack consent-management: Consent capture and ledger, cookie preferences</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>new (registry dependency 'dns')</t>
+          <t>new (registry dependency)</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Core platform</t>
+          <t>Security &amp; compliance</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -8289,7 +8285,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F42" s="10" t="inlineStr">
+      <c r="F42" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8307,29 +8303,29 @@
       <c r="I42" s="3" t="inlineStr"/>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>Custom domains exist for published apps (R-510).</t>
+          <t>Cookie consent component exists (R-402).</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>HP-data-import-export</t>
+          <t>HP-custom-domains</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack data-import-export: CSV/Excel import with mapping and validation; bulk export</t>
+          <t>Horizontal pack custom-domains: Custom domains, DNS, TLS certificates</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>new (registry dependency 'dns')</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>Data &amp; storage</t>
+          <t>Core platform</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -8337,7 +8333,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F43" s="10" t="inlineStr">
+      <c r="F43" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8355,29 +8351,29 @@
       <c r="I43" s="3" t="inlineStr"/>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>CSV/JSON export exists (R-271, R-308).</t>
+          <t>Custom domains exist for published apps (R-510).</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>HP-data-tables</t>
+          <t>HP-data-import-export</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack data-tables: Virtualised tables, grouping, column picker, export</t>
+          <t>Horizontal pack data-import-export: CSV/Excel import with mapping and validation; bulk export</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>registry</t>
+          <t>new</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>UI &amp; experience</t>
+          <t>Data &amp; storage</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -8385,7 +8381,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F44" s="10" t="inlineStr">
+      <c r="F44" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8403,19 +8399,19 @@
       <c r="I44" s="3" t="inlineStr"/>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>Data grid exists (R-329).</t>
+          <t>CSV/JSON export exists (R-271, R-308).</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>HP-database-pg</t>
+          <t>HP-data-tables</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack database-pg: PostgreSQL schema, migrations, seeds, row-level security</t>
+          <t>Horizontal pack data-tables: Virtualised tables, grouping, column picker, export</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -8425,7 +8421,7 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Core platform</t>
+          <t>UI &amp; experience</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -8433,37 +8429,37 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F45" s="10" t="inlineStr">
+      <c r="F45" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G45" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G45" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>PC-073</t>
+          <t>PC-078</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr"/>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>Schema/migrations/seeds exist (R-238, R-248).</t>
+          <t>Data grid exists (R-329).</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>HP-design-system</t>
+          <t>HP-database-pg</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack design-system: Design tokens, components, motion, dark mode</t>
+          <t>Horizontal pack database-pg: PostgreSQL schema, migrations, seeds, row-level security</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -8473,7 +8469,7 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>UI &amp; experience</t>
+          <t>Core platform</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -8481,7 +8477,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F46" s="10" t="inlineStr">
+      <c r="F46" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8499,29 +8495,29 @@
       <c r="I46" s="3" t="inlineStr"/>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>Design system exists (R-558, R-324, R-491).</t>
+          <t>Schema/migrations/seeds exist (R-238, R-248).</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>HP-e-sign</t>
+          <t>HP-design-system</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack e-sign: Document signing, signer flows, certificates</t>
+          <t>Horizontal pack design-system: Design tokens, components, motion, dark mode</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>new (registry dependency)</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>Business logic &amp; workflow</t>
+          <t>UI &amp; experience</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -8529,47 +8525,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F47" s="10" t="inlineStr">
+      <c r="F47" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G47" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>PC-078</t>
+          <t>PC-073</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr"/>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>Signature pad exists (R-372).</t>
+          <t>Design system exists (R-558, R-324, R-491).</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>HP-integration-hub</t>
+          <t>HP-e-sign</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack integration-hub: Connectors (Slack, HubSpot, Salesforce ...), workflow builder</t>
+          <t>Horizontal pack e-sign: Document signing, signer flows, certificates</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>registry</t>
+          <t>new (registry dependency)</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Integration &amp; AI</t>
+          <t>Business logic &amp; workflow</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
@@ -8577,7 +8573,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F48" s="10" t="inlineStr">
+      <c r="F48" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8595,29 +8591,29 @@
       <c r="I48" s="3" t="inlineStr"/>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>Connectors v1 exist (R-511).</t>
+          <t>Signature pad exists (R-372).</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>HP-maps-geo</t>
+          <t>HP-integration-hub</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack maps-geo: Maps, geocoding, geofences, routes, address autocomplete</t>
+          <t>Horizontal pack integration-hub: Connectors (Slack, HubSpot, Salesforce ...), workflow builder</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>registry ('mapping', listed under mobility), PRD</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>UI &amp; experience</t>
+          <t>Integration &amp; AI</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -8625,47 +8621,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F49" s="10" t="inlineStr">
+      <c r="F49" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G49" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G49" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>PC-073</t>
+          <t>PC-078</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr"/>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>Geo-map component exists (R-387).</t>
+          <t>Connectors v1 exist (R-511).</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>HP-media-player-device</t>
+          <t>HP-maps-geo</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack media-player-device: Audio/video playback, background audio, casting</t>
+          <t>Horizontal pack maps-geo: Maps, geocoding, geofences, routes, address autocomplete</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>registry ('mapping', listed under mobility), PRD</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Mobile &amp; device (stack-aware: React Native, Kotlin, Swift)</t>
+          <t>UI &amp; experience</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -8673,47 +8669,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F50" s="10" t="inlineStr">
+      <c r="F50" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G50" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>PC-079</t>
+          <t>PC-073</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr"/>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>Web media players exist (R-376, R-390).</t>
+          <t>Geo-map component exists (R-387).</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>HP-multi-app</t>
+          <t>HP-media-player-device</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack multi-app: Shared API, cross-app auth, preview proxy, deploy coordination</t>
+          <t>Horizontal pack media-player-device: Audio/video playback, background audio, casting</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>spec</t>
+          <t>new</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Core platform</t>
+          <t>Mobile &amp; device (stack-aware: React Native, Kotlin, Swift)</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -8721,47 +8717,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F51" s="10" t="inlineStr">
+      <c r="F51" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G51" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G51" s="12" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>PC-073</t>
+          <t>PC-079</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr"/>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>Ecosystem monorepo exists (R-554, R-447, R-553).</t>
+          <t>Web media players exist (R-376, R-390).</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>HP-multi-currency</t>
+          <t>HP-multi-app</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack multi-currency: Currencies, exchange rates, price lists</t>
+          <t>Horizontal pack multi-app: Shared API, cross-app auth, preview proxy, deploy coordination</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>registry (listed under commerce)</t>
+          <t>spec</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Commerce &amp; payments</t>
+          <t>Core platform</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
@@ -8769,47 +8765,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F52" s="10" t="inlineStr">
+      <c r="F52" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G52" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G52" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>PC-078</t>
+          <t>PC-073</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr"/>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>Currency input exists (R-409).</t>
+          <t>Ecosystem monorepo exists (R-554, R-447, R-553).</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>HP-notifications</t>
+          <t>HP-multi-currency</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack notifications: Email, SMS, push, in-app centre, preferences, digests</t>
+          <t>Horizontal pack multi-currency: Currencies, exchange rates, price lists</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>spec, registry</t>
+          <t>registry (listed under commerce)</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Realtime &amp; communication</t>
+          <t>Commerce &amp; payments</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
@@ -8817,47 +8813,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F53" s="10" t="inlineStr">
+      <c r="F53" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G53" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G53" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>PC-073</t>
+          <t>PC-078</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr"/>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>Email exists (R-516); PC-053.</t>
+          <t>Currency input exists (R-409).</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>HP-onboarding-tours</t>
+          <t>HP-notifications</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack onboarding-tours: Product tours and spotlight guides</t>
+          <t>Horizontal pack notifications: Email, SMS, push, in-app centre, preferences, digests</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>spec, registry</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>UI &amp; experience</t>
+          <t>Realtime &amp; communication</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
@@ -8865,47 +8861,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F54" s="10" t="inlineStr">
+      <c r="F54" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G54" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>PC-079</t>
+          <t>PC-073</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr"/>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>Tour component exists (R-363).</t>
+          <t>Email exists (R-516); PC-053.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>HP-payments-core</t>
+          <t>HP-onboarding-tours</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack payments-core: Stripe/Razorpay/Paddle payments, refunds, disputes</t>
+          <t>Horizontal pack onboarding-tours: Product tours and spotlight guides</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>spec, registry, PRD</t>
+          <t>new</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Commerce &amp; payments</t>
+          <t>UI &amp; experience</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -8913,47 +8909,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F55" s="10" t="inlineStr">
+      <c r="F55" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G55" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G55" s="12" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>PC-073</t>
+          <t>PC-079</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr"/>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>Checkout exists (R-512).</t>
+          <t>Tour component exists (R-363).</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>HP-pdf-documents</t>
+          <t>HP-payments-core</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack pdf-documents: Document templates, PDF generation, document store</t>
+          <t>Horizontal pack payments-core: Stripe/Razorpay/Paddle payments, refunds, disputes</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>new (registry dependencies 'documents', 'pdf-generation')</t>
+          <t>spec, registry, PRD</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Data &amp; storage</t>
+          <t>Commerce &amp; payments</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
@@ -8961,47 +8957,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F56" s="10" t="inlineStr">
+      <c r="F56" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G56" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G56" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>PC-078</t>
+          <t>PC-073</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr"/>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>PDF viewer component exists (R-388).</t>
+          <t>Checkout exists (R-512).</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>HP-pwa</t>
+          <t>HP-pdf-documents</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack pwa: Installable app, service worker, offline, push, QR</t>
+          <t>Horizontal pack pdf-documents: Document templates, PDF generation, document store</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>spec</t>
+          <t>new (registry dependencies 'documents', 'pdf-generation')</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>UI &amp; experience</t>
+          <t>Data &amp; storage</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
@@ -9009,37 +9005,37 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F57" s="10" t="inlineStr">
+      <c r="F57" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G57" s="6" t="inlineStr">
-        <is>
-          <t>P0</t>
+      <c r="G57" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>PC-073</t>
+          <t>PC-078</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr"/>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>R-573.</t>
+          <t>PDF viewer component exists (R-388).</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>HP-ratings-reviews</t>
+          <t>HP-pwa</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack ratings-reviews: Stars, reviews, moderation, aggregates</t>
+          <t>Horizontal pack pwa: Installable app, service worker, offline, push, QR</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -9049,7 +9045,7 @@
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Business logic &amp; workflow</t>
+          <t>UI &amp; experience</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
@@ -9057,47 +9053,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F58" s="10" t="inlineStr">
+      <c r="F58" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G58" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>PC-078</t>
+          <t>PC-073</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr"/>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>Rating component exists (R-333).</t>
+          <t>R-573.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>HP-rich-text</t>
+          <t>HP-ratings-reviews</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack rich-text: Rich text editor, mentions, slash commands</t>
+          <t>Horizontal pack ratings-reviews: Stars, reviews, moderation, aggregates</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>registry</t>
+          <t>spec</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>UI &amp; experience</t>
+          <t>Business logic &amp; workflow</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -9105,7 +9101,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F59" s="10" t="inlineStr">
+      <c r="F59" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9123,29 +9119,29 @@
       <c r="I59" s="3" t="inlineStr"/>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>Markdown editor exists (R-365).</t>
+          <t>Rating component exists (R-333).</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>HP-scheduling</t>
+          <t>HP-rich-text</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack scheduling: Calendars, recurrence, conflicts, time zones, bookings, reminders</t>
+          <t>Horizontal pack rich-text: Rich text editor, mentions, slash commands</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>spec, registry</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Business logic &amp; workflow</t>
+          <t>UI &amp; experience</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
@@ -9153,37 +9149,37 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F60" s="10" t="inlineStr">
+      <c r="F60" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G60" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G60" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>PC-073</t>
+          <t>PC-078</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr"/>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>Calendar/time-picker components exist (R-366, R-371).</t>
+          <t>Markdown editor exists (R-365).</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>HP-search-engine</t>
+          <t>HP-scheduling</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack search-engine: Meilisearch/Typesense, facets, typo tolerance</t>
+          <t>Horizontal pack scheduling: Calendars, recurrence, conflicts, time zones, bookings, reminders</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -9193,7 +9189,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Data &amp; storage</t>
+          <t>Business logic &amp; workflow</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
@@ -9201,47 +9197,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F61" s="10" t="inlineStr">
+      <c r="F61" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G61" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="G61" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>PC-079</t>
+          <t>PC-073</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr"/>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>Keyword search exists (R-261); PC-058.</t>
+          <t>Calendar/time-picker components exist (R-366, R-371).</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>HP-secrets</t>
+          <t>HP-search-engine</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack secrets: Secret management, rotation, audit</t>
+          <t>Horizontal pack search-engine: Meilisearch/Typesense, facets, typo tolerance</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>spec</t>
+          <t>spec, registry</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>Security &amp; compliance</t>
+          <t>Data &amp; storage</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
@@ -9249,47 +9245,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F62" s="10" t="inlineStr">
+      <c r="F62" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G62" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G62" s="12" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>PC-078</t>
+          <t>PC-079</t>
         </is>
       </c>
       <c r="I62" s="3" t="inlineStr"/>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>Platform secrets exist (R-503).</t>
+          <t>Keyword search exists (R-261); PC-058.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>HP-seo</t>
+          <t>HP-secrets</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack seo: Metadata, sitemaps, structured data, AI-search readiness</t>
+          <t>Horizontal pack secrets: Secret management, rotation, audit</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>new (registry dependency)</t>
+          <t>spec</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>UI &amp; experience</t>
+          <t>Security &amp; compliance</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
@@ -9297,7 +9293,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F63" s="10" t="inlineStr">
+      <c r="F63" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9315,29 +9311,29 @@
       <c r="I63" s="3" t="inlineStr"/>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>SEO exists (R-505).</t>
+          <t>Platform secrets exist (R-503).</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>HP-task-management</t>
+          <t>HP-seo</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack task-management: Tasks, assignees, due dates, boards</t>
+          <t>Horizontal pack seo: Metadata, sitemaps, structured data, AI-search readiness</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>new (registry dependency 'tasks')</t>
+          <t>new (registry dependency)</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>Business logic &amp; workflow</t>
+          <t>UI &amp; experience</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
@@ -9345,7 +9341,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F64" s="10" t="inlineStr">
+      <c r="F64" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9363,29 +9359,29 @@
       <c r="I64" s="3" t="inlineStr"/>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>Kanban component exists (R-367).</t>
+          <t>SEO exists (R-505).</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>HP-theming-branding</t>
+          <t>HP-task-management</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack theming-branding: Brand kit applied to every surface</t>
+          <t>Horizontal pack task-management: Tasks, assignees, due dates, boards</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>new (registry dependency 'tasks')</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>UI &amp; experience</t>
+          <t>Business logic &amp; workflow</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
@@ -9393,7 +9389,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F65" s="10" t="inlineStr">
+      <c r="F65" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9411,29 +9407,29 @@
       <c r="I65" s="3" t="inlineStr"/>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>brand.json exists (R-548); PC-020.</t>
+          <t>Kanban component exists (R-367).</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>HP-webhooks</t>
+          <t>HP-theming-branding</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack webhooks: Outgoing webhooks, retries, signatures, replay</t>
+          <t>Horizontal pack theming-branding: Brand kit applied to every surface</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>spec, registry</t>
+          <t>new</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>Realtime &amp; communication</t>
+          <t>UI &amp; experience</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
@@ -9441,7 +9437,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F66" s="10" t="inlineStr">
+      <c r="F66" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9459,19 +9455,19 @@
       <c r="I66" s="3" t="inlineStr"/>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>Cross-surface webhooks exist (R-448); PC-057.</t>
+          <t>brand.json exists (R-548); PC-020.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>HP-workflows-core</t>
+          <t>HP-webhooks</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack workflows-core: State machines, transitions, guards, actions, audit</t>
+          <t>Horizontal pack webhooks: Outgoing webhooks, retries, signatures, replay</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -9481,7 +9477,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>Business logic &amp; workflow</t>
+          <t>Realtime &amp; communication</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
@@ -9489,51 +9485,55 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F67" s="10" t="inlineStr">
+      <c r="F67" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G67" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G67" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H67" s="3" t="inlineStr">
         <is>
-          <t>PC-073</t>
+          <t>PC-078</t>
         </is>
       </c>
       <c r="I67" s="3" t="inlineStr"/>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>Transitions done (R-566, R-588, R-589); guards R-571; buttons R-590.</t>
+          <t>Cross-surface webhooks exist (R-448); PC-057.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>PG-17</t>
+          <t>HP-workflows-core</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>A fresh AI/developer session resumes the task from Git + durable state</t>
+          <t>Horizontal pack workflows-core: State machines, transitions, guards, actions, audit</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>Tracker Production_Gates</t>
-        </is>
-      </c>
-      <c r="D68" s="3" t="inlineStr"/>
+          <t>spec, registry</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Business logic &amp; workflow</t>
+        </is>
+      </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>4 Production ops</t>
-        </is>
-      </c>
-      <c r="F68" s="10" t="inlineStr">
+          <t>2 Maximum features</t>
+        </is>
+      </c>
+      <c r="F68" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9545,25 +9545,25 @@
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>PC-067</t>
+          <t>PC-073</t>
         </is>
       </c>
       <c r="I68" s="3" t="inlineStr"/>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>AGENTS.md, CURRENT_TASK.yaml and this queue exist; the formal drill does not.</t>
+          <t>Transitions done (R-566, R-588, R-589); guards R-571; buttons R-590.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>PG-19</t>
+          <t>PG-17</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Local model endpoint exposure/auth/network policy</t>
+          <t>A fresh AI/developer session resumes the task from Git + durable state</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
@@ -9574,10 +9574,10 @@
       <c r="D69" s="3" t="inlineStr"/>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>1 Vibe Mode live</t>
-        </is>
-      </c>
-      <c r="F69" s="10" t="inlineStr">
+          <t>4 Production ops</t>
+        </is>
+      </c>
+      <c r="F69" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9589,43 +9589,39 @@
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>PC-014</t>
+          <t>PC-067</t>
         </is>
       </c>
       <c r="I69" s="3" t="inlineStr"/>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>Ollama is loopback-only (R-003).</t>
+          <t>AGENTS.md, CURRENT_TASK.yaml and this queue exist; the formal drill does not.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>R-027</t>
+          <t>PG-19</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>pgvector initially</t>
+          <t>Local model endpoint exposure/auth/network policy</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>Execution_Tracker_v6</t>
-        </is>
-      </c>
-      <c r="D70" s="3" t="inlineStr">
-        <is>
-          <t>Data</t>
-        </is>
-      </c>
+          <t>Tracker Production_Gates</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr"/>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>3 Engineering Mode</t>
-        </is>
-      </c>
-      <c r="F70" s="10" t="inlineStr">
+          <t>1 Vibe Mode live</t>
+        </is>
+      </c>
+      <c r="F70" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9637,25 +9633,25 @@
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>R-581</t>
+          <t>PC-014</t>
         </is>
       </c>
       <c r="I70" s="3" t="inlineStr"/>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>Extension installed, no embeddings table.</t>
+          <t>Ollama is loopback-only (R-003).</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>R-040</t>
+          <t>R-027</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>Migration safety checks</t>
+          <t>pgvector initially</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -9665,15 +9661,15 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>4 Production ops</t>
-        </is>
-      </c>
-      <c r="F71" s="10" t="inlineStr">
+          <t>3 Engineering Mode</t>
+        </is>
+      </c>
+      <c r="F71" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9685,21 +9681,25 @@
       </c>
       <c r="H71" s="3" t="inlineStr">
         <is>
-          <t>PC-036</t>
+          <t>R-581</t>
         </is>
       </c>
       <c r="I71" s="3" t="inlineStr"/>
-      <c r="J71" s="3" t="inlineStr"/>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>Extension installed, no embeddings table.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>R-055</t>
+          <t>R-040</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>Verified integration catalog</t>
+          <t>Migration safety checks</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -9709,15 +9709,15 @@
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>Integrations</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>1 Vibe Mode live</t>
-        </is>
-      </c>
-      <c r="F72" s="10" t="inlineStr">
+          <t>4 Production ops</t>
+        </is>
+      </c>
+      <c r="F72" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9729,7 +9729,7 @@
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>PC-013</t>
+          <t>PC-036</t>
         </is>
       </c>
       <c r="I72" s="3" t="inlineStr"/>
@@ -9738,12 +9738,12 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>R-062</t>
+          <t>R-055</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>App Store / TestFlight automation</t>
+          <t>Verified integration catalog</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -9753,7 +9753,7 @@
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>Deployment</t>
+          <t>Integrations</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
@@ -9761,7 +9761,7 @@
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="F73" s="10" t="inlineStr">
+      <c r="F73" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9773,25 +9773,21 @@
       </c>
       <c r="H73" s="3" t="inlineStr">
         <is>
-          <t>R-574</t>
+          <t>PC-013</t>
         </is>
       </c>
       <c r="I73" s="3" t="inlineStr"/>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>React Native first; native reuses the pipeline (PC-044).</t>
-        </is>
-      </c>
+      <c r="J73" s="3" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>R-063</t>
+          <t>R-062</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>Play Store automation</t>
+          <t>App Store / TestFlight automation</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -9809,7 +9805,7 @@
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="F74" s="10" t="inlineStr">
+      <c r="F74" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9834,12 +9830,12 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>R-064</t>
+          <t>R-063</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>RBAC + approvals</t>
+          <t>Play Store automation</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -9849,41 +9845,45 @@
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Deployment</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>3 Engineering Mode</t>
-        </is>
-      </c>
-      <c r="F75" s="10" t="inlineStr">
+          <t>1 Vibe Mode live</t>
+        </is>
+      </c>
+      <c r="F75" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G75" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G75" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H75" s="3" t="inlineStr">
         <is>
-          <t>PC-029</t>
+          <t>R-574</t>
         </is>
       </c>
       <c r="I75" s="3" t="inlineStr"/>
-      <c r="J75" s="3" t="inlineStr"/>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>React Native first; native reuses the pipeline (PC-044).</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>R-080</t>
+          <t>R-064</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>Self-hosted/local models</t>
+          <t>RBAC + approvals</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -9893,45 +9893,41 @@
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>Models</t>
+          <t>Collaboration</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>1 Vibe Mode live</t>
-        </is>
-      </c>
-      <c r="F76" s="10" t="inlineStr">
+          <t>3 Engineering Mode</t>
+        </is>
+      </c>
+      <c r="F76" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G76" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G76" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>PC-014</t>
+          <t>PC-029</t>
         </is>
       </c>
       <c r="I76" s="3" t="inlineStr"/>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>Ollama adapter exists (R-003, R-006).</t>
-        </is>
-      </c>
+      <c r="J76" s="3" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>R-126</t>
+          <t>R-080</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>Organization &gt; Workspace &gt; Project &gt; Environment model</t>
+          <t>Self-hosted/local models</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
@@ -9941,45 +9937,45 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>Product Foundation</t>
+          <t>Models</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>4 Production ops</t>
-        </is>
-      </c>
-      <c r="F77" s="10" t="inlineStr">
+          <t>1 Vibe Mode live</t>
+        </is>
+      </c>
+      <c r="F77" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G77" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G77" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H77" s="3" t="inlineStr">
         <is>
-          <t>PC-040</t>
+          <t>PC-014</t>
         </is>
       </c>
       <c r="I77" s="3" t="inlineStr"/>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>Org, workspace and project exist (R-499, R-515).</t>
+          <t>Ollama adapter exists (R-003, R-006).</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>R-135</t>
+          <t>R-126</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>Stack selection wizard</t>
+          <t>Organization &gt; Workspace &gt; Project &gt; Environment model</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -9989,41 +9985,45 @@
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>Framework Strategy</t>
+          <t>Product Foundation</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>3 Engineering Mode</t>
-        </is>
-      </c>
-      <c r="F78" s="10" t="inlineStr">
+          <t>4 Production ops</t>
+        </is>
+      </c>
+      <c r="F78" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G78" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G78" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>PC-023</t>
+          <t>PC-040</t>
         </is>
       </c>
       <c r="I78" s="3" t="inlineStr"/>
-      <c r="J78" s="3" t="inlineStr"/>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>Org, workspace and project exist (R-499, R-515).</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>R-194</t>
+          <t>R-135</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>Hybrid BYOK/local mode</t>
+          <t>Stack selection wizard</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
@@ -10033,15 +10033,15 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Framework Strategy</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>1 Vibe Mode live</t>
-        </is>
-      </c>
-      <c r="F79" s="10" t="inlineStr">
+          <t>3 Engineering Mode</t>
+        </is>
+      </c>
+      <c r="F79" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10053,7 +10053,7 @@
       </c>
       <c r="H79" s="3" t="inlineStr">
         <is>
-          <t>PC-014</t>
+          <t>PC-023</t>
         </is>
       </c>
       <c r="I79" s="3" t="inlineStr"/>
@@ -10062,26 +10062,30 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>SPEC-PACK-01</t>
+          <t>R-194</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>Pack manifest v2 schema</t>
+          <t>Hybrid BYOK/local mode</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>specs/pack-framework/01</t>
-        </is>
-      </c>
-      <c r="D80" s="3" t="inlineStr"/>
+          <t>Execution_Tracker_v6</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>Execution</t>
+        </is>
+      </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>2 Maximum features</t>
-        </is>
-      </c>
-      <c r="F80" s="10" t="inlineStr">
+          <t>1 Vibe Mode live</t>
+        </is>
+      </c>
+      <c r="F80" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10093,30 +10097,26 @@
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>PC-017</t>
+          <t>PC-014</t>
         </is>
       </c>
       <c r="I80" s="3" t="inlineStr"/>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>Draft spec (called R-600 inside).</t>
-        </is>
-      </c>
+      <c r="J80" s="3" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>SPEC-PACK-06B</t>
+          <t>SPEC-PACK-01</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>Role-based app generator</t>
+          <t>Pack manifest v2 schema</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>specs/pack-framework/06b</t>
+          <t>specs/pack-framework/01</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr"/>
@@ -10125,7 +10125,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F81" s="10" t="inlineStr">
+      <c r="F81" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10137,30 +10137,30 @@
       </c>
       <c r="H81" s="3" t="inlineStr">
         <is>
-          <t>PC-075</t>
+          <t>PC-017</t>
         </is>
       </c>
       <c r="I81" s="3" t="inlineStr"/>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>R-555 and R-562 build one app per role; the spec asks for more.</t>
+          <t>Draft spec (called R-600 inside).</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>SPEC-PACK-06E</t>
+          <t>SPEC-PACK-06B</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>Rich seed data generator</t>
+          <t>Role-based app generator</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>specs/pack-framework/06e</t>
+          <t>specs/pack-framework/06b</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr"/>
@@ -10169,86 +10169,86 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F82" s="10" t="inlineStr">
+      <c r="F82" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G82" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G82" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>PC-077</t>
+          <t>PC-075</t>
         </is>
       </c>
       <c r="I82" s="3" t="inlineStr"/>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>Seeds exist (R-248); the spec asks for realistic volume.</t>
+          <t>R-555 and R-562 build one app per role; the spec asks for more.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>SPEC-TS-01</t>
+          <t>SPEC-PACK-06E</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>Instant chat -&gt; pretty UI</t>
+          <t>Rich seed data generator</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>specs/table-stakes/01</t>
+          <t>specs/pack-framework/06e</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr"/>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>Delivered</t>
-        </is>
-      </c>
-      <c r="F83" s="10" t="inlineStr">
+          <t>2 Maximum features</t>
+        </is>
+      </c>
+      <c r="F83" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G83" s="6" t="inlineStr">
-        <is>
-          <t>P0</t>
+      <c r="G83" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H83" s="3" t="inlineStr">
         <is>
-          <t>PC-006</t>
+          <t>PC-077</t>
         </is>
       </c>
       <c r="I83" s="3" t="inlineStr"/>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>Draft spec.</t>
+          <t>Seeds exist (R-248); the spec asks for realistic volume.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>SPEC-TS-03</t>
+          <t>SPEC-TS-01</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>One-click deploy</t>
+          <t>Instant chat -&gt; pretty UI</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>specs/table-stakes/03</t>
+          <t>specs/table-stakes/01</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr"/>
@@ -10257,7 +10257,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F84" s="10" t="inlineStr">
+      <c r="F84" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10269,7 +10269,7 @@
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>PC-008</t>
+          <t>PC-006</t>
         </is>
       </c>
       <c r="I84" s="3" t="inlineStr"/>
@@ -10282,60 +10282,56 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>VP-appointments</t>
+          <t>SPEC-TS-03</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>Vertical pack appointments: Appointments, slots, reminders, waitlist</t>
+          <t>One-click deploy</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>registry</t>
-        </is>
-      </c>
-      <c r="D85" s="3" t="inlineStr">
-        <is>
-          <t>Healthcare &amp; life sciences (healthcare-core)</t>
-        </is>
-      </c>
+          <t>specs/table-stakes/03</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr"/>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>2 Maximum features</t>
-        </is>
-      </c>
-      <c r="F85" s="10" t="inlineStr">
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="F85" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G85" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G85" s="6" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="H85" s="3" t="inlineStr">
         <is>
-          <t>PC-074</t>
+          <t>PC-008</t>
         </is>
       </c>
       <c r="I85" s="3" t="inlineStr"/>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>CareClinic template.</t>
+          <t>Draft spec.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>VP-cart-checkout</t>
+          <t>VP-appointments</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>Vertical pack cart-checkout: Cart, coupons, checkout sessions</t>
+          <t>Vertical pack appointments: Appointments, slots, reminders, waitlist</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -10345,7 +10341,7 @@
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>Marketplace &amp; commerce (commerce-core)</t>
+          <t>Healthcare &amp; life sciences (healthcare-core)</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
@@ -10353,7 +10349,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F86" s="10" t="inlineStr">
+      <c r="F86" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10371,19 +10367,19 @@
       <c r="I86" s="3" t="inlineStr"/>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>Bazaar template.</t>
+          <t>CareClinic template.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>VP-commissions</t>
+          <t>VP-cart-checkout</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>Vertical pack commissions: Commission rules, splits, payout cycles</t>
+          <t>Vertical pack cart-checkout: Cart, coupons, checkout sessions</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
@@ -10401,7 +10397,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F87" s="10" t="inlineStr">
+      <c r="F87" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10419,19 +10415,19 @@
       <c r="I87" s="3" t="inlineStr"/>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>Bazaar ledger.</t>
+          <t>Bazaar template.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>VP-dispatch</t>
+          <t>VP-commissions</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>Vertical pack dispatch: Zones, assignment rules, heatmaps</t>
+          <t>Vertical pack commissions: Commission rules, splits, payout cycles</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
@@ -10441,7 +10437,7 @@
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>Mobility &amp; on-demand (mobility-core)</t>
+          <t>Marketplace &amp; commerce (commerce-core)</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
@@ -10449,7 +10445,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F88" s="10" t="inlineStr">
+      <c r="F88" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10467,19 +10463,19 @@
       <c r="I88" s="3" t="inlineStr"/>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>RideNow template (partial).</t>
+          <t>Bazaar ledger.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>VP-drivers</t>
+          <t>VP-dispatch</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>Vertical pack drivers: Drivers, vehicles, documents, earnings</t>
+          <t>Vertical pack dispatch: Zones, assignment rules, heatmaps</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
@@ -10497,7 +10493,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F89" s="10" t="inlineStr">
+      <c r="F89" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10515,19 +10511,19 @@
       <c r="I89" s="3" t="inlineStr"/>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>RideNow template.</t>
+          <t>RideNow template (partial).</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>VP-emr</t>
+          <t>VP-drivers</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>Vertical pack emr: Encounters, notes, diagnoses, vitals</t>
+          <t>Vertical pack drivers: Drivers, vehicles, documents, earnings</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
@@ -10537,7 +10533,7 @@
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>Healthcare &amp; life sciences (healthcare-core)</t>
+          <t>Mobility &amp; on-demand (mobility-core)</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
@@ -10545,7 +10541,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F90" s="10" t="inlineStr">
+      <c r="F90" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10563,19 +10559,19 @@
       <c r="I90" s="3" t="inlineStr"/>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>CareClinic template (partial).</t>
+          <t>RideNow template.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>VP-listings</t>
+          <t>VP-emr</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>Vertical pack listings: Listings, categories, variants, media</t>
+          <t>Vertical pack emr: Encounters, notes, diagnoses, vitals</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -10585,7 +10581,7 @@
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>Marketplace &amp; commerce (commerce-core)</t>
+          <t>Healthcare &amp; life sciences (healthcare-core)</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
@@ -10593,7 +10589,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F91" s="10" t="inlineStr">
+      <c r="F91" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10611,24 +10607,24 @@
       <c r="I91" s="3" t="inlineStr"/>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>Bazaar template.</t>
+          <t>CareClinic template (partial).</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>VP-orders</t>
+          <t>VP-listings</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>Vertical pack orders: Orders, line items, timelines</t>
+          <t>Vertical pack listings: Listings, categories, variants, media</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>new (registry dependency)</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
@@ -10641,7 +10637,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F92" s="10" t="inlineStr">
+      <c r="F92" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10666,22 +10662,22 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>VP-patients</t>
+          <t>VP-orders</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>Vertical pack patients: Patients, records, insurance, consent</t>
+          <t>Vertical pack orders: Orders, line items, timelines</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>registry</t>
+          <t>new (registry dependency)</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>Healthcare &amp; life sciences (healthcare-core)</t>
+          <t>Marketplace &amp; commerce (commerce-core)</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
@@ -10689,7 +10685,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F93" s="10" t="inlineStr">
+      <c r="F93" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10707,19 +10703,19 @@
       <c r="I93" s="3" t="inlineStr"/>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>CareClinic template.</t>
+          <t>Bazaar template.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>VP-prescriptions</t>
+          <t>VP-patients</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>Vertical pack prescriptions: Prescriptions, medications, pharmacies</t>
+          <t>Vertical pack patients: Patients, records, insurance, consent</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -10737,7 +10733,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F94" s="10" t="inlineStr">
+      <c r="F94" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10755,19 +10751,19 @@
       <c r="I94" s="3" t="inlineStr"/>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>CareClinic template (partial).</t>
+          <t>CareClinic template.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>VP-providers</t>
+          <t>VP-prescriptions</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>Vertical pack providers: Providers, specialties, licences, schedules</t>
+          <t>Vertical pack prescriptions: Prescriptions, medications, pharmacies</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -10785,7 +10781,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F95" s="10" t="inlineStr">
+      <c r="F95" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10803,19 +10799,19 @@
       <c r="I95" s="3" t="inlineStr"/>
       <c r="J95" s="3" t="inlineStr">
         <is>
-          <t>CareClinic template.</t>
+          <t>CareClinic template (partial).</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>VP-rides</t>
+          <t>VP-providers</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>Vertical pack rides: Rides, routes, fares, matching, receipts</t>
+          <t>Vertical pack providers: Providers, specialties, licences, schedules</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
@@ -10825,7 +10821,7 @@
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>Mobility &amp; on-demand (mobility-core)</t>
+          <t>Healthcare &amp; life sciences (healthcare-core)</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
@@ -10833,7 +10829,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F96" s="10" t="inlineStr">
+      <c r="F96" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10851,19 +10847,19 @@
       <c r="I96" s="3" t="inlineStr"/>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>RideNow template.</t>
+          <t>CareClinic template.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>VP-telehealth</t>
+          <t>VP-rides</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>Vertical pack telehealth: Video consults, consent, technical checks</t>
+          <t>Vertical pack rides: Rides, routes, fares, matching, receipts</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
@@ -10873,7 +10869,7 @@
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>Healthcare &amp; life sciences (healthcare-core)</t>
+          <t>Mobility &amp; on-demand (mobility-core)</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
@@ -10881,7 +10877,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F97" s="10" t="inlineStr">
+      <c r="F97" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10899,19 +10895,19 @@
       <c r="I97" s="3" t="inlineStr"/>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>CareClinic template.</t>
+          <t>RideNow template.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>VP-vendors</t>
+          <t>VP-telehealth</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>Vertical pack vendors: Vendors, storefronts, verification</t>
+          <t>Vertical pack telehealth: Video consults, consent, technical checks</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
@@ -10921,7 +10917,7 @@
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>Marketplace &amp; commerce (commerce-core)</t>
+          <t>Healthcare &amp; life sciences (healthcare-core)</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
@@ -10929,7 +10925,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F98" s="10" t="inlineStr">
+      <c r="F98" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10947,63 +10943,67 @@
       <c r="I98" s="3" t="inlineStr"/>
       <c r="J98" s="3" t="inlineStr">
         <is>
-          <t>Bazaar template.</t>
+          <t>CareClinic template.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>PC-096</t>
+          <t>VP-vendors</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>In-browser WebContainer preview engine behind the PC-007 engine switch (Node in the visitor's browser; licence key supplied at PC-070)</t>
+          <t>Vertical pack vendors: Vendors, storefronts, verification</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>Platform_Completion queue</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>Vibe</t>
+          <t>Marketplace &amp; commerce (commerce-core)</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>1 Vibe Mode live</t>
-        </is>
-      </c>
-      <c r="F99" s="8" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G99" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="H99" s="3" t="inlineStr"/>
+          <t>2 Maximum features</t>
+        </is>
+      </c>
+      <c r="F99" s="11" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G99" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>PC-074</t>
+        </is>
+      </c>
       <c r="I99" s="3" t="inlineStr"/>
       <c r="J99" s="3" t="inlineStr">
         <is>
-          <t>Split out of PC-007 on 2026-09-27: PC-007 delivers the engine switch and the open-source container engine; WebContainer needs StackBlitz's commercial licence (D-6) and runs Node only, so Python/Go APIs still need a server-side engine behind it.</t>
+          <t>Bazaar template.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>PC-097</t>
+          <t>PC-096</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>Compile repair covers every Next surface (admin console and ecosystem role surfaces), not only the main web app</t>
+          <t>In-browser WebContainer preview engine behind the PC-007 engine switch (Node in the visitor's browser; licence key supplied at PC-070)</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
@@ -11013,7 +11013,7 @@
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Vibe</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
@@ -11026,28 +11026,28 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G100" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G100" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H100" s="3" t="inlineStr"/>
       <c r="I100" s="3" t="inlineStr"/>
       <c r="J100" s="3" t="inlineStr">
         <is>
-          <t>Found publishing a clinic app on 2026-09-27: the `provider` role surface shipped a model-written page with an invented import and misused components; the build never checked it. PC-008 now type-checks every Next surface and publish refuses a broken app with the compiler's reason; this task makes the repair loop fix or revert those pages as it does for web.</t>
+          <t>Split out of PC-007 on 2026-09-27: PC-007 delivers the engine switch and the open-source container engine; WebContainer needs StackBlitz's commercial licence (D-6) and runs Node only, so Python/Go APIs still need a server-side engine behind it.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>PC-011</t>
+          <t>PC-097</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>Plans, entitlements, credit top-up and super_admin console (Phase E)</t>
+          <t>Compile repair covers every Next surface (admin console and ecosystem role surfaces), not only the main web app</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
@@ -11057,7 +11057,7 @@
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>Platform</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
@@ -11070,16 +11070,16 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G101" s="6" t="inlineStr">
-        <is>
-          <t>P0</t>
+      <c r="G101" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H101" s="3" t="inlineStr"/>
       <c r="I101" s="3" t="inlineStr"/>
       <c r="J101" s="3" t="inlineStr">
         <is>
-          <t>Stripe and Razorpay adapters complete and tested in their test modes; live keys (D-3) at PC-070. Found in R-590: self-registered users get role 'user', which is not one of the plan's roles, so role-guarded actions need an admin to assign roles — include a role manager in the generated admin console.</t>
+          <t>Found publishing a clinic app on 2026-09-27: the `provider` role surface shipped a model-written page with an invented import and misused components; the build never checked it. PC-008 now type-checks every Next surface and publish refuses a broken app with the compiler's reason; this task makes the repair loop fix or revert those pages as it does for web.</t>
         </is>
       </c>
     </row>
@@ -11926,7 +11926,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G121" s="11" t="inlineStr">
+      <c r="G121" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -11970,7 +11970,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G122" s="11" t="inlineStr">
+      <c r="G122" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -12146,7 +12146,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G126" s="11" t="inlineStr">
+      <c r="G126" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -12190,7 +12190,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G127" s="11" t="inlineStr">
+      <c r="G127" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -12234,7 +12234,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G128" s="11" t="inlineStr">
+      <c r="G128" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -12278,7 +12278,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G129" s="11" t="inlineStr">
+      <c r="G129" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -12322,7 +12322,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G130" s="11" t="inlineStr">
+      <c r="G130" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -12410,7 +12410,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G132" s="11" t="inlineStr">
+      <c r="G132" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -12806,7 +12806,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G141" s="11" t="inlineStr">
+      <c r="G141" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -12850,7 +12850,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G142" s="11" t="inlineStr">
+      <c r="G142" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -12894,7 +12894,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G143" s="11" t="inlineStr">
+      <c r="G143" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -14086,7 +14086,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G172" s="11" t="inlineStr">
+      <c r="G172" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -14126,7 +14126,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G173" s="11" t="inlineStr">
+      <c r="G173" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -14170,7 +14170,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G174" s="11" t="inlineStr">
+      <c r="G174" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -14686,7 +14686,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G186" s="11" t="inlineStr">
+      <c r="G186" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -14854,7 +14854,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G190" s="11" t="inlineStr">
+      <c r="G190" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -15418,7 +15418,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G204" s="11" t="inlineStr">
+      <c r="G204" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -15782,7 +15782,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G213" s="11" t="inlineStr">
+      <c r="G213" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -16282,7 +16282,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G225" s="11" t="inlineStr">
+      <c r="G225" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -16506,7 +16506,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G230" s="11" t="inlineStr">
+      <c r="G230" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -16638,7 +16638,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G233" s="11" t="inlineStr">
+      <c r="G233" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -16682,7 +16682,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G234" s="11" t="inlineStr">
+      <c r="G234" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -16906,7 +16906,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G239" s="11" t="inlineStr">
+      <c r="G239" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -17082,7 +17082,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G243" s="11" t="inlineStr">
+      <c r="G243" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -17218,7 +17218,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G246" s="11" t="inlineStr">
+      <c r="G246" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -17306,7 +17306,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G248" s="11" t="inlineStr">
+      <c r="G248" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -17402,7 +17402,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G250" s="11" t="inlineStr">
+      <c r="G250" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -17494,7 +17494,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G252" s="11" t="inlineStr">
+      <c r="G252" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -17538,7 +17538,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G253" s="11" t="inlineStr">
+      <c r="G253" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -17630,7 +17630,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G255" s="11" t="inlineStr">
+      <c r="G255" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -17674,7 +17674,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G256" s="11" t="inlineStr">
+      <c r="G256" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -17854,7 +17854,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G260" s="11" t="inlineStr">
+      <c r="G260" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -17994,7 +17994,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G263" s="11" t="inlineStr">
+      <c r="G263" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -18038,7 +18038,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G264" s="11" t="inlineStr">
+      <c r="G264" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -18446,7 +18446,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G273" s="11" t="inlineStr">
+      <c r="G273" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -18678,7 +18678,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G278" s="11" t="inlineStr">
+      <c r="G278" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -18902,7 +18902,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G283" s="11" t="inlineStr">
+      <c r="G283" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -18946,7 +18946,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G284" s="11" t="inlineStr">
+      <c r="G284" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -19082,7 +19082,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G287" s="11" t="inlineStr">
+      <c r="G287" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -21050,7 +21050,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G333" s="11" t="inlineStr">
+      <c r="G333" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -22818,7 +22818,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G373" s="11" t="inlineStr">
+      <c r="G373" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -22862,7 +22862,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G374" s="11" t="inlineStr">
+      <c r="G374" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -22906,7 +22906,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G375" s="11" t="inlineStr">
+      <c r="G375" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -24706,7 +24706,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G416" s="11" t="inlineStr">
+      <c r="G416" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -24750,7 +24750,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G417" s="11" t="inlineStr">
+      <c r="G417" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -24838,7 +24838,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G419" s="11" t="inlineStr">
+      <c r="G419" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -24970,7 +24970,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G422" s="11" t="inlineStr">
+      <c r="G422" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25146,7 +25146,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G426" s="11" t="inlineStr">
+      <c r="G426" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25190,7 +25190,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G427" s="11" t="inlineStr">
+      <c r="G427" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25498,7 +25498,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G434" s="11" t="inlineStr">
+      <c r="G434" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25542,7 +25542,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G435" s="11" t="inlineStr">
+      <c r="G435" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25586,7 +25586,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G436" s="11" t="inlineStr">
+      <c r="G436" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25630,7 +25630,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G437" s="11" t="inlineStr">
+      <c r="G437" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25674,7 +25674,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G438" s="11" t="inlineStr">
+      <c r="G438" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25718,7 +25718,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G439" s="11" t="inlineStr">
+      <c r="G439" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25762,7 +25762,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G440" s="11" t="inlineStr">
+      <c r="G440" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25894,7 +25894,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G443" s="11" t="inlineStr">
+      <c r="G443" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -26026,7 +26026,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G446" s="11" t="inlineStr">
+      <c r="G446" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -26202,7 +26202,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G450" s="11" t="inlineStr">
+      <c r="G450" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -26246,7 +26246,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G451" s="11" t="inlineStr">
+      <c r="G451" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -26422,7 +26422,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G455" s="11" t="inlineStr">
+      <c r="G455" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -26466,7 +26466,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G456" s="11" t="inlineStr">
+      <c r="G456" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -26554,7 +26554,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G458" s="11" t="inlineStr">
+      <c r="G458" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -26730,7 +26730,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G462" s="11" t="inlineStr">
+      <c r="G462" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -26774,7 +26774,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G463" s="11" t="inlineStr">
+      <c r="G463" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -27038,7 +27038,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G469" s="11" t="inlineStr">
+      <c r="G469" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -27082,7 +27082,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G470" s="11" t="inlineStr">
+      <c r="G470" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -27302,7 +27302,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G475" s="11" t="inlineStr">
+      <c r="G475" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -27346,7 +27346,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G476" s="11" t="inlineStr">
+      <c r="G476" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -27390,7 +27390,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G477" s="11" t="inlineStr">
+      <c r="G477" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -27434,7 +27434,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G478" s="11" t="inlineStr">
+      <c r="G478" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -27478,7 +27478,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G479" s="11" t="inlineStr">
+      <c r="G479" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -27522,7 +27522,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G480" s="11" t="inlineStr">
+      <c r="G480" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -27698,7 +27698,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G484" s="11" t="inlineStr">
+      <c r="G484" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -27918,7 +27918,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G489" s="11" t="inlineStr">
+      <c r="G489" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -28006,7 +28006,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G491" s="11" t="inlineStr">
+      <c r="G491" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -28050,7 +28050,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G492" s="11" t="inlineStr">
+      <c r="G492" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -28138,7 +28138,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G494" s="11" t="inlineStr">
+      <c r="G494" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -28358,7 +28358,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G499" s="11" t="inlineStr">
+      <c r="G499" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -28402,7 +28402,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G500" s="11" t="inlineStr">
+      <c r="G500" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -28842,7 +28842,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G510" s="11" t="inlineStr">
+      <c r="G510" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -29106,7 +29106,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G516" s="11" t="inlineStr">
+      <c r="G516" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -29238,7 +29238,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G519" s="11" t="inlineStr">
+      <c r="G519" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -29414,7 +29414,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G523" s="11" t="inlineStr">
+      <c r="G523" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -29458,7 +29458,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G524" s="11" t="inlineStr">
+      <c r="G524" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -29634,7 +29634,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G528" s="11" t="inlineStr">
+      <c r="G528" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -29678,7 +29678,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G529" s="11" t="inlineStr">
+      <c r="G529" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -29766,7 +29766,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G531" s="11" t="inlineStr">
+      <c r="G531" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -29854,7 +29854,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G533" s="11" t="inlineStr">
+      <c r="G533" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -29942,7 +29942,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G535" s="11" t="inlineStr">
+      <c r="G535" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30030,7 +30030,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G537" s="11" t="inlineStr">
+      <c r="G537" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30074,7 +30074,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G538" s="11" t="inlineStr">
+      <c r="G538" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30118,7 +30118,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G539" s="11" t="inlineStr">
+      <c r="G539" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30206,7 +30206,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G541" s="11" t="inlineStr">
+      <c r="G541" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30250,7 +30250,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G542" s="11" t="inlineStr">
+      <c r="G542" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30294,7 +30294,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G543" s="11" t="inlineStr">
+      <c r="G543" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30338,7 +30338,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G544" s="11" t="inlineStr">
+      <c r="G544" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30426,7 +30426,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G546" s="11" t="inlineStr">
+      <c r="G546" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30470,7 +30470,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G547" s="11" t="inlineStr">
+      <c r="G547" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30514,7 +30514,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G548" s="11" t="inlineStr">
+      <c r="G548" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30646,7 +30646,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G551" s="11" t="inlineStr">
+      <c r="G551" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30778,7 +30778,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G554" s="11" t="inlineStr">
+      <c r="G554" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30866,7 +30866,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G556" s="11" t="inlineStr">
+      <c r="G556" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30954,7 +30954,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G558" s="11" t="inlineStr">
+      <c r="G558" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -31042,7 +31042,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G560" s="11" t="inlineStr">
+      <c r="G560" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -31262,7 +31262,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G565" s="11" t="inlineStr">
+      <c r="G565" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -31306,7 +31306,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G566" s="11" t="inlineStr">
+      <c r="G566" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -31394,7 +31394,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G568" s="11" t="inlineStr">
+      <c r="G568" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -31526,7 +31526,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G571" s="11" t="inlineStr">
+      <c r="G571" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -31658,7 +31658,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G574" s="11" t="inlineStr">
+      <c r="G574" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -31746,7 +31746,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G576" s="11" t="inlineStr">
+      <c r="G576" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -31790,7 +31790,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G577" s="11" t="inlineStr">
+      <c r="G577" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -31966,7 +31966,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G581" s="11" t="inlineStr">
+      <c r="G581" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -32010,7 +32010,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G582" s="11" t="inlineStr">
+      <c r="G582" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -32318,7 +32318,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G589" s="11" t="inlineStr">
+      <c r="G589" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -32362,7 +32362,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G590" s="11" t="inlineStr">
+      <c r="G590" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -32406,7 +32406,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G591" s="11" t="inlineStr">
+      <c r="G591" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -32494,7 +32494,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G593" s="11" t="inlineStr">
+      <c r="G593" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -32670,7 +32670,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G597" s="11" t="inlineStr">
+      <c r="G597" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -32802,7 +32802,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G600" s="11" t="inlineStr">
+      <c r="G600" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -32846,7 +32846,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G601" s="11" t="inlineStr">
+      <c r="G601" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -32934,7 +32934,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G603" s="11" t="inlineStr">
+      <c r="G603" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -33022,7 +33022,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G605" s="11" t="inlineStr">
+      <c r="G605" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -33242,7 +33242,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G610" s="11" t="inlineStr">
+      <c r="G610" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -33321,7 +33321,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F612" s="11" t="inlineStr">
+      <c r="F612" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33365,7 +33365,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F613" s="11" t="inlineStr">
+      <c r="F613" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33409,7 +33409,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F614" s="11" t="inlineStr">
+      <c r="F614" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33453,7 +33453,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F615" s="11" t="inlineStr">
+      <c r="F615" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33497,7 +33497,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F616" s="11" t="inlineStr">
+      <c r="F616" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33541,7 +33541,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F617" s="11" t="inlineStr">
+      <c r="F617" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33585,7 +33585,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F618" s="11" t="inlineStr">
+      <c r="F618" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33629,7 +33629,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F619" s="11" t="inlineStr">
+      <c r="F619" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33669,7 +33669,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F620" s="11" t="inlineStr">
+      <c r="F620" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33713,7 +33713,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F621" s="11" t="inlineStr">
+      <c r="F621" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33753,7 +33753,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F622" s="11" t="inlineStr">
+      <c r="F622" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33797,7 +33797,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F623" s="11" t="inlineStr">
+      <c r="F623" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33837,12 +33837,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F624" s="12" t="inlineStr">
+      <c r="F624" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G624" s="11" t="inlineStr">
+      <c r="G624" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -33881,12 +33881,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F625" s="12" t="inlineStr">
+      <c r="F625" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G625" s="11" t="inlineStr">
+      <c r="G625" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -33925,12 +33925,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F626" s="12" t="inlineStr">
+      <c r="F626" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G626" s="11" t="inlineStr">
+      <c r="G626" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -33969,7 +33969,7 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F627" s="12" t="inlineStr">
+      <c r="F627" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
@@ -34013,12 +34013,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F628" s="12" t="inlineStr">
+      <c r="F628" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G628" s="11" t="inlineStr">
+      <c r="G628" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34057,12 +34057,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F629" s="12" t="inlineStr">
+      <c r="F629" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G629" s="11" t="inlineStr">
+      <c r="G629" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34097,12 +34097,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F630" s="12" t="inlineStr">
+      <c r="F630" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G630" s="11" t="inlineStr">
+      <c r="G630" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34141,12 +34141,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F631" s="12" t="inlineStr">
+      <c r="F631" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G631" s="11" t="inlineStr">
+      <c r="G631" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34185,12 +34185,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F632" s="12" t="inlineStr">
+      <c r="F632" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G632" s="11" t="inlineStr">
+      <c r="G632" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34229,12 +34229,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F633" s="12" t="inlineStr">
+      <c r="F633" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G633" s="11" t="inlineStr">
+      <c r="G633" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34269,12 +34269,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F634" s="12" t="inlineStr">
+      <c r="F634" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G634" s="11" t="inlineStr">
+      <c r="G634" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34313,12 +34313,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F635" s="12" t="inlineStr">
+      <c r="F635" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G635" s="11" t="inlineStr">
+      <c r="G635" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34357,12 +34357,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F636" s="12" t="inlineStr">
+      <c r="F636" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G636" s="11" t="inlineStr">
+      <c r="G636" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34401,12 +34401,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F637" s="12" t="inlineStr">
+      <c r="F637" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G637" s="11" t="inlineStr">
+      <c r="G637" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34445,12 +34445,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F638" s="12" t="inlineStr">
+      <c r="F638" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G638" s="11" t="inlineStr">
+      <c r="G638" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34489,12 +34489,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F639" s="12" t="inlineStr">
+      <c r="F639" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G639" s="11" t="inlineStr">
+      <c r="G639" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34533,12 +34533,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F640" s="12" t="inlineStr">
+      <c r="F640" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G640" s="11" t="inlineStr">
+      <c r="G640" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34577,12 +34577,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F641" s="12" t="inlineStr">
+      <c r="F641" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G641" s="11" t="inlineStr">
+      <c r="G641" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34621,12 +34621,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F642" s="12" t="inlineStr">
+      <c r="F642" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G642" s="11" t="inlineStr">
+      <c r="G642" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34665,12 +34665,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F643" s="12" t="inlineStr">
+      <c r="F643" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G643" s="11" t="inlineStr">
+      <c r="G643" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34709,12 +34709,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F644" s="12" t="inlineStr">
+      <c r="F644" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G644" s="11" t="inlineStr">
+      <c r="G644" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34753,12 +34753,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F645" s="12" t="inlineStr">
+      <c r="F645" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G645" s="11" t="inlineStr">
+      <c r="G645" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34797,12 +34797,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F646" s="12" t="inlineStr">
+      <c r="F646" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G646" s="11" t="inlineStr">
+      <c r="G646" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34841,12 +34841,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F647" s="12" t="inlineStr">
+      <c r="F647" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G647" s="11" t="inlineStr">
+      <c r="G647" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34885,12 +34885,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F648" s="12" t="inlineStr">
+      <c r="F648" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G648" s="11" t="inlineStr">
+      <c r="G648" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34925,12 +34925,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F649" s="12" t="inlineStr">
+      <c r="F649" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G649" s="11" t="inlineStr">
+      <c r="G649" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34969,12 +34969,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F650" s="12" t="inlineStr">
+      <c r="F650" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G650" s="11" t="inlineStr">
+      <c r="G650" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35013,12 +35013,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F651" s="12" t="inlineStr">
+      <c r="F651" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G651" s="11" t="inlineStr">
+      <c r="G651" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35053,12 +35053,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F652" s="12" t="inlineStr">
+      <c r="F652" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G652" s="11" t="inlineStr">
+      <c r="G652" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35097,12 +35097,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F653" s="12" t="inlineStr">
+      <c r="F653" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G653" s="11" t="inlineStr">
+      <c r="G653" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35137,12 +35137,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F654" s="12" t="inlineStr">
+      <c r="F654" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G654" s="11" t="inlineStr">
+      <c r="G654" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35177,12 +35177,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F655" s="12" t="inlineStr">
+      <c r="F655" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G655" s="11" t="inlineStr">
+      <c r="G655" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35217,12 +35217,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F656" s="12" t="inlineStr">
+      <c r="F656" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G656" s="11" t="inlineStr">
+      <c r="G656" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35257,12 +35257,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F657" s="12" t="inlineStr">
+      <c r="F657" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G657" s="11" t="inlineStr">
+      <c r="G657" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35301,12 +35301,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F658" s="12" t="inlineStr">
+      <c r="F658" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G658" s="11" t="inlineStr">
+      <c r="G658" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35345,12 +35345,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F659" s="12" t="inlineStr">
+      <c r="F659" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G659" s="11" t="inlineStr">
+      <c r="G659" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35389,12 +35389,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F660" s="12" t="inlineStr">
+      <c r="F660" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G660" s="11" t="inlineStr">
+      <c r="G660" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35429,12 +35429,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F661" s="12" t="inlineStr">
+      <c r="F661" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G661" s="11" t="inlineStr">
+      <c r="G661" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35469,12 +35469,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F662" s="12" t="inlineStr">
+      <c r="F662" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G662" s="11" t="inlineStr">
+      <c r="G662" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35509,12 +35509,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F663" s="12" t="inlineStr">
+      <c r="F663" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G663" s="11" t="inlineStr">
+      <c r="G663" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35549,12 +35549,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F664" s="12" t="inlineStr">
+      <c r="F664" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G664" s="11" t="inlineStr">
+      <c r="G664" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35589,12 +35589,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F665" s="12" t="inlineStr">
+      <c r="F665" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G665" s="11" t="inlineStr">
+      <c r="G665" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35633,12 +35633,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F666" s="12" t="inlineStr">
+      <c r="F666" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G666" s="11" t="inlineStr">
+      <c r="G666" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35673,12 +35673,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F667" s="12" t="inlineStr">
+      <c r="F667" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G667" s="11" t="inlineStr">
+      <c r="G667" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35713,12 +35713,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F668" s="12" t="inlineStr">
+      <c r="F668" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G668" s="11" t="inlineStr">
+      <c r="G668" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35753,12 +35753,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F669" s="12" t="inlineStr">
+      <c r="F669" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G669" s="11" t="inlineStr">
+      <c r="G669" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35793,12 +35793,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F670" s="12" t="inlineStr">
+      <c r="F670" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G670" s="11" t="inlineStr">
+      <c r="G670" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35837,12 +35837,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F671" s="12" t="inlineStr">
+      <c r="F671" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G671" s="11" t="inlineStr">
+      <c r="G671" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35881,12 +35881,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F672" s="12" t="inlineStr">
+      <c r="F672" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G672" s="11" t="inlineStr">
+      <c r="G672" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35925,12 +35925,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F673" s="12" t="inlineStr">
+      <c r="F673" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G673" s="11" t="inlineStr">
+      <c r="G673" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35969,12 +35969,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F674" s="12" t="inlineStr">
+      <c r="F674" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G674" s="11" t="inlineStr">
+      <c r="G674" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -36013,12 +36013,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F675" s="12" t="inlineStr">
+      <c r="F675" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G675" s="11" t="inlineStr">
+      <c r="G675" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -36057,12 +36057,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F676" s="12" t="inlineStr">
+      <c r="F676" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G676" s="11" t="inlineStr">
+      <c r="G676" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -36101,12 +36101,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F677" s="12" t="inlineStr">
+      <c r="F677" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G677" s="11" t="inlineStr">
+      <c r="G677" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -36145,12 +36145,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F678" s="12" t="inlineStr">
+      <c r="F678" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G678" s="11" t="inlineStr">
+      <c r="G678" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -36189,12 +36189,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F679" s="12" t="inlineStr">
+      <c r="F679" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G679" s="11" t="inlineStr">
+      <c r="G679" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -36229,12 +36229,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F680" s="12" t="inlineStr">
+      <c r="F680" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G680" s="11" t="inlineStr">
+      <c r="G680" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -36265,7 +36265,7 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F681" s="13" t="inlineStr">
+      <c r="F681" s="14" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -36305,7 +36305,7 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F682" s="13" t="inlineStr">
+      <c r="F682" s="14" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -36345,7 +36345,7 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F683" s="13" t="inlineStr">
+      <c r="F683" s="14" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -36385,7 +36385,7 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F684" s="13" t="inlineStr">
+      <c r="F684" s="14" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -36425,7 +36425,7 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F685" s="13" t="inlineStr">
+      <c r="F685" s="14" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -36465,7 +36465,7 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F686" s="13" t="inlineStr">
+      <c r="F686" s="14" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -36505,7 +36505,7 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F687" s="13" t="inlineStr">
+      <c r="F687" s="14" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -36545,7 +36545,7 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F688" s="13" t="inlineStr">
+      <c r="F688" s="14" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -36585,7 +36585,7 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F689" s="13" t="inlineStr">
+      <c r="F689" s="14" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -38649,7 +38649,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F736" s="14" t="inlineStr">
+      <c r="F736" s="15" t="inlineStr">
         <is>
           <t>Completed - needs live proof</t>
         </is>
@@ -51265,7 +51265,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F1055" s="14" t="inlineStr">
+      <c r="F1055" s="15" t="inlineStr">
         <is>
           <t>Completed - needs live proof</t>
         </is>
@@ -51313,7 +51313,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F1056" s="14" t="inlineStr">
+      <c r="F1056" s="15" t="inlineStr">
         <is>
           <t>Completed - needs live proof</t>
         </is>
@@ -51361,7 +51361,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F1057" s="14" t="inlineStr">
+      <c r="F1057" s="15" t="inlineStr">
         <is>
           <t>Completed - needs live proof</t>
         </is>
@@ -51409,7 +51409,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F1058" s="14" t="inlineStr">
+      <c r="F1058" s="15" t="inlineStr">
         <is>
           <t>Completed - needs live proof</t>
         </is>
@@ -51457,7 +51457,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F1059" s="14" t="inlineStr">
+      <c r="F1059" s="15" t="inlineStr">
         <is>
           <t>Completed - needs live proof</t>
         </is>
@@ -51577,7 +51577,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F1062" s="14" t="inlineStr">
+      <c r="F1062" s="15" t="inlineStr">
         <is>
           <t>Completed - needs live proof</t>
         </is>
@@ -52709,7 +52709,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F1093" s="14" t="inlineStr">
+      <c r="F1093" s="15" t="inlineStr">
         <is>
           <t>Completed - needs live proof</t>
         </is>
@@ -53706,62 +53706,62 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="B1" s="15" t="inlineStr">
+      <c r="B1" s="16" t="inlineStr">
         <is>
           <t>0 Foundation</t>
         </is>
       </c>
-      <c r="C1" s="15" t="inlineStr">
+      <c r="C1" s="16" t="inlineStr">
         <is>
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="D1" s="15" t="inlineStr">
+      <c r="D1" s="16" t="inlineStr">
         <is>
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="E1" s="15" t="inlineStr">
+      <c r="E1" s="16" t="inlineStr">
         <is>
           <t>3 Engineering Mode</t>
         </is>
       </c>
-      <c r="F1" s="15" t="inlineStr">
+      <c r="F1" s="16" t="inlineStr">
         <is>
           <t>4 Production ops</t>
         </is>
       </c>
-      <c r="G1" s="15" t="inlineStr">
+      <c r="G1" s="16" t="inlineStr">
         <is>
           <t>5 Native mobile (last)</t>
         </is>
       </c>
-      <c r="H1" s="15" t="inlineStr">
+      <c r="H1" s="16" t="inlineStr">
         <is>
           <t>6 Go-live (credentials last)</t>
         </is>
       </c>
-      <c r="I1" s="15" t="inlineStr">
+      <c r="I1" s="16" t="inlineStr">
         <is>
           <t>7 Win the category</t>
         </is>
       </c>
-      <c r="J1" s="15" t="inlineStr">
+      <c r="J1" s="16" t="inlineStr">
         <is>
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="K1" s="15" t="inlineStr">
+      <c r="K1" s="16" t="inlineStr">
         <is>
           <t>Delivered</t>
         </is>
       </c>
-      <c r="L1" s="15" t="inlineStr">
+      <c r="L1" s="16" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
@@ -53857,7 +53857,7 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -53884,7 +53884,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -53937,7 +53937,7 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D6" t="n">
         <v>336</v>
@@ -53964,7 +53964,7 @@
         <v>20</v>
       </c>
       <c r="L6" t="n">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="7">
@@ -54128,62 +54128,62 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Open queue by priority</t>
         </is>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>0 Foundation</t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="D12" s="15" t="inlineStr">
+      <c r="D12" s="16" t="inlineStr">
         <is>
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="E12" s="15" t="inlineStr">
+      <c r="E12" s="16" t="inlineStr">
         <is>
           <t>3 Engineering Mode</t>
         </is>
       </c>
-      <c r="F12" s="15" t="inlineStr">
+      <c r="F12" s="16" t="inlineStr">
         <is>
           <t>4 Production ops</t>
         </is>
       </c>
-      <c r="G12" s="15" t="inlineStr">
+      <c r="G12" s="16" t="inlineStr">
         <is>
           <t>5 Native mobile (last)</t>
         </is>
       </c>
-      <c r="H12" s="15" t="inlineStr">
+      <c r="H12" s="16" t="inlineStr">
         <is>
           <t>6 Go-live (credentials last)</t>
         </is>
       </c>
-      <c r="I12" s="15" t="inlineStr">
+      <c r="I12" s="16" t="inlineStr">
         <is>
           <t>7 Win the category</t>
         </is>
       </c>
-      <c r="J12" s="15" t="inlineStr">
+      <c r="J12" s="16" t="inlineStr">
         <is>
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="K12" s="15" t="inlineStr">
+      <c r="K12" s="16" t="inlineStr">
         <is>
           <t>Delivered</t>
         </is>
       </c>
-      <c r="L12" s="15" t="inlineStr">
+      <c r="L12" s="16" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
@@ -55498,7 +55498,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="F2" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -55602,7 +55602,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -55654,7 +55654,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F5" s="10" t="inlineStr">
+      <c r="F5" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -55706,7 +55706,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -55758,7 +55758,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F7" s="10" t="inlineStr">
+      <c r="F7" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -55810,7 +55810,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="F8" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -55958,7 +55958,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="F11" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -56062,7 +56062,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="F13" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -56119,7 +56119,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G14" s="11" t="inlineStr">
+      <c r="G14" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -56162,7 +56162,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F15" s="10" t="inlineStr">
+      <c r="F15" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -56414,7 +56414,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F20" s="10" t="inlineStr">
+      <c r="F20" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -56518,7 +56518,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F22" s="10" t="inlineStr">
+      <c r="F22" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -56623,7 +56623,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G24" s="11" t="inlineStr">
+      <c r="G24" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -56767,7 +56767,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G27" s="11" t="inlineStr">
+      <c r="G27" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -56914,12 +56914,12 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F30" s="10" t="inlineStr">
+      <c r="F30" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G30" s="11" t="inlineStr">
+      <c r="G30" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -56971,7 +56971,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G31" s="11" t="inlineStr">
+      <c r="G31" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -57014,7 +57014,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F32" s="10" t="inlineStr">
+      <c r="F32" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -57066,7 +57066,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F33" s="10" t="inlineStr">
+      <c r="F33" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -57118,7 +57118,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F34" s="10" t="inlineStr">
+      <c r="F34" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -57223,7 +57223,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G36" s="11" t="inlineStr">
+      <c r="G36" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -57271,7 +57271,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G37" s="11" t="inlineStr">
+      <c r="G37" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -57414,7 +57414,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F40" s="10" t="inlineStr">
+      <c r="F40" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -57466,7 +57466,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F41" s="10" t="inlineStr">
+      <c r="F41" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -57518,7 +57518,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F42" s="10" t="inlineStr">
+      <c r="F42" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -57618,7 +57618,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F44" s="10" t="inlineStr">
+      <c r="F44" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -57718,7 +57718,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F46" s="10" t="inlineStr">
+      <c r="F46" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -57822,7 +57822,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F48" s="10" t="inlineStr">
+      <c r="F48" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -57970,7 +57970,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F51" s="10" t="inlineStr">
+      <c r="F51" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -58070,7 +58070,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F53" s="10" t="inlineStr">
+      <c r="F53" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -58175,7 +58175,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G55" s="11" t="inlineStr">
+      <c r="G55" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -58270,7 +58270,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F57" s="10" t="inlineStr">
+      <c r="F57" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -58327,7 +58327,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G58" s="11" t="inlineStr">
+      <c r="G58" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -58375,7 +58375,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G59" s="11" t="inlineStr">
+      <c r="G59" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -58471,7 +58471,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G61" s="11" t="inlineStr">
+      <c r="G61" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -58514,7 +58514,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F62" s="10" t="inlineStr">
+      <c r="F62" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -58775,7 +58775,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G67" s="11" t="inlineStr">
+      <c r="G67" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -58866,7 +58866,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F69" s="10" t="inlineStr">
+      <c r="F69" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -58918,7 +58918,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F70" s="10" t="inlineStr">
+      <c r="F70" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -58970,7 +58970,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F71" s="10" t="inlineStr">
+      <c r="F71" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -59022,7 +59022,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F72" s="10" t="inlineStr">
+      <c r="F72" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -59126,7 +59126,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F74" s="10" t="inlineStr">
+      <c r="F74" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -59178,7 +59178,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F75" s="10" t="inlineStr">
+      <c r="F75" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -59230,7 +59230,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F76" s="10" t="inlineStr">
+      <c r="F76" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -59282,7 +59282,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F77" s="10" t="inlineStr">
+      <c r="F77" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -59386,7 +59386,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F79" s="10" t="inlineStr">
+      <c r="F79" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -59490,7 +59490,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F81" s="10" t="inlineStr">
+      <c r="F81" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -59590,12 +59590,12 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F83" s="10" t="inlineStr">
+      <c r="F83" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G83" s="11" t="inlineStr">
+      <c r="G83" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -59647,7 +59647,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G84" s="11" t="inlineStr">
+      <c r="G84" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -59842,7 +59842,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F88" s="10" t="inlineStr">
+      <c r="F88" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -60090,7 +60090,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F93" s="10" t="inlineStr">
+      <c r="F93" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -60286,12 +60286,12 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F97" s="10" t="inlineStr">
+      <c r="F97" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G97" s="11" t="inlineStr">
+      <c r="G97" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -60343,7 +60343,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G98" s="11" t="inlineStr">
+      <c r="G98" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -60391,7 +60391,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G99" s="11" t="inlineStr">
+      <c r="G99" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -60439,7 +60439,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G100" s="11" t="inlineStr">
+      <c r="G100" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -60534,7 +60534,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F102" s="10" t="inlineStr">
+      <c r="F102" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -60591,7 +60591,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G103" s="11" t="inlineStr">
+      <c r="G103" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -60639,7 +60639,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G104" s="11" t="inlineStr">
+      <c r="G104" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -60687,7 +60687,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G105" s="11" t="inlineStr">
+      <c r="G105" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -60735,7 +60735,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G106" s="11" t="inlineStr">
+      <c r="G106" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -60783,7 +60783,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G107" s="11" t="inlineStr">
+      <c r="G107" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -60831,7 +60831,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G108" s="11" t="inlineStr">
+      <c r="G108" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -60926,7 +60926,7 @@
           <t>Patient: App + Web; Doctor / provider: Web + App; Pharmacy / lab: Web; Clinic operator: Admin</t>
         </is>
       </c>
-      <c r="F110" s="10" t="inlineStr">
+      <c r="F110" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -60978,7 +60978,7 @@
           <t>Patient: App + Web; Doctor / provider: Web + App; Pharmacy / lab: Web; Clinic operator: Admin</t>
         </is>
       </c>
-      <c r="F111" s="10" t="inlineStr">
+      <c r="F111" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -61030,7 +61030,7 @@
           <t>Patient: App + Web; Doctor / provider: Web + App; Pharmacy / lab: Web; Clinic operator: Admin</t>
         </is>
       </c>
-      <c r="F112" s="10" t="inlineStr">
+      <c r="F112" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -61082,7 +61082,7 @@
           <t>Patient: App + Web; Doctor / provider: Web + App; Pharmacy / lab: Web; Clinic operator: Admin</t>
         </is>
       </c>
-      <c r="F113" s="10" t="inlineStr">
+      <c r="F113" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -61134,7 +61134,7 @@
           <t>Patient: App + Web; Doctor / provider: Web + App; Pharmacy / lab: Web; Clinic operator: Admin</t>
         </is>
       </c>
-      <c r="F114" s="10" t="inlineStr">
+      <c r="F114" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -61234,7 +61234,7 @@
           <t>Patient: App + Web; Doctor / provider: Web + App; Pharmacy / lab: Web; Clinic operator: Admin</t>
         </is>
       </c>
-      <c r="F116" s="10" t="inlineStr">
+      <c r="F116" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -61622,7 +61622,7 @@
           <t>Rider: App + Web; Driver: App; Dispatcher: Web; Operator: Admin</t>
         </is>
       </c>
-      <c r="F124" s="10" t="inlineStr">
+      <c r="F124" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -61674,7 +61674,7 @@
           <t>Rider: App + Web; Driver: App; Dispatcher: Web; Operator: Admin</t>
         </is>
       </c>
-      <c r="F125" s="10" t="inlineStr">
+      <c r="F125" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -61726,7 +61726,7 @@
           <t>Rider: App + Web; Driver: App; Dispatcher: Web; Operator: Admin</t>
         </is>
       </c>
-      <c r="F126" s="10" t="inlineStr">
+      <c r="F126" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -62162,7 +62162,7 @@
           <t>Buyer: App + Web; Seller / vendor: Web + App; Marketplace operator: Admin</t>
         </is>
       </c>
-      <c r="F135" s="10" t="inlineStr">
+      <c r="F135" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -62214,7 +62214,7 @@
           <t>Buyer: App + Web; Seller / vendor: Web + App; Marketplace operator: Admin</t>
         </is>
       </c>
-      <c r="F136" s="10" t="inlineStr">
+      <c r="F136" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -62266,7 +62266,7 @@
           <t>Buyer: App + Web; Seller / vendor: Web + App; Marketplace operator: Admin</t>
         </is>
       </c>
-      <c r="F137" s="10" t="inlineStr">
+      <c r="F137" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -62414,7 +62414,7 @@
           <t>Buyer: App + Web; Seller / vendor: Web + App; Marketplace operator: Admin</t>
         </is>
       </c>
-      <c r="F140" s="10" t="inlineStr">
+      <c r="F140" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -62466,7 +62466,7 @@
           <t>Buyer: App + Web; Seller / vendor: Web + App; Marketplace operator: Admin</t>
         </is>
       </c>
-      <c r="F141" s="10" t="inlineStr">
+      <c r="F141" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -67323,7 +67323,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G242" s="11" t="inlineStr">
+      <c r="G242" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67371,7 +67371,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G243" s="11" t="inlineStr">
+      <c r="G243" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67419,7 +67419,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G244" s="11" t="inlineStr">
+      <c r="G244" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67467,7 +67467,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G245" s="11" t="inlineStr">
+      <c r="G245" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67515,7 +67515,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G246" s="11" t="inlineStr">
+      <c r="G246" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67563,7 +67563,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G247" s="11" t="inlineStr">
+      <c r="G247" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67611,7 +67611,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G248" s="11" t="inlineStr">
+      <c r="G248" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67659,7 +67659,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G249" s="11" t="inlineStr">
+      <c r="G249" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67707,7 +67707,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G250" s="11" t="inlineStr">
+      <c r="G250" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67755,7 +67755,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G251" s="11" t="inlineStr">
+      <c r="G251" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67803,7 +67803,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G252" s="11" t="inlineStr">
+      <c r="G252" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67851,7 +67851,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G253" s="11" t="inlineStr">
+      <c r="G253" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67899,7 +67899,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G254" s="11" t="inlineStr">
+      <c r="G254" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67947,7 +67947,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G255" s="11" t="inlineStr">
+      <c r="G255" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67995,7 +67995,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G256" s="11" t="inlineStr">
+      <c r="G256" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68043,7 +68043,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G257" s="11" t="inlineStr">
+      <c r="G257" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68091,7 +68091,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G258" s="11" t="inlineStr">
+      <c r="G258" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68139,7 +68139,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G259" s="11" t="inlineStr">
+      <c r="G259" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68187,7 +68187,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G260" s="11" t="inlineStr">
+      <c r="G260" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68235,7 +68235,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G261" s="11" t="inlineStr">
+      <c r="G261" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68283,7 +68283,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G262" s="11" t="inlineStr">
+      <c r="G262" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68331,7 +68331,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G263" s="11" t="inlineStr">
+      <c r="G263" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68379,7 +68379,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G264" s="11" t="inlineStr">
+      <c r="G264" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68427,7 +68427,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G265" s="11" t="inlineStr">
+      <c r="G265" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68475,7 +68475,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G266" s="11" t="inlineStr">
+      <c r="G266" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68523,7 +68523,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G267" s="11" t="inlineStr">
+      <c r="G267" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68571,7 +68571,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G268" s="11" t="inlineStr">
+      <c r="G268" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68619,7 +68619,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G269" s="11" t="inlineStr">
+      <c r="G269" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68667,7 +68667,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G270" s="11" t="inlineStr">
+      <c r="G270" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68715,7 +68715,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G271" s="11" t="inlineStr">
+      <c r="G271" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68763,7 +68763,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G272" s="11" t="inlineStr">
+      <c r="G272" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68811,7 +68811,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G273" s="11" t="inlineStr">
+      <c r="G273" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68859,7 +68859,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G274" s="11" t="inlineStr">
+      <c r="G274" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68907,7 +68907,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G275" s="11" t="inlineStr">
+      <c r="G275" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68955,7 +68955,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G276" s="11" t="inlineStr">
+      <c r="G276" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69003,7 +69003,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G277" s="11" t="inlineStr">
+      <c r="G277" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69051,7 +69051,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G278" s="11" t="inlineStr">
+      <c r="G278" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69099,7 +69099,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G279" s="11" t="inlineStr">
+      <c r="G279" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69147,7 +69147,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G280" s="11" t="inlineStr">
+      <c r="G280" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69195,7 +69195,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G281" s="11" t="inlineStr">
+      <c r="G281" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69243,7 +69243,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G282" s="11" t="inlineStr">
+      <c r="G282" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69291,7 +69291,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G283" s="11" t="inlineStr">
+      <c r="G283" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69339,7 +69339,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G284" s="11" t="inlineStr">
+      <c r="G284" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69387,7 +69387,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G285" s="11" t="inlineStr">
+      <c r="G285" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69435,7 +69435,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G286" s="11" t="inlineStr">
+      <c r="G286" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69483,7 +69483,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G287" s="11" t="inlineStr">
+      <c r="G287" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69531,7 +69531,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G288" s="11" t="inlineStr">
+      <c r="G288" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69579,7 +69579,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G289" s="11" t="inlineStr">
+      <c r="G289" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69627,7 +69627,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G290" s="11" t="inlineStr">
+      <c r="G290" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69675,7 +69675,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G291" s="11" t="inlineStr">
+      <c r="G291" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69723,7 +69723,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G292" s="11" t="inlineStr">
+      <c r="G292" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69771,7 +69771,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G293" s="11" t="inlineStr">
+      <c r="G293" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69819,7 +69819,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G294" s="11" t="inlineStr">
+      <c r="G294" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69867,7 +69867,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G295" s="11" t="inlineStr">
+      <c r="G295" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69915,7 +69915,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G296" s="11" t="inlineStr">
+      <c r="G296" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69963,7 +69963,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G297" s="11" t="inlineStr">
+      <c r="G297" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70011,7 +70011,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G298" s="11" t="inlineStr">
+      <c r="G298" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70059,7 +70059,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G299" s="11" t="inlineStr">
+      <c r="G299" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70107,7 +70107,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G300" s="11" t="inlineStr">
+      <c r="G300" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70155,7 +70155,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G301" s="11" t="inlineStr">
+      <c r="G301" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70203,7 +70203,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G302" s="11" t="inlineStr">
+      <c r="G302" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70251,7 +70251,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G303" s="11" t="inlineStr">
+      <c r="G303" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70299,7 +70299,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G304" s="11" t="inlineStr">
+      <c r="G304" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70347,7 +70347,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G305" s="11" t="inlineStr">
+      <c r="G305" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70395,7 +70395,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G306" s="11" t="inlineStr">
+      <c r="G306" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70443,7 +70443,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G307" s="11" t="inlineStr">
+      <c r="G307" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70491,7 +70491,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G308" s="11" t="inlineStr">
+      <c r="G308" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70539,7 +70539,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G309" s="11" t="inlineStr">
+      <c r="G309" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70587,7 +70587,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G310" s="11" t="inlineStr">
+      <c r="G310" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70635,7 +70635,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G311" s="11" t="inlineStr">
+      <c r="G311" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70683,7 +70683,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G312" s="11" t="inlineStr">
+      <c r="G312" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70731,7 +70731,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G313" s="11" t="inlineStr">
+      <c r="G313" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70779,7 +70779,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G314" s="11" t="inlineStr">
+      <c r="G314" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70827,7 +70827,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G315" s="11" t="inlineStr">
+      <c r="G315" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70875,7 +70875,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G316" s="11" t="inlineStr">
+      <c r="G316" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70923,7 +70923,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G317" s="11" t="inlineStr">
+      <c r="G317" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70971,7 +70971,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G318" s="11" t="inlineStr">
+      <c r="G318" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -71019,7 +71019,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G319" s="11" t="inlineStr">
+      <c r="G319" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -71067,7 +71067,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G320" s="11" t="inlineStr">
+      <c r="G320" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -71115,7 +71115,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G321" s="11" t="inlineStr">
+      <c r="G321" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -71163,7 +71163,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G322" s="11" t="inlineStr">
+      <c r="G322" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -71719,7 +71719,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>Completed - needs live proof</t>
         </is>
@@ -71731,7 +71731,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="16" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
@@ -71743,7 +71743,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -71767,7 +71767,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -71779,7 +71779,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
@@ -71791,7 +71791,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -71839,7 +71839,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>

--- a/R_&_D/Platform_Completion/OmniStackAI_Master_Tasks.xlsx
+++ b/R_&_D/Platform_Completion/OmniStackAI_Master_Tasks.xlsx
@@ -92,6 +92,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00BDD7EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFE699"/>
       </patternFill>
     </fill>
@@ -113,11 +118,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2F0D9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00BDD7EE"/>
       </patternFill>
     </fill>
   </fills>
@@ -173,10 +173,10 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1937,9 +1937,9 @@
           <t>Platform</t>
         </is>
       </c>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
@@ -1979,7 +1979,7 @@
           <t>Vibe</t>
         </is>
       </c>
-      <c r="F26" s="10" t="inlineStr">
+      <c r="F26" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2025,7 +2025,7 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="F27" s="10" t="inlineStr">
+      <c r="F27" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2071,7 +2071,7 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="F28" s="10" t="inlineStr">
+      <c r="F28" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2687,7 +2687,7 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="F42" s="10" t="inlineStr">
+      <c r="F42" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2737,7 +2737,7 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="F43" s="10" t="inlineStr">
+      <c r="F43" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2837,7 +2837,7 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="F45" s="10" t="inlineStr">
+      <c r="F45" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2983,7 +2983,7 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="F48" s="10" t="inlineStr">
+      <c r="F48" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -3033,7 +3033,7 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="F49" s="10" t="inlineStr">
+      <c r="F49" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -3188,7 +3188,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G52" s="11" t="inlineStr">
+      <c r="G52" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -3238,7 +3238,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G53" s="11" t="inlineStr">
+      <c r="G53" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -3426,7 +3426,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G57" s="11" t="inlineStr">
+      <c r="G57" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -3468,7 +3468,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G58" s="11" t="inlineStr">
+      <c r="G58" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -3514,7 +3514,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G59" s="11" t="inlineStr">
+      <c r="G59" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -3556,7 +3556,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G60" s="11" t="inlineStr">
+      <c r="G60" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -3598,7 +3598,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G61" s="11" t="inlineStr">
+      <c r="G61" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -3681,7 +3681,7 @@
           <t>Vibe</t>
         </is>
       </c>
-      <c r="F63" s="10" t="inlineStr">
+      <c r="F63" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -3732,7 +3732,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G64" s="11" t="inlineStr">
+      <c r="G64" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -4158,7 +4158,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G73" s="11" t="inlineStr">
+      <c r="G73" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -4204,7 +4204,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G74" s="11" t="inlineStr">
+      <c r="G74" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -4250,7 +4250,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G75" s="11" t="inlineStr">
+      <c r="G75" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -4337,7 +4337,7 @@
           <t>Engineering</t>
         </is>
       </c>
-      <c r="F77" s="10" t="inlineStr">
+      <c r="F77" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -4475,7 +4475,7 @@
           <t>Engineering</t>
         </is>
       </c>
-      <c r="F80" s="10" t="inlineStr">
+      <c r="F80" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -4571,7 +4571,7 @@
           <t>Engineering</t>
         </is>
       </c>
-      <c r="F82" s="10" t="inlineStr">
+      <c r="F82" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -4843,7 +4843,7 @@
           <t>Engineering</t>
         </is>
       </c>
-      <c r="F88" s="10" t="inlineStr">
+      <c r="F88" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -5161,7 +5161,7 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="F95" s="10" t="inlineStr">
+      <c r="F95" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -5806,7 +5806,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G109" s="11" t="inlineStr">
+      <c r="G109" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -5852,7 +5852,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G110" s="11" t="inlineStr">
+      <c r="G110" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -5898,7 +5898,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G111" s="11" t="inlineStr">
+      <c r="G111" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -6466,12 +6466,12 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>PC-013</t>
+          <t>PC-012</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Verified integrations catalog with health tests</t>
+          <t>Legal and account basics: ToS, privacy, retention, deletion/export, email verification</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Vibe</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -6491,31 +6491,27 @@
       </c>
       <c r="F2" s="10" t="inlineStr">
         <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr"/>
       <c r="I2" s="3" t="inlineStr"/>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>R-511 Connectors v1 exists.</t>
-        </is>
-      </c>
+      <c r="J2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>PC-014</t>
+          <t>PC-013</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Local/offline models as a first-class path: build fully on Ollama, recommend a model per machine</t>
+          <t>Verified integrations catalog with health tests</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -6525,7 +6521,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Vibe</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -6533,7 +6529,7 @@
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="F3" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6547,19 +6543,19 @@
       <c r="I3" s="3" t="inlineStr"/>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>Ollama adapter exists (R-003/R-006). Found in PC-084: .env names qwen2.5-coder:14b but only 7b is installed, and the adapter refuses a pinned model it was not configured with — detect installed models instead of trusting the setting.</t>
+          <t>R-511 Connectors v1 exists.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>R-574</t>
+          <t>PC-014</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Store publishing for React Native apps: EAS build and submit to Play Store and App Store, proven with real accounts</t>
+          <t>Local/offline models as a first-class path: build fully on Ollama, recommend a model per machine</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -6577,7 +6573,7 @@
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6591,19 +6587,19 @@
       <c r="I4" s="3" t="inlineStr"/>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>R-546/R-547 generate the EAS config. Everything up to the upload is built and tested; the Apple and Google accounts (D-7) are plugged in at PC-070.</t>
+          <t>Ollama adapter exists (R-003/R-006). Found in PC-084: .env names qwen2.5-coder:14b but only 7b is installed, and the adapter refuses a pinned model it was not configured with — detect installed models instead of trusting the setting.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>PC-017</t>
+          <t>R-574</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Pack framework core: manifest v2 schema, registry/loader, composer (merge, wire, validate, conflict rules)</t>
+          <t>Store publishing for React Native apps: EAS build and submit to Play Store and App Store, proven with real accounts</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -6618,10 +6614,10 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>2 Maximum features</t>
-        </is>
-      </c>
-      <c r="F5" s="10" t="inlineStr">
+          <t>1 Vibe Mode live</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6635,19 +6631,19 @@
       <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>Solution Pack manifests, registry and application exist (R-434..R-445); v2 adds ir_delta, state machines, page templates, dependencies. From specs/pack-framework 01, 02.</t>
+          <t>R-546/R-547 generate the EAS config. Everything up to the upload is built and tested; the Apple and Google accounts (D-7) are plugged in at PC-070.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>PC-075</t>
+          <t>PC-017</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Role-based app generator: a complete app per role (nav, pages, API scope, permissions)</t>
+          <t>Pack framework core: manifest v2 schema, registry/loader, composer (merge, wire, validate, conflict rules)</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -6665,7 +6661,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6679,19 +6675,19 @@
       <c r="I6" s="3" t="inlineStr"/>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>R-555/R-562 already build one app per role; the spec asks for role-scoped pages and APIs. From specs/pack-framework/06b.</t>
+          <t>Solution Pack manifests, registry and application exist (R-434..R-445); v2 adds ir_delta, state machines, page templates, dependencies. From specs/pack-framework 01, 02.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>PC-077</t>
+          <t>PC-075</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Rich seed data generator: realistic, domain-aware, deterministic demo data</t>
+          <t>Role-based app generator: a complete app per role (nav, pages, API scope, permissions)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -6709,33 +6705,33 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F7" s="10" t="inlineStr">
+      <c r="F7" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G7" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr"/>
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>Fixture seeds exist (R-248) and must stay deterministic (R-586). From specs/pack-framework/06e.</t>
+          <t>R-555/R-562 already build one app per role; the spec asks for role-scoped pages and APIs. From specs/pack-framework/06b.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>PC-073</t>
+          <t>PC-077</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Horizontal packs, wave 1: the P0/P1 universal packs as manifest v2 packs that work alone and compose (HP-* rows)</t>
+          <t>Rich seed data generator: realistic, domain-aware, deterministic demo data</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -6753,33 +6749,33 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="F8" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr"/>
       <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>Core first (auth, database, API, design system, admin, payments, notifications, files, realtime, workflows), then the mobile &amp; device and AI packs. Each pack packages a capability built by its own task. Full list: PACK_CATALOG.md.</t>
+          <t>Fixture seeds exist (R-248) and must stay deterministic (R-586). From specs/pack-framework/06e.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>PC-074</t>
+          <t>PC-073</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Vertical packs, wave 1: healthcare, mobility, commerce (VP-* rows) on every surface: API, web, app, admin panel</t>
+          <t>Horizontal packs, wave 1: the P0/P1 universal packs as manifest v2 packs that work alone and compose (HP-* rows)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -6797,7 +6793,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr">
+      <c r="F9" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6811,19 +6807,19 @@
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>Built from the CareClinic, RideNow and Bazaar templates.</t>
+          <t>Core first (auth, database, API, design system, admin, payments, notifications, files, realtime, workflows), then the mobile &amp; device and AI packs. Each pack packages a capability built by its own task. Full list: PACK_CATALOG.md.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>PC-020</t>
+          <t>PC-074</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Brand kit / Style DNA UI across all surfaces</t>
+          <t>Vertical packs, wave 1: healthcare, mobility, commerce (VP-* rows) on every surface: API, web, app, admin panel</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -6833,7 +6829,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Vibe</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -6841,33 +6837,33 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G10" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr"/>
       <c r="I10" s="3" t="inlineStr"/>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>brand.json exists (R-548); needs the UI. Buildout idea 'R-526'.</t>
+          <t>Built from the CareClinic, RideNow and Bazaar templates.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>PC-023</t>
+          <t>PC-020</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Stack chooser: pick web/admin/mobile/backend, refused with a reason when unsupported</t>
+          <t>Brand kit / Style DNA UI across all surfaces</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -6877,41 +6873,41 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Vibe</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>3 Engineering Mode</t>
-        </is>
-      </c>
-      <c r="F11" s="10" t="inlineStr">
+          <t>2 Maximum features</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr"/>
       <c r="I11" s="3" t="inlineStr"/>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>R-565 carries the stack in the IR; needs the UI.</t>
+          <t>brand.json exists (R-548); needs the UI. Buildout idea 'R-526'.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>R-579</t>
+          <t>PC-023</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>GitHub import and push-back</t>
+          <t>Stack chooser: pick web/admin/mobile/backend, refused with a reason when unsupported</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -6929,7 +6925,7 @@
           <t>3 Engineering Mode</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr">
+      <c r="F12" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6943,19 +6939,19 @@
       <c r="I12" s="3" t="inlineStr"/>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>R-501 can push a generated project; import is missing.</t>
+          <t>R-565 carries the stack in the IR; needs the UI.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>PC-025</t>
+          <t>R-579</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Verification report view: per-surface compile, tests, security, in the Studio</t>
+          <t>GitHub import and push-back</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -6973,7 +6969,7 @@
           <t>3 Engineering Mode</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="F13" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6987,19 +6983,19 @@
       <c r="I13" s="3" t="inlineStr"/>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>R-560/R-561/R-508 produce the data; nothing shows it as a report.</t>
+          <t>R-501 can push a generated project; import is missing.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>PC-029</t>
+          <t>PC-025</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Team collaboration: roles, approvals, preview comments</t>
+          <t>Verification report view: per-surface compile, tests, security, in the Studio</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -7017,33 +7013,33 @@
           <t>3 Engineering Mode</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr">
+      <c r="F14" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G14" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr"/>
       <c r="I14" s="3" t="inlineStr"/>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>R-515 gives teams.</t>
+          <t>R-560/R-561/R-508 produce the data; nothing shows it as a report.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>PC-036</t>
+          <t>PC-029</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Migration safety checks for generated schema changes</t>
+          <t>Team collaboration: roles, approvals, preview comments</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -7053,55 +7049,59 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>4 Production ops</t>
-        </is>
-      </c>
-      <c r="F15" s="10" t="inlineStr">
+          <t>3 Engineering Mode</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr"/>
       <c r="I15" s="3" t="inlineStr"/>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>R-584 flags data loss; needs a real gate.</t>
+          <t>R-515 gives teams.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>ARCH-DOMAIN-IR</t>
+          <t>PC-036</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Domain IR: guards, business rules, field masks, row filters, page templates</t>
+          <t>Migration safety checks for generated schema changes</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>docs/ARCHITECTURE_MASTER_PLAN.md §5.2</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr"/>
+          <t>Platform_Completion queue</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>2 Maximum features</t>
-        </is>
-      </c>
-      <c r="F16" s="10" t="inlineStr">
+          <t>4 Production ops</t>
+        </is>
+      </c>
+      <c r="F16" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7111,32 +7111,28 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>R-570</t>
-        </is>
-      </c>
+      <c r="H16" s="3" t="inlineStr"/>
       <c r="I16" s="3" t="inlineStr"/>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>State machines done (R-566); field masks and row filters are R-570; guards and rules R-571.</t>
+          <t>R-584 flags data loss; needs a real gate.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>ARCH-GENERATORS</t>
+          <t>ARCH-DOMAIN-IR</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Advanced generators: state machine, role app, page template, shared package, seed data, form wizard, realtime</t>
+          <t>Domain IR: guards, business rules, field masks, row filters, page templates</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>docs/ARCHITECTURE_MASTER_PLAN.md §5.3</t>
+          <t>docs/ARCHITECTURE_MASTER_PLAN.md §5.2</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr"/>
@@ -7145,7 +7141,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F17" s="10" t="inlineStr">
+      <c r="F17" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7157,74 +7153,74 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>PC-017</t>
+          <t>R-570</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr"/>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>State machine done (R-566/588/589); shared package R-572; form wizard PC-059; realtime R-569.</t>
+          <t>State machines done (R-566); field masks and row filters are R-570; guards and rules R-571.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>ARCH-PIPELINE</t>
+          <t>ARCH-GENERATORS</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Vibe pipeline: classify -&gt; select packs -&gt; compose IR -&gt; generate -&gt; provision -&gt; preview in 90 s</t>
+          <t>Advanced generators: state machine, role app, page template, shared package, seed data, form wizard, realtime</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>docs/ARCHITECTURE_MASTER_PLAN.md §4.1</t>
+          <t>docs/ARCHITECTURE_MASTER_PLAN.md §5.3</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr"/>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Delivered</t>
-        </is>
-      </c>
-      <c r="F18" s="10" t="inlineStr">
+          <t>2 Maximum features</t>
+        </is>
+      </c>
+      <c r="F18" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>P0</t>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>PC-004</t>
+          <t>PC-017</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr"/>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>Generate and preview exist; provision is PC-049.</t>
+          <t>State machine done (R-566/588/589); shared package R-572; form wizard PC-059; realtime R-569.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>ARCH-PWA</t>
+          <t>ARCH-PIPELINE</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>PWA / offline support</t>
+          <t>Vibe pipeline: classify -&gt; select packs -&gt; compose IR -&gt; generate -&gt; provision -&gt; preview in 90 s</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>docs/ARCHITECTURE_MASTER_PLAN.md §10 Phase 4</t>
+          <t>docs/ARCHITECTURE_MASTER_PLAN.md §4.1</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr"/>
@@ -7233,7 +7229,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F19" s="10" t="inlineStr">
+      <c r="F19" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7245,47 +7241,51 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>R-573</t>
+          <t>PC-004</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr"/>
-      <c r="J19" s="3" t="inlineStr"/>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>Generate and preview exist; provision is PC-049.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>BP-BRANDKIT</t>
+          <t>ARCH-PWA</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Style DNA UI and brand kit studio</t>
+          <t>PWA / offline support</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Platform_Buildout section 8 ('R-526')</t>
+          <t>docs/ARCHITECTURE_MASTER_PLAN.md §10 Phase 4</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr"/>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>2 Maximum features</t>
-        </is>
-      </c>
-      <c r="F20" s="10" t="inlineStr">
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="F20" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G20" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>PC-020</t>
+          <t>R-573</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr"/>
@@ -7294,70 +7294,66 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>BP-SWITCHER</t>
+          <t>BP-BRANDKIT</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Multi-app ecosystem switcher and persona simulator</t>
+          <t>Style DNA UI and brand kit studio</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Platform_Buildout section 8 ('R-521')</t>
+          <t>Platform_Buildout section 8 ('R-526')</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr"/>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Delivered</t>
-        </is>
-      </c>
-      <c r="F21" s="10" t="inlineStr">
+          <t>2 Maximum features</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>PC-006</t>
+          <t>PC-020</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr"/>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>Multi-app preview exists (R-520, R-553); personas do not.</t>
-        </is>
-      </c>
+      <c r="J21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>GA-03</t>
+          <t>BP-SWITCHER</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>First-class Ollama-compatible provider with quality eval</t>
+          <t>Multi-app ecosystem switcher and persona simulator</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Tracker RND_Gap_Audit</t>
+          <t>Platform_Buildout section 8 ('R-521')</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr"/>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>1 Vibe Mode live</t>
-        </is>
-      </c>
-      <c r="F22" s="10" t="inlineStr">
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="F22" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7369,25 +7365,25 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>PC-014</t>
+          <t>PC-006</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr"/>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>Provider done (R-006); eval missing.</t>
+          <t>Multi-app preview exists (R-520, R-553); personas do not.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>GA-04</t>
+          <t>GA-03</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Per-model safe context registry, no silent truncation</t>
+          <t>First-class Ollama-compatible provider with quality eval</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -7401,7 +7397,7 @@
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="F23" s="10" t="inlineStr">
+      <c r="F23" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7419,19 +7415,19 @@
       <c r="I23" s="3" t="inlineStr"/>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>Safe input budget exists (R-522).</t>
+          <t>Provider done (R-006); eval missing.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>GA-05</t>
+          <t>GA-04</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Route by measured task, eval, latency, context and cost</t>
+          <t>Per-model safe context registry, no silent truncation</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -7445,14 +7441,14 @@
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="F24" s="10" t="inlineStr">
+      <c r="F24" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G24" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -7461,17 +7457,21 @@
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr"/>
-      <c r="J24" s="3" t="inlineStr"/>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>Safe input budget exists (R-522).</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>GA-07</t>
+          <t>GA-05</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Environments local -&gt; test -&gt; preview -&gt; staging -&gt; prod with typed config</t>
+          <t>Route by measured task, eval, latency, context and cost</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -7482,10 +7482,10 @@
       <c r="D25" s="3" t="inlineStr"/>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>4 Production ops</t>
-        </is>
-      </c>
-      <c r="F25" s="10" t="inlineStr">
+          <t>1 Vibe Mode live</t>
+        </is>
+      </c>
+      <c r="F25" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7497,7 +7497,7 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>PC-040</t>
+          <t>PC-014</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr"/>
@@ -7506,12 +7506,12 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>GA-11</t>
+          <t>GA-07</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Pinned supply chain, SBOM/provenance, patch SLA</t>
+          <t>Environments local -&gt; test -&gt; preview -&gt; staging -&gt; prod with typed config</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -7525,7 +7525,7 @@
           <t>4 Production ops</t>
         </is>
       </c>
-      <c r="F26" s="10" t="inlineStr">
+      <c r="F26" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7537,30 +7537,26 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>PC-035</t>
+          <t>PC-040</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr"/>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>Lockfiles pinned; SBOM missing.</t>
-        </is>
-      </c>
+      <c r="J26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>GAP-TESTTOOLS</t>
+          <t>GA-11</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Pin the testing toolchain (Playwright, pytest, go test, k6)</t>
+          <t>Pinned supply chain, SBOM/provenance, patch SLA</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>V6_Review_and_Gap_Analysis section 3</t>
+          <t>Tracker RND_Gap_Audit</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr"/>
@@ -7569,7 +7565,7 @@
           <t>4 Production ops</t>
         </is>
       </c>
-      <c r="F27" s="10" t="inlineStr">
+      <c r="F27" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7581,43 +7577,39 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>PC-037</t>
+          <t>PC-035</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr"/>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>pytest/unittest, go test and Playwright (templates) are in use; k6 is not.</t>
+          <t>Lockfiles pinned; SBOM missing.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>HP-accessibility</t>
+          <t>GAP-TESTTOOLS</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack accessibility: WCAG 2.1 AA, automated axe checks</t>
+          <t>Pin the testing toolchain (Playwright, pytest, go test, k6)</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>spec</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>UI &amp; experience</t>
-        </is>
-      </c>
+          <t>V6_Review_and_Gap_Analysis section 3</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr"/>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>2 Maximum features</t>
-        </is>
-      </c>
-      <c r="F28" s="10" t="inlineStr">
+          <t>4 Production ops</t>
+        </is>
+      </c>
+      <c r="F28" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7629,35 +7621,35 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>PC-078</t>
+          <t>PC-037</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr"/>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>Accessible UI exists (R-296).</t>
+          <t>pytest/unittest, go test and Playwright (templates) are in use; k6 is not.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>HP-activity-feed</t>
+          <t>HP-accessibility</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack activity-feed: Activity streams, timelines, follow/subscribe</t>
+          <t>Horizontal pack accessibility: WCAG 2.1 AA, automated axe checks</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>new (registry dependency)</t>
+          <t>spec</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Realtime &amp; communication</t>
+          <t>UI &amp; experience</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -7665,7 +7657,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F29" s="10" t="inlineStr">
+      <c r="F29" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7683,29 +7675,29 @@
       <c r="I29" s="3" t="inlineStr"/>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>Timeline component exists (R-336).</t>
+          <t>Accessible UI exists (R-296).</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>HP-admin-crud</t>
+          <t>HP-activity-feed</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack admin-crud: Generated admin: tables, filters, bulk actions, exports</t>
+          <t>Horizontal pack activity-feed: Activity streams, timelines, follow/subscribe</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>spec</t>
+          <t>new (registry dependency)</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Core platform</t>
+          <t>Realtime &amp; communication</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -7713,47 +7705,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F30" s="10" t="inlineStr">
+      <c r="F30" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G30" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>PC-073</t>
+          <t>PC-078</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr"/>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>Admin app exists (R-542, R-270, R-271).</t>
+          <t>Timeline component exists (R-336).</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>HP-analytics-events</t>
+          <t>HP-admin-crud</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack analytics-events: Event tracking, funnels, cohorts (PostHog/GA4)</t>
+          <t>Horizontal pack admin-crud: Generated admin: tables, filters, bulk actions, exports</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>spec, registry</t>
+          <t>spec</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Data &amp; storage</t>
+          <t>Core platform</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -7761,47 +7753,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F31" s="10" t="inlineStr">
+      <c r="F31" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G31" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>PC-078</t>
+          <t>PC-073</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr"/>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>Published-app analytics exists (R-513).</t>
+          <t>Admin app exists (R-542, R-270, R-271).</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>HP-api-core</t>
+          <t>HP-analytics-events</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack api-core: REST API, validation, OpenAPI, errors, rate limiting</t>
+          <t>Horizontal pack analytics-events: Event tracking, funnels, cohorts (PostHog/GA4)</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>registry</t>
+          <t>spec, registry</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Core platform</t>
+          <t>Data &amp; storage</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -7809,42 +7801,42 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F32" s="10" t="inlineStr">
+      <c r="F32" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G32" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G32" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>PC-073</t>
+          <t>PC-078</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr"/>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>Python/Go/Node APIs exist (R-229, R-230, R-517).</t>
+          <t>Published-app analytics exists (R-513).</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>HP-api-docs</t>
+          <t>HP-api-core</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack api-docs: OpenAPI, Swagger UI, Postman collection, SDKs</t>
+          <t>Horizontal pack api-core: REST API, validation, OpenAPI, errors, rate limiting</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>spec</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -7857,47 +7849,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F33" s="10" t="inlineStr">
+      <c r="F33" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G33" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>PC-078</t>
+          <t>PC-073</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr"/>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>OpenAPI exists (R-260, R-588).</t>
+          <t>Python/Go/Node APIs exist (R-229, R-230, R-517).</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>HP-app-store-assets</t>
+          <t>HP-api-docs</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack app-store-assets: Icons, splash, screenshots, store listing metadata</t>
+          <t>Horizontal pack api-docs: OpenAPI, Swagger UI, Postman collection, SDKs</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>spec</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Mobile &amp; device (stack-aware: React Native, Kotlin, Swift)</t>
+          <t>Core platform</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -7905,47 +7897,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F34" s="10" t="inlineStr">
+      <c r="F34" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G34" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>PC-073</t>
+          <t>PC-078</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr"/>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>Icons and EAS config exist (R-546, R-547); R-574.</t>
+          <t>OpenAPI exists (R-260, R-588).</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>HP-auth-rbac</t>
+          <t>HP-app-store-assets</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack auth-rbac: Login, register, roles, sessions, MFA, OAuth, passkeys</t>
+          <t>Horizontal pack app-store-assets: Icons, splash, screenshots, store listing metadata</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>spec, registry</t>
+          <t>new</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Core platform</t>
+          <t>Mobile &amp; device (stack-aware: React Native, Kotlin, Swift)</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -7953,7 +7945,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F35" s="10" t="inlineStr">
+      <c r="F35" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7971,29 +7963,29 @@
       <c r="I35" s="3" t="inlineStr"/>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>Auth exists (R-461, R-241..R-243); Go login R-591.</t>
+          <t>Icons and EAS config exist (R-546, R-547); R-574.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>HP-camera-qr</t>
+          <t>HP-auth-rbac</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack camera-qr: Camera, photo/video capture, QR and barcode scanning</t>
+          <t>Horizontal pack auth-rbac: Login, register, roles, sessions, MFA, OAuth, passkeys</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>PRD (+ registry 'barcode')</t>
+          <t>spec, registry</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Mobile &amp; device (stack-aware: React Native, Kotlin, Swift)</t>
+          <t>Core platform</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -8001,7 +7993,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F36" s="10" t="inlineStr">
+      <c r="F36" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8019,29 +8011,29 @@
       <c r="I36" s="3" t="inlineStr"/>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>QR generation exists (R-382).</t>
+          <t>Auth exists (R-461, R-241..R-243); Go login R-591.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>HP-charts-dashboards</t>
+          <t>HP-camera-qr</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack charts-dashboards: Charts, dashboards, live series</t>
+          <t>Horizontal pack camera-qr: Camera, photo/video capture, QR and barcode scanning</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>registry</t>
+          <t>PRD (+ registry 'barcode')</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>UI &amp; experience</t>
+          <t>Mobile &amp; device (stack-aware: React Native, Kotlin, Swift)</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -8049,37 +8041,37 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F37" s="10" t="inlineStr">
+      <c r="F37" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G37" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>PC-078</t>
+          <t>PC-073</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr"/>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>Chart suite exists (R-370).</t>
+          <t>QR generation exists (R-382).</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>HP-ci-cd</t>
+          <t>HP-charts-dashboards</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack ci-cd: CI workflows, containers, Helm, preview environments</t>
+          <t>Horizontal pack charts-dashboards: Charts, dashboards, live series</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -8089,7 +8081,7 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Core platform</t>
+          <t>UI &amp; experience</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -8097,7 +8089,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F38" s="10" t="inlineStr">
+      <c r="F38" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8115,29 +8107,29 @@
       <c r="I38" s="3" t="inlineStr"/>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>CI/CD workflow generation exists (R-452).</t>
+          <t>Chart suite exists (R-370).</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>HP-communications</t>
+          <t>HP-ci-cd</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack communications: 1:1 and group chat, threads, mentions, reactions, attachments</t>
+          <t>Horizontal pack ci-cd: CI workflows, containers, Helm, preview environments</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>spec, registry</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Realtime &amp; communication</t>
+          <t>Core platform</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -8145,7 +8137,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F39" s="10" t="inlineStr">
+      <c r="F39" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8163,29 +8155,29 @@
       <c r="I39" s="3" t="inlineStr"/>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>Chat component exists (R-384).</t>
+          <t>CI/CD workflow generation exists (R-452).</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>HP-config-env</t>
+          <t>HP-communications</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack config-env: Typed env config, secret references, multi-environment</t>
+          <t>Horizontal pack communications: 1:1 and group chat, threads, mentions, reactions, attachments</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>registry</t>
+          <t>spec, registry</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Core platform</t>
+          <t>Realtime &amp; communication</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -8193,7 +8185,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F40" s="10" t="inlineStr">
+      <c r="F40" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8211,29 +8203,29 @@
       <c r="I40" s="3" t="inlineStr"/>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>Credential templates exist (R-547).</t>
+          <t>Chat component exists (R-384).</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>HP-consent-management</t>
+          <t>HP-config-env</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack consent-management: Consent capture and ledger, cookie preferences</t>
+          <t>Horizontal pack config-env: Typed env config, secret references, multi-environment</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>new (registry dependency)</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Security &amp; compliance</t>
+          <t>Core platform</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -8241,7 +8233,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F41" s="10" t="inlineStr">
+      <c r="F41" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8259,29 +8251,29 @@
       <c r="I41" s="3" t="inlineStr"/>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>Cookie consent component exists (R-402).</t>
+          <t>Credential templates exist (R-547).</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>HP-custom-domains</t>
+          <t>HP-consent-management</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack custom-domains: Custom domains, DNS, TLS certificates</t>
+          <t>Horizontal pack consent-management: Consent capture and ledger, cookie preferences</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>new (registry dependency 'dns')</t>
+          <t>new (registry dependency)</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Core platform</t>
+          <t>Security &amp; compliance</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -8289,7 +8281,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F42" s="10" t="inlineStr">
+      <c r="F42" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8307,29 +8299,29 @@
       <c r="I42" s="3" t="inlineStr"/>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>Custom domains exist for published apps (R-510).</t>
+          <t>Cookie consent component exists (R-402).</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>HP-data-import-export</t>
+          <t>HP-custom-domains</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack data-import-export: CSV/Excel import with mapping and validation; bulk export</t>
+          <t>Horizontal pack custom-domains: Custom domains, DNS, TLS certificates</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>new (registry dependency 'dns')</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>Data &amp; storage</t>
+          <t>Core platform</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -8337,7 +8329,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F43" s="10" t="inlineStr">
+      <c r="F43" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8355,29 +8347,29 @@
       <c r="I43" s="3" t="inlineStr"/>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>CSV/JSON export exists (R-271, R-308).</t>
+          <t>Custom domains exist for published apps (R-510).</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>HP-data-tables</t>
+          <t>HP-data-import-export</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack data-tables: Virtualised tables, grouping, column picker, export</t>
+          <t>Horizontal pack data-import-export: CSV/Excel import with mapping and validation; bulk export</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>registry</t>
+          <t>new</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>UI &amp; experience</t>
+          <t>Data &amp; storage</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -8385,7 +8377,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F44" s="10" t="inlineStr">
+      <c r="F44" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8403,19 +8395,19 @@
       <c r="I44" s="3" t="inlineStr"/>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>Data grid exists (R-329).</t>
+          <t>CSV/JSON export exists (R-271, R-308).</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>HP-database-pg</t>
+          <t>HP-data-tables</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack database-pg: PostgreSQL schema, migrations, seeds, row-level security</t>
+          <t>Horizontal pack data-tables: Virtualised tables, grouping, column picker, export</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -8425,7 +8417,7 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Core platform</t>
+          <t>UI &amp; experience</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -8433,37 +8425,37 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F45" s="10" t="inlineStr">
+      <c r="F45" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G45" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G45" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>PC-073</t>
+          <t>PC-078</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr"/>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>Schema/migrations/seeds exist (R-238, R-248).</t>
+          <t>Data grid exists (R-329).</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>HP-design-system</t>
+          <t>HP-database-pg</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack design-system: Design tokens, components, motion, dark mode</t>
+          <t>Horizontal pack database-pg: PostgreSQL schema, migrations, seeds, row-level security</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -8473,7 +8465,7 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>UI &amp; experience</t>
+          <t>Core platform</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -8481,7 +8473,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F46" s="10" t="inlineStr">
+      <c r="F46" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8499,29 +8491,29 @@
       <c r="I46" s="3" t="inlineStr"/>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>Design system exists (R-558, R-324, R-491).</t>
+          <t>Schema/migrations/seeds exist (R-238, R-248).</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>HP-e-sign</t>
+          <t>HP-design-system</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack e-sign: Document signing, signer flows, certificates</t>
+          <t>Horizontal pack design-system: Design tokens, components, motion, dark mode</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>new (registry dependency)</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>Business logic &amp; workflow</t>
+          <t>UI &amp; experience</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -8529,47 +8521,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F47" s="10" t="inlineStr">
+      <c r="F47" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G47" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>PC-078</t>
+          <t>PC-073</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr"/>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>Signature pad exists (R-372).</t>
+          <t>Design system exists (R-558, R-324, R-491).</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>HP-integration-hub</t>
+          <t>HP-e-sign</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack integration-hub: Connectors (Slack, HubSpot, Salesforce ...), workflow builder</t>
+          <t>Horizontal pack e-sign: Document signing, signer flows, certificates</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>registry</t>
+          <t>new (registry dependency)</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Integration &amp; AI</t>
+          <t>Business logic &amp; workflow</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
@@ -8577,7 +8569,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F48" s="10" t="inlineStr">
+      <c r="F48" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8595,29 +8587,29 @@
       <c r="I48" s="3" t="inlineStr"/>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>Connectors v1 exist (R-511).</t>
+          <t>Signature pad exists (R-372).</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>HP-maps-geo</t>
+          <t>HP-integration-hub</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack maps-geo: Maps, geocoding, geofences, routes, address autocomplete</t>
+          <t>Horizontal pack integration-hub: Connectors (Slack, HubSpot, Salesforce ...), workflow builder</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>registry ('mapping', listed under mobility), PRD</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>UI &amp; experience</t>
+          <t>Integration &amp; AI</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -8625,47 +8617,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F49" s="10" t="inlineStr">
+      <c r="F49" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G49" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G49" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>PC-073</t>
+          <t>PC-078</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr"/>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>Geo-map component exists (R-387).</t>
+          <t>Connectors v1 exist (R-511).</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>HP-media-player-device</t>
+          <t>HP-maps-geo</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack media-player-device: Audio/video playback, background audio, casting</t>
+          <t>Horizontal pack maps-geo: Maps, geocoding, geofences, routes, address autocomplete</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>registry ('mapping', listed under mobility), PRD</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Mobile &amp; device (stack-aware: React Native, Kotlin, Swift)</t>
+          <t>UI &amp; experience</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -8673,47 +8665,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F50" s="10" t="inlineStr">
+      <c r="F50" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G50" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>PC-079</t>
+          <t>PC-073</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr"/>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>Web media players exist (R-376, R-390).</t>
+          <t>Geo-map component exists (R-387).</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>HP-multi-app</t>
+          <t>HP-media-player-device</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack multi-app: Shared API, cross-app auth, preview proxy, deploy coordination</t>
+          <t>Horizontal pack media-player-device: Audio/video playback, background audio, casting</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>spec</t>
+          <t>new</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Core platform</t>
+          <t>Mobile &amp; device (stack-aware: React Native, Kotlin, Swift)</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -8721,47 +8713,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F51" s="10" t="inlineStr">
+      <c r="F51" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G51" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G51" s="12" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>PC-073</t>
+          <t>PC-079</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr"/>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>Ecosystem monorepo exists (R-554, R-447, R-553).</t>
+          <t>Web media players exist (R-376, R-390).</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>HP-multi-currency</t>
+          <t>HP-multi-app</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack multi-currency: Currencies, exchange rates, price lists</t>
+          <t>Horizontal pack multi-app: Shared API, cross-app auth, preview proxy, deploy coordination</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>registry (listed under commerce)</t>
+          <t>spec</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Commerce &amp; payments</t>
+          <t>Core platform</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
@@ -8769,47 +8761,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F52" s="10" t="inlineStr">
+      <c r="F52" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G52" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G52" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>PC-078</t>
+          <t>PC-073</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr"/>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>Currency input exists (R-409).</t>
+          <t>Ecosystem monorepo exists (R-554, R-447, R-553).</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>HP-notifications</t>
+          <t>HP-multi-currency</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack notifications: Email, SMS, push, in-app centre, preferences, digests</t>
+          <t>Horizontal pack multi-currency: Currencies, exchange rates, price lists</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>spec, registry</t>
+          <t>registry (listed under commerce)</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Realtime &amp; communication</t>
+          <t>Commerce &amp; payments</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
@@ -8817,47 +8809,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F53" s="10" t="inlineStr">
+      <c r="F53" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G53" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G53" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>PC-073</t>
+          <t>PC-078</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr"/>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>Email exists (R-516); PC-053.</t>
+          <t>Currency input exists (R-409).</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>HP-onboarding-tours</t>
+          <t>HP-notifications</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack onboarding-tours: Product tours and spotlight guides</t>
+          <t>Horizontal pack notifications: Email, SMS, push, in-app centre, preferences, digests</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>spec, registry</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>UI &amp; experience</t>
+          <t>Realtime &amp; communication</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
@@ -8865,47 +8857,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F54" s="10" t="inlineStr">
+      <c r="F54" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G54" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>PC-079</t>
+          <t>PC-073</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr"/>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>Tour component exists (R-363).</t>
+          <t>Email exists (R-516); PC-053.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>HP-payments-core</t>
+          <t>HP-onboarding-tours</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack payments-core: Stripe/Razorpay/Paddle payments, refunds, disputes</t>
+          <t>Horizontal pack onboarding-tours: Product tours and spotlight guides</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>spec, registry, PRD</t>
+          <t>new</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Commerce &amp; payments</t>
+          <t>UI &amp; experience</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -8913,47 +8905,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F55" s="10" t="inlineStr">
+      <c r="F55" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G55" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G55" s="12" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>PC-073</t>
+          <t>PC-079</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr"/>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>Checkout exists (R-512).</t>
+          <t>Tour component exists (R-363).</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>HP-pdf-documents</t>
+          <t>HP-payments-core</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack pdf-documents: Document templates, PDF generation, document store</t>
+          <t>Horizontal pack payments-core: Stripe/Razorpay/Paddle payments, refunds, disputes</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>new (registry dependencies 'documents', 'pdf-generation')</t>
+          <t>spec, registry, PRD</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Data &amp; storage</t>
+          <t>Commerce &amp; payments</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
@@ -8961,47 +8953,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F56" s="10" t="inlineStr">
+      <c r="F56" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G56" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G56" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>PC-078</t>
+          <t>PC-073</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr"/>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>PDF viewer component exists (R-388).</t>
+          <t>Checkout exists (R-512).</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>HP-pwa</t>
+          <t>HP-pdf-documents</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack pwa: Installable app, service worker, offline, push, QR</t>
+          <t>Horizontal pack pdf-documents: Document templates, PDF generation, document store</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>spec</t>
+          <t>new (registry dependencies 'documents', 'pdf-generation')</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>UI &amp; experience</t>
+          <t>Data &amp; storage</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
@@ -9009,37 +9001,37 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F57" s="10" t="inlineStr">
+      <c r="F57" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G57" s="6" t="inlineStr">
-        <is>
-          <t>P0</t>
+      <c r="G57" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>PC-073</t>
+          <t>PC-078</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr"/>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>R-573.</t>
+          <t>PDF viewer component exists (R-388).</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>HP-ratings-reviews</t>
+          <t>HP-pwa</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack ratings-reviews: Stars, reviews, moderation, aggregates</t>
+          <t>Horizontal pack pwa: Installable app, service worker, offline, push, QR</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -9049,7 +9041,7 @@
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Business logic &amp; workflow</t>
+          <t>UI &amp; experience</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
@@ -9057,47 +9049,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F58" s="10" t="inlineStr">
+      <c r="F58" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G58" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>PC-078</t>
+          <t>PC-073</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr"/>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>Rating component exists (R-333).</t>
+          <t>R-573.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>HP-rich-text</t>
+          <t>HP-ratings-reviews</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack rich-text: Rich text editor, mentions, slash commands</t>
+          <t>Horizontal pack ratings-reviews: Stars, reviews, moderation, aggregates</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>registry</t>
+          <t>spec</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>UI &amp; experience</t>
+          <t>Business logic &amp; workflow</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -9105,7 +9097,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F59" s="10" t="inlineStr">
+      <c r="F59" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9123,29 +9115,29 @@
       <c r="I59" s="3" t="inlineStr"/>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>Markdown editor exists (R-365).</t>
+          <t>Rating component exists (R-333).</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>HP-scheduling</t>
+          <t>HP-rich-text</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack scheduling: Calendars, recurrence, conflicts, time zones, bookings, reminders</t>
+          <t>Horizontal pack rich-text: Rich text editor, mentions, slash commands</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>spec, registry</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Business logic &amp; workflow</t>
+          <t>UI &amp; experience</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
@@ -9153,37 +9145,37 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F60" s="10" t="inlineStr">
+      <c r="F60" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G60" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G60" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>PC-073</t>
+          <t>PC-078</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr"/>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>Calendar/time-picker components exist (R-366, R-371).</t>
+          <t>Markdown editor exists (R-365).</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>HP-search-engine</t>
+          <t>HP-scheduling</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack search-engine: Meilisearch/Typesense, facets, typo tolerance</t>
+          <t>Horizontal pack scheduling: Calendars, recurrence, conflicts, time zones, bookings, reminders</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -9193,7 +9185,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Data &amp; storage</t>
+          <t>Business logic &amp; workflow</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
@@ -9201,47 +9193,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F61" s="10" t="inlineStr">
+      <c r="F61" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G61" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="G61" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>PC-079</t>
+          <t>PC-073</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr"/>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>Keyword search exists (R-261); PC-058.</t>
+          <t>Calendar/time-picker components exist (R-366, R-371).</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>HP-secrets</t>
+          <t>HP-search-engine</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack secrets: Secret management, rotation, audit</t>
+          <t>Horizontal pack search-engine: Meilisearch/Typesense, facets, typo tolerance</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>spec</t>
+          <t>spec, registry</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>Security &amp; compliance</t>
+          <t>Data &amp; storage</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
@@ -9249,47 +9241,47 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F62" s="10" t="inlineStr">
+      <c r="F62" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G62" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G62" s="12" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>PC-078</t>
+          <t>PC-079</t>
         </is>
       </c>
       <c r="I62" s="3" t="inlineStr"/>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>Platform secrets exist (R-503).</t>
+          <t>Keyword search exists (R-261); PC-058.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>HP-seo</t>
+          <t>HP-secrets</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack seo: Metadata, sitemaps, structured data, AI-search readiness</t>
+          <t>Horizontal pack secrets: Secret management, rotation, audit</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>new (registry dependency)</t>
+          <t>spec</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>UI &amp; experience</t>
+          <t>Security &amp; compliance</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
@@ -9297,7 +9289,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F63" s="10" t="inlineStr">
+      <c r="F63" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9315,29 +9307,29 @@
       <c r="I63" s="3" t="inlineStr"/>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>SEO exists (R-505).</t>
+          <t>Platform secrets exist (R-503).</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>HP-task-management</t>
+          <t>HP-seo</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack task-management: Tasks, assignees, due dates, boards</t>
+          <t>Horizontal pack seo: Metadata, sitemaps, structured data, AI-search readiness</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>new (registry dependency 'tasks')</t>
+          <t>new (registry dependency)</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>Business logic &amp; workflow</t>
+          <t>UI &amp; experience</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
@@ -9345,7 +9337,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F64" s="10" t="inlineStr">
+      <c r="F64" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9363,29 +9355,29 @@
       <c r="I64" s="3" t="inlineStr"/>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>Kanban component exists (R-367).</t>
+          <t>SEO exists (R-505).</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>HP-theming-branding</t>
+          <t>HP-task-management</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack theming-branding: Brand kit applied to every surface</t>
+          <t>Horizontal pack task-management: Tasks, assignees, due dates, boards</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>new (registry dependency 'tasks')</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>UI &amp; experience</t>
+          <t>Business logic &amp; workflow</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
@@ -9393,7 +9385,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F65" s="10" t="inlineStr">
+      <c r="F65" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9411,29 +9403,29 @@
       <c r="I65" s="3" t="inlineStr"/>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>brand.json exists (R-548); PC-020.</t>
+          <t>Kanban component exists (R-367).</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>HP-webhooks</t>
+          <t>HP-theming-branding</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack webhooks: Outgoing webhooks, retries, signatures, replay</t>
+          <t>Horizontal pack theming-branding: Brand kit applied to every surface</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>spec, registry</t>
+          <t>new</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>Realtime &amp; communication</t>
+          <t>UI &amp; experience</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
@@ -9441,7 +9433,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F66" s="10" t="inlineStr">
+      <c r="F66" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9459,19 +9451,19 @@
       <c r="I66" s="3" t="inlineStr"/>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>Cross-surface webhooks exist (R-448); PC-057.</t>
+          <t>brand.json exists (R-548); PC-020.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>HP-workflows-core</t>
+          <t>HP-webhooks</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Horizontal pack workflows-core: State machines, transitions, guards, actions, audit</t>
+          <t>Horizontal pack webhooks: Outgoing webhooks, retries, signatures, replay</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -9481,7 +9473,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>Business logic &amp; workflow</t>
+          <t>Realtime &amp; communication</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
@@ -9489,51 +9481,55 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F67" s="10" t="inlineStr">
+      <c r="F67" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G67" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G67" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H67" s="3" t="inlineStr">
         <is>
-          <t>PC-073</t>
+          <t>PC-078</t>
         </is>
       </c>
       <c r="I67" s="3" t="inlineStr"/>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>Transitions done (R-566, R-588, R-589); guards R-571; buttons R-590.</t>
+          <t>Cross-surface webhooks exist (R-448); PC-057.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>PG-17</t>
+          <t>HP-workflows-core</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>A fresh AI/developer session resumes the task from Git + durable state</t>
+          <t>Horizontal pack workflows-core: State machines, transitions, guards, actions, audit</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>Tracker Production_Gates</t>
-        </is>
-      </c>
-      <c r="D68" s="3" t="inlineStr"/>
+          <t>spec, registry</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Business logic &amp; workflow</t>
+        </is>
+      </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>4 Production ops</t>
-        </is>
-      </c>
-      <c r="F68" s="10" t="inlineStr">
+          <t>2 Maximum features</t>
+        </is>
+      </c>
+      <c r="F68" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9545,25 +9541,25 @@
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>PC-067</t>
+          <t>PC-073</t>
         </is>
       </c>
       <c r="I68" s="3" t="inlineStr"/>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>AGENTS.md, CURRENT_TASK.yaml and this queue exist; the formal drill does not.</t>
+          <t>Transitions done (R-566, R-588, R-589); guards R-571; buttons R-590.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>PG-19</t>
+          <t>PG-17</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Local model endpoint exposure/auth/network policy</t>
+          <t>A fresh AI/developer session resumes the task from Git + durable state</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
@@ -9574,10 +9570,10 @@
       <c r="D69" s="3" t="inlineStr"/>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>1 Vibe Mode live</t>
-        </is>
-      </c>
-      <c r="F69" s="10" t="inlineStr">
+          <t>4 Production ops</t>
+        </is>
+      </c>
+      <c r="F69" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9589,43 +9585,39 @@
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>PC-014</t>
+          <t>PC-067</t>
         </is>
       </c>
       <c r="I69" s="3" t="inlineStr"/>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>Ollama is loopback-only (R-003).</t>
+          <t>AGENTS.md, CURRENT_TASK.yaml and this queue exist; the formal drill does not.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>R-027</t>
+          <t>PG-19</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>pgvector initially</t>
+          <t>Local model endpoint exposure/auth/network policy</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>Execution_Tracker_v6</t>
-        </is>
-      </c>
-      <c r="D70" s="3" t="inlineStr">
-        <is>
-          <t>Data</t>
-        </is>
-      </c>
+          <t>Tracker Production_Gates</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr"/>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>3 Engineering Mode</t>
-        </is>
-      </c>
-      <c r="F70" s="10" t="inlineStr">
+          <t>1 Vibe Mode live</t>
+        </is>
+      </c>
+      <c r="F70" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9637,25 +9629,25 @@
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>R-581</t>
+          <t>PC-014</t>
         </is>
       </c>
       <c r="I70" s="3" t="inlineStr"/>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>Extension installed, no embeddings table.</t>
+          <t>Ollama is loopback-only (R-003).</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>R-040</t>
+          <t>R-027</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>Migration safety checks</t>
+          <t>pgvector initially</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -9665,15 +9657,15 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>4 Production ops</t>
-        </is>
-      </c>
-      <c r="F71" s="10" t="inlineStr">
+          <t>3 Engineering Mode</t>
+        </is>
+      </c>
+      <c r="F71" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9685,21 +9677,25 @@
       </c>
       <c r="H71" s="3" t="inlineStr">
         <is>
-          <t>PC-036</t>
+          <t>R-581</t>
         </is>
       </c>
       <c r="I71" s="3" t="inlineStr"/>
-      <c r="J71" s="3" t="inlineStr"/>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>Extension installed, no embeddings table.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>R-055</t>
+          <t>R-040</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>Verified integration catalog</t>
+          <t>Migration safety checks</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -9709,15 +9705,15 @@
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>Integrations</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>1 Vibe Mode live</t>
-        </is>
-      </c>
-      <c r="F72" s="10" t="inlineStr">
+          <t>4 Production ops</t>
+        </is>
+      </c>
+      <c r="F72" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9729,7 +9725,7 @@
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>PC-013</t>
+          <t>PC-036</t>
         </is>
       </c>
       <c r="I72" s="3" t="inlineStr"/>
@@ -9738,12 +9734,12 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>R-062</t>
+          <t>R-055</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>App Store / TestFlight automation</t>
+          <t>Verified integration catalog</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -9753,7 +9749,7 @@
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>Deployment</t>
+          <t>Integrations</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
@@ -9761,7 +9757,7 @@
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="F73" s="10" t="inlineStr">
+      <c r="F73" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9773,25 +9769,21 @@
       </c>
       <c r="H73" s="3" t="inlineStr">
         <is>
-          <t>R-574</t>
+          <t>PC-013</t>
         </is>
       </c>
       <c r="I73" s="3" t="inlineStr"/>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>React Native first; native reuses the pipeline (PC-044).</t>
-        </is>
-      </c>
+      <c r="J73" s="3" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>R-063</t>
+          <t>R-062</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>Play Store automation</t>
+          <t>App Store / TestFlight automation</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -9809,7 +9801,7 @@
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="F74" s="10" t="inlineStr">
+      <c r="F74" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9834,12 +9826,12 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>R-064</t>
+          <t>R-063</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>RBAC + approvals</t>
+          <t>Play Store automation</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -9849,41 +9841,45 @@
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Deployment</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>3 Engineering Mode</t>
-        </is>
-      </c>
-      <c r="F75" s="10" t="inlineStr">
+          <t>1 Vibe Mode live</t>
+        </is>
+      </c>
+      <c r="F75" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G75" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G75" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H75" s="3" t="inlineStr">
         <is>
-          <t>PC-029</t>
+          <t>R-574</t>
         </is>
       </c>
       <c r="I75" s="3" t="inlineStr"/>
-      <c r="J75" s="3" t="inlineStr"/>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>React Native first; native reuses the pipeline (PC-044).</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>R-080</t>
+          <t>R-064</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>Self-hosted/local models</t>
+          <t>RBAC + approvals</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -9893,45 +9889,41 @@
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>Models</t>
+          <t>Collaboration</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>1 Vibe Mode live</t>
-        </is>
-      </c>
-      <c r="F76" s="10" t="inlineStr">
+          <t>3 Engineering Mode</t>
+        </is>
+      </c>
+      <c r="F76" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G76" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G76" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>PC-014</t>
+          <t>PC-029</t>
         </is>
       </c>
       <c r="I76" s="3" t="inlineStr"/>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>Ollama adapter exists (R-003, R-006).</t>
-        </is>
-      </c>
+      <c r="J76" s="3" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>R-126</t>
+          <t>R-080</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>Organization &gt; Workspace &gt; Project &gt; Environment model</t>
+          <t>Self-hosted/local models</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
@@ -9941,45 +9933,45 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>Product Foundation</t>
+          <t>Models</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>4 Production ops</t>
-        </is>
-      </c>
-      <c r="F77" s="10" t="inlineStr">
+          <t>1 Vibe Mode live</t>
+        </is>
+      </c>
+      <c r="F77" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G77" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G77" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H77" s="3" t="inlineStr">
         <is>
-          <t>PC-040</t>
+          <t>PC-014</t>
         </is>
       </c>
       <c r="I77" s="3" t="inlineStr"/>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>Org, workspace and project exist (R-499, R-515).</t>
+          <t>Ollama adapter exists (R-003, R-006).</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>R-135</t>
+          <t>R-126</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>Stack selection wizard</t>
+          <t>Organization &gt; Workspace &gt; Project &gt; Environment model</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -9989,41 +9981,45 @@
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>Framework Strategy</t>
+          <t>Product Foundation</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>3 Engineering Mode</t>
-        </is>
-      </c>
-      <c r="F78" s="10" t="inlineStr">
+          <t>4 Production ops</t>
+        </is>
+      </c>
+      <c r="F78" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G78" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G78" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>PC-023</t>
+          <t>PC-040</t>
         </is>
       </c>
       <c r="I78" s="3" t="inlineStr"/>
-      <c r="J78" s="3" t="inlineStr"/>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>Org, workspace and project exist (R-499, R-515).</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>R-194</t>
+          <t>R-135</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>Hybrid BYOK/local mode</t>
+          <t>Stack selection wizard</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
@@ -10033,15 +10029,15 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Framework Strategy</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>1 Vibe Mode live</t>
-        </is>
-      </c>
-      <c r="F79" s="10" t="inlineStr">
+          <t>3 Engineering Mode</t>
+        </is>
+      </c>
+      <c r="F79" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10053,7 +10049,7 @@
       </c>
       <c r="H79" s="3" t="inlineStr">
         <is>
-          <t>PC-014</t>
+          <t>PC-023</t>
         </is>
       </c>
       <c r="I79" s="3" t="inlineStr"/>
@@ -10062,26 +10058,30 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>SPEC-PACK-01</t>
+          <t>R-194</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>Pack manifest v2 schema</t>
+          <t>Hybrid BYOK/local mode</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>specs/pack-framework/01</t>
-        </is>
-      </c>
-      <c r="D80" s="3" t="inlineStr"/>
+          <t>Execution_Tracker_v6</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>Execution</t>
+        </is>
+      </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>2 Maximum features</t>
-        </is>
-      </c>
-      <c r="F80" s="10" t="inlineStr">
+          <t>1 Vibe Mode live</t>
+        </is>
+      </c>
+      <c r="F80" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10093,30 +10093,26 @@
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>PC-017</t>
+          <t>PC-014</t>
         </is>
       </c>
       <c r="I80" s="3" t="inlineStr"/>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>Draft spec (called R-600 inside).</t>
-        </is>
-      </c>
+      <c r="J80" s="3" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>SPEC-PACK-06B</t>
+          <t>SPEC-PACK-01</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>Role-based app generator</t>
+          <t>Pack manifest v2 schema</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>specs/pack-framework/06b</t>
+          <t>specs/pack-framework/01</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr"/>
@@ -10125,7 +10121,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F81" s="10" t="inlineStr">
+      <c r="F81" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10137,30 +10133,30 @@
       </c>
       <c r="H81" s="3" t="inlineStr">
         <is>
-          <t>PC-075</t>
+          <t>PC-017</t>
         </is>
       </c>
       <c r="I81" s="3" t="inlineStr"/>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>R-555 and R-562 build one app per role; the spec asks for more.</t>
+          <t>Draft spec (called R-600 inside).</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>SPEC-PACK-06E</t>
+          <t>SPEC-PACK-06B</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>Rich seed data generator</t>
+          <t>Role-based app generator</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>specs/pack-framework/06e</t>
+          <t>specs/pack-framework/06b</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr"/>
@@ -10169,86 +10165,86 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F82" s="10" t="inlineStr">
+      <c r="F82" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G82" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="G82" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>PC-077</t>
+          <t>PC-075</t>
         </is>
       </c>
       <c r="I82" s="3" t="inlineStr"/>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>Seeds exist (R-248); the spec asks for realistic volume.</t>
+          <t>R-555 and R-562 build one app per role; the spec asks for more.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>SPEC-TS-01</t>
+          <t>SPEC-PACK-06E</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>Instant chat -&gt; pretty UI</t>
+          <t>Rich seed data generator</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>specs/table-stakes/01</t>
+          <t>specs/pack-framework/06e</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr"/>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>Delivered</t>
-        </is>
-      </c>
-      <c r="F83" s="10" t="inlineStr">
+          <t>2 Maximum features</t>
+        </is>
+      </c>
+      <c r="F83" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G83" s="6" t="inlineStr">
-        <is>
-          <t>P0</t>
+      <c r="G83" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H83" s="3" t="inlineStr">
         <is>
-          <t>PC-006</t>
+          <t>PC-077</t>
         </is>
       </c>
       <c r="I83" s="3" t="inlineStr"/>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>Draft spec.</t>
+          <t>Seeds exist (R-248); the spec asks for realistic volume.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>SPEC-TS-03</t>
+          <t>SPEC-TS-01</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>One-click deploy</t>
+          <t>Instant chat -&gt; pretty UI</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>specs/table-stakes/03</t>
+          <t>specs/table-stakes/01</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr"/>
@@ -10257,7 +10253,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F84" s="10" t="inlineStr">
+      <c r="F84" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10269,7 +10265,7 @@
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>PC-008</t>
+          <t>PC-006</t>
         </is>
       </c>
       <c r="I84" s="3" t="inlineStr"/>
@@ -10282,60 +10278,56 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>VP-appointments</t>
+          <t>SPEC-TS-03</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>Vertical pack appointments: Appointments, slots, reminders, waitlist</t>
+          <t>One-click deploy</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>registry</t>
-        </is>
-      </c>
-      <c r="D85" s="3" t="inlineStr">
-        <is>
-          <t>Healthcare &amp; life sciences (healthcare-core)</t>
-        </is>
-      </c>
+          <t>specs/table-stakes/03</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr"/>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>2 Maximum features</t>
-        </is>
-      </c>
-      <c r="F85" s="10" t="inlineStr">
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="F85" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G85" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G85" s="6" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="H85" s="3" t="inlineStr">
         <is>
-          <t>PC-074</t>
+          <t>PC-008</t>
         </is>
       </c>
       <c r="I85" s="3" t="inlineStr"/>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>CareClinic template.</t>
+          <t>Draft spec.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>VP-cart-checkout</t>
+          <t>VP-appointments</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>Vertical pack cart-checkout: Cart, coupons, checkout sessions</t>
+          <t>Vertical pack appointments: Appointments, slots, reminders, waitlist</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -10345,7 +10337,7 @@
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>Marketplace &amp; commerce (commerce-core)</t>
+          <t>Healthcare &amp; life sciences (healthcare-core)</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
@@ -10353,7 +10345,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F86" s="10" t="inlineStr">
+      <c r="F86" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10371,19 +10363,19 @@
       <c r="I86" s="3" t="inlineStr"/>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>Bazaar template.</t>
+          <t>CareClinic template.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>VP-commissions</t>
+          <t>VP-cart-checkout</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>Vertical pack commissions: Commission rules, splits, payout cycles</t>
+          <t>Vertical pack cart-checkout: Cart, coupons, checkout sessions</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
@@ -10401,7 +10393,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F87" s="10" t="inlineStr">
+      <c r="F87" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10419,19 +10411,19 @@
       <c r="I87" s="3" t="inlineStr"/>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>Bazaar ledger.</t>
+          <t>Bazaar template.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>VP-dispatch</t>
+          <t>VP-commissions</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>Vertical pack dispatch: Zones, assignment rules, heatmaps</t>
+          <t>Vertical pack commissions: Commission rules, splits, payout cycles</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
@@ -10441,7 +10433,7 @@
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>Mobility &amp; on-demand (mobility-core)</t>
+          <t>Marketplace &amp; commerce (commerce-core)</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
@@ -10449,7 +10441,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F88" s="10" t="inlineStr">
+      <c r="F88" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10467,19 +10459,19 @@
       <c r="I88" s="3" t="inlineStr"/>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>RideNow template (partial).</t>
+          <t>Bazaar ledger.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>VP-drivers</t>
+          <t>VP-dispatch</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>Vertical pack drivers: Drivers, vehicles, documents, earnings</t>
+          <t>Vertical pack dispatch: Zones, assignment rules, heatmaps</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
@@ -10497,7 +10489,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F89" s="10" t="inlineStr">
+      <c r="F89" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10515,19 +10507,19 @@
       <c r="I89" s="3" t="inlineStr"/>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>RideNow template.</t>
+          <t>RideNow template (partial).</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>VP-emr</t>
+          <t>VP-drivers</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>Vertical pack emr: Encounters, notes, diagnoses, vitals</t>
+          <t>Vertical pack drivers: Drivers, vehicles, documents, earnings</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
@@ -10537,7 +10529,7 @@
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>Healthcare &amp; life sciences (healthcare-core)</t>
+          <t>Mobility &amp; on-demand (mobility-core)</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
@@ -10545,7 +10537,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F90" s="10" t="inlineStr">
+      <c r="F90" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10563,19 +10555,19 @@
       <c r="I90" s="3" t="inlineStr"/>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>CareClinic template (partial).</t>
+          <t>RideNow template.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>VP-listings</t>
+          <t>VP-emr</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>Vertical pack listings: Listings, categories, variants, media</t>
+          <t>Vertical pack emr: Encounters, notes, diagnoses, vitals</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -10585,7 +10577,7 @@
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>Marketplace &amp; commerce (commerce-core)</t>
+          <t>Healthcare &amp; life sciences (healthcare-core)</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
@@ -10593,7 +10585,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F91" s="10" t="inlineStr">
+      <c r="F91" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10611,24 +10603,24 @@
       <c r="I91" s="3" t="inlineStr"/>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>Bazaar template.</t>
+          <t>CareClinic template (partial).</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>VP-orders</t>
+          <t>VP-listings</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>Vertical pack orders: Orders, line items, timelines</t>
+          <t>Vertical pack listings: Listings, categories, variants, media</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>new (registry dependency)</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
@@ -10641,7 +10633,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F92" s="10" t="inlineStr">
+      <c r="F92" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10666,22 +10658,22 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>VP-patients</t>
+          <t>VP-orders</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>Vertical pack patients: Patients, records, insurance, consent</t>
+          <t>Vertical pack orders: Orders, line items, timelines</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>registry</t>
+          <t>new (registry dependency)</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>Healthcare &amp; life sciences (healthcare-core)</t>
+          <t>Marketplace &amp; commerce (commerce-core)</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
@@ -10689,7 +10681,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F93" s="10" t="inlineStr">
+      <c r="F93" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10707,19 +10699,19 @@
       <c r="I93" s="3" t="inlineStr"/>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>CareClinic template.</t>
+          <t>Bazaar template.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>VP-prescriptions</t>
+          <t>VP-patients</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>Vertical pack prescriptions: Prescriptions, medications, pharmacies</t>
+          <t>Vertical pack patients: Patients, records, insurance, consent</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -10737,7 +10729,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F94" s="10" t="inlineStr">
+      <c r="F94" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10755,19 +10747,19 @@
       <c r="I94" s="3" t="inlineStr"/>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>CareClinic template (partial).</t>
+          <t>CareClinic template.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>VP-providers</t>
+          <t>VP-prescriptions</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>Vertical pack providers: Providers, specialties, licences, schedules</t>
+          <t>Vertical pack prescriptions: Prescriptions, medications, pharmacies</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -10785,7 +10777,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F95" s="10" t="inlineStr">
+      <c r="F95" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10803,19 +10795,19 @@
       <c r="I95" s="3" t="inlineStr"/>
       <c r="J95" s="3" t="inlineStr">
         <is>
-          <t>CareClinic template.</t>
+          <t>CareClinic template (partial).</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>VP-rides</t>
+          <t>VP-providers</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>Vertical pack rides: Rides, routes, fares, matching, receipts</t>
+          <t>Vertical pack providers: Providers, specialties, licences, schedules</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
@@ -10825,7 +10817,7 @@
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>Mobility &amp; on-demand (mobility-core)</t>
+          <t>Healthcare &amp; life sciences (healthcare-core)</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
@@ -10833,7 +10825,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F96" s="10" t="inlineStr">
+      <c r="F96" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10851,19 +10843,19 @@
       <c r="I96" s="3" t="inlineStr"/>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>RideNow template.</t>
+          <t>CareClinic template.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>VP-telehealth</t>
+          <t>VP-rides</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>Vertical pack telehealth: Video consults, consent, technical checks</t>
+          <t>Vertical pack rides: Rides, routes, fares, matching, receipts</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
@@ -10873,7 +10865,7 @@
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>Healthcare &amp; life sciences (healthcare-core)</t>
+          <t>Mobility &amp; on-demand (mobility-core)</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
@@ -10881,7 +10873,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F97" s="10" t="inlineStr">
+      <c r="F97" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10899,19 +10891,19 @@
       <c r="I97" s="3" t="inlineStr"/>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>CareClinic template.</t>
+          <t>RideNow template.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>VP-vendors</t>
+          <t>VP-telehealth</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>Vertical pack vendors: Vendors, storefronts, verification</t>
+          <t>Vertical pack telehealth: Video consults, consent, technical checks</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
@@ -10921,7 +10913,7 @@
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>Marketplace &amp; commerce (commerce-core)</t>
+          <t>Healthcare &amp; life sciences (healthcare-core)</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
@@ -10929,7 +10921,7 @@
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="F98" s="10" t="inlineStr">
+      <c r="F98" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10947,63 +10939,67 @@
       <c r="I98" s="3" t="inlineStr"/>
       <c r="J98" s="3" t="inlineStr">
         <is>
-          <t>Bazaar template.</t>
+          <t>CareClinic template.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>PC-096</t>
+          <t>VP-vendors</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>In-browser WebContainer preview engine behind the PC-007 engine switch (Node in the visitor's browser; licence key supplied at PC-070)</t>
+          <t>Vertical pack vendors: Vendors, storefronts, verification</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>Platform_Completion queue</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>Vibe</t>
+          <t>Marketplace &amp; commerce (commerce-core)</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>1 Vibe Mode live</t>
-        </is>
-      </c>
-      <c r="F99" s="8" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G99" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="H99" s="3" t="inlineStr"/>
+          <t>2 Maximum features</t>
+        </is>
+      </c>
+      <c r="F99" s="11" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G99" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>PC-074</t>
+        </is>
+      </c>
       <c r="I99" s="3" t="inlineStr"/>
       <c r="J99" s="3" t="inlineStr">
         <is>
-          <t>Split out of PC-007 on 2026-09-27: PC-007 delivers the engine switch and the open-source container engine; WebContainer needs StackBlitz's commercial licence (D-6) and runs Node only, so Python/Go APIs still need a server-side engine behind it.</t>
+          <t>Bazaar template.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>PC-097</t>
+          <t>PC-096</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>Compile repair covers every Next surface (admin console and ecosystem role surfaces), not only the main web app</t>
+          <t>In-browser WebContainer preview engine behind the PC-007 engine switch (Node in the visitor's browser; licence key supplied at PC-070)</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
@@ -11013,7 +11009,7 @@
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Vibe</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
@@ -11026,28 +11022,28 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G100" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G100" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H100" s="3" t="inlineStr"/>
       <c r="I100" s="3" t="inlineStr"/>
       <c r="J100" s="3" t="inlineStr">
         <is>
-          <t>Found publishing a clinic app on 2026-09-27: the `provider` role surface shipped a model-written page with an invented import and misused components; the build never checked it. PC-008 now type-checks every Next surface and publish refuses a broken app with the compiler's reason; this task makes the repair loop fix or revert those pages as it does for web.</t>
+          <t>Split out of PC-007 on 2026-09-27: PC-007 delivers the engine switch and the open-source container engine; WebContainer needs StackBlitz's commercial licence (D-6) and runs Node only, so Python/Go APIs still need a server-side engine behind it.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>PC-012</t>
+          <t>PC-097</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>Legal and account basics: ToS, privacy, retention, deletion/export, email verification</t>
+          <t>Compile repair covers every Next surface (admin console and ecosystem role surfaces), not only the main web app</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
@@ -11057,7 +11053,7 @@
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>Platform</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
@@ -11070,14 +11066,18 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G101" s="6" t="inlineStr">
-        <is>
-          <t>P0</t>
+      <c r="G101" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H101" s="3" t="inlineStr"/>
       <c r="I101" s="3" t="inlineStr"/>
-      <c r="J101" s="3" t="inlineStr"/>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>Found publishing a clinic app on 2026-09-27: the `provider` role surface shipped a model-written page with an invented import and misused components; the build never checked it. PC-008 now type-checks every Next surface and publish refuses a broken app with the compiler's reason; this task makes the repair loop fix or revert those pages as it does for web.</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
@@ -11882,7 +11882,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G120" s="11" t="inlineStr">
+      <c r="G120" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -11926,7 +11926,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G121" s="11" t="inlineStr">
+      <c r="G121" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -12102,7 +12102,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G125" s="11" t="inlineStr">
+      <c r="G125" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -12146,7 +12146,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G126" s="11" t="inlineStr">
+      <c r="G126" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -12190,7 +12190,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G127" s="11" t="inlineStr">
+      <c r="G127" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -12234,7 +12234,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G128" s="11" t="inlineStr">
+      <c r="G128" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -12278,7 +12278,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G129" s="11" t="inlineStr">
+      <c r="G129" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -12366,7 +12366,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G131" s="11" t="inlineStr">
+      <c r="G131" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -12762,7 +12762,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G140" s="11" t="inlineStr">
+      <c r="G140" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -12806,7 +12806,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G141" s="11" t="inlineStr">
+      <c r="G141" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -12850,7 +12850,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G142" s="11" t="inlineStr">
+      <c r="G142" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -14042,7 +14042,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G171" s="11" t="inlineStr">
+      <c r="G171" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -14082,7 +14082,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G172" s="11" t="inlineStr">
+      <c r="G172" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -14126,7 +14126,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G173" s="11" t="inlineStr">
+      <c r="G173" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -14642,7 +14642,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G185" s="11" t="inlineStr">
+      <c r="G185" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -14810,7 +14810,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G189" s="11" t="inlineStr">
+      <c r="G189" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -15374,7 +15374,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G203" s="11" t="inlineStr">
+      <c r="G203" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -15738,7 +15738,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G212" s="11" t="inlineStr">
+      <c r="G212" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -16238,7 +16238,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G224" s="11" t="inlineStr">
+      <c r="G224" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -16462,7 +16462,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G229" s="11" t="inlineStr">
+      <c r="G229" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -16594,7 +16594,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G232" s="11" t="inlineStr">
+      <c r="G232" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -16638,7 +16638,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G233" s="11" t="inlineStr">
+      <c r="G233" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -16862,7 +16862,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G238" s="11" t="inlineStr">
+      <c r="G238" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -17038,7 +17038,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G242" s="11" t="inlineStr">
+      <c r="G242" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -17174,7 +17174,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G245" s="11" t="inlineStr">
+      <c r="G245" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -17262,7 +17262,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G247" s="11" t="inlineStr">
+      <c r="G247" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -17358,7 +17358,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G249" s="11" t="inlineStr">
+      <c r="G249" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -17450,7 +17450,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G251" s="11" t="inlineStr">
+      <c r="G251" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -17494,7 +17494,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G252" s="11" t="inlineStr">
+      <c r="G252" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -17586,7 +17586,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G254" s="11" t="inlineStr">
+      <c r="G254" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -17630,7 +17630,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G255" s="11" t="inlineStr">
+      <c r="G255" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -17810,7 +17810,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G259" s="11" t="inlineStr">
+      <c r="G259" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -17950,7 +17950,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G262" s="11" t="inlineStr">
+      <c r="G262" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -17994,7 +17994,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G263" s="11" t="inlineStr">
+      <c r="G263" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -18402,7 +18402,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G272" s="11" t="inlineStr">
+      <c r="G272" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -18634,7 +18634,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G277" s="11" t="inlineStr">
+      <c r="G277" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -18858,7 +18858,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G282" s="11" t="inlineStr">
+      <c r="G282" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -18902,7 +18902,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G283" s="11" t="inlineStr">
+      <c r="G283" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -19038,7 +19038,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G286" s="11" t="inlineStr">
+      <c r="G286" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -21006,7 +21006,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G332" s="11" t="inlineStr">
+      <c r="G332" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -22774,7 +22774,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G372" s="11" t="inlineStr">
+      <c r="G372" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -22818,7 +22818,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G373" s="11" t="inlineStr">
+      <c r="G373" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -22862,7 +22862,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G374" s="11" t="inlineStr">
+      <c r="G374" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -24662,7 +24662,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G415" s="11" t="inlineStr">
+      <c r="G415" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -24706,7 +24706,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G416" s="11" t="inlineStr">
+      <c r="G416" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -24794,7 +24794,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G418" s="11" t="inlineStr">
+      <c r="G418" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -24926,7 +24926,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G421" s="11" t="inlineStr">
+      <c r="G421" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25102,7 +25102,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G425" s="11" t="inlineStr">
+      <c r="G425" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25146,7 +25146,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G426" s="11" t="inlineStr">
+      <c r="G426" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25454,7 +25454,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G433" s="11" t="inlineStr">
+      <c r="G433" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25498,7 +25498,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G434" s="11" t="inlineStr">
+      <c r="G434" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25542,7 +25542,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G435" s="11" t="inlineStr">
+      <c r="G435" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25586,7 +25586,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G436" s="11" t="inlineStr">
+      <c r="G436" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25630,7 +25630,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G437" s="11" t="inlineStr">
+      <c r="G437" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25674,7 +25674,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G438" s="11" t="inlineStr">
+      <c r="G438" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25718,7 +25718,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G439" s="11" t="inlineStr">
+      <c r="G439" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25850,7 +25850,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G442" s="11" t="inlineStr">
+      <c r="G442" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -25982,7 +25982,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G445" s="11" t="inlineStr">
+      <c r="G445" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -26158,7 +26158,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G449" s="11" t="inlineStr">
+      <c r="G449" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -26202,7 +26202,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G450" s="11" t="inlineStr">
+      <c r="G450" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -26378,7 +26378,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G454" s="11" t="inlineStr">
+      <c r="G454" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -26422,7 +26422,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G455" s="11" t="inlineStr">
+      <c r="G455" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -26510,7 +26510,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G457" s="11" t="inlineStr">
+      <c r="G457" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -26686,7 +26686,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G461" s="11" t="inlineStr">
+      <c r="G461" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -26730,7 +26730,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G462" s="11" t="inlineStr">
+      <c r="G462" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -26994,7 +26994,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G468" s="11" t="inlineStr">
+      <c r="G468" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -27038,7 +27038,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G469" s="11" t="inlineStr">
+      <c r="G469" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -27258,7 +27258,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G474" s="11" t="inlineStr">
+      <c r="G474" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -27302,7 +27302,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G475" s="11" t="inlineStr">
+      <c r="G475" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -27346,7 +27346,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G476" s="11" t="inlineStr">
+      <c r="G476" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -27390,7 +27390,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G477" s="11" t="inlineStr">
+      <c r="G477" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -27434,7 +27434,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G478" s="11" t="inlineStr">
+      <c r="G478" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -27478,7 +27478,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G479" s="11" t="inlineStr">
+      <c r="G479" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -27654,7 +27654,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G483" s="11" t="inlineStr">
+      <c r="G483" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -27874,7 +27874,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G488" s="11" t="inlineStr">
+      <c r="G488" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -27962,7 +27962,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G490" s="11" t="inlineStr">
+      <c r="G490" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -28006,7 +28006,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G491" s="11" t="inlineStr">
+      <c r="G491" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -28094,7 +28094,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G493" s="11" t="inlineStr">
+      <c r="G493" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -28314,7 +28314,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G498" s="11" t="inlineStr">
+      <c r="G498" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -28358,7 +28358,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G499" s="11" t="inlineStr">
+      <c r="G499" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -28798,7 +28798,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G509" s="11" t="inlineStr">
+      <c r="G509" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -29062,7 +29062,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G515" s="11" t="inlineStr">
+      <c r="G515" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -29194,7 +29194,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G518" s="11" t="inlineStr">
+      <c r="G518" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -29370,7 +29370,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G522" s="11" t="inlineStr">
+      <c r="G522" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -29414,7 +29414,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G523" s="11" t="inlineStr">
+      <c r="G523" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -29590,7 +29590,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G527" s="11" t="inlineStr">
+      <c r="G527" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -29634,7 +29634,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G528" s="11" t="inlineStr">
+      <c r="G528" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -29722,7 +29722,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G530" s="11" t="inlineStr">
+      <c r="G530" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -29810,7 +29810,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G532" s="11" t="inlineStr">
+      <c r="G532" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -29898,7 +29898,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G534" s="11" t="inlineStr">
+      <c r="G534" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -29986,7 +29986,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G536" s="11" t="inlineStr">
+      <c r="G536" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30030,7 +30030,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G537" s="11" t="inlineStr">
+      <c r="G537" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30074,7 +30074,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G538" s="11" t="inlineStr">
+      <c r="G538" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30162,7 +30162,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G540" s="11" t="inlineStr">
+      <c r="G540" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30206,7 +30206,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G541" s="11" t="inlineStr">
+      <c r="G541" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30250,7 +30250,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G542" s="11" t="inlineStr">
+      <c r="G542" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30294,7 +30294,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G543" s="11" t="inlineStr">
+      <c r="G543" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30382,7 +30382,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G545" s="11" t="inlineStr">
+      <c r="G545" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30426,7 +30426,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G546" s="11" t="inlineStr">
+      <c r="G546" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30470,7 +30470,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G547" s="11" t="inlineStr">
+      <c r="G547" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30602,7 +30602,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G550" s="11" t="inlineStr">
+      <c r="G550" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30734,7 +30734,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G553" s="11" t="inlineStr">
+      <c r="G553" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30822,7 +30822,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G555" s="11" t="inlineStr">
+      <c r="G555" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30910,7 +30910,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G557" s="11" t="inlineStr">
+      <c r="G557" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -30998,7 +30998,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G559" s="11" t="inlineStr">
+      <c r="G559" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -31218,7 +31218,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G564" s="11" t="inlineStr">
+      <c r="G564" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -31262,7 +31262,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G565" s="11" t="inlineStr">
+      <c r="G565" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -31350,7 +31350,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G567" s="11" t="inlineStr">
+      <c r="G567" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -31482,7 +31482,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G570" s="11" t="inlineStr">
+      <c r="G570" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -31614,7 +31614,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G573" s="11" t="inlineStr">
+      <c r="G573" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -31702,7 +31702,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G575" s="11" t="inlineStr">
+      <c r="G575" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -31746,7 +31746,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G576" s="11" t="inlineStr">
+      <c r="G576" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -31922,7 +31922,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G580" s="11" t="inlineStr">
+      <c r="G580" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -31966,7 +31966,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G581" s="11" t="inlineStr">
+      <c r="G581" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -32274,7 +32274,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G588" s="11" t="inlineStr">
+      <c r="G588" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -32318,7 +32318,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G589" s="11" t="inlineStr">
+      <c r="G589" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -32362,7 +32362,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G590" s="11" t="inlineStr">
+      <c r="G590" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -32450,7 +32450,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G592" s="11" t="inlineStr">
+      <c r="G592" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -32626,7 +32626,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G596" s="11" t="inlineStr">
+      <c r="G596" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -32758,7 +32758,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G599" s="11" t="inlineStr">
+      <c r="G599" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -32802,7 +32802,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G600" s="11" t="inlineStr">
+      <c r="G600" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -32890,7 +32890,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G602" s="11" t="inlineStr">
+      <c r="G602" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -32978,7 +32978,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G604" s="11" t="inlineStr">
+      <c r="G604" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -33198,7 +33198,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G609" s="11" t="inlineStr">
+      <c r="G609" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -33277,7 +33277,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F611" s="11" t="inlineStr">
+      <c r="F611" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33321,7 +33321,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F612" s="11" t="inlineStr">
+      <c r="F612" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33365,7 +33365,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F613" s="11" t="inlineStr">
+      <c r="F613" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33409,7 +33409,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F614" s="11" t="inlineStr">
+      <c r="F614" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33453,7 +33453,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F615" s="11" t="inlineStr">
+      <c r="F615" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33497,7 +33497,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F616" s="11" t="inlineStr">
+      <c r="F616" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33541,7 +33541,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F617" s="11" t="inlineStr">
+      <c r="F617" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33585,7 +33585,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F618" s="11" t="inlineStr">
+      <c r="F618" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33625,7 +33625,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F619" s="11" t="inlineStr">
+      <c r="F619" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33669,7 +33669,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F620" s="11" t="inlineStr">
+      <c r="F620" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33709,7 +33709,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F621" s="11" t="inlineStr">
+      <c r="F621" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33753,7 +33753,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F622" s="11" t="inlineStr">
+      <c r="F622" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -33793,12 +33793,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F623" s="12" t="inlineStr">
+      <c r="F623" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G623" s="11" t="inlineStr">
+      <c r="G623" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -33837,12 +33837,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F624" s="12" t="inlineStr">
+      <c r="F624" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G624" s="11" t="inlineStr">
+      <c r="G624" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -33881,12 +33881,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F625" s="12" t="inlineStr">
+      <c r="F625" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G625" s="11" t="inlineStr">
+      <c r="G625" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -33925,7 +33925,7 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F626" s="12" t="inlineStr">
+      <c r="F626" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
@@ -33969,12 +33969,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F627" s="12" t="inlineStr">
+      <c r="F627" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G627" s="11" t="inlineStr">
+      <c r="G627" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34013,12 +34013,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F628" s="12" t="inlineStr">
+      <c r="F628" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G628" s="11" t="inlineStr">
+      <c r="G628" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34053,12 +34053,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F629" s="12" t="inlineStr">
+      <c r="F629" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G629" s="11" t="inlineStr">
+      <c r="G629" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34097,12 +34097,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F630" s="12" t="inlineStr">
+      <c r="F630" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G630" s="11" t="inlineStr">
+      <c r="G630" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34141,12 +34141,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F631" s="12" t="inlineStr">
+      <c r="F631" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G631" s="11" t="inlineStr">
+      <c r="G631" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34185,12 +34185,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F632" s="12" t="inlineStr">
+      <c r="F632" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G632" s="11" t="inlineStr">
+      <c r="G632" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34225,12 +34225,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F633" s="12" t="inlineStr">
+      <c r="F633" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G633" s="11" t="inlineStr">
+      <c r="G633" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34269,12 +34269,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F634" s="12" t="inlineStr">
+      <c r="F634" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G634" s="11" t="inlineStr">
+      <c r="G634" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34313,12 +34313,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F635" s="12" t="inlineStr">
+      <c r="F635" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G635" s="11" t="inlineStr">
+      <c r="G635" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34357,12 +34357,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F636" s="12" t="inlineStr">
+      <c r="F636" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G636" s="11" t="inlineStr">
+      <c r="G636" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34401,12 +34401,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F637" s="12" t="inlineStr">
+      <c r="F637" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G637" s="11" t="inlineStr">
+      <c r="G637" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34445,12 +34445,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F638" s="12" t="inlineStr">
+      <c r="F638" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G638" s="11" t="inlineStr">
+      <c r="G638" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34489,12 +34489,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F639" s="12" t="inlineStr">
+      <c r="F639" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G639" s="11" t="inlineStr">
+      <c r="G639" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34533,12 +34533,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F640" s="12" t="inlineStr">
+      <c r="F640" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G640" s="11" t="inlineStr">
+      <c r="G640" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34577,12 +34577,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F641" s="12" t="inlineStr">
+      <c r="F641" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G641" s="11" t="inlineStr">
+      <c r="G641" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34621,12 +34621,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F642" s="12" t="inlineStr">
+      <c r="F642" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G642" s="11" t="inlineStr">
+      <c r="G642" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34665,12 +34665,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F643" s="12" t="inlineStr">
+      <c r="F643" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G643" s="11" t="inlineStr">
+      <c r="G643" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34709,12 +34709,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F644" s="12" t="inlineStr">
+      <c r="F644" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G644" s="11" t="inlineStr">
+      <c r="G644" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34753,12 +34753,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F645" s="12" t="inlineStr">
+      <c r="F645" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G645" s="11" t="inlineStr">
+      <c r="G645" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34797,12 +34797,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F646" s="12" t="inlineStr">
+      <c r="F646" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G646" s="11" t="inlineStr">
+      <c r="G646" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34841,12 +34841,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F647" s="12" t="inlineStr">
+      <c r="F647" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G647" s="11" t="inlineStr">
+      <c r="G647" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34881,12 +34881,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F648" s="12" t="inlineStr">
+      <c r="F648" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G648" s="11" t="inlineStr">
+      <c r="G648" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34925,12 +34925,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F649" s="12" t="inlineStr">
+      <c r="F649" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G649" s="11" t="inlineStr">
+      <c r="G649" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -34969,12 +34969,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F650" s="12" t="inlineStr">
+      <c r="F650" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G650" s="11" t="inlineStr">
+      <c r="G650" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35009,12 +35009,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F651" s="12" t="inlineStr">
+      <c r="F651" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G651" s="11" t="inlineStr">
+      <c r="G651" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35053,12 +35053,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F652" s="12" t="inlineStr">
+      <c r="F652" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G652" s="11" t="inlineStr">
+      <c r="G652" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35093,12 +35093,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F653" s="12" t="inlineStr">
+      <c r="F653" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G653" s="11" t="inlineStr">
+      <c r="G653" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35133,12 +35133,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F654" s="12" t="inlineStr">
+      <c r="F654" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G654" s="11" t="inlineStr">
+      <c r="G654" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35173,12 +35173,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F655" s="12" t="inlineStr">
+      <c r="F655" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G655" s="11" t="inlineStr">
+      <c r="G655" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35213,12 +35213,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F656" s="12" t="inlineStr">
+      <c r="F656" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G656" s="11" t="inlineStr">
+      <c r="G656" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35257,12 +35257,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F657" s="12" t="inlineStr">
+      <c r="F657" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G657" s="11" t="inlineStr">
+      <c r="G657" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35301,12 +35301,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F658" s="12" t="inlineStr">
+      <c r="F658" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G658" s="11" t="inlineStr">
+      <c r="G658" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35345,12 +35345,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F659" s="12" t="inlineStr">
+      <c r="F659" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G659" s="11" t="inlineStr">
+      <c r="G659" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35385,12 +35385,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F660" s="12" t="inlineStr">
+      <c r="F660" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G660" s="11" t="inlineStr">
+      <c r="G660" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35425,12 +35425,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F661" s="12" t="inlineStr">
+      <c r="F661" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G661" s="11" t="inlineStr">
+      <c r="G661" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35465,12 +35465,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F662" s="12" t="inlineStr">
+      <c r="F662" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G662" s="11" t="inlineStr">
+      <c r="G662" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35505,12 +35505,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F663" s="12" t="inlineStr">
+      <c r="F663" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G663" s="11" t="inlineStr">
+      <c r="G663" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35545,12 +35545,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F664" s="12" t="inlineStr">
+      <c r="F664" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G664" s="11" t="inlineStr">
+      <c r="G664" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35589,12 +35589,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F665" s="12" t="inlineStr">
+      <c r="F665" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G665" s="11" t="inlineStr">
+      <c r="G665" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35629,12 +35629,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F666" s="12" t="inlineStr">
+      <c r="F666" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G666" s="11" t="inlineStr">
+      <c r="G666" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35669,12 +35669,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F667" s="12" t="inlineStr">
+      <c r="F667" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G667" s="11" t="inlineStr">
+      <c r="G667" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35709,12 +35709,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F668" s="12" t="inlineStr">
+      <c r="F668" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G668" s="11" t="inlineStr">
+      <c r="G668" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35749,12 +35749,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F669" s="12" t="inlineStr">
+      <c r="F669" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G669" s="11" t="inlineStr">
+      <c r="G669" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35793,12 +35793,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F670" s="12" t="inlineStr">
+      <c r="F670" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G670" s="11" t="inlineStr">
+      <c r="G670" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35837,12 +35837,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F671" s="12" t="inlineStr">
+      <c r="F671" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G671" s="11" t="inlineStr">
+      <c r="G671" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35881,12 +35881,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F672" s="12" t="inlineStr">
+      <c r="F672" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G672" s="11" t="inlineStr">
+      <c r="G672" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35925,12 +35925,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F673" s="12" t="inlineStr">
+      <c r="F673" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G673" s="11" t="inlineStr">
+      <c r="G673" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -35969,12 +35969,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F674" s="12" t="inlineStr">
+      <c r="F674" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G674" s="11" t="inlineStr">
+      <c r="G674" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -36013,12 +36013,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F675" s="12" t="inlineStr">
+      <c r="F675" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G675" s="11" t="inlineStr">
+      <c r="G675" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -36057,12 +36057,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F676" s="12" t="inlineStr">
+      <c r="F676" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G676" s="11" t="inlineStr">
+      <c r="G676" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -36101,12 +36101,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F677" s="12" t="inlineStr">
+      <c r="F677" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G677" s="11" t="inlineStr">
+      <c r="G677" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -36145,12 +36145,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F678" s="12" t="inlineStr">
+      <c r="F678" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G678" s="11" t="inlineStr">
+      <c r="G678" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -36185,12 +36185,12 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F679" s="12" t="inlineStr">
+      <c r="F679" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G679" s="11" t="inlineStr">
+      <c r="G679" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -36221,7 +36221,7 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F680" s="13" t="inlineStr">
+      <c r="F680" s="14" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -36261,7 +36261,7 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F681" s="13" t="inlineStr">
+      <c r="F681" s="14" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -36301,7 +36301,7 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F682" s="13" t="inlineStr">
+      <c r="F682" s="14" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -36341,7 +36341,7 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F683" s="13" t="inlineStr">
+      <c r="F683" s="14" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -36381,7 +36381,7 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F684" s="13" t="inlineStr">
+      <c r="F684" s="14" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -36421,7 +36421,7 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F685" s="13" t="inlineStr">
+      <c r="F685" s="14" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -36461,7 +36461,7 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F686" s="13" t="inlineStr">
+      <c r="F686" s="14" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -36501,7 +36501,7 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F687" s="13" t="inlineStr">
+      <c r="F687" s="14" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -36541,7 +36541,7 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="F688" s="13" t="inlineStr">
+      <c r="F688" s="14" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -38653,7 +38653,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F736" s="14" t="inlineStr">
+      <c r="F736" s="15" t="inlineStr">
         <is>
           <t>Completed - needs live proof</t>
         </is>
@@ -51269,7 +51269,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F1055" s="14" t="inlineStr">
+      <c r="F1055" s="15" t="inlineStr">
         <is>
           <t>Completed - needs live proof</t>
         </is>
@@ -51317,7 +51317,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F1056" s="14" t="inlineStr">
+      <c r="F1056" s="15" t="inlineStr">
         <is>
           <t>Completed - needs live proof</t>
         </is>
@@ -51365,7 +51365,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F1057" s="14" t="inlineStr">
+      <c r="F1057" s="15" t="inlineStr">
         <is>
           <t>Completed - needs live proof</t>
         </is>
@@ -51413,7 +51413,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F1058" s="14" t="inlineStr">
+      <c r="F1058" s="15" t="inlineStr">
         <is>
           <t>Completed - needs live proof</t>
         </is>
@@ -51461,7 +51461,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F1059" s="14" t="inlineStr">
+      <c r="F1059" s="15" t="inlineStr">
         <is>
           <t>Completed - needs live proof</t>
         </is>
@@ -51581,7 +51581,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F1062" s="14" t="inlineStr">
+      <c r="F1062" s="15" t="inlineStr">
         <is>
           <t>Completed - needs live proof</t>
         </is>
@@ -52713,7 +52713,7 @@
           <t>Delivered</t>
         </is>
       </c>
-      <c r="F1093" s="14" t="inlineStr">
+      <c r="F1093" s="15" t="inlineStr">
         <is>
           <t>Completed - needs live proof</t>
         </is>
@@ -53710,62 +53710,62 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="B1" s="15" t="inlineStr">
+      <c r="B1" s="16" t="inlineStr">
         <is>
           <t>0 Foundation</t>
         </is>
       </c>
-      <c r="C1" s="15" t="inlineStr">
+      <c r="C1" s="16" t="inlineStr">
         <is>
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="D1" s="15" t="inlineStr">
+      <c r="D1" s="16" t="inlineStr">
         <is>
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="E1" s="15" t="inlineStr">
+      <c r="E1" s="16" t="inlineStr">
         <is>
           <t>3 Engineering Mode</t>
         </is>
       </c>
-      <c r="F1" s="15" t="inlineStr">
+      <c r="F1" s="16" t="inlineStr">
         <is>
           <t>4 Production ops</t>
         </is>
       </c>
-      <c r="G1" s="15" t="inlineStr">
+      <c r="G1" s="16" t="inlineStr">
         <is>
           <t>5 Native mobile (last)</t>
         </is>
       </c>
-      <c r="H1" s="15" t="inlineStr">
+      <c r="H1" s="16" t="inlineStr">
         <is>
           <t>6 Go-live (credentials last)</t>
         </is>
       </c>
-      <c r="I1" s="15" t="inlineStr">
+      <c r="I1" s="16" t="inlineStr">
         <is>
           <t>7 Win the category</t>
         </is>
       </c>
-      <c r="J1" s="15" t="inlineStr">
+      <c r="J1" s="16" t="inlineStr">
         <is>
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="K1" s="15" t="inlineStr">
+      <c r="K1" s="16" t="inlineStr">
         <is>
           <t>Delivered</t>
         </is>
       </c>
-      <c r="L1" s="15" t="inlineStr">
+      <c r="L1" s="16" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
@@ -53861,7 +53861,7 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -53888,7 +53888,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -53941,7 +53941,7 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D6" t="n">
         <v>336</v>
@@ -53968,7 +53968,7 @@
         <v>23</v>
       </c>
       <c r="L6" t="n">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="7">
@@ -54132,62 +54132,62 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Open queue by priority</t>
         </is>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>0 Foundation</t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>1 Vibe Mode live</t>
         </is>
       </c>
-      <c r="D12" s="15" t="inlineStr">
+      <c r="D12" s="16" t="inlineStr">
         <is>
           <t>2 Maximum features</t>
         </is>
       </c>
-      <c r="E12" s="15" t="inlineStr">
+      <c r="E12" s="16" t="inlineStr">
         <is>
           <t>3 Engineering Mode</t>
         </is>
       </c>
-      <c r="F12" s="15" t="inlineStr">
+      <c r="F12" s="16" t="inlineStr">
         <is>
           <t>4 Production ops</t>
         </is>
       </c>
-      <c r="G12" s="15" t="inlineStr">
+      <c r="G12" s="16" t="inlineStr">
         <is>
           <t>5 Native mobile (last)</t>
         </is>
       </c>
-      <c r="H12" s="15" t="inlineStr">
+      <c r="H12" s="16" t="inlineStr">
         <is>
           <t>6 Go-live (credentials last)</t>
         </is>
       </c>
-      <c r="I12" s="15" t="inlineStr">
+      <c r="I12" s="16" t="inlineStr">
         <is>
           <t>7 Win the category</t>
         </is>
       </c>
-      <c r="J12" s="15" t="inlineStr">
+      <c r="J12" s="16" t="inlineStr">
         <is>
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="K12" s="15" t="inlineStr">
+      <c r="K12" s="16" t="inlineStr">
         <is>
           <t>Delivered</t>
         </is>
       </c>
-      <c r="L12" s="15" t="inlineStr">
+      <c r="L12" s="16" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
@@ -55502,7 +55502,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="F2" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -55606,7 +55606,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -55658,7 +55658,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F5" s="10" t="inlineStr">
+      <c r="F5" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -55710,7 +55710,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -55762,7 +55762,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F7" s="10" t="inlineStr">
+      <c r="F7" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -55814,7 +55814,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="F8" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -55962,7 +55962,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="F11" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -56066,7 +56066,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="F13" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -56123,7 +56123,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G14" s="11" t="inlineStr">
+      <c r="G14" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -56166,7 +56166,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F15" s="10" t="inlineStr">
+      <c r="F15" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -56418,7 +56418,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F20" s="10" t="inlineStr">
+      <c r="F20" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -56522,7 +56522,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F22" s="10" t="inlineStr">
+      <c r="F22" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -56627,7 +56627,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G24" s="11" t="inlineStr">
+      <c r="G24" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -56771,7 +56771,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G27" s="11" t="inlineStr">
+      <c r="G27" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -56918,12 +56918,12 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F30" s="10" t="inlineStr">
+      <c r="F30" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G30" s="11" t="inlineStr">
+      <c r="G30" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -56975,7 +56975,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G31" s="11" t="inlineStr">
+      <c r="G31" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -57018,7 +57018,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F32" s="10" t="inlineStr">
+      <c r="F32" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -57070,7 +57070,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F33" s="10" t="inlineStr">
+      <c r="F33" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -57122,7 +57122,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F34" s="10" t="inlineStr">
+      <c r="F34" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -57227,7 +57227,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G36" s="11" t="inlineStr">
+      <c r="G36" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -57275,7 +57275,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G37" s="11" t="inlineStr">
+      <c r="G37" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -57418,7 +57418,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F40" s="10" t="inlineStr">
+      <c r="F40" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -57470,7 +57470,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F41" s="10" t="inlineStr">
+      <c r="F41" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -57522,7 +57522,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F42" s="10" t="inlineStr">
+      <c r="F42" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -57622,7 +57622,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F44" s="10" t="inlineStr">
+      <c r="F44" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -57722,7 +57722,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F46" s="10" t="inlineStr">
+      <c r="F46" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -57826,7 +57826,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F48" s="10" t="inlineStr">
+      <c r="F48" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -57974,7 +57974,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F51" s="10" t="inlineStr">
+      <c r="F51" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -58074,7 +58074,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F53" s="10" t="inlineStr">
+      <c r="F53" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -58179,7 +58179,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G55" s="11" t="inlineStr">
+      <c r="G55" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -58274,7 +58274,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F57" s="10" t="inlineStr">
+      <c r="F57" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -58331,7 +58331,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G58" s="11" t="inlineStr">
+      <c r="G58" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -58379,7 +58379,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G59" s="11" t="inlineStr">
+      <c r="G59" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -58475,7 +58475,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G61" s="11" t="inlineStr">
+      <c r="G61" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -58518,7 +58518,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F62" s="10" t="inlineStr">
+      <c r="F62" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -58779,7 +58779,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G67" s="11" t="inlineStr">
+      <c r="G67" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -58870,7 +58870,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F69" s="10" t="inlineStr">
+      <c r="F69" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -58922,7 +58922,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F70" s="10" t="inlineStr">
+      <c r="F70" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -58974,7 +58974,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F71" s="10" t="inlineStr">
+      <c r="F71" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -59026,7 +59026,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F72" s="10" t="inlineStr">
+      <c r="F72" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -59130,7 +59130,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F74" s="10" t="inlineStr">
+      <c r="F74" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -59182,7 +59182,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F75" s="10" t="inlineStr">
+      <c r="F75" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -59234,7 +59234,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F76" s="10" t="inlineStr">
+      <c r="F76" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -59286,7 +59286,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F77" s="10" t="inlineStr">
+      <c r="F77" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -59390,7 +59390,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F79" s="10" t="inlineStr">
+      <c r="F79" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -59494,7 +59494,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F81" s="10" t="inlineStr">
+      <c r="F81" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -59594,12 +59594,12 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F83" s="10" t="inlineStr">
+      <c r="F83" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G83" s="11" t="inlineStr">
+      <c r="G83" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -59651,7 +59651,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G84" s="11" t="inlineStr">
+      <c r="G84" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -59846,7 +59846,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F88" s="10" t="inlineStr">
+      <c r="F88" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -60094,7 +60094,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F93" s="10" t="inlineStr">
+      <c r="F93" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -60290,12 +60290,12 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F97" s="10" t="inlineStr">
+      <c r="F97" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G97" s="11" t="inlineStr">
+      <c r="G97" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -60347,7 +60347,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G98" s="11" t="inlineStr">
+      <c r="G98" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -60395,7 +60395,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G99" s="11" t="inlineStr">
+      <c r="G99" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -60443,7 +60443,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G100" s="11" t="inlineStr">
+      <c r="G100" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -60538,7 +60538,7 @@
           <t>API + Web + App + Admin, each stack (RN first; Kotlin/Swift in PC-082)</t>
         </is>
       </c>
-      <c r="F102" s="10" t="inlineStr">
+      <c r="F102" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -60595,7 +60595,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G103" s="11" t="inlineStr">
+      <c r="G103" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -60643,7 +60643,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G104" s="11" t="inlineStr">
+      <c r="G104" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -60691,7 +60691,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G105" s="11" t="inlineStr">
+      <c r="G105" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -60739,7 +60739,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G106" s="11" t="inlineStr">
+      <c r="G106" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -60787,7 +60787,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G107" s="11" t="inlineStr">
+      <c r="G107" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -60835,7 +60835,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G108" s="11" t="inlineStr">
+      <c r="G108" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -60930,7 +60930,7 @@
           <t>Patient: App + Web; Doctor / provider: Web + App; Pharmacy / lab: Web; Clinic operator: Admin</t>
         </is>
       </c>
-      <c r="F110" s="10" t="inlineStr">
+      <c r="F110" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -60982,7 +60982,7 @@
           <t>Patient: App + Web; Doctor / provider: Web + App; Pharmacy / lab: Web; Clinic operator: Admin</t>
         </is>
       </c>
-      <c r="F111" s="10" t="inlineStr">
+      <c r="F111" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -61034,7 +61034,7 @@
           <t>Patient: App + Web; Doctor / provider: Web + App; Pharmacy / lab: Web; Clinic operator: Admin</t>
         </is>
       </c>
-      <c r="F112" s="10" t="inlineStr">
+      <c r="F112" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -61086,7 +61086,7 @@
           <t>Patient: App + Web; Doctor / provider: Web + App; Pharmacy / lab: Web; Clinic operator: Admin</t>
         </is>
       </c>
-      <c r="F113" s="10" t="inlineStr">
+      <c r="F113" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -61138,7 +61138,7 @@
           <t>Patient: App + Web; Doctor / provider: Web + App; Pharmacy / lab: Web; Clinic operator: Admin</t>
         </is>
       </c>
-      <c r="F114" s="10" t="inlineStr">
+      <c r="F114" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -61238,7 +61238,7 @@
           <t>Patient: App + Web; Doctor / provider: Web + App; Pharmacy / lab: Web; Clinic operator: Admin</t>
         </is>
       </c>
-      <c r="F116" s="10" t="inlineStr">
+      <c r="F116" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -61626,7 +61626,7 @@
           <t>Rider: App + Web; Driver: App; Dispatcher: Web; Operator: Admin</t>
         </is>
       </c>
-      <c r="F124" s="10" t="inlineStr">
+      <c r="F124" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -61678,7 +61678,7 @@
           <t>Rider: App + Web; Driver: App; Dispatcher: Web; Operator: Admin</t>
         </is>
       </c>
-      <c r="F125" s="10" t="inlineStr">
+      <c r="F125" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -61730,7 +61730,7 @@
           <t>Rider: App + Web; Driver: App; Dispatcher: Web; Operator: Admin</t>
         </is>
       </c>
-      <c r="F126" s="10" t="inlineStr">
+      <c r="F126" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -62166,7 +62166,7 @@
           <t>Buyer: App + Web; Seller / vendor: Web + App; Marketplace operator: Admin</t>
         </is>
       </c>
-      <c r="F135" s="10" t="inlineStr">
+      <c r="F135" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -62218,7 +62218,7 @@
           <t>Buyer: App + Web; Seller / vendor: Web + App; Marketplace operator: Admin</t>
         </is>
       </c>
-      <c r="F136" s="10" t="inlineStr">
+      <c r="F136" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -62270,7 +62270,7 @@
           <t>Buyer: App + Web; Seller / vendor: Web + App; Marketplace operator: Admin</t>
         </is>
       </c>
-      <c r="F137" s="10" t="inlineStr">
+      <c r="F137" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -62418,7 +62418,7 @@
           <t>Buyer: App + Web; Seller / vendor: Web + App; Marketplace operator: Admin</t>
         </is>
       </c>
-      <c r="F140" s="10" t="inlineStr">
+      <c r="F140" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -62470,7 +62470,7 @@
           <t>Buyer: App + Web; Seller / vendor: Web + App; Marketplace operator: Admin</t>
         </is>
       </c>
-      <c r="F141" s="10" t="inlineStr">
+      <c r="F141" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -67327,7 +67327,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G242" s="11" t="inlineStr">
+      <c r="G242" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67375,7 +67375,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G243" s="11" t="inlineStr">
+      <c r="G243" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67423,7 +67423,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G244" s="11" t="inlineStr">
+      <c r="G244" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67471,7 +67471,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G245" s="11" t="inlineStr">
+      <c r="G245" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67519,7 +67519,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G246" s="11" t="inlineStr">
+      <c r="G246" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67567,7 +67567,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G247" s="11" t="inlineStr">
+      <c r="G247" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67615,7 +67615,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G248" s="11" t="inlineStr">
+      <c r="G248" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67663,7 +67663,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G249" s="11" t="inlineStr">
+      <c r="G249" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67711,7 +67711,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G250" s="11" t="inlineStr">
+      <c r="G250" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67759,7 +67759,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G251" s="11" t="inlineStr">
+      <c r="G251" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67807,7 +67807,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G252" s="11" t="inlineStr">
+      <c r="G252" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67855,7 +67855,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G253" s="11" t="inlineStr">
+      <c r="G253" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67903,7 +67903,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G254" s="11" t="inlineStr">
+      <c r="G254" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67951,7 +67951,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G255" s="11" t="inlineStr">
+      <c r="G255" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -67999,7 +67999,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G256" s="11" t="inlineStr">
+      <c r="G256" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68047,7 +68047,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G257" s="11" t="inlineStr">
+      <c r="G257" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68095,7 +68095,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G258" s="11" t="inlineStr">
+      <c r="G258" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68143,7 +68143,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G259" s="11" t="inlineStr">
+      <c r="G259" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68191,7 +68191,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G260" s="11" t="inlineStr">
+      <c r="G260" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68239,7 +68239,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G261" s="11" t="inlineStr">
+      <c r="G261" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68287,7 +68287,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G262" s="11" t="inlineStr">
+      <c r="G262" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68335,7 +68335,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G263" s="11" t="inlineStr">
+      <c r="G263" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68383,7 +68383,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G264" s="11" t="inlineStr">
+      <c r="G264" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68431,7 +68431,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G265" s="11" t="inlineStr">
+      <c r="G265" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68479,7 +68479,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G266" s="11" t="inlineStr">
+      <c r="G266" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68527,7 +68527,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G267" s="11" t="inlineStr">
+      <c r="G267" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68575,7 +68575,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G268" s="11" t="inlineStr">
+      <c r="G268" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68623,7 +68623,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G269" s="11" t="inlineStr">
+      <c r="G269" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68671,7 +68671,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G270" s="11" t="inlineStr">
+      <c r="G270" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68719,7 +68719,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G271" s="11" t="inlineStr">
+      <c r="G271" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68767,7 +68767,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G272" s="11" t="inlineStr">
+      <c r="G272" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68815,7 +68815,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G273" s="11" t="inlineStr">
+      <c r="G273" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68863,7 +68863,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G274" s="11" t="inlineStr">
+      <c r="G274" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68911,7 +68911,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G275" s="11" t="inlineStr">
+      <c r="G275" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -68959,7 +68959,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G276" s="11" t="inlineStr">
+      <c r="G276" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69007,7 +69007,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G277" s="11" t="inlineStr">
+      <c r="G277" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69055,7 +69055,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G278" s="11" t="inlineStr">
+      <c r="G278" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69103,7 +69103,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G279" s="11" t="inlineStr">
+      <c r="G279" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69151,7 +69151,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G280" s="11" t="inlineStr">
+      <c r="G280" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69199,7 +69199,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G281" s="11" t="inlineStr">
+      <c r="G281" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69247,7 +69247,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G282" s="11" t="inlineStr">
+      <c r="G282" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69295,7 +69295,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G283" s="11" t="inlineStr">
+      <c r="G283" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69343,7 +69343,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G284" s="11" t="inlineStr">
+      <c r="G284" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69391,7 +69391,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G285" s="11" t="inlineStr">
+      <c r="G285" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69439,7 +69439,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G286" s="11" t="inlineStr">
+      <c r="G286" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69487,7 +69487,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G287" s="11" t="inlineStr">
+      <c r="G287" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69535,7 +69535,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G288" s="11" t="inlineStr">
+      <c r="G288" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69583,7 +69583,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G289" s="11" t="inlineStr">
+      <c r="G289" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69631,7 +69631,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G290" s="11" t="inlineStr">
+      <c r="G290" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69679,7 +69679,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G291" s="11" t="inlineStr">
+      <c r="G291" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69727,7 +69727,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G292" s="11" t="inlineStr">
+      <c r="G292" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69775,7 +69775,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G293" s="11" t="inlineStr">
+      <c r="G293" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69823,7 +69823,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G294" s="11" t="inlineStr">
+      <c r="G294" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69871,7 +69871,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G295" s="11" t="inlineStr">
+      <c r="G295" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69919,7 +69919,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G296" s="11" t="inlineStr">
+      <c r="G296" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -69967,7 +69967,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G297" s="11" t="inlineStr">
+      <c r="G297" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70015,7 +70015,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G298" s="11" t="inlineStr">
+      <c r="G298" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70063,7 +70063,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G299" s="11" t="inlineStr">
+      <c r="G299" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70111,7 +70111,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G300" s="11" t="inlineStr">
+      <c r="G300" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70159,7 +70159,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G301" s="11" t="inlineStr">
+      <c r="G301" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70207,7 +70207,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G302" s="11" t="inlineStr">
+      <c r="G302" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70255,7 +70255,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G303" s="11" t="inlineStr">
+      <c r="G303" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70303,7 +70303,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G304" s="11" t="inlineStr">
+      <c r="G304" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70351,7 +70351,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G305" s="11" t="inlineStr">
+      <c r="G305" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70399,7 +70399,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G306" s="11" t="inlineStr">
+      <c r="G306" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70447,7 +70447,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G307" s="11" t="inlineStr">
+      <c r="G307" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70495,7 +70495,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G308" s="11" t="inlineStr">
+      <c r="G308" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70543,7 +70543,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G309" s="11" t="inlineStr">
+      <c r="G309" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70591,7 +70591,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G310" s="11" t="inlineStr">
+      <c r="G310" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70639,7 +70639,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G311" s="11" t="inlineStr">
+      <c r="G311" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70687,7 +70687,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G312" s="11" t="inlineStr">
+      <c r="G312" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70735,7 +70735,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G313" s="11" t="inlineStr">
+      <c r="G313" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70783,7 +70783,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G314" s="11" t="inlineStr">
+      <c r="G314" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70831,7 +70831,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G315" s="11" t="inlineStr">
+      <c r="G315" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70879,7 +70879,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G316" s="11" t="inlineStr">
+      <c r="G316" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70927,7 +70927,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G317" s="11" t="inlineStr">
+      <c r="G317" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -70975,7 +70975,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G318" s="11" t="inlineStr">
+      <c r="G318" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -71023,7 +71023,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G319" s="11" t="inlineStr">
+      <c r="G319" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -71071,7 +71071,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G320" s="11" t="inlineStr">
+      <c r="G320" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -71119,7 +71119,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G321" s="11" t="inlineStr">
+      <c r="G321" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -71167,7 +71167,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G322" s="11" t="inlineStr">
+      <c r="G322" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -71723,7 +71723,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>Completed - needs live proof</t>
         </is>
@@ -71735,7 +71735,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="16" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
@@ -71747,7 +71747,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -71771,7 +71771,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -71783,7 +71783,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
@@ -71795,7 +71795,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -71843,7 +71843,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>

--- a/R_&_D/Platform_Completion/OmniStackAI_Master_Tasks.xlsx
+++ b/R_&_D/Platform_Completion/OmniStackAI_Master_Tasks.xlsx
@@ -3181,7 +3181,7 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>R-512 gives Stripe/Razorpay checkout; this is the ledger. Done 2026-10-01: a `money` capability; every backend gets server-priced checkout, a double-entry ledger, commission splits, refunds and payouts, mock offline and verified Stripe/Razorpay webhooks. Real provider accounts are PC-070/PC-071; the screens are PC-113.</t>
+          <t>R-512 gives Stripe/Razorpay checkout; this is the ledger. Done 2026-10-01: a `money` capability; every backend gets server-priced checkout, a double-entry ledger, commission splits, refunds and payouts, mock offline and verified Stripe/Razorpay webhooks. Real provider accounts are PC-070/PC-071; the screens are PC-113. Proved with real test-mode accounts 2026-10-01 on the console-built Bazaar Lite: Stripe (card, webhook via the Stripe CLI) and Razorpay (netbanking, webhook via a tunnel) each took ₹799, credited the seller ₹719.10 and refunded ₹100 through the provider.</t>
         </is>
       </c>
     </row>
@@ -6835,7 +6835,7 @@
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
-          <t>Publish to a real URL, a real payment, a real email, EAS/store uploads to both stores.</t>
+          <t>Publish to a real URL, a real payment, a real email, EAS/store uploads to both stores. Payments in test mode done 2026-10-01 (Stripe and Razorpay, see R-567); live-mode keys remain.</t>
         </is>
       </c>
     </row>
@@ -14659,7 +14659,7 @@
       <c r="I166" s="3" t="inlineStr"/>
       <c r="J166" s="3" t="inlineStr">
         <is>
-          <t>Publish to a real URL, a real payment, a real email, EAS/store uploads to both stores.</t>
+          <t>Publish to a real URL, a real payment, a real email, EAS/store uploads to both stores. Payments in test mode done 2026-10-01 (Stripe and Razorpay, see R-567); live-mode keys remain.</t>
         </is>
       </c>
     </row>
@@ -39243,7 +39243,7 @@
       </c>
       <c r="J726" s="3" t="inlineStr">
         <is>
-          <t>R-512 gives Stripe/Razorpay checkout; this is the ledger. Done 2026-10-01: a `money` capability; every backend gets server-priced checkout, a double-entry ledger, commission splits, refunds and payouts, mock offline and verified Stripe/Razorpay webhooks. Real provider accounts are PC-070/PC-071; the screens are PC-113.</t>
+          <t>R-512 gives Stripe/Razorpay checkout; this is the ledger. Done 2026-10-01: a `money` capability; every backend gets server-priced checkout, a double-entry ledger, commission splits, refunds and payouts, mock offline and verified Stripe/Razorpay webhooks. Real provider accounts are PC-070/PC-071; the screens are PC-113. Proved with real test-mode accounts 2026-10-01 on the console-built Bazaar Lite: Stripe (card, webhook via the Stripe CLI) and Razorpay (netbanking, webhook via a tunnel) each took ₹799, credited the seller ₹719.10 and refunded ₹100 through the provider.</t>
         </is>
       </c>
     </row>
